--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -3345,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF140"/>
+  <dimension ref="A1:AG140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3419,7 +3419,8 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="92" t="n"/>
+      <c r="AF1" s="91" t="n"/>
+      <c r="AG1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
@@ -3456,12 +3457,8 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
-        </is>
-      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -3868,7 +3865,7 @@
       <c r="S5" s="67" t="n"/>
       <c r="T5" s="73" t="n"/>
       <c r="U5" s="74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V5" s="66" t="inlineStr">
         <is>
@@ -3964,7 +3961,7 @@
       <c r="S6" s="76" t="n"/>
       <c r="T6" s="82" t="n"/>
       <c r="U6" s="83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V6" s="75" t="inlineStr">
         <is>
@@ -4060,7 +4057,7 @@
       <c r="S7" s="67" t="n"/>
       <c r="T7" s="66" t="n"/>
       <c r="U7" s="74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V7" s="66" t="inlineStr">
         <is>
@@ -4156,7 +4153,7 @@
       <c r="S8" s="76" t="n"/>
       <c r="T8" s="75" t="n"/>
       <c r="U8" s="83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V8" s="75" t="inlineStr">
         <is>
@@ -4252,7 +4249,7 @@
       <c r="S9" s="67" t="n"/>
       <c r="T9" s="66" t="n"/>
       <c r="U9" s="74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V9" s="66" t="inlineStr">
         <is>
@@ -4348,7 +4345,7 @@
       <c r="S10" s="76" t="n"/>
       <c r="T10" s="82" t="n"/>
       <c r="U10" s="83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V10" s="75" t="inlineStr">
         <is>
@@ -4444,7 +4441,7 @@
       <c r="S11" s="67" t="n"/>
       <c r="T11" s="73" t="n"/>
       <c r="U11" s="74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V11" s="66" t="inlineStr">
         <is>
@@ -4540,7 +4537,7 @@
       <c r="S12" s="76" t="n"/>
       <c r="T12" s="75" t="n"/>
       <c r="U12" s="83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V12" s="75" t="inlineStr">
         <is>
@@ -4636,7 +4633,7 @@
       <c r="S13" s="67" t="n"/>
       <c r="T13" s="73" t="n"/>
       <c r="U13" s="74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V13" s="66" t="inlineStr">
         <is>
@@ -4732,7 +4729,7 @@
       <c r="S14" s="76" t="n"/>
       <c r="T14" s="82" t="n"/>
       <c r="U14" s="83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V14" s="75" t="inlineStr">
         <is>
@@ -4828,7 +4825,7 @@
       <c r="S15" s="67" t="n"/>
       <c r="T15" s="73" t="n"/>
       <c r="U15" s="74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V15" s="66" t="inlineStr">
         <is>
@@ -4924,7 +4921,7 @@
       <c r="S16" s="76" t="n"/>
       <c r="T16" s="82" t="n"/>
       <c r="U16" s="83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V16" s="75" t="inlineStr">
         <is>
@@ -5020,7 +5017,7 @@
       <c r="S17" s="67" t="n"/>
       <c r="T17" s="73" t="n"/>
       <c r="U17" s="74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V17" s="66" t="inlineStr">
         <is>
@@ -5120,7 +5117,7 @@
       <c r="S18" s="76" t="n"/>
       <c r="T18" s="82" t="n"/>
       <c r="U18" s="83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V18" s="75" t="inlineStr">
         <is>
@@ -5216,7 +5213,7 @@
       <c r="S19" s="67" t="n"/>
       <c r="T19" s="73" t="n"/>
       <c r="U19" s="74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V19" s="66" t="inlineStr">
         <is>
@@ -5312,7 +5309,7 @@
       <c r="S20" s="76" t="n"/>
       <c r="T20" s="75" t="n"/>
       <c r="U20" s="83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V20" s="75" t="inlineStr">
         <is>
@@ -5408,7 +5405,7 @@
       <c r="S21" s="67" t="n"/>
       <c r="T21" s="73" t="n"/>
       <c r="U21" s="74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V21" s="66" t="inlineStr">
         <is>
@@ -5504,7 +5501,7 @@
       <c r="S22" s="76" t="n"/>
       <c r="T22" s="75" t="n"/>
       <c r="U22" s="83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V22" s="75" t="inlineStr">
         <is>
@@ -5600,7 +5597,7 @@
       <c r="S23" s="67" t="n"/>
       <c r="T23" s="66" t="n"/>
       <c r="U23" s="74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V23" s="66" t="inlineStr">
         <is>
@@ -5696,7 +5693,7 @@
       <c r="S24" s="76" t="n"/>
       <c r="T24" s="82" t="n"/>
       <c r="U24" s="83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V24" s="75" t="inlineStr">
         <is>
@@ -5792,7 +5789,7 @@
       <c r="S25" s="67" t="n"/>
       <c r="T25" s="73" t="n"/>
       <c r="U25" s="74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V25" s="66" t="inlineStr">
         <is>
@@ -5888,7 +5885,7 @@
       <c r="S26" s="76" t="n"/>
       <c r="T26" s="82" t="n"/>
       <c r="U26" s="83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V26" s="75" t="inlineStr">
         <is>
@@ -5984,7 +5981,7 @@
       <c r="S27" s="67" t="n"/>
       <c r="T27" s="73" t="n"/>
       <c r="U27" s="74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V27" s="66" t="inlineStr">
         <is>
@@ -6084,7 +6081,7 @@
       <c r="S28" s="76" t="n"/>
       <c r="T28" s="82" t="n"/>
       <c r="U28" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V28" s="75" t="inlineStr">
         <is>
@@ -6180,7 +6177,7 @@
       <c r="S29" s="67" t="n"/>
       <c r="T29" s="73" t="n"/>
       <c r="U29" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V29" s="66" t="inlineStr">
         <is>
@@ -6276,7 +6273,7 @@
       <c r="S30" s="76" t="n"/>
       <c r="T30" s="82" t="n"/>
       <c r="U30" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V30" s="75" t="inlineStr">
         <is>
@@ -6372,7 +6369,7 @@
       <c r="S31" s="67" t="n"/>
       <c r="T31" s="73" t="n"/>
       <c r="U31" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V31" s="66" t="inlineStr">
         <is>
@@ -6468,7 +6465,7 @@
       <c r="S32" s="76" t="n"/>
       <c r="T32" s="82" t="n"/>
       <c r="U32" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V32" s="75" t="inlineStr">
         <is>
@@ -6564,7 +6561,7 @@
       <c r="S33" s="67" t="n"/>
       <c r="T33" s="73" t="n"/>
       <c r="U33" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V33" s="66" t="inlineStr">
         <is>
@@ -6660,7 +6657,7 @@
       <c r="S34" s="76" t="n"/>
       <c r="T34" s="82" t="n"/>
       <c r="U34" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V34" s="75" t="inlineStr">
         <is>
@@ -6756,7 +6753,7 @@
       <c r="S35" s="67" t="n"/>
       <c r="T35" s="73" t="n"/>
       <c r="U35" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V35" s="66" t="inlineStr">
         <is>
@@ -6852,7 +6849,7 @@
       <c r="S36" s="76" t="n"/>
       <c r="T36" s="82" t="n"/>
       <c r="U36" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V36" s="75" t="inlineStr">
         <is>
@@ -6948,7 +6945,7 @@
       <c r="S37" s="67" t="n"/>
       <c r="T37" s="73" t="n"/>
       <c r="U37" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V37" s="66" t="inlineStr">
         <is>
@@ -7044,7 +7041,7 @@
       <c r="S38" s="76" t="n"/>
       <c r="T38" s="82" t="n"/>
       <c r="U38" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V38" s="75" t="inlineStr">
         <is>
@@ -7140,7 +7137,7 @@
       <c r="S39" s="67" t="n"/>
       <c r="T39" s="73" t="n"/>
       <c r="U39" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V39" s="66" t="inlineStr">
         <is>
@@ -7236,7 +7233,7 @@
       <c r="S40" s="76" t="n"/>
       <c r="T40" s="82" t="n"/>
       <c r="U40" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V40" s="75" t="inlineStr">
         <is>
@@ -7336,7 +7333,7 @@
       <c r="S41" s="67" t="n"/>
       <c r="T41" s="73" t="n"/>
       <c r="U41" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V41" s="66" t="inlineStr">
         <is>
@@ -7436,7 +7433,7 @@
       <c r="S42" s="76" t="n"/>
       <c r="T42" s="82" t="n"/>
       <c r="U42" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V42" s="75" t="inlineStr">
         <is>
@@ -7536,7 +7533,7 @@
       <c r="S43" s="67" t="n"/>
       <c r="T43" s="66" t="n"/>
       <c r="U43" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V43" s="66" t="inlineStr">
         <is>
@@ -7636,7 +7633,7 @@
       <c r="S44" s="76" t="n"/>
       <c r="T44" s="75" t="n"/>
       <c r="U44" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V44" s="75" t="inlineStr">
         <is>
@@ -7736,7 +7733,7 @@
       <c r="S45" s="67" t="n"/>
       <c r="T45" s="66" t="n"/>
       <c r="U45" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V45" s="66" t="inlineStr">
         <is>
@@ -7836,7 +7833,7 @@
       <c r="S46" s="76" t="n"/>
       <c r="T46" s="75" t="n"/>
       <c r="U46" s="83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V46" s="75" t="inlineStr">
         <is>
@@ -7932,7 +7929,7 @@
       <c r="S47" s="67" t="n"/>
       <c r="T47" s="73" t="n"/>
       <c r="U47" s="74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V47" s="66" t="inlineStr">
         <is>
@@ -8032,7 +8029,7 @@
       <c r="S48" s="76" t="n"/>
       <c r="T48" s="82" t="n"/>
       <c r="U48" s="83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V48" s="75" t="inlineStr">
         <is>
@@ -8132,7 +8129,7 @@
       <c r="S49" s="67" t="n"/>
       <c r="T49" s="73" t="n"/>
       <c r="U49" s="74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V49" s="66" t="inlineStr">
         <is>
@@ -8232,7 +8229,7 @@
       <c r="S50" s="76" t="n"/>
       <c r="T50" s="82" t="n"/>
       <c r="U50" s="83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V50" s="75" t="inlineStr">
         <is>
@@ -8332,7 +8329,7 @@
       <c r="S51" s="67" t="n"/>
       <c r="T51" s="73" t="n"/>
       <c r="U51" s="74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V51" s="66" t="inlineStr">
         <is>
@@ -8428,7 +8425,7 @@
       <c r="S52" s="76" t="n"/>
       <c r="T52" s="82" t="n"/>
       <c r="U52" s="83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V52" s="75" t="inlineStr">
         <is>
@@ -8524,7 +8521,7 @@
       <c r="S53" s="67" t="n"/>
       <c r="T53" s="73" t="n"/>
       <c r="U53" s="74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V53" s="66" t="inlineStr">
         <is>
@@ -8620,7 +8617,7 @@
       <c r="S54" s="76" t="n"/>
       <c r="T54" s="75" t="n"/>
       <c r="U54" s="83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V54" s="75" t="inlineStr">
         <is>
@@ -8716,7 +8713,7 @@
       <c r="S55" s="67" t="n"/>
       <c r="T55" s="66" t="n"/>
       <c r="U55" s="74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V55" s="66" t="inlineStr">
         <is>
@@ -8816,7 +8813,7 @@
       <c r="S56" s="76" t="n"/>
       <c r="T56" s="82" t="n"/>
       <c r="U56" s="83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V56" s="75" t="inlineStr">
         <is>
@@ -8912,7 +8909,7 @@
       <c r="S57" s="67" t="n"/>
       <c r="T57" s="73" t="n"/>
       <c r="U57" s="74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V57" s="66" t="inlineStr">
         <is>
@@ -9008,7 +9005,7 @@
       <c r="S58" s="76" t="n"/>
       <c r="T58" s="82" t="n"/>
       <c r="U58" s="83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V58" s="75" t="inlineStr">
         <is>
@@ -9104,7 +9101,7 @@
       <c r="S59" s="67" t="n"/>
       <c r="T59" s="73" t="n"/>
       <c r="U59" s="74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V59" s="66" t="inlineStr">
         <is>
@@ -9200,7 +9197,7 @@
       <c r="S60" s="76" t="n"/>
       <c r="T60" s="82" t="n"/>
       <c r="U60" s="83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V60" s="75" t="inlineStr">
         <is>
@@ -9296,7 +9293,7 @@
       <c r="S61" s="67" t="n"/>
       <c r="T61" s="73" t="n"/>
       <c r="U61" s="74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V61" s="66" t="inlineStr">
         <is>
@@ -9396,7 +9393,7 @@
       <c r="S62" s="76" t="n"/>
       <c r="T62" s="75" t="n"/>
       <c r="U62" s="83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V62" s="75" t="inlineStr">
         <is>
@@ -9492,7 +9489,7 @@
       <c r="S63" s="67" t="n"/>
       <c r="T63" s="73" t="n"/>
       <c r="U63" s="74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V63" s="66" t="inlineStr">
         <is>
@@ -9592,7 +9589,7 @@
       <c r="S64" s="76" t="n"/>
       <c r="T64" s="75" t="n"/>
       <c r="U64" s="83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V64" s="75" t="inlineStr">
         <is>
@@ -9692,7 +9689,7 @@
       <c r="S65" s="67" t="n"/>
       <c r="T65" s="73" t="n"/>
       <c r="U65" s="74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V65" s="66" t="inlineStr">
         <is>
@@ -9792,7 +9789,7 @@
       <c r="S66" s="76" t="n"/>
       <c r="T66" s="75" t="n"/>
       <c r="U66" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V66" s="75" t="inlineStr">
         <is>
@@ -9892,7 +9889,7 @@
       <c r="S67" s="67" t="n"/>
       <c r="T67" s="66" t="n"/>
       <c r="U67" s="74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V67" s="66" t="inlineStr">
         <is>
@@ -9992,7 +9989,7 @@
       <c r="S68" s="76" t="n"/>
       <c r="T68" s="75" t="n"/>
       <c r="U68" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V68" s="75" t="inlineStr">
         <is>
@@ -10092,7 +10089,7 @@
       <c r="S69" s="67" t="n"/>
       <c r="T69" s="66" t="n"/>
       <c r="U69" s="74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V69" s="66" t="inlineStr">
         <is>
@@ -10188,7 +10185,7 @@
       <c r="S70" s="76" t="n"/>
       <c r="T70" s="82" t="n"/>
       <c r="U70" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V70" s="75" t="inlineStr">
         <is>
@@ -10284,7 +10281,7 @@
       <c r="S71" s="67" t="n"/>
       <c r="T71" s="66" t="n"/>
       <c r="U71" s="74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V71" s="66" t="inlineStr">
         <is>
@@ -10380,7 +10377,7 @@
       <c r="S72" s="76" t="n"/>
       <c r="T72" s="82" t="n"/>
       <c r="U72" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V72" s="75" t="inlineStr">
         <is>
@@ -10476,7 +10473,7 @@
       <c r="S73" s="67" t="n"/>
       <c r="T73" s="73" t="n"/>
       <c r="U73" s="74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V73" s="66" t="inlineStr">
         <is>
@@ -10572,7 +10569,7 @@
       <c r="S74" s="76" t="n"/>
       <c r="T74" s="75" t="n"/>
       <c r="U74" s="83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V74" s="75" t="inlineStr">
         <is>
@@ -10668,7 +10665,7 @@
       <c r="S75" s="67" t="n"/>
       <c r="T75" s="66" t="n"/>
       <c r="U75" s="74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V75" s="66" t="inlineStr">
         <is>
@@ -10764,7 +10761,7 @@
       <c r="S76" s="76" t="n"/>
       <c r="T76" s="82" t="n"/>
       <c r="U76" s="83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V76" s="75" t="inlineStr">
         <is>
@@ -10860,7 +10857,7 @@
       <c r="S77" s="67" t="n"/>
       <c r="T77" s="73" t="n"/>
       <c r="U77" s="74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V77" s="66" t="inlineStr">
         <is>
@@ -10960,7 +10957,7 @@
       <c r="S78" s="76" t="n"/>
       <c r="T78" s="82" t="n"/>
       <c r="U78" s="83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V78" s="75" t="inlineStr">
         <is>
@@ -11056,7 +11053,7 @@
       <c r="S79" s="67" t="n"/>
       <c r="T79" s="73" t="n"/>
       <c r="U79" s="74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V79" s="66" t="inlineStr">
         <is>
@@ -11156,7 +11153,7 @@
       <c r="S80" s="76" t="n"/>
       <c r="T80" s="82" t="n"/>
       <c r="U80" s="83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V80" s="75" t="inlineStr">
         <is>
@@ -11256,7 +11253,7 @@
       <c r="S81" s="67" t="n"/>
       <c r="T81" s="73" t="n"/>
       <c r="U81" s="74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V81" s="66" t="inlineStr">
         <is>
@@ -11356,7 +11353,7 @@
       <c r="S82" s="76" t="n"/>
       <c r="T82" s="82" t="n"/>
       <c r="U82" s="83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V82" s="75" t="inlineStr">
         <is>
@@ -11452,7 +11449,7 @@
       <c r="S83" s="67" t="n"/>
       <c r="T83" s="73" t="n"/>
       <c r="U83" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V83" s="66" t="inlineStr">
         <is>
@@ -11548,7 +11545,7 @@
       <c r="S84" s="76" t="n"/>
       <c r="T84" s="82" t="n"/>
       <c r="U84" s="83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V84" s="75" t="inlineStr">
         <is>
@@ -11644,7 +11641,7 @@
       <c r="S85" s="67" t="n"/>
       <c r="T85" s="73" t="n"/>
       <c r="U85" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V85" s="66" t="inlineStr">
         <is>
@@ -11740,7 +11737,7 @@
       <c r="S86" s="76" t="n"/>
       <c r="T86" s="82" t="n"/>
       <c r="U86" s="83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V86" s="75" t="inlineStr">
         <is>
@@ -11840,7 +11837,7 @@
       <c r="S87" s="67" t="n"/>
       <c r="T87" s="73" t="n"/>
       <c r="U87" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V87" s="66" t="inlineStr">
         <is>
@@ -11936,7 +11933,7 @@
       <c r="S88" s="76" t="n"/>
       <c r="T88" s="82" t="n"/>
       <c r="U88" s="83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V88" s="75" t="inlineStr">
         <is>
@@ -12032,7 +12029,7 @@
       <c r="S89" s="67" t="n"/>
       <c r="T89" s="73" t="n"/>
       <c r="U89" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V89" s="66" t="inlineStr">
         <is>
@@ -12128,7 +12125,7 @@
       <c r="S90" s="76" t="n"/>
       <c r="T90" s="82" t="n"/>
       <c r="U90" s="83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V90" s="75" t="inlineStr">
         <is>
@@ -12228,7 +12225,7 @@
       <c r="S91" s="67" t="n"/>
       <c r="T91" s="73" t="n"/>
       <c r="U91" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V91" s="66" t="inlineStr">
         <is>
@@ -12324,7 +12321,7 @@
       <c r="S92" s="76" t="n"/>
       <c r="T92" s="82" t="n"/>
       <c r="U92" s="83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V92" s="75" t="inlineStr">
         <is>
@@ -12420,7 +12417,7 @@
       <c r="S93" s="67" t="n"/>
       <c r="T93" s="73" t="n"/>
       <c r="U93" s="74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V93" s="66" t="inlineStr">
         <is>
@@ -12520,7 +12517,7 @@
       <c r="S94" s="76" t="n"/>
       <c r="T94" s="82" t="n"/>
       <c r="U94" s="83" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="V94" s="75" t="inlineStr">
         <is>
@@ -12620,7 +12617,7 @@
       <c r="S95" s="67" t="n"/>
       <c r="T95" s="66" t="n"/>
       <c r="U95" s="74" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="V95" s="66" t="inlineStr">
         <is>
@@ -12720,7 +12717,7 @@
       <c r="S96" s="76" t="n"/>
       <c r="T96" s="82" t="n"/>
       <c r="U96" s="83" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="V96" s="75" t="inlineStr">
         <is>
@@ -12820,7 +12817,7 @@
       <c r="S97" s="67" t="n"/>
       <c r="T97" s="66" t="n"/>
       <c r="U97" s="74" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="V97" s="66" t="inlineStr">
         <is>
@@ -12916,7 +12913,7 @@
       <c r="S98" s="76" t="n"/>
       <c r="T98" s="82" t="n"/>
       <c r="U98" s="83" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="V98" s="75" t="inlineStr">
         <is>
@@ -13012,7 +13009,7 @@
       <c r="S99" s="67" t="n"/>
       <c r="T99" s="66" t="n"/>
       <c r="U99" s="74" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="V99" s="66" t="inlineStr">
         <is>
@@ -13112,7 +13109,7 @@
       <c r="S100" s="76" t="n"/>
       <c r="T100" s="82" t="n"/>
       <c r="U100" s="83" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="V100" s="75" t="inlineStr">
         <is>
@@ -13208,7 +13205,7 @@
       <c r="S101" s="67" t="n"/>
       <c r="T101" s="73" t="n"/>
       <c r="U101" s="74" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="V101" s="66" t="inlineStr">
         <is>
@@ -13304,7 +13301,7 @@
       <c r="S102" s="76" t="n"/>
       <c r="T102" s="82" t="n"/>
       <c r="U102" s="83" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="V102" s="75" t="inlineStr">
         <is>
@@ -13400,7 +13397,7 @@
       <c r="S103" s="67" t="n"/>
       <c r="T103" s="73" t="n"/>
       <c r="U103" s="74" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="V103" s="66" t="inlineStr">
         <is>
@@ -13496,7 +13493,7 @@
       <c r="S104" s="76" t="n"/>
       <c r="T104" s="75" t="n"/>
       <c r="U104" s="83" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="V104" s="75" t="inlineStr">
         <is>
@@ -13972,7 +13969,7 @@
       <c r="S109" s="67" t="n"/>
       <c r="T109" s="66" t="n"/>
       <c r="U109" s="74" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="V109" s="66" t="n"/>
       <c r="W109" s="68" t="n"/>
@@ -14056,7 +14053,7 @@
       <c r="S110" s="76" t="n"/>
       <c r="T110" s="82" t="n"/>
       <c r="U110" s="83" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="V110" s="75" t="n"/>
       <c r="W110" s="77" t="n"/>
@@ -25905,7 +25902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AG103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -25979,7 +25976,8 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="92" t="n"/>
+      <c r="AF1" s="91" t="n"/>
+      <c r="AG1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
@@ -26016,12 +26014,8 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
-        </is>
-      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -41329,7 +41323,7 @@
       </c>
       <c r="F5" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G5" s="66" t="inlineStr">
@@ -41364,7 +41358,7 @@
       </c>
       <c r="F6" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G6" s="75" t="inlineStr">
@@ -41399,7 +41393,7 @@
       </c>
       <c r="F7" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G7" s="66" t="inlineStr">
@@ -41434,7 +41428,7 @@
       </c>
       <c r="F8" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G8" s="75" t="inlineStr">
@@ -41469,7 +41463,7 @@
       </c>
       <c r="F9" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G9" s="66" t="inlineStr">
@@ -41504,7 +41498,7 @@
       </c>
       <c r="F10" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G10" s="75" t="inlineStr">
@@ -41539,7 +41533,7 @@
       </c>
       <c r="F11" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G11" s="66" t="inlineStr">
@@ -41574,7 +41568,7 @@
       </c>
       <c r="F12" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G12" s="75" t="inlineStr">
@@ -41609,7 +41603,7 @@
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G13" s="66" t="inlineStr">
@@ -41644,7 +41638,7 @@
       </c>
       <c r="F14" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G14" s="75" t="inlineStr">
@@ -41679,7 +41673,7 @@
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G15" s="66" t="inlineStr">
@@ -41714,7 +41708,7 @@
       </c>
       <c r="F16" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G16" s="75" t="inlineStr">
@@ -41749,7 +41743,7 @@
       </c>
       <c r="F17" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G17" s="66" t="inlineStr">
@@ -41784,7 +41778,7 @@
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G18" s="75" t="inlineStr">
@@ -41819,7 +41813,7 @@
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G19" s="66" t="inlineStr">
@@ -41854,7 +41848,7 @@
       </c>
       <c r="F20" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G20" s="75" t="inlineStr">
@@ -41889,7 +41883,7 @@
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G21" s="66" t="inlineStr">
@@ -41924,7 +41918,7 @@
       </c>
       <c r="F22" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G22" s="75" t="inlineStr">
@@ -41959,7 +41953,7 @@
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G23" s="66" t="inlineStr">
@@ -41994,7 +41988,7 @@
       </c>
       <c r="F24" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G24" s="75" t="inlineStr">
@@ -42029,7 +42023,7 @@
       </c>
       <c r="F25" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G25" s="66" t="inlineStr">
@@ -42064,7 +42058,7 @@
       </c>
       <c r="F26" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G26" s="75" t="inlineStr">
@@ -42099,7 +42093,7 @@
       </c>
       <c r="F27" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G27" s="66" t="inlineStr">
@@ -42134,7 +42128,7 @@
       </c>
       <c r="F28" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G28" s="75" t="inlineStr">
@@ -42169,7 +42163,7 @@
       </c>
       <c r="F29" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G29" s="66" t="inlineStr">
@@ -42204,7 +42198,7 @@
       </c>
       <c r="F30" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G30" s="75" t="inlineStr">
@@ -42239,7 +42233,7 @@
       </c>
       <c r="F31" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G31" s="66" t="inlineStr">
@@ -42274,7 +42268,7 @@
       </c>
       <c r="F32" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G32" s="75" t="inlineStr">
@@ -42309,7 +42303,7 @@
       </c>
       <c r="F33" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G33" s="66" t="inlineStr">
@@ -42344,7 +42338,7 @@
       </c>
       <c r="F34" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G34" s="75" t="inlineStr">
@@ -42379,7 +42373,7 @@
       </c>
       <c r="F35" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G35" s="66" t="inlineStr">
@@ -42414,7 +42408,7 @@
       </c>
       <c r="F36" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G36" s="75" t="inlineStr">
@@ -42449,7 +42443,7 @@
       </c>
       <c r="F37" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G37" s="66" t="inlineStr">
@@ -42484,7 +42478,7 @@
       </c>
       <c r="F38" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G38" s="75" t="inlineStr">
@@ -42519,7 +42513,7 @@
       </c>
       <c r="F39" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G39" s="66" t="inlineStr">
@@ -42554,7 +42548,7 @@
       </c>
       <c r="F40" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G40" s="75" t="inlineStr">
@@ -42589,7 +42583,7 @@
       </c>
       <c r="F41" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G41" s="66" t="inlineStr">
@@ -42624,7 +42618,7 @@
       </c>
       <c r="F42" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G42" s="75" t="inlineStr">
@@ -42659,7 +42653,7 @@
       </c>
       <c r="F43" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G43" s="66" t="inlineStr">
@@ -42694,7 +42688,7 @@
       </c>
       <c r="F44" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G44" s="75" t="inlineStr">
@@ -42729,7 +42723,7 @@
       </c>
       <c r="F45" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G45" s="66" t="inlineStr">
@@ -42764,7 +42758,7 @@
       </c>
       <c r="F46" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G46" s="75" t="inlineStr">
@@ -42799,7 +42793,7 @@
       </c>
       <c r="F47" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G47" s="66" t="inlineStr">
@@ -42834,7 +42828,7 @@
       </c>
       <c r="F48" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G48" s="75" t="inlineStr">
@@ -42869,7 +42863,7 @@
       </c>
       <c r="F49" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G49" s="66" t="inlineStr">
@@ -42904,7 +42898,7 @@
       </c>
       <c r="F50" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G50" s="75" t="inlineStr">
@@ -42939,7 +42933,7 @@
       </c>
       <c r="F51" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G51" s="66" t="inlineStr">
@@ -42974,7 +42968,7 @@
       </c>
       <c r="F52" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G52" s="75" t="inlineStr">
@@ -43009,7 +43003,7 @@
       </c>
       <c r="F53" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G53" s="66" t="inlineStr">
@@ -43044,7 +43038,7 @@
       </c>
       <c r="F54" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G54" s="75" t="inlineStr">
@@ -43079,7 +43073,7 @@
       </c>
       <c r="F55" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G55" s="66" t="inlineStr">
@@ -43114,7 +43108,7 @@
       </c>
       <c r="F56" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G56" s="75" t="inlineStr">
@@ -43149,7 +43143,7 @@
       </c>
       <c r="F57" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G57" s="66" t="inlineStr">
@@ -43184,7 +43178,7 @@
       </c>
       <c r="F58" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G58" s="75" t="inlineStr">
@@ -43219,7 +43213,7 @@
       </c>
       <c r="F59" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G59" s="66" t="inlineStr">
@@ -43254,7 +43248,7 @@
       </c>
       <c r="F60" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G60" s="75" t="inlineStr">
@@ -43289,7 +43283,7 @@
       </c>
       <c r="F61" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G61" s="66" t="inlineStr">
@@ -43324,7 +43318,7 @@
       </c>
       <c r="F62" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G62" s="75" t="inlineStr">
@@ -43359,7 +43353,7 @@
       </c>
       <c r="F63" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G63" s="66" t="inlineStr">
@@ -43394,7 +43388,7 @@
       </c>
       <c r="F64" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G64" s="75" t="inlineStr">
@@ -43429,7 +43423,7 @@
       </c>
       <c r="F65" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G65" s="66" t="inlineStr">
@@ -43464,7 +43458,7 @@
       </c>
       <c r="F66" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G66" s="75" t="inlineStr">
@@ -43499,7 +43493,7 @@
       </c>
       <c r="F67" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G67" s="66" t="inlineStr">
@@ -43534,7 +43528,7 @@
       </c>
       <c r="F68" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G68" s="75" t="inlineStr">
@@ -43569,7 +43563,7 @@
       </c>
       <c r="F69" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G69" s="66" t="inlineStr">
@@ -43604,7 +43598,7 @@
       </c>
       <c r="F70" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G70" s="75" t="inlineStr">
@@ -43639,7 +43633,7 @@
       </c>
       <c r="F71" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G71" s="66" t="inlineStr">
@@ -43674,7 +43668,7 @@
       </c>
       <c r="F72" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G72" s="75" t="inlineStr">
@@ -43709,7 +43703,7 @@
       </c>
       <c r="F73" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G73" s="66" t="inlineStr">
@@ -43744,7 +43738,7 @@
       </c>
       <c r="F74" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G74" s="75" t="inlineStr">
@@ -43779,7 +43773,7 @@
       </c>
       <c r="F75" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G75" s="66" t="inlineStr">
@@ -43814,7 +43808,7 @@
       </c>
       <c r="F76" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G76" s="75" t="inlineStr">
@@ -43849,7 +43843,7 @@
       </c>
       <c r="F77" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G77" s="66" t="inlineStr">
@@ -43884,7 +43878,7 @@
       </c>
       <c r="F78" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G78" s="75" t="inlineStr">
@@ -43919,7 +43913,7 @@
       </c>
       <c r="F79" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G79" s="66" t="inlineStr">
@@ -43954,7 +43948,7 @@
       </c>
       <c r="F80" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G80" s="75" t="inlineStr">
@@ -43989,7 +43983,7 @@
       </c>
       <c r="F81" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G81" s="66" t="inlineStr">
@@ -44024,7 +44018,7 @@
       </c>
       <c r="F82" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G82" s="75" t="inlineStr">
@@ -44059,7 +44053,7 @@
       </c>
       <c r="F83" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G83" s="66" t="inlineStr">
@@ -44094,7 +44088,7 @@
       </c>
       <c r="F84" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G84" s="75" t="inlineStr">
@@ -44129,7 +44123,7 @@
       </c>
       <c r="F85" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G85" s="66" t="inlineStr">
@@ -44164,7 +44158,7 @@
       </c>
       <c r="F86" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G86" s="75" t="inlineStr">
@@ -44199,7 +44193,7 @@
       </c>
       <c r="F87" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G87" s="66" t="inlineStr">
@@ -44234,7 +44228,7 @@
       </c>
       <c r="F88" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G88" s="75" t="inlineStr">
@@ -44269,7 +44263,7 @@
       </c>
       <c r="F89" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G89" s="66" t="inlineStr">
@@ -44304,7 +44298,7 @@
       </c>
       <c r="F90" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G90" s="75" t="inlineStr">
@@ -44339,7 +44333,7 @@
       </c>
       <c r="F91" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G91" s="66" t="inlineStr">
@@ -44374,7 +44368,7 @@
       </c>
       <c r="F92" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G92" s="75" t="inlineStr">
@@ -44409,7 +44403,7 @@
       </c>
       <c r="F93" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G93" s="66" t="inlineStr">
@@ -44444,7 +44438,7 @@
       </c>
       <c r="F94" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G94" s="75" t="inlineStr">
@@ -44479,7 +44473,7 @@
       </c>
       <c r="F95" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G95" s="66" t="inlineStr">
@@ -44514,7 +44508,7 @@
       </c>
       <c r="F96" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G96" s="75" t="inlineStr">
@@ -44549,7 +44543,7 @@
       </c>
       <c r="F97" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G97" s="66" t="inlineStr">
@@ -44584,7 +44578,7 @@
       </c>
       <c r="F98" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G98" s="75" t="inlineStr">
@@ -44619,7 +44613,7 @@
       </c>
       <c r="F99" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G99" s="66" t="inlineStr">
@@ -44654,7 +44648,7 @@
       </c>
       <c r="F100" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G100" s="75" t="inlineStr">
@@ -44689,7 +44683,7 @@
       </c>
       <c r="F101" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G101" s="66" t="inlineStr">
@@ -44724,7 +44718,7 @@
       </c>
       <c r="F102" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G102" s="75" t="inlineStr">
@@ -44759,7 +44753,7 @@
       </c>
       <c r="F103" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G103" s="66" t="inlineStr">
@@ -44794,7 +44788,7 @@
       </c>
       <c r="F104" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G104" s="75" t="inlineStr">
@@ -44829,7 +44823,7 @@
       </c>
       <c r="F105" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G105" s="66" t="inlineStr">
@@ -44864,7 +44858,7 @@
       </c>
       <c r="F106" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G106" s="75" t="inlineStr">
@@ -44899,7 +44893,7 @@
       </c>
       <c r="F107" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G107" s="66" t="inlineStr">
@@ -44934,7 +44928,7 @@
       </c>
       <c r="F108" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G108" s="75" t="inlineStr">
@@ -44969,7 +44963,7 @@
       </c>
       <c r="F109" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G109" s="66" t="inlineStr">
@@ -45004,7 +44998,7 @@
       </c>
       <c r="F110" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G110" s="75" t="inlineStr">
@@ -46033,7 +46027,7 @@
       </c>
       <c r="F5" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46063,7 +46057,7 @@
       </c>
       <c r="F6" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46093,7 +46087,7 @@
       </c>
       <c r="F7" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46123,7 +46117,7 @@
       </c>
       <c r="F8" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46153,7 +46147,7 @@
       </c>
       <c r="F9" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46183,7 +46177,7 @@
       </c>
       <c r="F10" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46213,7 +46207,7 @@
       </c>
       <c r="F11" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46243,7 +46237,7 @@
       </c>
       <c r="F12" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46273,7 +46267,7 @@
       </c>
       <c r="F13" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46303,7 +46297,7 @@
       </c>
       <c r="F14" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46327,7 @@
       </c>
       <c r="F15" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46363,7 +46357,7 @@
       </c>
       <c r="F16" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46393,7 +46387,7 @@
       </c>
       <c r="F17" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46423,7 +46417,7 @@
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46453,7 +46447,7 @@
       </c>
       <c r="F19" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46483,7 +46477,7 @@
       </c>
       <c r="F20" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46513,7 +46507,7 @@
       </c>
       <c r="F21" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46543,7 +46537,7 @@
       </c>
       <c r="F22" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46573,7 +46567,7 @@
       </c>
       <c r="F23" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46603,7 +46597,7 @@
       </c>
       <c r="F24" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46633,7 +46627,7 @@
       </c>
       <c r="F25" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46663,7 +46657,7 @@
       </c>
       <c r="F26" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46693,7 +46687,7 @@
       </c>
       <c r="F27" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46723,7 +46717,7 @@
       </c>
       <c r="F28" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46753,7 +46747,7 @@
       </c>
       <c r="F29" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46783,7 +46777,7 @@
       </c>
       <c r="F30" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46813,7 +46807,7 @@
       </c>
       <c r="F31" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46843,7 +46837,7 @@
       </c>
       <c r="F32" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46873,7 +46867,7 @@
       </c>
       <c r="F33" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46903,7 +46897,7 @@
       </c>
       <c r="F34" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46933,7 +46927,7 @@
       </c>
       <c r="F35" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46963,7 +46957,7 @@
       </c>
       <c r="F36" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -46993,7 +46987,7 @@
       </c>
       <c r="F37" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47023,7 +47017,7 @@
       </c>
       <c r="F38" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47053,7 +47047,7 @@
       </c>
       <c r="F39" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47083,7 +47077,7 @@
       </c>
       <c r="F40" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47113,7 +47107,7 @@
       </c>
       <c r="F41" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47143,7 +47137,7 @@
       </c>
       <c r="F42" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47173,7 +47167,7 @@
       </c>
       <c r="F43" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47197,7 @@
       </c>
       <c r="F44" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47233,7 +47227,7 @@
       </c>
       <c r="F45" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47263,7 +47257,7 @@
       </c>
       <c r="F46" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47293,7 +47287,7 @@
       </c>
       <c r="F47" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47323,7 +47317,7 @@
       </c>
       <c r="F48" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47353,7 +47347,7 @@
       </c>
       <c r="F49" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47383,7 +47377,7 @@
       </c>
       <c r="F50" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47413,7 +47407,7 @@
       </c>
       <c r="F51" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47443,7 +47437,7 @@
       </c>
       <c r="F52" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47473,7 +47467,7 @@
       </c>
       <c r="F53" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47503,7 +47497,7 @@
       </c>
       <c r="F54" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47533,7 +47527,7 @@
       </c>
       <c r="F55" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47563,7 +47557,7 @@
       </c>
       <c r="F56" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47593,7 +47587,7 @@
       </c>
       <c r="F57" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47623,7 +47617,7 @@
       </c>
       <c r="F58" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47653,7 +47647,7 @@
       </c>
       <c r="F59" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47683,7 +47677,7 @@
       </c>
       <c r="F60" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47713,7 +47707,7 @@
       </c>
       <c r="F61" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47743,7 +47737,7 @@
       </c>
       <c r="F62" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47773,7 +47767,7 @@
       </c>
       <c r="F63" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47803,7 +47797,7 @@
       </c>
       <c r="F64" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47833,7 +47827,7 @@
       </c>
       <c r="F65" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47863,7 +47857,7 @@
       </c>
       <c r="F66" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47893,7 +47887,7 @@
       </c>
       <c r="F67" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47917,7 @@
       </c>
       <c r="F68" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47953,7 +47947,7 @@
       </c>
       <c r="F69" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -47983,7 +47977,7 @@
       </c>
       <c r="F70" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48013,7 +48007,7 @@
       </c>
       <c r="F71" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48043,7 +48037,7 @@
       </c>
       <c r="F72" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48073,7 +48067,7 @@
       </c>
       <c r="F73" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48103,7 +48097,7 @@
       </c>
       <c r="F74" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48133,7 +48127,7 @@
       </c>
       <c r="F75" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48163,7 +48157,7 @@
       </c>
       <c r="F76" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48193,7 +48187,7 @@
       </c>
       <c r="F77" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48223,7 +48217,7 @@
       </c>
       <c r="F78" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48253,7 +48247,7 @@
       </c>
       <c r="F79" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48283,7 +48277,7 @@
       </c>
       <c r="F80" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48313,7 +48307,7 @@
       </c>
       <c r="F81" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48343,7 +48337,7 @@
       </c>
       <c r="F82" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48373,7 +48367,7 @@
       </c>
       <c r="F83" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48403,7 +48397,7 @@
       </c>
       <c r="F84" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48433,7 +48427,7 @@
       </c>
       <c r="F85" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48463,7 +48457,7 @@
       </c>
       <c r="F86" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48493,7 +48487,7 @@
       </c>
       <c r="F87" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48523,7 +48517,7 @@
       </c>
       <c r="F88" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48553,7 +48547,7 @@
       </c>
       <c r="F89" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48583,7 +48577,7 @@
       </c>
       <c r="F90" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48613,7 +48607,7 @@
       </c>
       <c r="F91" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48643,7 +48637,7 @@
       </c>
       <c r="F92" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48673,7 +48667,7 @@
       </c>
       <c r="F93" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48703,7 +48697,7 @@
       </c>
       <c r="F94" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48733,7 +48727,7 @@
       </c>
       <c r="F95" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48763,7 +48757,7 @@
       </c>
       <c r="F96" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48793,7 +48787,7 @@
       </c>
       <c r="F97" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48823,7 +48817,7 @@
       </c>
       <c r="F98" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48853,7 +48847,7 @@
       </c>
       <c r="F99" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48883,7 +48877,7 @@
       </c>
       <c r="F100" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48913,7 +48907,7 @@
       </c>
       <c r="F101" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48943,7 +48937,7 @@
       </c>
       <c r="F102" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -48973,7 +48967,7 @@
       </c>
       <c r="F103" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49003,7 +48997,7 @@
       </c>
       <c r="F104" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49033,7 +49027,7 @@
       </c>
       <c r="F105" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49057,7 @@
       </c>
       <c r="F106" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49093,7 +49087,7 @@
       </c>
       <c r="F107" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49123,7 +49117,7 @@
       </c>
       <c r="F108" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49153,7 +49147,7 @@
       </c>
       <c r="F109" s="66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49183,7 +49177,7 @@
       </c>
       <c r="F110" s="75" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -49980,7 +49974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF34"/>
+  <dimension ref="A1:AG34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50054,7 +50048,8 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="92" t="n"/>
+      <c r="AF1" s="91" t="n"/>
+      <c r="AG1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="93" t="inlineStr">
@@ -50091,12 +50086,8 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
-        </is>
-      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -51522,7 +51513,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="99" t="inlineStr">
         <is>
-          <t>㈜케이엔케이 │ 관리코드 일관성 불일치 보고 │ 2026-05-02</t>
+          <t>㈜케이엔케이 │ 관리코드 일관성 불일치 보고 │ 2026-05-03</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -765,6 +765,24 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1878,35 +1896,32 @@
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
@@ -3345,7 +3360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG140"/>
+  <dimension ref="A1:AF140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3378,13 +3393,13 @@
     <col width="13" customWidth="1" style="34" min="28" max="28"/>
     <col width="8" customWidth="1" style="34" min="29" max="31"/>
     <col width="8" customWidth="1" style="34" min="30" max="30"/>
-    <col width="8" customWidth="1" style="34" min="31" max="31"/>
+    <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3419,11 +3434,10 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="91" t="n"/>
-      <c r="AG1" s="92" t="n"/>
+      <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3457,8 +3471,12 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="91" t="n"/>
-      <c r="AF2" s="92" t="n"/>
+      <c r="AE2" s="92" t="n"/>
+      <c r="AF2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:43</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -3849,7 +3867,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="95" t="n">
+      <c r="P5" s="71" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -3908,12 +3926,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="98" t="inlineStr">
+      <c r="G6" s="77" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -3945,7 +3963,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="96" t="n">
+      <c r="P6" s="80" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -4041,7 +4059,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="95" t="n">
+      <c r="P7" s="71" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -4105,7 +4123,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="97" t="inlineStr">
+      <c r="H8" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4137,7 +4155,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="96" t="n">
+      <c r="P8" s="80" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -4201,7 +4219,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="97" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4233,7 +4251,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="95" t="n">
+      <c r="P9" s="71" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -4292,12 +4310,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="98" t="inlineStr">
+      <c r="G10" s="77" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="98" t="inlineStr">
+      <c r="H10" s="77" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -4329,7 +4347,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="96" t="n">
+      <c r="P10" s="80" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -4425,7 +4443,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="95" t="n">
+      <c r="P11" s="71" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -4521,7 +4539,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="96" t="n">
+      <c r="P12" s="80" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -4617,7 +4635,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="95" t="n">
+      <c r="P13" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -4713,7 +4731,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="96" t="n">
+      <c r="P14" s="80" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -4905,7 +4923,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="96" t="n">
+      <c r="P16" s="80" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -5101,7 +5119,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="96" t="n">
+      <c r="P18" s="80" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -5160,12 +5178,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="98" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="98" t="inlineStr">
+      <c r="H19" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5197,7 +5215,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="95" t="n">
+      <c r="P19" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -5261,7 +5279,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="97" t="inlineStr">
+      <c r="H20" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5293,7 +5311,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="96" t="n">
+      <c r="P20" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -5352,12 +5370,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="98" t="inlineStr">
+      <c r="G21" s="68" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="98" t="inlineStr">
+      <c r="H21" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5389,7 +5407,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="95" t="n">
+      <c r="P21" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -5453,7 +5471,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="97" t="inlineStr">
+      <c r="H22" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5485,7 +5503,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="96" t="n">
+      <c r="P22" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -5549,7 +5567,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="97" t="inlineStr">
+      <c r="H23" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5581,7 +5599,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="95" t="n">
+      <c r="P23" s="71" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -5677,7 +5695,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="96" t="n">
+      <c r="P24" s="80" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -5773,7 +5791,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="95" t="n">
+      <c r="P25" s="71" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -5869,7 +5887,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="96" t="n">
+      <c r="P26" s="80" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -5965,7 +5983,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="95" t="n">
+      <c r="P27" s="71" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -6065,7 +6083,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="96" t="n">
+      <c r="P28" s="80" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -6161,7 +6179,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="95" t="n">
+      <c r="P29" s="71" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -6257,7 +6275,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="96" t="n">
+      <c r="P30" s="80" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -6353,7 +6371,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="95" t="n">
+      <c r="P31" s="71" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -6449,7 +6467,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="96" t="n">
+      <c r="P32" s="80" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -6545,7 +6563,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="95" t="n">
+      <c r="P33" s="71" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -6641,7 +6659,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="96" t="n">
+      <c r="P34" s="80" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -6737,7 +6755,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="95" t="n">
+      <c r="P35" s="71" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -6833,7 +6851,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="96" t="n">
+      <c r="P36" s="80" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -6929,7 +6947,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="95" t="n">
+      <c r="P37" s="71" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -6988,12 +7006,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="98" t="inlineStr">
+      <c r="G38" s="77" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="98" t="inlineStr">
+      <c r="H38" s="77" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -7025,7 +7043,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="96" t="n">
+      <c r="P38" s="80" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -7121,7 +7139,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="95" t="n">
+      <c r="P39" s="71" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -7180,12 +7198,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="98" t="inlineStr">
+      <c r="G40" s="77" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="98" t="inlineStr">
+      <c r="H40" s="77" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -7217,7 +7235,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="96" t="n">
+      <c r="P40" s="80" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -7280,12 +7298,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="98" t="inlineStr">
+      <c r="G41" s="68" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="98" t="inlineStr">
+      <c r="H41" s="68" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -7317,7 +7335,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="95" t="n">
+      <c r="P41" s="71" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -7380,12 +7398,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="98" t="inlineStr">
+      <c r="G42" s="77" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="98" t="inlineStr">
+      <c r="H42" s="77" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -7417,7 +7435,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="96" t="n">
+      <c r="P42" s="80" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -7517,7 +7535,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="95" t="n">
+      <c r="P43" s="71" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -7617,7 +7635,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="96" t="n">
+      <c r="P44" s="80" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -7680,7 +7698,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="97" t="inlineStr">
+      <c r="G45" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7717,7 +7735,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="95" t="n">
+      <c r="P45" s="71" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -7780,7 +7798,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="97" t="inlineStr">
+      <c r="G46" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7817,7 +7835,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="96" t="n">
+      <c r="P46" s="80" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -7876,12 +7894,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="98" t="inlineStr">
+      <c r="G47" s="68" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="98" t="inlineStr">
+      <c r="H47" s="68" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -7913,7 +7931,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="95" t="n">
+      <c r="P47" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -8013,7 +8031,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="96" t="n">
+      <c r="P48" s="80" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -8113,7 +8131,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="95" t="n">
+      <c r="P49" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -8213,7 +8231,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="96" t="n">
+      <c r="P50" s="80" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -8313,7 +8331,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="95" t="n">
+      <c r="P51" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -8409,7 +8427,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="96" t="n">
+      <c r="P52" s="80" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -8505,7 +8523,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="95" t="n">
+      <c r="P53" s="71" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -8601,7 +8619,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="96" t="n">
+      <c r="P54" s="80" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -8697,7 +8715,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="95" t="n">
+      <c r="P55" s="71" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -8797,7 +8815,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="96" t="n">
+      <c r="P56" s="80" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -8893,7 +8911,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="95" t="n">
+      <c r="P57" s="71" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -8989,7 +9007,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="96" t="n">
+      <c r="P58" s="80" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -9085,7 +9103,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="95" t="n">
+      <c r="P59" s="71" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -9181,7 +9199,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="96" t="n">
+      <c r="P60" s="80" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -9240,12 +9258,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="98" t="inlineStr">
+      <c r="G61" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="98" t="inlineStr">
+      <c r="H61" s="68" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -9277,7 +9295,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="95" t="n">
+      <c r="P61" s="71" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -9341,7 +9359,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="97" t="inlineStr">
+      <c r="H62" s="77" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -9436,12 +9454,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="98" t="inlineStr">
+      <c r="G63" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="98" t="inlineStr">
+      <c r="H63" s="68" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -9473,7 +9491,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="95" t="n">
+      <c r="P63" s="71" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -9537,7 +9555,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="97" t="inlineStr">
+      <c r="H64" s="77" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -9673,7 +9691,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="95" t="n">
+      <c r="P65" s="71" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -9773,7 +9791,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="96" t="n">
+      <c r="P66" s="80" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -9873,7 +9891,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="95" t="n">
+      <c r="P67" s="71" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -9936,7 +9954,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="97" t="inlineStr">
+      <c r="G68" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9973,7 +9991,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="96" t="n">
+      <c r="P68" s="80" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -10036,7 +10054,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="97" t="inlineStr">
+      <c r="G69" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -10073,7 +10091,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="95" t="n">
+      <c r="P69" s="71" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -10169,7 +10187,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="96" t="n">
+      <c r="P70" s="80" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -10233,7 +10251,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="97" t="inlineStr">
+      <c r="H71" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -10265,7 +10283,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="95" t="n">
+      <c r="P71" s="71" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -10361,7 +10379,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="96" t="n">
+      <c r="P72" s="80" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -10457,7 +10475,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="95" t="n">
+      <c r="P73" s="71" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -10521,7 +10539,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="97" t="inlineStr">
+      <c r="H74" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -10553,7 +10571,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="96" t="n">
+      <c r="P74" s="80" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -10649,7 +10667,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="95" t="n">
+      <c r="P75" s="71" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -10745,7 +10763,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="96" t="n">
+      <c r="P76" s="80" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -10841,7 +10859,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="95" t="n">
+      <c r="P77" s="71" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -10941,7 +10959,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="96" t="n">
+      <c r="P78" s="80" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -11037,7 +11055,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="95" t="n">
+      <c r="P79" s="71" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -11137,7 +11155,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="96" t="n">
+      <c r="P80" s="80" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -11237,7 +11255,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="95" t="n">
+      <c r="P81" s="71" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -11337,7 +11355,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="96" t="n">
+      <c r="P82" s="80" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -11433,7 +11451,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="95" t="n">
+      <c r="P83" s="71" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -11529,7 +11547,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="96" t="n">
+      <c r="P84" s="80" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -11625,7 +11643,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="95" t="n">
+      <c r="P85" s="71" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -11721,7 +11739,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="96" t="n">
+      <c r="P86" s="80" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -11821,7 +11839,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="95" t="n">
+      <c r="P87" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -11917,7 +11935,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="96" t="n">
+      <c r="P88" s="80" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -12013,7 +12031,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="95" t="n">
+      <c r="P89" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -12109,7 +12127,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="96" t="n">
+      <c r="P90" s="80" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -12209,7 +12227,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="95" t="n">
+      <c r="P91" s="71" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -12305,7 +12323,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="96" t="n">
+      <c r="P92" s="80" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -12401,7 +12419,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="95" t="n">
+      <c r="P93" s="71" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -12501,7 +12519,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="96" t="n">
+      <c r="P94" s="80" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -12601,7 +12619,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="95" t="n">
+      <c r="P95" s="71" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -12701,7 +12719,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="96" t="n">
+      <c r="P96" s="80" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -12801,7 +12819,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="95" t="n">
+      <c r="P97" s="71" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -12897,7 +12915,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="96" t="n">
+      <c r="P98" s="80" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -12956,7 +12974,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="97" t="inlineStr">
+      <c r="G99" s="68" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -12993,7 +13011,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="95" t="n">
+      <c r="P99" s="71" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -13093,7 +13111,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="96" t="n">
+      <c r="P100" s="80" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -13189,7 +13207,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="95" t="n">
+      <c r="P101" s="71" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -13285,7 +13303,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="96" t="n">
+      <c r="P102" s="80" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -13381,7 +13399,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="95" t="n">
+      <c r="P103" s="71" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -13440,12 +13458,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="97" t="inlineStr">
+      <c r="G104" s="77" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="97" t="inlineStr">
+      <c r="H104" s="77" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -13477,7 +13495,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="96" t="n">
+      <c r="P104" s="80" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -13573,7 +13591,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="95" t="n">
+      <c r="P105" s="71" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -13667,7 +13685,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="96" t="n">
+      <c r="P106" s="80" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -13761,7 +13779,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="95" t="n">
+      <c r="P107" s="71" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -13855,7 +13873,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="96" t="n">
+      <c r="P108" s="80" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -13953,7 +13971,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="95" t="n">
+      <c r="P109" s="71" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -14037,7 +14055,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="96" t="n">
+      <c r="P110" s="80" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -15090,10 +15108,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:AE2"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="13">
     <dataValidation sqref="I5:I140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -15131,9 +15149,6 @@
       <formula1>"제외"</formula1>
     </dataValidation>
     <dataValidation sqref="AD5:AD140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE5:AE140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15188,10 +15203,10 @@
     <col width="8" customWidth="1" min="34" max="34"/>
     <col width="8" customWidth="1" min="35" max="35"/>
     <col width="8" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
     <col width="8" customWidth="1" min="38" max="41"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="8" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
     <col width="8" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="43"/>
     <col width="10" customWidth="1" min="43" max="43"/>
@@ -15199,7 +15214,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -15243,13 +15258,10 @@
       <c r="AL1" s="91" t="n"/>
       <c r="AM1" s="91" t="n"/>
       <c r="AN1" s="91" t="n"/>
-      <c r="AO1" s="91" t="n"/>
-      <c r="AP1" s="91" t="n"/>
-      <c r="AQ1" s="91" t="n"/>
-      <c r="AR1" s="92" t="n"/>
+      <c r="AO1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15292,11 +15304,13 @@
       <c r="AK2" s="91" t="n"/>
       <c r="AL2" s="91" t="n"/>
       <c r="AM2" s="91" t="n"/>
-      <c r="AN2" s="91" t="n"/>
-      <c r="AO2" s="91" t="n"/>
-      <c r="AP2" s="91" t="n"/>
-      <c r="AQ2" s="92" t="n"/>
-      <c r="AR2" s="94" t="inlineStr">
+      <c r="AN2" s="92" t="n"/>
+      <c r="AO2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:43</t>
+        </is>
+      </c>
+      <c r="AR2" s="108" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:43</t>
         </is>
@@ -15730,38 +15744,38 @@
       </c>
       <c r="AJ4" s="64" t="inlineStr">
         <is>
-          <t>가공팀
-핀블럭</t>
-        </is>
-      </c>
-      <c r="AK4" s="64" t="inlineStr">
-        <is>
-          <t>가공팀
-일반가공품</t>
-        </is>
-      </c>
-      <c r="AL4" s="64" t="inlineStr">
-        <is>
-          <t>가공팀
-소계</t>
-        </is>
-      </c>
-      <c r="AM4" s="64" t="inlineStr">
-        <is>
           <t>베트남
 설계</t>
         </is>
       </c>
-      <c r="AN4" s="64" t="inlineStr">
+      <c r="AK4" s="64" t="inlineStr">
         <is>
           <t>베트남
 가공</t>
         </is>
       </c>
-      <c r="AO4" s="64" t="inlineStr">
+      <c r="AL4" s="64" t="inlineStr">
         <is>
           <t>베트남
 조립</t>
+        </is>
+      </c>
+      <c r="AM4" s="64" t="inlineStr">
+        <is>
+          <t>베트남
+동작검증</t>
+        </is>
+      </c>
+      <c r="AN4" s="64" t="inlineStr">
+        <is>
+          <t>베트남
+출하검증</t>
+        </is>
+      </c>
+      <c r="AO4" s="64" t="inlineStr">
+        <is>
+          <t>베트남
+소계</t>
         </is>
       </c>
       <c r="AP4" s="64" t="inlineStr">
@@ -24790,8 +24804,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AR1"/>
-    <mergeCell ref="A2:AQ2"/>
+    <mergeCell ref="A2:AN2"/>
+    <mergeCell ref="A1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -24834,7 +24848,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -24863,7 +24877,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -24889,9 +24903,9 @@
       <c r="T2" s="91" t="n"/>
       <c r="U2" s="91" t="n"/>
       <c r="V2" s="92" t="n"/>
-      <c r="W2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="W2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:43</t>
         </is>
       </c>
     </row>
@@ -25902,7 +25916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG103"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -25935,13 +25949,13 @@
     <col width="13" customWidth="1" style="34" min="28" max="28"/>
     <col width="8" customWidth="1" style="34" min="29" max="31"/>
     <col width="8" customWidth="1" style="34" min="30" max="30"/>
-    <col width="8" customWidth="1" style="34" min="31" max="31"/>
+    <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -25976,11 +25990,10 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="91" t="n"/>
-      <c r="AG1" s="92" t="n"/>
+      <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -26014,8 +26027,12 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="91" t="n"/>
-      <c r="AF2" s="92" t="n"/>
+      <c r="AE2" s="92" t="n"/>
+      <c r="AF2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -33763,10 +33780,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:AE2"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="13">
     <dataValidation sqref="I5:I103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -33806,9 +33823,6 @@
     <dataValidation sqref="AD5:AD103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE5:AE103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -33836,7 +33850,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -33850,7 +33864,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -33861,9 +33875,9 @@
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="91" t="n"/>
       <c r="G2" s="92" t="n"/>
-      <c r="H2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="H2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -41181,20 +41195,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="3"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -41207,7 +41221,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -41217,9 +41231,9 @@
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="92" t="n"/>
-      <c r="G2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="G2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -45276,609 +45290,6 @@
       <c r="E140" s="85" t="n"/>
       <c r="F140" s="75" t="n"/>
       <c r="G140" s="75" t="n"/>
-    </row>
-    <row r="141" ht="22.05" customHeight="1">
-      <c r="A141" s="66" t="n"/>
-      <c r="B141" s="66" t="n"/>
-      <c r="C141" s="66" t="n"/>
-      <c r="D141" s="66" t="n"/>
-      <c r="E141" s="84" t="n"/>
-      <c r="F141" s="66" t="n"/>
-      <c r="G141" s="66" t="n"/>
-    </row>
-    <row r="142" ht="22.05" customHeight="1">
-      <c r="A142" s="75" t="n"/>
-      <c r="B142" s="75" t="n"/>
-      <c r="C142" s="75" t="n"/>
-      <c r="D142" s="75" t="n"/>
-      <c r="E142" s="85" t="n"/>
-      <c r="F142" s="75" t="n"/>
-      <c r="G142" s="75" t="n"/>
-    </row>
-    <row r="143" ht="22.05" customHeight="1">
-      <c r="A143" s="66" t="n"/>
-      <c r="B143" s="66" t="n"/>
-      <c r="C143" s="66" t="n"/>
-      <c r="D143" s="66" t="n"/>
-      <c r="E143" s="84" t="n"/>
-      <c r="F143" s="66" t="n"/>
-      <c r="G143" s="66" t="n"/>
-    </row>
-    <row r="144" ht="22.05" customHeight="1">
-      <c r="A144" s="75" t="n"/>
-      <c r="B144" s="75" t="n"/>
-      <c r="C144" s="75" t="n"/>
-      <c r="D144" s="75" t="n"/>
-      <c r="E144" s="85" t="n"/>
-      <c r="F144" s="75" t="n"/>
-      <c r="G144" s="75" t="n"/>
-    </row>
-    <row r="145" ht="22.05" customHeight="1">
-      <c r="A145" s="66" t="n"/>
-      <c r="B145" s="66" t="n"/>
-      <c r="C145" s="66" t="n"/>
-      <c r="D145" s="66" t="n"/>
-      <c r="E145" s="84" t="n"/>
-      <c r="F145" s="66" t="n"/>
-      <c r="G145" s="66" t="n"/>
-    </row>
-    <row r="146" ht="22.05" customHeight="1">
-      <c r="A146" s="75" t="n"/>
-      <c r="B146" s="75" t="n"/>
-      <c r="C146" s="75" t="n"/>
-      <c r="D146" s="75" t="n"/>
-      <c r="E146" s="85" t="n"/>
-      <c r="F146" s="75" t="n"/>
-      <c r="G146" s="75" t="n"/>
-    </row>
-    <row r="147" ht="22.05" customHeight="1">
-      <c r="A147" s="66" t="n"/>
-      <c r="B147" s="66" t="n"/>
-      <c r="C147" s="66" t="n"/>
-      <c r="D147" s="66" t="n"/>
-      <c r="E147" s="84" t="n"/>
-      <c r="F147" s="66" t="n"/>
-      <c r="G147" s="66" t="n"/>
-    </row>
-    <row r="148" ht="22.05" customHeight="1">
-      <c r="A148" s="75" t="n"/>
-      <c r="B148" s="75" t="n"/>
-      <c r="C148" s="75" t="n"/>
-      <c r="D148" s="75" t="n"/>
-      <c r="E148" s="85" t="n"/>
-      <c r="F148" s="75" t="n"/>
-      <c r="G148" s="75" t="n"/>
-    </row>
-    <row r="149" ht="22.05" customHeight="1">
-      <c r="A149" s="66" t="n"/>
-      <c r="B149" s="66" t="n"/>
-      <c r="C149" s="66" t="n"/>
-      <c r="D149" s="66" t="n"/>
-      <c r="E149" s="84" t="n"/>
-      <c r="F149" s="66" t="n"/>
-      <c r="G149" s="66" t="n"/>
-    </row>
-    <row r="150" ht="22.05" customHeight="1">
-      <c r="A150" s="75" t="n"/>
-      <c r="B150" s="75" t="n"/>
-      <c r="C150" s="75" t="n"/>
-      <c r="D150" s="75" t="n"/>
-      <c r="E150" s="85" t="n"/>
-      <c r="F150" s="75" t="n"/>
-      <c r="G150" s="75" t="n"/>
-    </row>
-    <row r="151" ht="22.05" customHeight="1">
-      <c r="A151" s="66" t="n"/>
-      <c r="B151" s="66" t="n"/>
-      <c r="C151" s="66" t="n"/>
-      <c r="D151" s="66" t="n"/>
-      <c r="E151" s="84" t="n"/>
-      <c r="F151" s="66" t="n"/>
-      <c r="G151" s="66" t="n"/>
-    </row>
-    <row r="152" ht="22.05" customHeight="1">
-      <c r="A152" s="75" t="n"/>
-      <c r="B152" s="75" t="n"/>
-      <c r="C152" s="75" t="n"/>
-      <c r="D152" s="75" t="n"/>
-      <c r="E152" s="85" t="n"/>
-      <c r="F152" s="75" t="n"/>
-      <c r="G152" s="75" t="n"/>
-    </row>
-    <row r="153" ht="22.05" customHeight="1">
-      <c r="A153" s="66" t="n"/>
-      <c r="B153" s="66" t="n"/>
-      <c r="C153" s="66" t="n"/>
-      <c r="D153" s="66" t="n"/>
-      <c r="E153" s="84" t="n"/>
-      <c r="F153" s="66" t="n"/>
-      <c r="G153" s="66" t="n"/>
-    </row>
-    <row r="154" ht="22.05" customHeight="1">
-      <c r="A154" s="75" t="n"/>
-      <c r="B154" s="75" t="n"/>
-      <c r="C154" s="75" t="n"/>
-      <c r="D154" s="75" t="n"/>
-      <c r="E154" s="85" t="n"/>
-      <c r="F154" s="75" t="n"/>
-      <c r="G154" s="75" t="n"/>
-    </row>
-    <row r="155" ht="22.05" customHeight="1">
-      <c r="A155" s="66" t="n"/>
-      <c r="B155" s="66" t="n"/>
-      <c r="C155" s="66" t="n"/>
-      <c r="D155" s="66" t="n"/>
-      <c r="E155" s="84" t="n"/>
-      <c r="F155" s="66" t="n"/>
-      <c r="G155" s="66" t="n"/>
-    </row>
-    <row r="156" ht="22.05" customHeight="1">
-      <c r="A156" s="75" t="n"/>
-      <c r="B156" s="75" t="n"/>
-      <c r="C156" s="75" t="n"/>
-      <c r="D156" s="75" t="n"/>
-      <c r="E156" s="85" t="n"/>
-      <c r="F156" s="75" t="n"/>
-      <c r="G156" s="75" t="n"/>
-    </row>
-    <row r="157" ht="22.05" customHeight="1">
-      <c r="A157" s="66" t="n"/>
-      <c r="B157" s="66" t="n"/>
-      <c r="C157" s="66" t="n"/>
-      <c r="D157" s="66" t="n"/>
-      <c r="E157" s="84" t="n"/>
-      <c r="F157" s="66" t="n"/>
-      <c r="G157" s="66" t="n"/>
-    </row>
-    <row r="158" ht="22.05" customHeight="1">
-      <c r="A158" s="75" t="n"/>
-      <c r="B158" s="75" t="n"/>
-      <c r="C158" s="75" t="n"/>
-      <c r="D158" s="75" t="n"/>
-      <c r="E158" s="85" t="n"/>
-      <c r="F158" s="75" t="n"/>
-      <c r="G158" s="75" t="n"/>
-    </row>
-    <row r="159" ht="22.05" customHeight="1">
-      <c r="A159" s="66" t="n"/>
-      <c r="B159" s="66" t="n"/>
-      <c r="C159" s="66" t="n"/>
-      <c r="D159" s="66" t="n"/>
-      <c r="E159" s="84" t="n"/>
-      <c r="F159" s="66" t="n"/>
-      <c r="G159" s="66" t="n"/>
-    </row>
-    <row r="160" ht="22.05" customHeight="1">
-      <c r="A160" s="75" t="n"/>
-      <c r="B160" s="75" t="n"/>
-      <c r="C160" s="75" t="n"/>
-      <c r="D160" s="75" t="n"/>
-      <c r="E160" s="85" t="n"/>
-      <c r="F160" s="75" t="n"/>
-      <c r="G160" s="75" t="n"/>
-    </row>
-    <row r="161" ht="22.05" customHeight="1">
-      <c r="A161" s="66" t="n"/>
-      <c r="B161" s="66" t="n"/>
-      <c r="C161" s="66" t="n"/>
-      <c r="D161" s="66" t="n"/>
-      <c r="E161" s="84" t="n"/>
-      <c r="F161" s="66" t="n"/>
-      <c r="G161" s="66" t="n"/>
-    </row>
-    <row r="162" ht="22.05" customHeight="1">
-      <c r="A162" s="75" t="n"/>
-      <c r="B162" s="75" t="n"/>
-      <c r="C162" s="75" t="n"/>
-      <c r="D162" s="75" t="n"/>
-      <c r="E162" s="85" t="n"/>
-      <c r="F162" s="75" t="n"/>
-      <c r="G162" s="75" t="n"/>
-    </row>
-    <row r="163" ht="22.05" customHeight="1">
-      <c r="A163" s="66" t="n"/>
-      <c r="B163" s="66" t="n"/>
-      <c r="C163" s="66" t="n"/>
-      <c r="D163" s="66" t="n"/>
-      <c r="E163" s="84" t="n"/>
-      <c r="F163" s="66" t="n"/>
-      <c r="G163" s="66" t="n"/>
-    </row>
-    <row r="164" ht="22.05" customHeight="1">
-      <c r="A164" s="75" t="n"/>
-      <c r="B164" s="75" t="n"/>
-      <c r="C164" s="75" t="n"/>
-      <c r="D164" s="75" t="n"/>
-      <c r="E164" s="85" t="n"/>
-      <c r="F164" s="75" t="n"/>
-      <c r="G164" s="75" t="n"/>
-    </row>
-    <row r="165" ht="22.05" customHeight="1">
-      <c r="A165" s="66" t="n"/>
-      <c r="B165" s="66" t="n"/>
-      <c r="C165" s="66" t="n"/>
-      <c r="D165" s="66" t="n"/>
-      <c r="E165" s="84" t="n"/>
-      <c r="F165" s="66" t="n"/>
-      <c r="G165" s="66" t="n"/>
-    </row>
-    <row r="166" ht="22.05" customHeight="1">
-      <c r="A166" s="75" t="n"/>
-      <c r="B166" s="75" t="n"/>
-      <c r="C166" s="75" t="n"/>
-      <c r="D166" s="75" t="n"/>
-      <c r="E166" s="85" t="n"/>
-      <c r="F166" s="75" t="n"/>
-      <c r="G166" s="75" t="n"/>
-    </row>
-    <row r="167" ht="22.05" customHeight="1">
-      <c r="A167" s="66" t="n"/>
-      <c r="B167" s="66" t="n"/>
-      <c r="C167" s="66" t="n"/>
-      <c r="D167" s="66" t="n"/>
-      <c r="E167" s="84" t="n"/>
-      <c r="F167" s="66" t="n"/>
-      <c r="G167" s="66" t="n"/>
-    </row>
-    <row r="168" ht="22.05" customHeight="1">
-      <c r="A168" s="75" t="n"/>
-      <c r="B168" s="75" t="n"/>
-      <c r="C168" s="75" t="n"/>
-      <c r="D168" s="75" t="n"/>
-      <c r="E168" s="85" t="n"/>
-      <c r="F168" s="75" t="n"/>
-      <c r="G168" s="75" t="n"/>
-    </row>
-    <row r="169" ht="22.05" customHeight="1">
-      <c r="A169" s="66" t="n"/>
-      <c r="B169" s="66" t="n"/>
-      <c r="C169" s="66" t="n"/>
-      <c r="D169" s="66" t="n"/>
-      <c r="E169" s="84" t="n"/>
-      <c r="F169" s="66" t="n"/>
-      <c r="G169" s="66" t="n"/>
-    </row>
-    <row r="170" ht="22.05" customHeight="1">
-      <c r="A170" s="75" t="n"/>
-      <c r="B170" s="75" t="n"/>
-      <c r="C170" s="75" t="n"/>
-      <c r="D170" s="75" t="n"/>
-      <c r="E170" s="85" t="n"/>
-      <c r="F170" s="75" t="n"/>
-      <c r="G170" s="75" t="n"/>
-    </row>
-    <row r="171" ht="22.05" customHeight="1">
-      <c r="A171" s="66" t="n"/>
-      <c r="B171" s="66" t="n"/>
-      <c r="C171" s="66" t="n"/>
-      <c r="D171" s="66" t="n"/>
-      <c r="E171" s="84" t="n"/>
-      <c r="F171" s="66" t="n"/>
-      <c r="G171" s="66" t="n"/>
-    </row>
-    <row r="172" ht="22.05" customHeight="1">
-      <c r="A172" s="75" t="n"/>
-      <c r="B172" s="75" t="n"/>
-      <c r="C172" s="75" t="n"/>
-      <c r="D172" s="75" t="n"/>
-      <c r="E172" s="85" t="n"/>
-      <c r="F172" s="75" t="n"/>
-      <c r="G172" s="75" t="n"/>
-    </row>
-    <row r="173" ht="22.05" customHeight="1">
-      <c r="A173" s="66" t="n"/>
-      <c r="B173" s="66" t="n"/>
-      <c r="C173" s="66" t="n"/>
-      <c r="D173" s="66" t="n"/>
-      <c r="E173" s="84" t="n"/>
-      <c r="F173" s="66" t="n"/>
-      <c r="G173" s="66" t="n"/>
-    </row>
-    <row r="174" ht="22.05" customHeight="1">
-      <c r="A174" s="75" t="n"/>
-      <c r="B174" s="75" t="n"/>
-      <c r="C174" s="75" t="n"/>
-      <c r="D174" s="75" t="n"/>
-      <c r="E174" s="85" t="n"/>
-      <c r="F174" s="75" t="n"/>
-      <c r="G174" s="75" t="n"/>
-    </row>
-    <row r="175" ht="22.05" customHeight="1">
-      <c r="A175" s="66" t="n"/>
-      <c r="B175" s="66" t="n"/>
-      <c r="C175" s="66" t="n"/>
-      <c r="D175" s="66" t="n"/>
-      <c r="E175" s="84" t="n"/>
-      <c r="F175" s="66" t="n"/>
-      <c r="G175" s="66" t="n"/>
-    </row>
-    <row r="176" ht="22.05" customHeight="1">
-      <c r="A176" s="75" t="n"/>
-      <c r="B176" s="75" t="n"/>
-      <c r="C176" s="75" t="n"/>
-      <c r="D176" s="75" t="n"/>
-      <c r="E176" s="85" t="n"/>
-      <c r="F176" s="75" t="n"/>
-      <c r="G176" s="75" t="n"/>
-    </row>
-    <row r="177" ht="22.05" customHeight="1">
-      <c r="A177" s="66" t="n"/>
-      <c r="B177" s="66" t="n"/>
-      <c r="C177" s="66" t="n"/>
-      <c r="D177" s="66" t="n"/>
-      <c r="E177" s="84" t="n"/>
-      <c r="F177" s="66" t="n"/>
-      <c r="G177" s="66" t="n"/>
-    </row>
-    <row r="178" ht="22.05" customHeight="1">
-      <c r="A178" s="75" t="n"/>
-      <c r="B178" s="75" t="n"/>
-      <c r="C178" s="75" t="n"/>
-      <c r="D178" s="75" t="n"/>
-      <c r="E178" s="85" t="n"/>
-      <c r="F178" s="75" t="n"/>
-      <c r="G178" s="75" t="n"/>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="66" t="n"/>
-      <c r="B179" s="66" t="n"/>
-      <c r="C179" s="66" t="n"/>
-      <c r="D179" s="66" t="n"/>
-      <c r="E179" s="84" t="n"/>
-      <c r="F179" s="66" t="n"/>
-      <c r="G179" s="66" t="n"/>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="75" t="n"/>
-      <c r="B180" s="75" t="n"/>
-      <c r="C180" s="75" t="n"/>
-      <c r="D180" s="75" t="n"/>
-      <c r="E180" s="85" t="n"/>
-      <c r="F180" s="75" t="n"/>
-      <c r="G180" s="75" t="n"/>
-    </row>
-    <row r="181" ht="22" customHeight="1">
-      <c r="A181" s="66" t="n"/>
-      <c r="B181" s="66" t="n"/>
-      <c r="C181" s="66" t="n"/>
-      <c r="D181" s="66" t="n"/>
-      <c r="E181" s="84" t="n"/>
-      <c r="F181" s="66" t="n"/>
-      <c r="G181" s="66" t="n"/>
-    </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="75" t="n"/>
-      <c r="B182" s="75" t="n"/>
-      <c r="C182" s="75" t="n"/>
-      <c r="D182" s="75" t="n"/>
-      <c r="E182" s="85" t="n"/>
-      <c r="F182" s="75" t="n"/>
-      <c r="G182" s="75" t="n"/>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="66" t="n"/>
-      <c r="B183" s="66" t="n"/>
-      <c r="C183" s="66" t="n"/>
-      <c r="D183" s="66" t="n"/>
-      <c r="E183" s="84" t="n"/>
-      <c r="F183" s="66" t="n"/>
-      <c r="G183" s="66" t="n"/>
-    </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="75" t="n"/>
-      <c r="B184" s="75" t="n"/>
-      <c r="C184" s="75" t="n"/>
-      <c r="D184" s="75" t="n"/>
-      <c r="E184" s="85" t="n"/>
-      <c r="F184" s="75" t="n"/>
-      <c r="G184" s="75" t="n"/>
-    </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="66" t="n"/>
-      <c r="B185" s="66" t="n"/>
-      <c r="C185" s="66" t="n"/>
-      <c r="D185" s="66" t="n"/>
-      <c r="E185" s="84" t="n"/>
-      <c r="F185" s="66" t="n"/>
-      <c r="G185" s="66" t="n"/>
-    </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="75" t="n"/>
-      <c r="B186" s="75" t="n"/>
-      <c r="C186" s="75" t="n"/>
-      <c r="D186" s="75" t="n"/>
-      <c r="E186" s="85" t="n"/>
-      <c r="F186" s="75" t="n"/>
-      <c r="G186" s="75" t="n"/>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="66" t="n"/>
-      <c r="B187" s="66" t="n"/>
-      <c r="C187" s="66" t="n"/>
-      <c r="D187" s="66" t="n"/>
-      <c r="E187" s="84" t="n"/>
-      <c r="F187" s="66" t="n"/>
-      <c r="G187" s="66" t="n"/>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="75" t="n"/>
-      <c r="B188" s="75" t="n"/>
-      <c r="C188" s="75" t="n"/>
-      <c r="D188" s="75" t="n"/>
-      <c r="E188" s="85" t="n"/>
-      <c r="F188" s="75" t="n"/>
-      <c r="G188" s="75" t="n"/>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="66" t="n"/>
-      <c r="B189" s="66" t="n"/>
-      <c r="C189" s="66" t="n"/>
-      <c r="D189" s="66" t="n"/>
-      <c r="E189" s="84" t="n"/>
-      <c r="F189" s="66" t="n"/>
-      <c r="G189" s="66" t="n"/>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="75" t="n"/>
-      <c r="B190" s="75" t="n"/>
-      <c r="C190" s="75" t="n"/>
-      <c r="D190" s="75" t="n"/>
-      <c r="E190" s="85" t="n"/>
-      <c r="F190" s="75" t="n"/>
-      <c r="G190" s="75" t="n"/>
-    </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="66" t="n"/>
-      <c r="B191" s="66" t="n"/>
-      <c r="C191" s="66" t="n"/>
-      <c r="D191" s="66" t="n"/>
-      <c r="E191" s="84" t="n"/>
-      <c r="F191" s="66" t="n"/>
-      <c r="G191" s="66" t="n"/>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="75" t="n"/>
-      <c r="B192" s="75" t="n"/>
-      <c r="C192" s="75" t="n"/>
-      <c r="D192" s="75" t="n"/>
-      <c r="E192" s="85" t="n"/>
-      <c r="F192" s="75" t="n"/>
-      <c r="G192" s="75" t="n"/>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="66" t="n"/>
-      <c r="B193" s="66" t="n"/>
-      <c r="C193" s="66" t="n"/>
-      <c r="D193" s="66" t="n"/>
-      <c r="E193" s="84" t="n"/>
-      <c r="F193" s="66" t="n"/>
-      <c r="G193" s="66" t="n"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="75" t="n"/>
-      <c r="B194" s="75" t="n"/>
-      <c r="C194" s="75" t="n"/>
-      <c r="D194" s="75" t="n"/>
-      <c r="E194" s="85" t="n"/>
-      <c r="F194" s="75" t="n"/>
-      <c r="G194" s="75" t="n"/>
-    </row>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="66" t="n"/>
-      <c r="B195" s="66" t="n"/>
-      <c r="C195" s="66" t="n"/>
-      <c r="D195" s="66" t="n"/>
-      <c r="E195" s="84" t="n"/>
-      <c r="F195" s="66" t="n"/>
-      <c r="G195" s="66" t="n"/>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="75" t="n"/>
-      <c r="B196" s="75" t="n"/>
-      <c r="C196" s="75" t="n"/>
-      <c r="D196" s="75" t="n"/>
-      <c r="E196" s="85" t="n"/>
-      <c r="F196" s="75" t="n"/>
-      <c r="G196" s="75" t="n"/>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="66" t="n"/>
-      <c r="B197" s="66" t="n"/>
-      <c r="C197" s="66" t="n"/>
-      <c r="D197" s="66" t="n"/>
-      <c r="E197" s="84" t="n"/>
-      <c r="F197" s="66" t="n"/>
-      <c r="G197" s="66" t="n"/>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="75" t="n"/>
-      <c r="B198" s="75" t="n"/>
-      <c r="C198" s="75" t="n"/>
-      <c r="D198" s="75" t="n"/>
-      <c r="E198" s="85" t="n"/>
-      <c r="F198" s="75" t="n"/>
-      <c r="G198" s="75" t="n"/>
-    </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="66" t="n"/>
-      <c r="B199" s="66" t="n"/>
-      <c r="C199" s="66" t="n"/>
-      <c r="D199" s="66" t="n"/>
-      <c r="E199" s="84" t="n"/>
-      <c r="F199" s="66" t="n"/>
-      <c r="G199" s="66" t="n"/>
-    </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="75" t="n"/>
-      <c r="B200" s="75" t="n"/>
-      <c r="C200" s="75" t="n"/>
-      <c r="D200" s="75" t="n"/>
-      <c r="E200" s="85" t="n"/>
-      <c r="F200" s="75" t="n"/>
-      <c r="G200" s="75" t="n"/>
-    </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="66" t="n"/>
-      <c r="B201" s="66" t="n"/>
-      <c r="C201" s="66" t="n"/>
-      <c r="D201" s="66" t="n"/>
-      <c r="E201" s="84" t="n"/>
-      <c r="F201" s="66" t="n"/>
-      <c r="G201" s="66" t="n"/>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="75" t="n"/>
-      <c r="B202" s="75" t="n"/>
-      <c r="C202" s="75" t="n"/>
-      <c r="D202" s="75" t="n"/>
-      <c r="E202" s="85" t="n"/>
-      <c r="F202" s="75" t="n"/>
-      <c r="G202" s="75" t="n"/>
-    </row>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="66" t="n"/>
-      <c r="B203" s="66" t="n"/>
-      <c r="C203" s="66" t="n"/>
-      <c r="D203" s="66" t="n"/>
-      <c r="E203" s="84" t="n"/>
-      <c r="F203" s="66" t="n"/>
-      <c r="G203" s="66" t="n"/>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="75" t="n"/>
-      <c r="B204" s="75" t="n"/>
-      <c r="C204" s="75" t="n"/>
-      <c r="D204" s="75" t="n"/>
-      <c r="E204" s="85" t="n"/>
-      <c r="F204" s="75" t="n"/>
-      <c r="G204" s="75" t="n"/>
-    </row>
-    <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="66" t="n"/>
-      <c r="B205" s="66" t="n"/>
-      <c r="C205" s="66" t="n"/>
-      <c r="D205" s="66" t="n"/>
-      <c r="E205" s="84" t="n"/>
-      <c r="F205" s="66" t="n"/>
-      <c r="G205" s="66" t="n"/>
-    </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="75" t="n"/>
-      <c r="B206" s="75" t="n"/>
-      <c r="C206" s="75" t="n"/>
-      <c r="D206" s="75" t="n"/>
-      <c r="E206" s="85" t="n"/>
-      <c r="F206" s="75" t="n"/>
-      <c r="G206" s="75" t="n"/>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="66" t="n"/>
-      <c r="B207" s="66" t="n"/>
-      <c r="C207" s="66" t="n"/>
-      <c r="D207" s="66" t="n"/>
-      <c r="E207" s="84" t="n"/>
-      <c r="F207" s="66" t="n"/>
-      <c r="G207" s="66" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
@@ -45898,19 +45309,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="3"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -45922,7 +45333,7 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -45931,9 +45342,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="94" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="F2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -49420,542 +48831,6 @@
       <c r="D140" s="75" t="n"/>
       <c r="E140" s="85" t="n"/>
       <c r="F140" s="75" t="n"/>
-    </row>
-    <row r="141" ht="22.05" customHeight="1">
-      <c r="A141" s="66" t="n"/>
-      <c r="B141" s="66" t="n"/>
-      <c r="C141" s="66" t="n"/>
-      <c r="D141" s="66" t="n"/>
-      <c r="E141" s="84" t="n"/>
-      <c r="F141" s="66" t="n"/>
-    </row>
-    <row r="142" ht="22.05" customHeight="1">
-      <c r="A142" s="75" t="n"/>
-      <c r="B142" s="75" t="n"/>
-      <c r="C142" s="75" t="n"/>
-      <c r="D142" s="75" t="n"/>
-      <c r="E142" s="85" t="n"/>
-      <c r="F142" s="75" t="n"/>
-    </row>
-    <row r="143" ht="22.05" customHeight="1">
-      <c r="A143" s="66" t="n"/>
-      <c r="B143" s="66" t="n"/>
-      <c r="C143" s="66" t="n"/>
-      <c r="D143" s="66" t="n"/>
-      <c r="E143" s="84" t="n"/>
-      <c r="F143" s="66" t="n"/>
-    </row>
-    <row r="144" ht="22.05" customHeight="1">
-      <c r="A144" s="75" t="n"/>
-      <c r="B144" s="75" t="n"/>
-      <c r="C144" s="75" t="n"/>
-      <c r="D144" s="75" t="n"/>
-      <c r="E144" s="85" t="n"/>
-      <c r="F144" s="75" t="n"/>
-    </row>
-    <row r="145" ht="22.05" customHeight="1">
-      <c r="A145" s="66" t="n"/>
-      <c r="B145" s="66" t="n"/>
-      <c r="C145" s="66" t="n"/>
-      <c r="D145" s="66" t="n"/>
-      <c r="E145" s="84" t="n"/>
-      <c r="F145" s="66" t="n"/>
-    </row>
-    <row r="146" ht="22.05" customHeight="1">
-      <c r="A146" s="75" t="n"/>
-      <c r="B146" s="75" t="n"/>
-      <c r="C146" s="75" t="n"/>
-      <c r="D146" s="75" t="n"/>
-      <c r="E146" s="85" t="n"/>
-      <c r="F146" s="75" t="n"/>
-    </row>
-    <row r="147" ht="22.05" customHeight="1">
-      <c r="A147" s="66" t="n"/>
-      <c r="B147" s="66" t="n"/>
-      <c r="C147" s="66" t="n"/>
-      <c r="D147" s="66" t="n"/>
-      <c r="E147" s="84" t="n"/>
-      <c r="F147" s="66" t="n"/>
-    </row>
-    <row r="148" ht="22.05" customHeight="1">
-      <c r="A148" s="75" t="n"/>
-      <c r="B148" s="75" t="n"/>
-      <c r="C148" s="75" t="n"/>
-      <c r="D148" s="75" t="n"/>
-      <c r="E148" s="85" t="n"/>
-      <c r="F148" s="75" t="n"/>
-    </row>
-    <row r="149" ht="22.05" customHeight="1">
-      <c r="A149" s="66" t="n"/>
-      <c r="B149" s="66" t="n"/>
-      <c r="C149" s="66" t="n"/>
-      <c r="D149" s="66" t="n"/>
-      <c r="E149" s="84" t="n"/>
-      <c r="F149" s="66" t="n"/>
-    </row>
-    <row r="150" ht="22.05" customHeight="1">
-      <c r="A150" s="75" t="n"/>
-      <c r="B150" s="75" t="n"/>
-      <c r="C150" s="75" t="n"/>
-      <c r="D150" s="75" t="n"/>
-      <c r="E150" s="85" t="n"/>
-      <c r="F150" s="75" t="n"/>
-    </row>
-    <row r="151" ht="22.05" customHeight="1">
-      <c r="A151" s="66" t="n"/>
-      <c r="B151" s="66" t="n"/>
-      <c r="C151" s="66" t="n"/>
-      <c r="D151" s="66" t="n"/>
-      <c r="E151" s="84" t="n"/>
-      <c r="F151" s="66" t="n"/>
-    </row>
-    <row r="152" ht="22.05" customHeight="1">
-      <c r="A152" s="75" t="n"/>
-      <c r="B152" s="75" t="n"/>
-      <c r="C152" s="75" t="n"/>
-      <c r="D152" s="75" t="n"/>
-      <c r="E152" s="85" t="n"/>
-      <c r="F152" s="75" t="n"/>
-    </row>
-    <row r="153" ht="22.05" customHeight="1">
-      <c r="A153" s="66" t="n"/>
-      <c r="B153" s="66" t="n"/>
-      <c r="C153" s="66" t="n"/>
-      <c r="D153" s="66" t="n"/>
-      <c r="E153" s="84" t="n"/>
-      <c r="F153" s="66" t="n"/>
-    </row>
-    <row r="154" ht="22.05" customHeight="1">
-      <c r="A154" s="75" t="n"/>
-      <c r="B154" s="75" t="n"/>
-      <c r="C154" s="75" t="n"/>
-      <c r="D154" s="75" t="n"/>
-      <c r="E154" s="85" t="n"/>
-      <c r="F154" s="75" t="n"/>
-    </row>
-    <row r="155" ht="22.05" customHeight="1">
-      <c r="A155" s="66" t="n"/>
-      <c r="B155" s="66" t="n"/>
-      <c r="C155" s="66" t="n"/>
-      <c r="D155" s="66" t="n"/>
-      <c r="E155" s="84" t="n"/>
-      <c r="F155" s="66" t="n"/>
-    </row>
-    <row r="156" ht="22.05" customHeight="1">
-      <c r="A156" s="75" t="n"/>
-      <c r="B156" s="75" t="n"/>
-      <c r="C156" s="75" t="n"/>
-      <c r="D156" s="75" t="n"/>
-      <c r="E156" s="85" t="n"/>
-      <c r="F156" s="75" t="n"/>
-    </row>
-    <row r="157" ht="22.05" customHeight="1">
-      <c r="A157" s="66" t="n"/>
-      <c r="B157" s="66" t="n"/>
-      <c r="C157" s="66" t="n"/>
-      <c r="D157" s="66" t="n"/>
-      <c r="E157" s="84" t="n"/>
-      <c r="F157" s="66" t="n"/>
-    </row>
-    <row r="158" ht="22.05" customHeight="1">
-      <c r="A158" s="75" t="n"/>
-      <c r="B158" s="75" t="n"/>
-      <c r="C158" s="75" t="n"/>
-      <c r="D158" s="75" t="n"/>
-      <c r="E158" s="85" t="n"/>
-      <c r="F158" s="75" t="n"/>
-    </row>
-    <row r="159" ht="22.05" customHeight="1">
-      <c r="A159" s="66" t="n"/>
-      <c r="B159" s="66" t="n"/>
-      <c r="C159" s="66" t="n"/>
-      <c r="D159" s="66" t="n"/>
-      <c r="E159" s="84" t="n"/>
-      <c r="F159" s="66" t="n"/>
-    </row>
-    <row r="160" ht="22.05" customHeight="1">
-      <c r="A160" s="75" t="n"/>
-      <c r="B160" s="75" t="n"/>
-      <c r="C160" s="75" t="n"/>
-      <c r="D160" s="75" t="n"/>
-      <c r="E160" s="85" t="n"/>
-      <c r="F160" s="75" t="n"/>
-    </row>
-    <row r="161" ht="22.05" customHeight="1">
-      <c r="A161" s="66" t="n"/>
-      <c r="B161" s="66" t="n"/>
-      <c r="C161" s="66" t="n"/>
-      <c r="D161" s="66" t="n"/>
-      <c r="E161" s="84" t="n"/>
-      <c r="F161" s="66" t="n"/>
-    </row>
-    <row r="162" ht="22.05" customHeight="1">
-      <c r="A162" s="75" t="n"/>
-      <c r="B162" s="75" t="n"/>
-      <c r="C162" s="75" t="n"/>
-      <c r="D162" s="75" t="n"/>
-      <c r="E162" s="85" t="n"/>
-      <c r="F162" s="75" t="n"/>
-    </row>
-    <row r="163" ht="22.05" customHeight="1">
-      <c r="A163" s="66" t="n"/>
-      <c r="B163" s="66" t="n"/>
-      <c r="C163" s="66" t="n"/>
-      <c r="D163" s="66" t="n"/>
-      <c r="E163" s="84" t="n"/>
-      <c r="F163" s="66" t="n"/>
-    </row>
-    <row r="164" ht="22.05" customHeight="1">
-      <c r="A164" s="75" t="n"/>
-      <c r="B164" s="75" t="n"/>
-      <c r="C164" s="75" t="n"/>
-      <c r="D164" s="75" t="n"/>
-      <c r="E164" s="85" t="n"/>
-      <c r="F164" s="75" t="n"/>
-    </row>
-    <row r="165" ht="22.05" customHeight="1">
-      <c r="A165" s="66" t="n"/>
-      <c r="B165" s="66" t="n"/>
-      <c r="C165" s="66" t="n"/>
-      <c r="D165" s="66" t="n"/>
-      <c r="E165" s="84" t="n"/>
-      <c r="F165" s="66" t="n"/>
-    </row>
-    <row r="166" ht="22.05" customHeight="1">
-      <c r="A166" s="75" t="n"/>
-      <c r="B166" s="75" t="n"/>
-      <c r="C166" s="75" t="n"/>
-      <c r="D166" s="75" t="n"/>
-      <c r="E166" s="85" t="n"/>
-      <c r="F166" s="75" t="n"/>
-    </row>
-    <row r="167" ht="22.05" customHeight="1">
-      <c r="A167" s="66" t="n"/>
-      <c r="B167" s="66" t="n"/>
-      <c r="C167" s="66" t="n"/>
-      <c r="D167" s="66" t="n"/>
-      <c r="E167" s="84" t="n"/>
-      <c r="F167" s="66" t="n"/>
-    </row>
-    <row r="168" ht="22.05" customHeight="1">
-      <c r="A168" s="75" t="n"/>
-      <c r="B168" s="75" t="n"/>
-      <c r="C168" s="75" t="n"/>
-      <c r="D168" s="75" t="n"/>
-      <c r="E168" s="85" t="n"/>
-      <c r="F168" s="75" t="n"/>
-    </row>
-    <row r="169" ht="22.05" customHeight="1">
-      <c r="A169" s="66" t="n"/>
-      <c r="B169" s="66" t="n"/>
-      <c r="C169" s="66" t="n"/>
-      <c r="D169" s="66" t="n"/>
-      <c r="E169" s="84" t="n"/>
-      <c r="F169" s="66" t="n"/>
-    </row>
-    <row r="170" ht="22.05" customHeight="1">
-      <c r="A170" s="75" t="n"/>
-      <c r="B170" s="75" t="n"/>
-      <c r="C170" s="75" t="n"/>
-      <c r="D170" s="75" t="n"/>
-      <c r="E170" s="85" t="n"/>
-      <c r="F170" s="75" t="n"/>
-    </row>
-    <row r="171" ht="22.05" customHeight="1">
-      <c r="A171" s="66" t="n"/>
-      <c r="B171" s="66" t="n"/>
-      <c r="C171" s="66" t="n"/>
-      <c r="D171" s="66" t="n"/>
-      <c r="E171" s="84" t="n"/>
-      <c r="F171" s="66" t="n"/>
-    </row>
-    <row r="172" ht="22.05" customHeight="1">
-      <c r="A172" s="75" t="n"/>
-      <c r="B172" s="75" t="n"/>
-      <c r="C172" s="75" t="n"/>
-      <c r="D172" s="75" t="n"/>
-      <c r="E172" s="85" t="n"/>
-      <c r="F172" s="75" t="n"/>
-    </row>
-    <row r="173" ht="22.05" customHeight="1">
-      <c r="A173" s="66" t="n"/>
-      <c r="B173" s="66" t="n"/>
-      <c r="C173" s="66" t="n"/>
-      <c r="D173" s="66" t="n"/>
-      <c r="E173" s="84" t="n"/>
-      <c r="F173" s="66" t="n"/>
-    </row>
-    <row r="174" ht="22.05" customHeight="1">
-      <c r="A174" s="75" t="n"/>
-      <c r="B174" s="75" t="n"/>
-      <c r="C174" s="75" t="n"/>
-      <c r="D174" s="75" t="n"/>
-      <c r="E174" s="85" t="n"/>
-      <c r="F174" s="75" t="n"/>
-    </row>
-    <row r="175" ht="22.05" customHeight="1">
-      <c r="A175" s="66" t="n"/>
-      <c r="B175" s="66" t="n"/>
-      <c r="C175" s="66" t="n"/>
-      <c r="D175" s="66" t="n"/>
-      <c r="E175" s="84" t="n"/>
-      <c r="F175" s="66" t="n"/>
-    </row>
-    <row r="176" ht="22.05" customHeight="1">
-      <c r="A176" s="75" t="n"/>
-      <c r="B176" s="75" t="n"/>
-      <c r="C176" s="75" t="n"/>
-      <c r="D176" s="75" t="n"/>
-      <c r="E176" s="85" t="n"/>
-      <c r="F176" s="75" t="n"/>
-    </row>
-    <row r="177" ht="22.05" customHeight="1">
-      <c r="A177" s="66" t="n"/>
-      <c r="B177" s="66" t="n"/>
-      <c r="C177" s="66" t="n"/>
-      <c r="D177" s="66" t="n"/>
-      <c r="E177" s="84" t="n"/>
-      <c r="F177" s="66" t="n"/>
-    </row>
-    <row r="178" ht="22.05" customHeight="1">
-      <c r="A178" s="75" t="n"/>
-      <c r="B178" s="75" t="n"/>
-      <c r="C178" s="75" t="n"/>
-      <c r="D178" s="75" t="n"/>
-      <c r="E178" s="85" t="n"/>
-      <c r="F178" s="75" t="n"/>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="66" t="n"/>
-      <c r="B179" s="66" t="n"/>
-      <c r="C179" s="66" t="n"/>
-      <c r="D179" s="66" t="n"/>
-      <c r="E179" s="84" t="n"/>
-      <c r="F179" s="66" t="n"/>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="75" t="n"/>
-      <c r="B180" s="75" t="n"/>
-      <c r="C180" s="75" t="n"/>
-      <c r="D180" s="75" t="n"/>
-      <c r="E180" s="85" t="n"/>
-      <c r="F180" s="75" t="n"/>
-    </row>
-    <row r="181" ht="22" customHeight="1">
-      <c r="A181" s="66" t="n"/>
-      <c r="B181" s="66" t="n"/>
-      <c r="C181" s="66" t="n"/>
-      <c r="D181" s="66" t="n"/>
-      <c r="E181" s="84" t="n"/>
-      <c r="F181" s="66" t="n"/>
-    </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="75" t="n"/>
-      <c r="B182" s="75" t="n"/>
-      <c r="C182" s="75" t="n"/>
-      <c r="D182" s="75" t="n"/>
-      <c r="E182" s="85" t="n"/>
-      <c r="F182" s="75" t="n"/>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="66" t="n"/>
-      <c r="B183" s="66" t="n"/>
-      <c r="C183" s="66" t="n"/>
-      <c r="D183" s="66" t="n"/>
-      <c r="E183" s="84" t="n"/>
-      <c r="F183" s="66" t="n"/>
-    </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="75" t="n"/>
-      <c r="B184" s="75" t="n"/>
-      <c r="C184" s="75" t="n"/>
-      <c r="D184" s="75" t="n"/>
-      <c r="E184" s="85" t="n"/>
-      <c r="F184" s="75" t="n"/>
-    </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="66" t="n"/>
-      <c r="B185" s="66" t="n"/>
-      <c r="C185" s="66" t="n"/>
-      <c r="D185" s="66" t="n"/>
-      <c r="E185" s="84" t="n"/>
-      <c r="F185" s="66" t="n"/>
-    </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="75" t="n"/>
-      <c r="B186" s="75" t="n"/>
-      <c r="C186" s="75" t="n"/>
-      <c r="D186" s="75" t="n"/>
-      <c r="E186" s="85" t="n"/>
-      <c r="F186" s="75" t="n"/>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="66" t="n"/>
-      <c r="B187" s="66" t="n"/>
-      <c r="C187" s="66" t="n"/>
-      <c r="D187" s="66" t="n"/>
-      <c r="E187" s="84" t="n"/>
-      <c r="F187" s="66" t="n"/>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="75" t="n"/>
-      <c r="B188" s="75" t="n"/>
-      <c r="C188" s="75" t="n"/>
-      <c r="D188" s="75" t="n"/>
-      <c r="E188" s="85" t="n"/>
-      <c r="F188" s="75" t="n"/>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="66" t="n"/>
-      <c r="B189" s="66" t="n"/>
-      <c r="C189" s="66" t="n"/>
-      <c r="D189" s="66" t="n"/>
-      <c r="E189" s="84" t="n"/>
-      <c r="F189" s="66" t="n"/>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="75" t="n"/>
-      <c r="B190" s="75" t="n"/>
-      <c r="C190" s="75" t="n"/>
-      <c r="D190" s="75" t="n"/>
-      <c r="E190" s="85" t="n"/>
-      <c r="F190" s="75" t="n"/>
-    </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="66" t="n"/>
-      <c r="B191" s="66" t="n"/>
-      <c r="C191" s="66" t="n"/>
-      <c r="D191" s="66" t="n"/>
-      <c r="E191" s="84" t="n"/>
-      <c r="F191" s="66" t="n"/>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="75" t="n"/>
-      <c r="B192" s="75" t="n"/>
-      <c r="C192" s="75" t="n"/>
-      <c r="D192" s="75" t="n"/>
-      <c r="E192" s="85" t="n"/>
-      <c r="F192" s="75" t="n"/>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="66" t="n"/>
-      <c r="B193" s="66" t="n"/>
-      <c r="C193" s="66" t="n"/>
-      <c r="D193" s="66" t="n"/>
-      <c r="E193" s="84" t="n"/>
-      <c r="F193" s="66" t="n"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="75" t="n"/>
-      <c r="B194" s="75" t="n"/>
-      <c r="C194" s="75" t="n"/>
-      <c r="D194" s="75" t="n"/>
-      <c r="E194" s="85" t="n"/>
-      <c r="F194" s="75" t="n"/>
-    </row>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="66" t="n"/>
-      <c r="B195" s="66" t="n"/>
-      <c r="C195" s="66" t="n"/>
-      <c r="D195" s="66" t="n"/>
-      <c r="E195" s="84" t="n"/>
-      <c r="F195" s="66" t="n"/>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="75" t="n"/>
-      <c r="B196" s="75" t="n"/>
-      <c r="C196" s="75" t="n"/>
-      <c r="D196" s="75" t="n"/>
-      <c r="E196" s="85" t="n"/>
-      <c r="F196" s="75" t="n"/>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="66" t="n"/>
-      <c r="B197" s="66" t="n"/>
-      <c r="C197" s="66" t="n"/>
-      <c r="D197" s="66" t="n"/>
-      <c r="E197" s="84" t="n"/>
-      <c r="F197" s="66" t="n"/>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="75" t="n"/>
-      <c r="B198" s="75" t="n"/>
-      <c r="C198" s="75" t="n"/>
-      <c r="D198" s="75" t="n"/>
-      <c r="E198" s="85" t="n"/>
-      <c r="F198" s="75" t="n"/>
-    </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="66" t="n"/>
-      <c r="B199" s="66" t="n"/>
-      <c r="C199" s="66" t="n"/>
-      <c r="D199" s="66" t="n"/>
-      <c r="E199" s="84" t="n"/>
-      <c r="F199" s="66" t="n"/>
-    </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="75" t="n"/>
-      <c r="B200" s="75" t="n"/>
-      <c r="C200" s="75" t="n"/>
-      <c r="D200" s="75" t="n"/>
-      <c r="E200" s="85" t="n"/>
-      <c r="F200" s="75" t="n"/>
-    </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="66" t="n"/>
-      <c r="B201" s="66" t="n"/>
-      <c r="C201" s="66" t="n"/>
-      <c r="D201" s="66" t="n"/>
-      <c r="E201" s="84" t="n"/>
-      <c r="F201" s="66" t="n"/>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="75" t="n"/>
-      <c r="B202" s="75" t="n"/>
-      <c r="C202" s="75" t="n"/>
-      <c r="D202" s="75" t="n"/>
-      <c r="E202" s="85" t="n"/>
-      <c r="F202" s="75" t="n"/>
-    </row>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="66" t="n"/>
-      <c r="B203" s="66" t="n"/>
-      <c r="C203" s="66" t="n"/>
-      <c r="D203" s="66" t="n"/>
-      <c r="E203" s="84" t="n"/>
-      <c r="F203" s="66" t="n"/>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="75" t="n"/>
-      <c r="B204" s="75" t="n"/>
-      <c r="C204" s="75" t="n"/>
-      <c r="D204" s="75" t="n"/>
-      <c r="E204" s="85" t="n"/>
-      <c r="F204" s="75" t="n"/>
-    </row>
-    <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="66" t="n"/>
-      <c r="B205" s="66" t="n"/>
-      <c r="C205" s="66" t="n"/>
-      <c r="D205" s="66" t="n"/>
-      <c r="E205" s="84" t="n"/>
-      <c r="F205" s="66" t="n"/>
-    </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="75" t="n"/>
-      <c r="B206" s="75" t="n"/>
-      <c r="C206" s="75" t="n"/>
-      <c r="D206" s="75" t="n"/>
-      <c r="E206" s="85" t="n"/>
-      <c r="F206" s="75" t="n"/>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="66" t="n"/>
-      <c r="B207" s="66" t="n"/>
-      <c r="C207" s="66" t="n"/>
-      <c r="D207" s="66" t="n"/>
-      <c r="E207" s="84" t="n"/>
-      <c r="F207" s="66" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
@@ -49974,7 +48849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG34"/>
+  <dimension ref="A1:AF34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50007,13 +48882,13 @@
     <col width="13" customWidth="1" style="34" min="28" max="28"/>
     <col width="8" customWidth="1" style="34" min="29" max="31"/>
     <col width="8" customWidth="1" style="34" min="30" max="30"/>
-    <col width="8" customWidth="1" style="34" min="31" max="31"/>
+    <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -50048,11 +48923,10 @@
       <c r="AC1" s="91" t="n"/>
       <c r="AD1" s="91" t="n"/>
       <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="91" t="n"/>
-      <c r="AG1" s="92" t="n"/>
+      <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -50086,8 +48960,12 @@
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="91" t="n"/>
-      <c r="AF2" s="92" t="n"/>
+      <c r="AE2" s="92" t="n"/>
+      <c r="AF2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -51439,10 +50317,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:AE2"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="13">
     <dataValidation sqref="I5:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -51482,9 +50360,6 @@
     <dataValidation sqref="AD5:AD34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE5:AE34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -3867,7 +3867,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="71" t="n">
+      <c r="P5" s="95" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -3926,12 +3926,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="98" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="77" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -3963,7 +3963,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="P6" s="96" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -4059,7 +4059,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="71" t="n">
+      <c r="P7" s="95" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -4123,7 +4123,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="77" t="inlineStr">
+      <c r="H8" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4155,7 +4155,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="80" t="n">
+      <c r="P8" s="96" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -4219,7 +4219,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4251,7 +4251,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="71" t="n">
+      <c r="P9" s="95" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -4310,12 +4310,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="77" t="inlineStr">
+      <c r="G10" s="98" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="77" t="inlineStr">
+      <c r="H10" s="98" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -4347,7 +4347,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="80" t="n">
+      <c r="P10" s="96" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -4443,7 +4443,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="71" t="n">
+      <c r="P11" s="95" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -4539,7 +4539,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="80" t="n">
+      <c r="P12" s="96" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -4635,7 +4635,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="71" t="n">
+      <c r="P13" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -4731,7 +4731,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="80" t="n">
+      <c r="P14" s="96" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -4923,7 +4923,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="80" t="n">
+      <c r="P16" s="96" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="80" t="n">
+      <c r="P18" s="96" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -5178,12 +5178,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="68" t="inlineStr">
+      <c r="G19" s="98" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="68" t="inlineStr">
+      <c r="H19" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5215,7 +5215,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="71" t="n">
+      <c r="P19" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -5279,7 +5279,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="77" t="inlineStr">
+      <c r="H20" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5311,7 +5311,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="80" t="n">
+      <c r="P20" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -5370,12 +5370,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="68" t="inlineStr">
+      <c r="G21" s="98" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="68" t="inlineStr">
+      <c r="H21" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5407,7 +5407,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="71" t="n">
+      <c r="P21" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -5471,7 +5471,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5503,7 +5503,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="80" t="n">
+      <c r="P22" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -5567,7 +5567,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="68" t="inlineStr">
+      <c r="H23" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5599,7 +5599,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="71" t="n">
+      <c r="P23" s="95" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -5695,7 +5695,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="80" t="n">
+      <c r="P24" s="96" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -5791,7 +5791,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="71" t="n">
+      <c r="P25" s="95" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -5887,7 +5887,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="80" t="n">
+      <c r="P26" s="96" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -5983,7 +5983,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="71" t="n">
+      <c r="P27" s="95" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -6083,7 +6083,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="80" t="n">
+      <c r="P28" s="96" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -6179,7 +6179,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="71" t="n">
+      <c r="P29" s="95" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -6275,7 +6275,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="80" t="n">
+      <c r="P30" s="96" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -6371,7 +6371,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="71" t="n">
+      <c r="P31" s="95" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -6467,7 +6467,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="80" t="n">
+      <c r="P32" s="96" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -6563,7 +6563,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="71" t="n">
+      <c r="P33" s="95" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -6659,7 +6659,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="80" t="n">
+      <c r="P34" s="96" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -6755,7 +6755,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="71" t="n">
+      <c r="P35" s="95" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -6851,7 +6851,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="80" t="n">
+      <c r="P36" s="96" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -6947,7 +6947,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="71" t="n">
+      <c r="P37" s="95" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -7006,12 +7006,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="77" t="inlineStr">
+      <c r="G38" s="98" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="77" t="inlineStr">
+      <c r="H38" s="98" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -7043,7 +7043,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="80" t="n">
+      <c r="P38" s="96" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -7139,7 +7139,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="71" t="n">
+      <c r="P39" s="95" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -7198,12 +7198,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="77" t="inlineStr">
+      <c r="G40" s="98" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="77" t="inlineStr">
+      <c r="H40" s="98" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -7235,7 +7235,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="80" t="n">
+      <c r="P40" s="96" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -7298,12 +7298,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="68" t="inlineStr">
+      <c r="G41" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="68" t="inlineStr">
+      <c r="H41" s="98" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -7335,7 +7335,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="71" t="n">
+      <c r="P41" s="95" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -7398,12 +7398,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="G42" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="H42" s="98" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -7435,7 +7435,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="80" t="n">
+      <c r="P42" s="96" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -7535,7 +7535,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="71" t="n">
+      <c r="P43" s="95" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -7635,7 +7635,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="80" t="n">
+      <c r="P44" s="96" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -7698,7 +7698,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="68" t="inlineStr">
+      <c r="G45" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7735,7 +7735,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="71" t="n">
+      <c r="P45" s="95" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -7798,7 +7798,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="77" t="inlineStr">
+      <c r="G46" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7835,7 +7835,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="80" t="n">
+      <c r="P46" s="96" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -7894,12 +7894,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="68" t="inlineStr">
+      <c r="G47" s="98" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="68" t="inlineStr">
+      <c r="H47" s="98" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -7931,7 +7931,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="71" t="n">
+      <c r="P47" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="80" t="n">
+      <c r="P48" s="96" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -8131,7 +8131,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="71" t="n">
+      <c r="P49" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -8231,7 +8231,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="80" t="n">
+      <c r="P50" s="96" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -8331,7 +8331,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="71" t="n">
+      <c r="P51" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -8427,7 +8427,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="80" t="n">
+      <c r="P52" s="96" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -8523,7 +8523,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="71" t="n">
+      <c r="P53" s="95" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -8619,7 +8619,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="80" t="n">
+      <c r="P54" s="96" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -8715,7 +8715,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="71" t="n">
+      <c r="P55" s="95" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -8815,7 +8815,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="80" t="n">
+      <c r="P56" s="96" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -8911,7 +8911,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="71" t="n">
+      <c r="P57" s="95" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -9007,7 +9007,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="80" t="n">
+      <c r="P58" s="96" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -9103,7 +9103,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="71" t="n">
+      <c r="P59" s="95" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -9199,7 +9199,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="80" t="n">
+      <c r="P60" s="96" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -9258,12 +9258,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="68" t="inlineStr">
+      <c r="G61" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="68" t="inlineStr">
+      <c r="H61" s="98" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -9295,7 +9295,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="71" t="n">
+      <c r="P61" s="95" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -9359,7 +9359,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="77" t="inlineStr">
+      <c r="H62" s="97" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -9454,12 +9454,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="68" t="inlineStr">
+      <c r="G63" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="68" t="inlineStr">
+      <c r="H63" s="98" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -9491,7 +9491,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="71" t="n">
+      <c r="P63" s="95" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -9555,7 +9555,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="77" t="inlineStr">
+      <c r="H64" s="97" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -9691,7 +9691,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="71" t="n">
+      <c r="P65" s="95" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -9791,7 +9791,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="80" t="n">
+      <c r="P66" s="96" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -9891,7 +9891,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="71" t="n">
+      <c r="P67" s="95" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -9954,7 +9954,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="77" t="inlineStr">
+      <c r="G68" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9991,7 +9991,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="80" t="n">
+      <c r="P68" s="96" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -10054,7 +10054,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="68" t="inlineStr">
+      <c r="G69" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -10091,7 +10091,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="71" t="n">
+      <c r="P69" s="95" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -10187,7 +10187,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="80" t="n">
+      <c r="P70" s="96" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -10251,7 +10251,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="68" t="inlineStr">
+      <c r="H71" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -10283,7 +10283,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="71" t="n">
+      <c r="P71" s="95" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -10379,7 +10379,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="80" t="n">
+      <c r="P72" s="96" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -10475,7 +10475,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="71" t="n">
+      <c r="P73" s="95" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -10539,7 +10539,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="77" t="inlineStr">
+      <c r="H74" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -10571,7 +10571,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="80" t="n">
+      <c r="P74" s="96" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -10667,7 +10667,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="71" t="n">
+      <c r="P75" s="95" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -10763,7 +10763,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="80" t="n">
+      <c r="P76" s="96" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -10859,7 +10859,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="71" t="n">
+      <c r="P77" s="95" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -10959,7 +10959,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="80" t="n">
+      <c r="P78" s="96" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -11055,7 +11055,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="71" t="n">
+      <c r="P79" s="95" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -11155,7 +11155,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="80" t="n">
+      <c r="P80" s="96" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -11255,7 +11255,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="71" t="n">
+      <c r="P81" s="95" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -11355,7 +11355,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="80" t="n">
+      <c r="P82" s="96" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -11451,7 +11451,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="71" t="n">
+      <c r="P83" s="95" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -11547,7 +11547,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="80" t="n">
+      <c r="P84" s="96" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -11643,7 +11643,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="71" t="n">
+      <c r="P85" s="95" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -11739,7 +11739,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="80" t="n">
+      <c r="P86" s="96" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -11839,7 +11839,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="71" t="n">
+      <c r="P87" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -11935,7 +11935,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="80" t="n">
+      <c r="P88" s="96" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -12031,7 +12031,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="71" t="n">
+      <c r="P89" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -12127,7 +12127,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="80" t="n">
+      <c r="P90" s="96" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -12227,7 +12227,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="71" t="n">
+      <c r="P91" s="95" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -12323,7 +12323,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="80" t="n">
+      <c r="P92" s="96" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -12419,7 +12419,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="71" t="n">
+      <c r="P93" s="95" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -12519,7 +12519,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="80" t="n">
+      <c r="P94" s="96" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -12619,7 +12619,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="71" t="n">
+      <c r="P95" s="95" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -12719,7 +12719,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="80" t="n">
+      <c r="P96" s="96" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -12819,7 +12819,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="71" t="n">
+      <c r="P97" s="95" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -12915,7 +12915,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="80" t="n">
+      <c r="P98" s="96" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="68" t="inlineStr">
+      <c r="G99" s="97" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -13011,7 +13011,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="71" t="n">
+      <c r="P99" s="95" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -13111,7 +13111,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="80" t="n">
+      <c r="P100" s="96" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -13207,7 +13207,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="71" t="n">
+      <c r="P101" s="95" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -13303,7 +13303,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="80" t="n">
+      <c r="P102" s="96" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -13399,7 +13399,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="71" t="n">
+      <c r="P103" s="95" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -13458,12 +13458,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="77" t="inlineStr">
+      <c r="G104" s="97" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="77" t="inlineStr">
+      <c r="H104" s="97" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -13495,7 +13495,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="80" t="n">
+      <c r="P104" s="96" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -13591,7 +13591,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="71" t="n">
+      <c r="P105" s="95" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -13685,7 +13685,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="80" t="n">
+      <c r="P106" s="96" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -13779,7 +13779,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="71" t="n">
+      <c r="P107" s="95" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -13873,7 +13873,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="80" t="n">
+      <c r="P108" s="96" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -13971,7 +13971,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="71" t="n">
+      <c r="P109" s="95" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -14055,7 +14055,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="80" t="n">
+      <c r="P110" s="96" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -15310,7 +15310,7 @@
           <t>업데이트: 2026-05-03 00:43</t>
         </is>
       </c>
-      <c r="AR2" s="108" t="inlineStr">
+      <c r="AR2" s="111" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:43</t>
         </is>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -765,6 +765,24 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1176,14 +1194,24 @@
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="G6" authorId="0" shapeId="0">
@@ -2004,15 +2032,25 @@
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분
-(직접 입력)</t>
+        <t>▣ 출하구분 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <t>▣ INV번호
-(출하코드)
-(직접 입력)</t>
+(출하코드) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
@@ -2062,26 +2100,46 @@
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로
-(직접 입력)</t>
+        <t>▣ 차수/경로 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형
-(직접 입력)</t>
+        <t>▣ 거래유형 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류
-(직접 입력)</t>
+        <t>▣ 통관분류 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일
-(직접 입력)</t>
+        <t>▣ 출하일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -2096,8 +2154,13 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율
-(직접 입력)</t>
+        <t>▣ 환율 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
@@ -2110,8 +2173,13 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수
-(직접 입력)</t>
+        <t>▣ BOX수 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
@@ -2125,20 +2193,35 @@
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD)
-(직접 입력)</t>
+        <t>▣ 인보이스(USD) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일
-(직접 입력)</t>
+        <t>▣ VN입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
@@ -2153,22 +2236,37 @@
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <t>▣ 입고
-완료
-(직접 입력)</t>
+완료 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>▣ 출하
-완료
-(직접 입력)</t>
+완료 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <t>▣ 조달
-진행률
-(직접 입력)</t>
+진행률 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2491,14 +2589,24 @@
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2657,14 +2765,24 @@
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일
-(직접 입력)</t>
+        <t>▣ 발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유
-(직접 입력)</t>
+        <t>▣ 발행사유 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2732,8 +2850,13 @@
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일
-(직접 입력)</t>
+        <t>▣ 생성일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3056,14 +3179,24 @@
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3399,7 +3532,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3437,7 +3570,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3472,9 +3605,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:43</t>
+      <c r="AF2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -3867,7 +4000,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="95" t="n">
+      <c r="P5" s="71" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -3926,12 +4059,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="98" t="inlineStr">
+      <c r="G6" s="77" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -3963,7 +4096,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="96" t="n">
+      <c r="P6" s="80" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -4059,7 +4192,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="95" t="n">
+      <c r="P7" s="71" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -4123,7 +4256,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="97" t="inlineStr">
+      <c r="H8" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4155,7 +4288,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="96" t="n">
+      <c r="P8" s="80" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -4219,7 +4352,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="97" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4251,7 +4384,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="95" t="n">
+      <c r="P9" s="71" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -4310,12 +4443,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="98" t="inlineStr">
+      <c r="G10" s="77" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="98" t="inlineStr">
+      <c r="H10" s="77" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -4347,7 +4480,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="96" t="n">
+      <c r="P10" s="80" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -4443,7 +4576,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="95" t="n">
+      <c r="P11" s="71" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -4539,7 +4672,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="96" t="n">
+      <c r="P12" s="80" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -4635,7 +4768,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="95" t="n">
+      <c r="P13" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -4731,7 +4864,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="96" t="n">
+      <c r="P14" s="80" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -4923,7 +5056,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="96" t="n">
+      <c r="P16" s="80" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -5119,7 +5252,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="96" t="n">
+      <c r="P18" s="80" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -5178,12 +5311,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="98" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="98" t="inlineStr">
+      <c r="H19" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5215,7 +5348,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="95" t="n">
+      <c r="P19" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -5279,7 +5412,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="97" t="inlineStr">
+      <c r="H20" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5311,7 +5444,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="96" t="n">
+      <c r="P20" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -5370,12 +5503,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="98" t="inlineStr">
+      <c r="G21" s="68" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="98" t="inlineStr">
+      <c r="H21" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5407,7 +5540,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="95" t="n">
+      <c r="P21" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -5471,7 +5604,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="97" t="inlineStr">
+      <c r="H22" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5503,7 +5636,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="96" t="n">
+      <c r="P22" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -5567,7 +5700,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="97" t="inlineStr">
+      <c r="H23" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5599,7 +5732,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="95" t="n">
+      <c r="P23" s="71" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -5695,7 +5828,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="96" t="n">
+      <c r="P24" s="80" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -5791,7 +5924,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="95" t="n">
+      <c r="P25" s="71" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -5887,7 +6020,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="96" t="n">
+      <c r="P26" s="80" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -5983,7 +6116,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="95" t="n">
+      <c r="P27" s="71" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -6083,7 +6216,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="96" t="n">
+      <c r="P28" s="80" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -6179,7 +6312,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="95" t="n">
+      <c r="P29" s="71" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -6275,7 +6408,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="96" t="n">
+      <c r="P30" s="80" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -6371,7 +6504,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="95" t="n">
+      <c r="P31" s="71" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -6467,7 +6600,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="96" t="n">
+      <c r="P32" s="80" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -6563,7 +6696,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="95" t="n">
+      <c r="P33" s="71" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -6659,7 +6792,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="96" t="n">
+      <c r="P34" s="80" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -6755,7 +6888,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="95" t="n">
+      <c r="P35" s="71" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -6851,7 +6984,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="96" t="n">
+      <c r="P36" s="80" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -6947,7 +7080,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="95" t="n">
+      <c r="P37" s="71" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -7006,12 +7139,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="98" t="inlineStr">
+      <c r="G38" s="77" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="98" t="inlineStr">
+      <c r="H38" s="77" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -7043,7 +7176,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="96" t="n">
+      <c r="P38" s="80" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -7139,7 +7272,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="95" t="n">
+      <c r="P39" s="71" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -7198,12 +7331,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="98" t="inlineStr">
+      <c r="G40" s="77" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="98" t="inlineStr">
+      <c r="H40" s="77" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -7235,7 +7368,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="96" t="n">
+      <c r="P40" s="80" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -7298,12 +7431,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="98" t="inlineStr">
+      <c r="G41" s="68" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="98" t="inlineStr">
+      <c r="H41" s="68" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -7335,7 +7468,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="95" t="n">
+      <c r="P41" s="71" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -7398,12 +7531,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="98" t="inlineStr">
+      <c r="G42" s="77" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="98" t="inlineStr">
+      <c r="H42" s="77" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -7435,7 +7568,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="96" t="n">
+      <c r="P42" s="80" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -7535,7 +7668,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="95" t="n">
+      <c r="P43" s="71" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -7635,7 +7768,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="96" t="n">
+      <c r="P44" s="80" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -7698,7 +7831,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="97" t="inlineStr">
+      <c r="G45" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7735,7 +7868,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="95" t="n">
+      <c r="P45" s="71" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -7798,7 +7931,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="97" t="inlineStr">
+      <c r="G46" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7835,7 +7968,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="96" t="n">
+      <c r="P46" s="80" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -7894,12 +8027,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="98" t="inlineStr">
+      <c r="G47" s="68" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="98" t="inlineStr">
+      <c r="H47" s="68" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -7931,7 +8064,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="95" t="n">
+      <c r="P47" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -8031,7 +8164,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="96" t="n">
+      <c r="P48" s="80" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -8131,7 +8264,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="95" t="n">
+      <c r="P49" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -8231,7 +8364,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="96" t="n">
+      <c r="P50" s="80" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -8331,7 +8464,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="95" t="n">
+      <c r="P51" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -8427,7 +8560,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="96" t="n">
+      <c r="P52" s="80" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -8523,7 +8656,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="95" t="n">
+      <c r="P53" s="71" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -8619,7 +8752,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="96" t="n">
+      <c r="P54" s="80" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -8715,7 +8848,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="95" t="n">
+      <c r="P55" s="71" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -8815,7 +8948,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="96" t="n">
+      <c r="P56" s="80" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -8911,7 +9044,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="95" t="n">
+      <c r="P57" s="71" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -9007,7 +9140,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="96" t="n">
+      <c r="P58" s="80" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -9103,7 +9236,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="95" t="n">
+      <c r="P59" s="71" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -9199,7 +9332,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="96" t="n">
+      <c r="P60" s="80" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -9258,12 +9391,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="98" t="inlineStr">
+      <c r="G61" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="98" t="inlineStr">
+      <c r="H61" s="68" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -9295,7 +9428,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="95" t="n">
+      <c r="P61" s="71" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -9359,7 +9492,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="97" t="inlineStr">
+      <c r="H62" s="77" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -9454,12 +9587,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="98" t="inlineStr">
+      <c r="G63" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="98" t="inlineStr">
+      <c r="H63" s="68" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -9491,7 +9624,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="95" t="n">
+      <c r="P63" s="71" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -9555,7 +9688,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="97" t="inlineStr">
+      <c r="H64" s="77" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -9691,7 +9824,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="95" t="n">
+      <c r="P65" s="71" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -9791,7 +9924,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="96" t="n">
+      <c r="P66" s="80" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -9891,7 +10024,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="95" t="n">
+      <c r="P67" s="71" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -9954,7 +10087,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="97" t="inlineStr">
+      <c r="G68" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9991,7 +10124,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="96" t="n">
+      <c r="P68" s="80" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -10054,7 +10187,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="97" t="inlineStr">
+      <c r="G69" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -10091,7 +10224,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="95" t="n">
+      <c r="P69" s="71" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -10187,7 +10320,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="96" t="n">
+      <c r="P70" s="80" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -10251,7 +10384,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="97" t="inlineStr">
+      <c r="H71" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -10283,7 +10416,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="95" t="n">
+      <c r="P71" s="71" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -10379,7 +10512,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="96" t="n">
+      <c r="P72" s="80" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -10475,7 +10608,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="95" t="n">
+      <c r="P73" s="71" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -10539,7 +10672,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="97" t="inlineStr">
+      <c r="H74" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -10571,7 +10704,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="96" t="n">
+      <c r="P74" s="80" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -10667,7 +10800,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="95" t="n">
+      <c r="P75" s="71" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -10763,7 +10896,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="96" t="n">
+      <c r="P76" s="80" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -10859,7 +10992,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="95" t="n">
+      <c r="P77" s="71" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -10959,7 +11092,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="96" t="n">
+      <c r="P78" s="80" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -11055,7 +11188,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="95" t="n">
+      <c r="P79" s="71" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -11155,7 +11288,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="96" t="n">
+      <c r="P80" s="80" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -11255,7 +11388,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="95" t="n">
+      <c r="P81" s="71" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -11355,7 +11488,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="96" t="n">
+      <c r="P82" s="80" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -11451,7 +11584,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="95" t="n">
+      <c r="P83" s="71" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -11547,7 +11680,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="96" t="n">
+      <c r="P84" s="80" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -11643,7 +11776,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="95" t="n">
+      <c r="P85" s="71" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -11739,7 +11872,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="96" t="n">
+      <c r="P86" s="80" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -11839,7 +11972,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="95" t="n">
+      <c r="P87" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -11935,7 +12068,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="96" t="n">
+      <c r="P88" s="80" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -12031,7 +12164,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="95" t="n">
+      <c r="P89" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -12127,7 +12260,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="96" t="n">
+      <c r="P90" s="80" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -12227,7 +12360,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="95" t="n">
+      <c r="P91" s="71" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -12323,7 +12456,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="96" t="n">
+      <c r="P92" s="80" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -12419,7 +12552,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="95" t="n">
+      <c r="P93" s="71" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -12519,7 +12652,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="96" t="n">
+      <c r="P94" s="80" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -12619,7 +12752,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="95" t="n">
+      <c r="P95" s="71" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -12719,7 +12852,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="96" t="n">
+      <c r="P96" s="80" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -12819,7 +12952,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="95" t="n">
+      <c r="P97" s="71" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -12915,7 +13048,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="96" t="n">
+      <c r="P98" s="80" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -12974,7 +13107,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="97" t="inlineStr">
+      <c r="G99" s="68" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -13011,7 +13144,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="95" t="n">
+      <c r="P99" s="71" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -13111,7 +13244,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="96" t="n">
+      <c r="P100" s="80" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -13207,7 +13340,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="95" t="n">
+      <c r="P101" s="71" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -13303,7 +13436,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="96" t="n">
+      <c r="P102" s="80" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -13399,7 +13532,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="95" t="n">
+      <c r="P103" s="71" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -13458,12 +13591,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="97" t="inlineStr">
+      <c r="G104" s="77" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="97" t="inlineStr">
+      <c r="H104" s="77" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -13495,7 +13628,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="96" t="n">
+      <c r="P104" s="80" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -13591,7 +13724,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="95" t="n">
+      <c r="P105" s="71" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -13685,7 +13818,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="96" t="n">
+      <c r="P106" s="80" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -13779,7 +13912,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="95" t="n">
+      <c r="P107" s="71" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -13873,7 +14006,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="96" t="n">
+      <c r="P108" s="80" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -13971,7 +14104,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="95" t="n">
+      <c r="P109" s="71" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -14055,7 +14188,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="96" t="n">
+      <c r="P110" s="80" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -15214,7 +15347,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -15261,7 +15394,7 @@
       <c r="AO1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15305,12 +15438,12 @@
       <c r="AL2" s="91" t="n"/>
       <c r="AM2" s="91" t="n"/>
       <c r="AN2" s="92" t="n"/>
-      <c r="AO2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:43</t>
-        </is>
-      </c>
-      <c r="AR2" s="111" t="inlineStr">
+      <c r="AO2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
+        </is>
+      </c>
+      <c r="AR2" s="114" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:43</t>
         </is>
@@ -24848,7 +24981,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -24877,7 +25010,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -24903,9 +25036,9 @@
       <c r="T2" s="91" t="n"/>
       <c r="U2" s="91" t="n"/>
       <c r="V2" s="92" t="n"/>
-      <c r="W2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:43</t>
+      <c r="W2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -25955,7 +26088,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -25993,7 +26126,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -26028,9 +26161,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="AF2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33983,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -33864,7 +33997,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -33875,9 +34008,9 @@
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="91" t="n"/>
       <c r="G2" s="92" t="n"/>
-      <c r="H2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="H2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -41208,7 +41341,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -41221,7 +41354,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -41231,9 +41364,9 @@
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="92" t="n"/>
-      <c r="G2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="G2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -45321,7 +45454,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -45333,7 +45466,7 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -45342,9 +45475,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="F2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>
@@ -48888,7 +49021,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -48926,7 +49059,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -48961,9 +49094,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="AF2" s="117" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -765,6 +765,42 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1692,317 +1728,6 @@
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="W4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="Y4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="Z4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AA4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AB4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AC4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AD4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AE4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AF4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AG4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AH4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AI4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 부서담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-      </text>
-    </comment>
-    <comment ref="AJ4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AK4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AL4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AM4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AN4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AO4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AP4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AQ4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 베트남 담당자
-• 3가지 입력 방식:
-  1) '제외' 선택 → 베트남 미참여
-  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
-• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-      </text>
-    </comment>
-    <comment ref="AR4" authorId="0" shapeId="0">
       <text>
         <t>▣ 베트남 담당자
 • 3가지 입력 방식:
@@ -3532,7 +3257,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3570,7 +3295,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3605,9 +3330,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="AF2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR140"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15308,13 +15033,13 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="19"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="19"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -15347,7 +15072,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -15365,38 +15090,12 @@
       <c r="L1" s="91" t="n"/>
       <c r="M1" s="91" t="n"/>
       <c r="N1" s="91" t="n"/>
-      <c r="O1" s="91" t="n"/>
-      <c r="P1" s="91" t="n"/>
-      <c r="Q1" s="91" t="n"/>
-      <c r="R1" s="91" t="n"/>
-      <c r="S1" s="91" t="n"/>
-      <c r="T1" s="91" t="n"/>
-      <c r="U1" s="91" t="n"/>
-      <c r="V1" s="91" t="n"/>
-      <c r="W1" s="91" t="n"/>
-      <c r="X1" s="91" t="n"/>
-      <c r="Y1" s="91" t="n"/>
-      <c r="Z1" s="91" t="n"/>
-      <c r="AA1" s="91" t="n"/>
-      <c r="AB1" s="91" t="n"/>
-      <c r="AC1" s="91" t="n"/>
-      <c r="AD1" s="91" t="n"/>
-      <c r="AE1" s="91" t="n"/>
-      <c r="AF1" s="91" t="n"/>
-      <c r="AG1" s="91" t="n"/>
-      <c r="AH1" s="91" t="n"/>
-      <c r="AI1" s="91" t="n"/>
-      <c r="AJ1" s="91" t="n"/>
-      <c r="AK1" s="91" t="n"/>
-      <c r="AL1" s="91" t="n"/>
-      <c r="AM1" s="91" t="n"/>
-      <c r="AN1" s="91" t="n"/>
-      <c r="AO1" s="92" t="n"/>
+      <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
-        <is>
-          <t>㈜케이엔케이  |  검사기 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
+      <c r="A2" s="128" t="inlineStr">
+        <is>
+          <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
@@ -15411,41 +15110,10 @@
       <c r="K2" s="91" t="n"/>
       <c r="L2" s="91" t="n"/>
       <c r="M2" s="91" t="n"/>
-      <c r="N2" s="91" t="n"/>
-      <c r="O2" s="91" t="n"/>
-      <c r="P2" s="91" t="n"/>
-      <c r="Q2" s="91" t="n"/>
-      <c r="R2" s="91" t="n"/>
-      <c r="S2" s="91" t="n"/>
-      <c r="T2" s="91" t="n"/>
-      <c r="U2" s="91" t="n"/>
-      <c r="V2" s="91" t="n"/>
-      <c r="W2" s="91" t="n"/>
-      <c r="X2" s="91" t="n"/>
-      <c r="Y2" s="91" t="n"/>
-      <c r="Z2" s="91" t="n"/>
-      <c r="AA2" s="91" t="n"/>
-      <c r="AB2" s="91" t="n"/>
-      <c r="AC2" s="91" t="n"/>
-      <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="91" t="n"/>
-      <c r="AF2" s="91" t="n"/>
-      <c r="AG2" s="91" t="n"/>
-      <c r="AH2" s="91" t="n"/>
-      <c r="AI2" s="91" t="n"/>
-      <c r="AJ2" s="91" t="n"/>
-      <c r="AK2" s="91" t="n"/>
-      <c r="AL2" s="91" t="n"/>
-      <c r="AM2" s="91" t="n"/>
-      <c r="AN2" s="92" t="n"/>
-      <c r="AO2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
-        </is>
-      </c>
-      <c r="AR2" s="114" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="N2" s="92" t="n"/>
+      <c r="O2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -15525,151 +15193,6 @@
           <t>🔒자동</t>
         </is>
       </c>
-      <c r="P3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="Q3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="R3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="S3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="T3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="U3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="V3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="W3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="X3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="Y3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="Z3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AA3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AB3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AC3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AD3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AE3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AF3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AG3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AH3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AI3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AJ3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AK3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AL3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AM3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AN3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AO3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AP3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AQ3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
-      <c r="AR3" s="57" t="inlineStr">
-        <is>
-          <t>🔒자동</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="60" t="inlineStr">
@@ -15716,217 +15239,43 @@
       <c r="I4" s="64" t="inlineStr">
         <is>
           <t>설계팀
-설계검토</t>
+완료일</t>
         </is>
       </c>
       <c r="J4" s="64" t="inlineStr">
         <is>
-          <t>설계팀
-3D/2D설계</t>
+          <t>검사기팀
+완료일</t>
         </is>
       </c>
       <c r="K4" s="64" t="inlineStr">
         <is>
-          <t>설계팀
-BOM작성</t>
+          <t>개발혁신팀
+완료일</t>
         </is>
       </c>
       <c r="L4" s="64" t="inlineStr">
         <is>
-          <t>설계팀
-가공발주</t>
+          <t>품질팀
+완료일</t>
         </is>
       </c>
       <c r="M4" s="64" t="inlineStr">
         <is>
-          <t>설계팀
-소계</t>
+          <t>제조기술1팀
+완료일</t>
         </is>
       </c>
       <c r="N4" s="64" t="inlineStr">
         <is>
-          <t>검사기팀
-검토</t>
+          <t>구매팀
+완료일</t>
         </is>
       </c>
       <c r="O4" s="64" t="inlineStr">
         <is>
-          <t>검사기팀
-PCB</t>
-        </is>
-      </c>
-      <c r="P4" s="64" t="inlineStr">
-        <is>
-          <t>검사기팀
-H/W</t>
-        </is>
-      </c>
-      <c r="Q4" s="64" t="inlineStr">
-        <is>
-          <t>검사기팀
-F/W</t>
-        </is>
-      </c>
-      <c r="R4" s="64" t="inlineStr">
-        <is>
-          <t>검사기팀
-동작검증</t>
-        </is>
-      </c>
-      <c r="S4" s="64" t="inlineStr">
-        <is>
-          <t>검사기팀
-소계</t>
-        </is>
-      </c>
-      <c r="T4" s="64" t="inlineStr">
-        <is>
-          <t>개발혁신팀
-검토</t>
-        </is>
-      </c>
-      <c r="U4" s="64" t="inlineStr">
-        <is>
-          <t>개발혁신팀
-프로그램</t>
-        </is>
-      </c>
-      <c r="V4" s="64" t="inlineStr">
-        <is>
-          <t>개발혁신팀
-동작검증</t>
-        </is>
-      </c>
-      <c r="W4" s="64" t="inlineStr">
-        <is>
-          <t>개발혁신팀
-소계</t>
-        </is>
-      </c>
-      <c r="X4" s="64" t="inlineStr">
-        <is>
-          <t>품질팀
-동작확인</t>
-        </is>
-      </c>
-      <c r="Y4" s="64" t="inlineStr">
-        <is>
-          <t>품질팀
-반복성검증</t>
-        </is>
-      </c>
-      <c r="Z4" s="64" t="inlineStr">
-        <is>
-          <t>품질팀
-성적서작성</t>
-        </is>
-      </c>
-      <c r="AA4" s="64" t="inlineStr">
-        <is>
-          <t>품질팀
-소계</t>
-        </is>
-      </c>
-      <c r="AB4" s="64" t="inlineStr">
-        <is>
-          <t>제조기술1팀
-조립</t>
-        </is>
-      </c>
-      <c r="AC4" s="64" t="inlineStr">
-        <is>
-          <t>제조기술1팀
-TURN-ON</t>
-        </is>
-      </c>
-      <c r="AD4" s="64" t="inlineStr">
-        <is>
-          <t>제조기술1팀
-소계</t>
-        </is>
-      </c>
-      <c r="AE4" s="64" t="inlineStr">
-        <is>
-          <t>구매팀
-BOM작성</t>
-        </is>
-      </c>
-      <c r="AF4" s="64" t="inlineStr">
-        <is>
-          <t>구매팀
-구매검토</t>
-        </is>
-      </c>
-      <c r="AG4" s="64" t="inlineStr">
-        <is>
-          <t>구매팀
-발주</t>
-        </is>
-      </c>
-      <c r="AH4" s="64" t="inlineStr">
-        <is>
-          <t>구매팀
-입고</t>
-        </is>
-      </c>
-      <c r="AI4" s="64" t="inlineStr">
-        <is>
-          <t>구매팀
-소계</t>
-        </is>
-      </c>
-      <c r="AJ4" s="64" t="inlineStr">
-        <is>
           <t>베트남
-설계</t>
-        </is>
-      </c>
-      <c r="AK4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-가공</t>
-        </is>
-      </c>
-      <c r="AL4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-조립</t>
-        </is>
-      </c>
-      <c r="AM4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-동작검증</t>
-        </is>
-      </c>
-      <c r="AN4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-출하검증</t>
-        </is>
-      </c>
-      <c r="AO4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-소계</t>
-        </is>
-      </c>
-      <c r="AP4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-동작검증</t>
-        </is>
-      </c>
-      <c r="AQ4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-출하검증</t>
-        </is>
-      </c>
-      <c r="AR4" s="64" t="inlineStr">
-        <is>
-          <t>베트남
-소계</t>
+완료일</t>
         </is>
       </c>
     </row>
@@ -15972,35 +15321,6 @@
       <c r="M5" s="73" t="n"/>
       <c r="N5" s="73" t="n"/>
       <c r="O5" s="73" t="n"/>
-      <c r="P5" s="73" t="n"/>
-      <c r="Q5" s="73" t="n"/>
-      <c r="R5" s="73" t="n"/>
-      <c r="S5" s="73" t="n"/>
-      <c r="T5" s="73" t="n"/>
-      <c r="U5" s="73" t="n"/>
-      <c r="V5" s="73" t="n"/>
-      <c r="W5" s="73" t="n"/>
-      <c r="X5" s="73" t="n"/>
-      <c r="Y5" s="73" t="n"/>
-      <c r="Z5" s="73" t="n"/>
-      <c r="AA5" s="73" t="n"/>
-      <c r="AB5" s="73" t="n"/>
-      <c r="AC5" s="73" t="n"/>
-      <c r="AD5" s="73" t="n"/>
-      <c r="AE5" s="73" t="n"/>
-      <c r="AF5" s="73" t="n"/>
-      <c r="AG5" s="73" t="n"/>
-      <c r="AH5" s="73" t="n"/>
-      <c r="AI5" s="73" t="n"/>
-      <c r="AJ5" s="73" t="n"/>
-      <c r="AK5" s="73" t="n"/>
-      <c r="AL5" s="73" t="n"/>
-      <c r="AM5" s="73" t="n"/>
-      <c r="AN5" s="73" t="n"/>
-      <c r="AO5" s="73" t="n"/>
-      <c r="AP5" s="73" t="n"/>
-      <c r="AQ5" s="73" t="n"/>
-      <c r="AR5" s="73" t="n"/>
     </row>
     <row r="6" ht="22.05" customHeight="1">
       <c r="A6" s="75" t="n">
@@ -16044,35 +15364,6 @@
       <c r="M6" s="82" t="n"/>
       <c r="N6" s="82" t="n"/>
       <c r="O6" s="82" t="n"/>
-      <c r="P6" s="82" t="n"/>
-      <c r="Q6" s="82" t="n"/>
-      <c r="R6" s="82" t="n"/>
-      <c r="S6" s="82" t="n"/>
-      <c r="T6" s="82" t="n"/>
-      <c r="U6" s="82" t="n"/>
-      <c r="V6" s="82" t="n"/>
-      <c r="W6" s="82" t="n"/>
-      <c r="X6" s="82" t="n"/>
-      <c r="Y6" s="82" t="n"/>
-      <c r="Z6" s="82" t="n"/>
-      <c r="AA6" s="82" t="n"/>
-      <c r="AB6" s="82" t="n"/>
-      <c r="AC6" s="82" t="n"/>
-      <c r="AD6" s="82" t="n"/>
-      <c r="AE6" s="82" t="n"/>
-      <c r="AF6" s="82" t="n"/>
-      <c r="AG6" s="82" t="n"/>
-      <c r="AH6" s="82" t="n"/>
-      <c r="AI6" s="82" t="n"/>
-      <c r="AJ6" s="82" t="n"/>
-      <c r="AK6" s="82" t="n"/>
-      <c r="AL6" s="82" t="n"/>
-      <c r="AM6" s="82" t="n"/>
-      <c r="AN6" s="82" t="n"/>
-      <c r="AO6" s="82" t="n"/>
-      <c r="AP6" s="82" t="n"/>
-      <c r="AQ6" s="82" t="n"/>
-      <c r="AR6" s="82" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1">
       <c r="A7" s="66" t="n">
@@ -16116,35 +15407,6 @@
       <c r="M7" s="73" t="n"/>
       <c r="N7" s="73" t="n"/>
       <c r="O7" s="73" t="n"/>
-      <c r="P7" s="73" t="n"/>
-      <c r="Q7" s="73" t="n"/>
-      <c r="R7" s="73" t="n"/>
-      <c r="S7" s="73" t="n"/>
-      <c r="T7" s="73" t="n"/>
-      <c r="U7" s="73" t="n"/>
-      <c r="V7" s="73" t="n"/>
-      <c r="W7" s="73" t="n"/>
-      <c r="X7" s="73" t="n"/>
-      <c r="Y7" s="73" t="n"/>
-      <c r="Z7" s="73" t="n"/>
-      <c r="AA7" s="73" t="n"/>
-      <c r="AB7" s="73" t="n"/>
-      <c r="AC7" s="73" t="n"/>
-      <c r="AD7" s="73" t="n"/>
-      <c r="AE7" s="73" t="n"/>
-      <c r="AF7" s="73" t="n"/>
-      <c r="AG7" s="73" t="n"/>
-      <c r="AH7" s="73" t="n"/>
-      <c r="AI7" s="73" t="n"/>
-      <c r="AJ7" s="73" t="n"/>
-      <c r="AK7" s="73" t="n"/>
-      <c r="AL7" s="73" t="n"/>
-      <c r="AM7" s="73" t="n"/>
-      <c r="AN7" s="73" t="n"/>
-      <c r="AO7" s="73" t="n"/>
-      <c r="AP7" s="73" t="n"/>
-      <c r="AQ7" s="73" t="n"/>
-      <c r="AR7" s="73" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1">
       <c r="A8" s="75" t="n">
@@ -16188,35 +15450,6 @@
       <c r="M8" s="82" t="n"/>
       <c r="N8" s="82" t="n"/>
       <c r="O8" s="82" t="n"/>
-      <c r="P8" s="82" t="n"/>
-      <c r="Q8" s="82" t="n"/>
-      <c r="R8" s="82" t="n"/>
-      <c r="S8" s="82" t="n"/>
-      <c r="T8" s="82" t="n"/>
-      <c r="U8" s="82" t="n"/>
-      <c r="V8" s="82" t="n"/>
-      <c r="W8" s="82" t="n"/>
-      <c r="X8" s="82" t="n"/>
-      <c r="Y8" s="82" t="n"/>
-      <c r="Z8" s="82" t="n"/>
-      <c r="AA8" s="82" t="n"/>
-      <c r="AB8" s="82" t="n"/>
-      <c r="AC8" s="82" t="n"/>
-      <c r="AD8" s="82" t="n"/>
-      <c r="AE8" s="82" t="n"/>
-      <c r="AF8" s="82" t="n"/>
-      <c r="AG8" s="82" t="n"/>
-      <c r="AH8" s="82" t="n"/>
-      <c r="AI8" s="82" t="n"/>
-      <c r="AJ8" s="82" t="n"/>
-      <c r="AK8" s="82" t="n"/>
-      <c r="AL8" s="82" t="n"/>
-      <c r="AM8" s="82" t="n"/>
-      <c r="AN8" s="82" t="n"/>
-      <c r="AO8" s="82" t="n"/>
-      <c r="AP8" s="82" t="n"/>
-      <c r="AQ8" s="82" t="n"/>
-      <c r="AR8" s="82" t="n"/>
     </row>
     <row r="9" ht="22.05" customHeight="1">
       <c r="A9" s="66" t="n">
@@ -16260,35 +15493,6 @@
       <c r="M9" s="73" t="n"/>
       <c r="N9" s="73" t="n"/>
       <c r="O9" s="73" t="n"/>
-      <c r="P9" s="73" t="n"/>
-      <c r="Q9" s="73" t="n"/>
-      <c r="R9" s="73" t="n"/>
-      <c r="S9" s="73" t="n"/>
-      <c r="T9" s="73" t="n"/>
-      <c r="U9" s="73" t="n"/>
-      <c r="V9" s="73" t="n"/>
-      <c r="W9" s="73" t="n"/>
-      <c r="X9" s="73" t="n"/>
-      <c r="Y9" s="73" t="n"/>
-      <c r="Z9" s="73" t="n"/>
-      <c r="AA9" s="73" t="n"/>
-      <c r="AB9" s="73" t="n"/>
-      <c r="AC9" s="73" t="n"/>
-      <c r="AD9" s="73" t="n"/>
-      <c r="AE9" s="73" t="n"/>
-      <c r="AF9" s="73" t="n"/>
-      <c r="AG9" s="73" t="n"/>
-      <c r="AH9" s="73" t="n"/>
-      <c r="AI9" s="73" t="n"/>
-      <c r="AJ9" s="73" t="n"/>
-      <c r="AK9" s="73" t="n"/>
-      <c r="AL9" s="73" t="n"/>
-      <c r="AM9" s="73" t="n"/>
-      <c r="AN9" s="73" t="n"/>
-      <c r="AO9" s="73" t="n"/>
-      <c r="AP9" s="73" t="n"/>
-      <c r="AQ9" s="73" t="n"/>
-      <c r="AR9" s="73" t="n"/>
     </row>
     <row r="10" ht="22.05" customHeight="1">
       <c r="A10" s="75" t="n">
@@ -16332,35 +15536,6 @@
       <c r="M10" s="82" t="n"/>
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
-      <c r="P10" s="82" t="n"/>
-      <c r="Q10" s="82" t="n"/>
-      <c r="R10" s="82" t="n"/>
-      <c r="S10" s="82" t="n"/>
-      <c r="T10" s="82" t="n"/>
-      <c r="U10" s="82" t="n"/>
-      <c r="V10" s="82" t="n"/>
-      <c r="W10" s="82" t="n"/>
-      <c r="X10" s="82" t="n"/>
-      <c r="Y10" s="82" t="n"/>
-      <c r="Z10" s="82" t="n"/>
-      <c r="AA10" s="82" t="n"/>
-      <c r="AB10" s="82" t="n"/>
-      <c r="AC10" s="82" t="n"/>
-      <c r="AD10" s="82" t="n"/>
-      <c r="AE10" s="82" t="n"/>
-      <c r="AF10" s="82" t="n"/>
-      <c r="AG10" s="82" t="n"/>
-      <c r="AH10" s="82" t="n"/>
-      <c r="AI10" s="82" t="n"/>
-      <c r="AJ10" s="82" t="n"/>
-      <c r="AK10" s="82" t="n"/>
-      <c r="AL10" s="82" t="n"/>
-      <c r="AM10" s="82" t="n"/>
-      <c r="AN10" s="82" t="n"/>
-      <c r="AO10" s="82" t="n"/>
-      <c r="AP10" s="82" t="n"/>
-      <c r="AQ10" s="82" t="n"/>
-      <c r="AR10" s="82" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1">
       <c r="A11" s="66" t="n">
@@ -16404,35 +15579,6 @@
       <c r="M11" s="73" t="n"/>
       <c r="N11" s="73" t="n"/>
       <c r="O11" s="73" t="n"/>
-      <c r="P11" s="73" t="n"/>
-      <c r="Q11" s="73" t="n"/>
-      <c r="R11" s="73" t="n"/>
-      <c r="S11" s="73" t="n"/>
-      <c r="T11" s="73" t="n"/>
-      <c r="U11" s="73" t="n"/>
-      <c r="V11" s="73" t="n"/>
-      <c r="W11" s="73" t="n"/>
-      <c r="X11" s="73" t="n"/>
-      <c r="Y11" s="73" t="n"/>
-      <c r="Z11" s="73" t="n"/>
-      <c r="AA11" s="73" t="n"/>
-      <c r="AB11" s="73" t="n"/>
-      <c r="AC11" s="73" t="n"/>
-      <c r="AD11" s="73" t="n"/>
-      <c r="AE11" s="73" t="n"/>
-      <c r="AF11" s="73" t="n"/>
-      <c r="AG11" s="73" t="n"/>
-      <c r="AH11" s="73" t="n"/>
-      <c r="AI11" s="73" t="n"/>
-      <c r="AJ11" s="73" t="n"/>
-      <c r="AK11" s="73" t="n"/>
-      <c r="AL11" s="73" t="n"/>
-      <c r="AM11" s="73" t="n"/>
-      <c r="AN11" s="73" t="n"/>
-      <c r="AO11" s="73" t="n"/>
-      <c r="AP11" s="73" t="n"/>
-      <c r="AQ11" s="73" t="n"/>
-      <c r="AR11" s="73" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
       <c r="A12" s="75" t="n">
@@ -16476,35 +15622,6 @@
       <c r="M12" s="82" t="n"/>
       <c r="N12" s="82" t="n"/>
       <c r="O12" s="82" t="n"/>
-      <c r="P12" s="82" t="n"/>
-      <c r="Q12" s="82" t="n"/>
-      <c r="R12" s="82" t="n"/>
-      <c r="S12" s="82" t="n"/>
-      <c r="T12" s="82" t="n"/>
-      <c r="U12" s="82" t="n"/>
-      <c r="V12" s="82" t="n"/>
-      <c r="W12" s="82" t="n"/>
-      <c r="X12" s="82" t="n"/>
-      <c r="Y12" s="82" t="n"/>
-      <c r="Z12" s="82" t="n"/>
-      <c r="AA12" s="82" t="n"/>
-      <c r="AB12" s="82" t="n"/>
-      <c r="AC12" s="82" t="n"/>
-      <c r="AD12" s="82" t="n"/>
-      <c r="AE12" s="82" t="n"/>
-      <c r="AF12" s="82" t="n"/>
-      <c r="AG12" s="82" t="n"/>
-      <c r="AH12" s="82" t="n"/>
-      <c r="AI12" s="82" t="n"/>
-      <c r="AJ12" s="82" t="n"/>
-      <c r="AK12" s="82" t="n"/>
-      <c r="AL12" s="82" t="n"/>
-      <c r="AM12" s="82" t="n"/>
-      <c r="AN12" s="82" t="n"/>
-      <c r="AO12" s="82" t="n"/>
-      <c r="AP12" s="82" t="n"/>
-      <c r="AQ12" s="82" t="n"/>
-      <c r="AR12" s="82" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
       <c r="A13" s="66" t="n">
@@ -16548,35 +15665,6 @@
       <c r="M13" s="73" t="n"/>
       <c r="N13" s="73" t="n"/>
       <c r="O13" s="73" t="n"/>
-      <c r="P13" s="73" t="n"/>
-      <c r="Q13" s="73" t="n"/>
-      <c r="R13" s="73" t="n"/>
-      <c r="S13" s="73" t="n"/>
-      <c r="T13" s="73" t="n"/>
-      <c r="U13" s="73" t="n"/>
-      <c r="V13" s="73" t="n"/>
-      <c r="W13" s="73" t="n"/>
-      <c r="X13" s="73" t="n"/>
-      <c r="Y13" s="73" t="n"/>
-      <c r="Z13" s="73" t="n"/>
-      <c r="AA13" s="73" t="n"/>
-      <c r="AB13" s="73" t="n"/>
-      <c r="AC13" s="73" t="n"/>
-      <c r="AD13" s="73" t="n"/>
-      <c r="AE13" s="73" t="n"/>
-      <c r="AF13" s="73" t="n"/>
-      <c r="AG13" s="73" t="n"/>
-      <c r="AH13" s="73" t="n"/>
-      <c r="AI13" s="73" t="n"/>
-      <c r="AJ13" s="73" t="n"/>
-      <c r="AK13" s="73" t="n"/>
-      <c r="AL13" s="73" t="n"/>
-      <c r="AM13" s="73" t="n"/>
-      <c r="AN13" s="73" t="n"/>
-      <c r="AO13" s="73" t="n"/>
-      <c r="AP13" s="73" t="n"/>
-      <c r="AQ13" s="73" t="n"/>
-      <c r="AR13" s="73" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
       <c r="A14" s="75" t="n">
@@ -16620,35 +15708,6 @@
       <c r="M14" s="82" t="n"/>
       <c r="N14" s="82" t="n"/>
       <c r="O14" s="82" t="n"/>
-      <c r="P14" s="82" t="n"/>
-      <c r="Q14" s="82" t="n"/>
-      <c r="R14" s="82" t="n"/>
-      <c r="S14" s="82" t="n"/>
-      <c r="T14" s="82" t="n"/>
-      <c r="U14" s="82" t="n"/>
-      <c r="V14" s="82" t="n"/>
-      <c r="W14" s="82" t="n"/>
-      <c r="X14" s="82" t="n"/>
-      <c r="Y14" s="82" t="n"/>
-      <c r="Z14" s="82" t="n"/>
-      <c r="AA14" s="82" t="n"/>
-      <c r="AB14" s="82" t="n"/>
-      <c r="AC14" s="82" t="n"/>
-      <c r="AD14" s="82" t="n"/>
-      <c r="AE14" s="82" t="n"/>
-      <c r="AF14" s="82" t="n"/>
-      <c r="AG14" s="82" t="n"/>
-      <c r="AH14" s="82" t="n"/>
-      <c r="AI14" s="82" t="n"/>
-      <c r="AJ14" s="82" t="n"/>
-      <c r="AK14" s="82" t="n"/>
-      <c r="AL14" s="82" t="n"/>
-      <c r="AM14" s="82" t="n"/>
-      <c r="AN14" s="82" t="n"/>
-      <c r="AO14" s="82" t="n"/>
-      <c r="AP14" s="82" t="n"/>
-      <c r="AQ14" s="82" t="n"/>
-      <c r="AR14" s="82" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
       <c r="A15" s="66" t="n">
@@ -16692,35 +15751,6 @@
       <c r="M15" s="73" t="n"/>
       <c r="N15" s="73" t="n"/>
       <c r="O15" s="73" t="n"/>
-      <c r="P15" s="73" t="n"/>
-      <c r="Q15" s="73" t="n"/>
-      <c r="R15" s="73" t="n"/>
-      <c r="S15" s="73" t="n"/>
-      <c r="T15" s="73" t="n"/>
-      <c r="U15" s="73" t="n"/>
-      <c r="V15" s="73" t="n"/>
-      <c r="W15" s="73" t="n"/>
-      <c r="X15" s="73" t="n"/>
-      <c r="Y15" s="73" t="n"/>
-      <c r="Z15" s="73" t="n"/>
-      <c r="AA15" s="73" t="n"/>
-      <c r="AB15" s="73" t="n"/>
-      <c r="AC15" s="73" t="n"/>
-      <c r="AD15" s="73" t="n"/>
-      <c r="AE15" s="73" t="n"/>
-      <c r="AF15" s="73" t="n"/>
-      <c r="AG15" s="73" t="n"/>
-      <c r="AH15" s="73" t="n"/>
-      <c r="AI15" s="73" t="n"/>
-      <c r="AJ15" s="73" t="n"/>
-      <c r="AK15" s="73" t="n"/>
-      <c r="AL15" s="73" t="n"/>
-      <c r="AM15" s="73" t="n"/>
-      <c r="AN15" s="73" t="n"/>
-      <c r="AO15" s="73" t="n"/>
-      <c r="AP15" s="73" t="n"/>
-      <c r="AQ15" s="73" t="n"/>
-      <c r="AR15" s="73" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
       <c r="A16" s="75" t="n">
@@ -16764,35 +15794,6 @@
       <c r="M16" s="82" t="n"/>
       <c r="N16" s="82" t="n"/>
       <c r="O16" s="82" t="n"/>
-      <c r="P16" s="82" t="n"/>
-      <c r="Q16" s="82" t="n"/>
-      <c r="R16" s="82" t="n"/>
-      <c r="S16" s="82" t="n"/>
-      <c r="T16" s="82" t="n"/>
-      <c r="U16" s="82" t="n"/>
-      <c r="V16" s="82" t="n"/>
-      <c r="W16" s="82" t="n"/>
-      <c r="X16" s="82" t="n"/>
-      <c r="Y16" s="82" t="n"/>
-      <c r="Z16" s="82" t="n"/>
-      <c r="AA16" s="82" t="n"/>
-      <c r="AB16" s="82" t="n"/>
-      <c r="AC16" s="82" t="n"/>
-      <c r="AD16" s="82" t="n"/>
-      <c r="AE16" s="82" t="n"/>
-      <c r="AF16" s="82" t="n"/>
-      <c r="AG16" s="82" t="n"/>
-      <c r="AH16" s="82" t="n"/>
-      <c r="AI16" s="82" t="n"/>
-      <c r="AJ16" s="82" t="n"/>
-      <c r="AK16" s="82" t="n"/>
-      <c r="AL16" s="82" t="n"/>
-      <c r="AM16" s="82" t="n"/>
-      <c r="AN16" s="82" t="n"/>
-      <c r="AO16" s="82" t="n"/>
-      <c r="AP16" s="82" t="n"/>
-      <c r="AQ16" s="82" t="n"/>
-      <c r="AR16" s="82" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
       <c r="A17" s="66" t="n">
@@ -16836,35 +15837,6 @@
       <c r="M17" s="73" t="n"/>
       <c r="N17" s="73" t="n"/>
       <c r="O17" s="73" t="n"/>
-      <c r="P17" s="73" t="n"/>
-      <c r="Q17" s="73" t="n"/>
-      <c r="R17" s="73" t="n"/>
-      <c r="S17" s="73" t="n"/>
-      <c r="T17" s="73" t="n"/>
-      <c r="U17" s="73" t="n"/>
-      <c r="V17" s="73" t="n"/>
-      <c r="W17" s="73" t="n"/>
-      <c r="X17" s="73" t="n"/>
-      <c r="Y17" s="73" t="n"/>
-      <c r="Z17" s="73" t="n"/>
-      <c r="AA17" s="73" t="n"/>
-      <c r="AB17" s="73" t="n"/>
-      <c r="AC17" s="73" t="n"/>
-      <c r="AD17" s="73" t="n"/>
-      <c r="AE17" s="73" t="n"/>
-      <c r="AF17" s="73" t="n"/>
-      <c r="AG17" s="73" t="n"/>
-      <c r="AH17" s="73" t="n"/>
-      <c r="AI17" s="73" t="n"/>
-      <c r="AJ17" s="73" t="n"/>
-      <c r="AK17" s="73" t="n"/>
-      <c r="AL17" s="73" t="n"/>
-      <c r="AM17" s="73" t="n"/>
-      <c r="AN17" s="73" t="n"/>
-      <c r="AO17" s="73" t="n"/>
-      <c r="AP17" s="73" t="n"/>
-      <c r="AQ17" s="73" t="n"/>
-      <c r="AR17" s="73" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
       <c r="A18" s="75" t="n">
@@ -16908,35 +15880,6 @@
       <c r="M18" s="82" t="n"/>
       <c r="N18" s="82" t="n"/>
       <c r="O18" s="82" t="n"/>
-      <c r="P18" s="82" t="n"/>
-      <c r="Q18" s="82" t="n"/>
-      <c r="R18" s="82" t="n"/>
-      <c r="S18" s="82" t="n"/>
-      <c r="T18" s="82" t="n"/>
-      <c r="U18" s="82" t="n"/>
-      <c r="V18" s="82" t="n"/>
-      <c r="W18" s="82" t="n"/>
-      <c r="X18" s="82" t="n"/>
-      <c r="Y18" s="82" t="n"/>
-      <c r="Z18" s="82" t="n"/>
-      <c r="AA18" s="82" t="n"/>
-      <c r="AB18" s="82" t="n"/>
-      <c r="AC18" s="82" t="n"/>
-      <c r="AD18" s="82" t="n"/>
-      <c r="AE18" s="82" t="n"/>
-      <c r="AF18" s="82" t="n"/>
-      <c r="AG18" s="82" t="n"/>
-      <c r="AH18" s="82" t="n"/>
-      <c r="AI18" s="82" t="n"/>
-      <c r="AJ18" s="82" t="n"/>
-      <c r="AK18" s="82" t="n"/>
-      <c r="AL18" s="82" t="n"/>
-      <c r="AM18" s="82" t="n"/>
-      <c r="AN18" s="82" t="n"/>
-      <c r="AO18" s="82" t="n"/>
-      <c r="AP18" s="82" t="n"/>
-      <c r="AQ18" s="82" t="n"/>
-      <c r="AR18" s="82" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
       <c r="A19" s="66" t="n">
@@ -16980,35 +15923,6 @@
       <c r="M19" s="73" t="n"/>
       <c r="N19" s="73" t="n"/>
       <c r="O19" s="73" t="n"/>
-      <c r="P19" s="73" t="n"/>
-      <c r="Q19" s="73" t="n"/>
-      <c r="R19" s="73" t="n"/>
-      <c r="S19" s="73" t="n"/>
-      <c r="T19" s="73" t="n"/>
-      <c r="U19" s="73" t="n"/>
-      <c r="V19" s="73" t="n"/>
-      <c r="W19" s="73" t="n"/>
-      <c r="X19" s="73" t="n"/>
-      <c r="Y19" s="73" t="n"/>
-      <c r="Z19" s="73" t="n"/>
-      <c r="AA19" s="73" t="n"/>
-      <c r="AB19" s="73" t="n"/>
-      <c r="AC19" s="73" t="n"/>
-      <c r="AD19" s="73" t="n"/>
-      <c r="AE19" s="73" t="n"/>
-      <c r="AF19" s="73" t="n"/>
-      <c r="AG19" s="73" t="n"/>
-      <c r="AH19" s="73" t="n"/>
-      <c r="AI19" s="73" t="n"/>
-      <c r="AJ19" s="73" t="n"/>
-      <c r="AK19" s="73" t="n"/>
-      <c r="AL19" s="73" t="n"/>
-      <c r="AM19" s="73" t="n"/>
-      <c r="AN19" s="73" t="n"/>
-      <c r="AO19" s="73" t="n"/>
-      <c r="AP19" s="73" t="n"/>
-      <c r="AQ19" s="73" t="n"/>
-      <c r="AR19" s="73" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
       <c r="A20" s="75" t="n">
@@ -17052,35 +15966,6 @@
       <c r="M20" s="82" t="n"/>
       <c r="N20" s="82" t="n"/>
       <c r="O20" s="82" t="n"/>
-      <c r="P20" s="82" t="n"/>
-      <c r="Q20" s="82" t="n"/>
-      <c r="R20" s="82" t="n"/>
-      <c r="S20" s="82" t="n"/>
-      <c r="T20" s="82" t="n"/>
-      <c r="U20" s="82" t="n"/>
-      <c r="V20" s="82" t="n"/>
-      <c r="W20" s="82" t="n"/>
-      <c r="X20" s="82" t="n"/>
-      <c r="Y20" s="82" t="n"/>
-      <c r="Z20" s="82" t="n"/>
-      <c r="AA20" s="82" t="n"/>
-      <c r="AB20" s="82" t="n"/>
-      <c r="AC20" s="82" t="n"/>
-      <c r="AD20" s="82" t="n"/>
-      <c r="AE20" s="82" t="n"/>
-      <c r="AF20" s="82" t="n"/>
-      <c r="AG20" s="82" t="n"/>
-      <c r="AH20" s="82" t="n"/>
-      <c r="AI20" s="82" t="n"/>
-      <c r="AJ20" s="82" t="n"/>
-      <c r="AK20" s="82" t="n"/>
-      <c r="AL20" s="82" t="n"/>
-      <c r="AM20" s="82" t="n"/>
-      <c r="AN20" s="82" t="n"/>
-      <c r="AO20" s="82" t="n"/>
-      <c r="AP20" s="82" t="n"/>
-      <c r="AQ20" s="82" t="n"/>
-      <c r="AR20" s="82" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
       <c r="A21" s="66" t="n">
@@ -17124,35 +16009,6 @@
       <c r="M21" s="73" t="n"/>
       <c r="N21" s="73" t="n"/>
       <c r="O21" s="73" t="n"/>
-      <c r="P21" s="73" t="n"/>
-      <c r="Q21" s="73" t="n"/>
-      <c r="R21" s="73" t="n"/>
-      <c r="S21" s="73" t="n"/>
-      <c r="T21" s="73" t="n"/>
-      <c r="U21" s="73" t="n"/>
-      <c r="V21" s="73" t="n"/>
-      <c r="W21" s="73" t="n"/>
-      <c r="X21" s="73" t="n"/>
-      <c r="Y21" s="73" t="n"/>
-      <c r="Z21" s="73" t="n"/>
-      <c r="AA21" s="73" t="n"/>
-      <c r="AB21" s="73" t="n"/>
-      <c r="AC21" s="73" t="n"/>
-      <c r="AD21" s="73" t="n"/>
-      <c r="AE21" s="73" t="n"/>
-      <c r="AF21" s="73" t="n"/>
-      <c r="AG21" s="73" t="n"/>
-      <c r="AH21" s="73" t="n"/>
-      <c r="AI21" s="73" t="n"/>
-      <c r="AJ21" s="73" t="n"/>
-      <c r="AK21" s="73" t="n"/>
-      <c r="AL21" s="73" t="n"/>
-      <c r="AM21" s="73" t="n"/>
-      <c r="AN21" s="73" t="n"/>
-      <c r="AO21" s="73" t="n"/>
-      <c r="AP21" s="73" t="n"/>
-      <c r="AQ21" s="73" t="n"/>
-      <c r="AR21" s="73" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
       <c r="A22" s="75" t="n">
@@ -17196,35 +16052,6 @@
       <c r="M22" s="82" t="n"/>
       <c r="N22" s="82" t="n"/>
       <c r="O22" s="82" t="n"/>
-      <c r="P22" s="82" t="n"/>
-      <c r="Q22" s="82" t="n"/>
-      <c r="R22" s="82" t="n"/>
-      <c r="S22" s="82" t="n"/>
-      <c r="T22" s="82" t="n"/>
-      <c r="U22" s="82" t="n"/>
-      <c r="V22" s="82" t="n"/>
-      <c r="W22" s="82" t="n"/>
-      <c r="X22" s="82" t="n"/>
-      <c r="Y22" s="82" t="n"/>
-      <c r="Z22" s="82" t="n"/>
-      <c r="AA22" s="82" t="n"/>
-      <c r="AB22" s="82" t="n"/>
-      <c r="AC22" s="82" t="n"/>
-      <c r="AD22" s="82" t="n"/>
-      <c r="AE22" s="82" t="n"/>
-      <c r="AF22" s="82" t="n"/>
-      <c r="AG22" s="82" t="n"/>
-      <c r="AH22" s="82" t="n"/>
-      <c r="AI22" s="82" t="n"/>
-      <c r="AJ22" s="82" t="n"/>
-      <c r="AK22" s="82" t="n"/>
-      <c r="AL22" s="82" t="n"/>
-      <c r="AM22" s="82" t="n"/>
-      <c r="AN22" s="82" t="n"/>
-      <c r="AO22" s="82" t="n"/>
-      <c r="AP22" s="82" t="n"/>
-      <c r="AQ22" s="82" t="n"/>
-      <c r="AR22" s="82" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1">
       <c r="A23" s="66" t="n">
@@ -17268,35 +16095,6 @@
       <c r="M23" s="73" t="n"/>
       <c r="N23" s="73" t="n"/>
       <c r="O23" s="73" t="n"/>
-      <c r="P23" s="73" t="n"/>
-      <c r="Q23" s="73" t="n"/>
-      <c r="R23" s="73" t="n"/>
-      <c r="S23" s="73" t="n"/>
-      <c r="T23" s="73" t="n"/>
-      <c r="U23" s="73" t="n"/>
-      <c r="V23" s="73" t="n"/>
-      <c r="W23" s="73" t="n"/>
-      <c r="X23" s="73" t="n"/>
-      <c r="Y23" s="73" t="n"/>
-      <c r="Z23" s="73" t="n"/>
-      <c r="AA23" s="73" t="n"/>
-      <c r="AB23" s="73" t="n"/>
-      <c r="AC23" s="73" t="n"/>
-      <c r="AD23" s="73" t="n"/>
-      <c r="AE23" s="73" t="n"/>
-      <c r="AF23" s="73" t="n"/>
-      <c r="AG23" s="73" t="n"/>
-      <c r="AH23" s="73" t="n"/>
-      <c r="AI23" s="73" t="n"/>
-      <c r="AJ23" s="73" t="n"/>
-      <c r="AK23" s="73" t="n"/>
-      <c r="AL23" s="73" t="n"/>
-      <c r="AM23" s="73" t="n"/>
-      <c r="AN23" s="73" t="n"/>
-      <c r="AO23" s="73" t="n"/>
-      <c r="AP23" s="73" t="n"/>
-      <c r="AQ23" s="73" t="n"/>
-      <c r="AR23" s="73" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1">
       <c r="A24" s="75" t="n">
@@ -17340,35 +16138,6 @@
       <c r="M24" s="82" t="n"/>
       <c r="N24" s="82" t="n"/>
       <c r="O24" s="82" t="n"/>
-      <c r="P24" s="82" t="n"/>
-      <c r="Q24" s="82" t="n"/>
-      <c r="R24" s="82" t="n"/>
-      <c r="S24" s="82" t="n"/>
-      <c r="T24" s="82" t="n"/>
-      <c r="U24" s="82" t="n"/>
-      <c r="V24" s="82" t="n"/>
-      <c r="W24" s="82" t="n"/>
-      <c r="X24" s="82" t="n"/>
-      <c r="Y24" s="82" t="n"/>
-      <c r="Z24" s="82" t="n"/>
-      <c r="AA24" s="82" t="n"/>
-      <c r="AB24" s="82" t="n"/>
-      <c r="AC24" s="82" t="n"/>
-      <c r="AD24" s="82" t="n"/>
-      <c r="AE24" s="82" t="n"/>
-      <c r="AF24" s="82" t="n"/>
-      <c r="AG24" s="82" t="n"/>
-      <c r="AH24" s="82" t="n"/>
-      <c r="AI24" s="82" t="n"/>
-      <c r="AJ24" s="82" t="n"/>
-      <c r="AK24" s="82" t="n"/>
-      <c r="AL24" s="82" t="n"/>
-      <c r="AM24" s="82" t="n"/>
-      <c r="AN24" s="82" t="n"/>
-      <c r="AO24" s="82" t="n"/>
-      <c r="AP24" s="82" t="n"/>
-      <c r="AQ24" s="82" t="n"/>
-      <c r="AR24" s="82" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1">
       <c r="A25" s="66" t="n">
@@ -17412,35 +16181,6 @@
       <c r="M25" s="73" t="n"/>
       <c r="N25" s="73" t="n"/>
       <c r="O25" s="73" t="n"/>
-      <c r="P25" s="73" t="n"/>
-      <c r="Q25" s="73" t="n"/>
-      <c r="R25" s="73" t="n"/>
-      <c r="S25" s="73" t="n"/>
-      <c r="T25" s="73" t="n"/>
-      <c r="U25" s="73" t="n"/>
-      <c r="V25" s="73" t="n"/>
-      <c r="W25" s="73" t="n"/>
-      <c r="X25" s="73" t="n"/>
-      <c r="Y25" s="73" t="n"/>
-      <c r="Z25" s="73" t="n"/>
-      <c r="AA25" s="73" t="n"/>
-      <c r="AB25" s="73" t="n"/>
-      <c r="AC25" s="73" t="n"/>
-      <c r="AD25" s="73" t="n"/>
-      <c r="AE25" s="73" t="n"/>
-      <c r="AF25" s="73" t="n"/>
-      <c r="AG25" s="73" t="n"/>
-      <c r="AH25" s="73" t="n"/>
-      <c r="AI25" s="73" t="n"/>
-      <c r="AJ25" s="73" t="n"/>
-      <c r="AK25" s="73" t="n"/>
-      <c r="AL25" s="73" t="n"/>
-      <c r="AM25" s="73" t="n"/>
-      <c r="AN25" s="73" t="n"/>
-      <c r="AO25" s="73" t="n"/>
-      <c r="AP25" s="73" t="n"/>
-      <c r="AQ25" s="73" t="n"/>
-      <c r="AR25" s="73" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1">
       <c r="A26" s="75" t="n">
@@ -17484,35 +16224,6 @@
       <c r="M26" s="82" t="n"/>
       <c r="N26" s="82" t="n"/>
       <c r="O26" s="82" t="n"/>
-      <c r="P26" s="82" t="n"/>
-      <c r="Q26" s="82" t="n"/>
-      <c r="R26" s="82" t="n"/>
-      <c r="S26" s="82" t="n"/>
-      <c r="T26" s="82" t="n"/>
-      <c r="U26" s="82" t="n"/>
-      <c r="V26" s="82" t="n"/>
-      <c r="W26" s="82" t="n"/>
-      <c r="X26" s="82" t="n"/>
-      <c r="Y26" s="82" t="n"/>
-      <c r="Z26" s="82" t="n"/>
-      <c r="AA26" s="82" t="n"/>
-      <c r="AB26" s="82" t="n"/>
-      <c r="AC26" s="82" t="n"/>
-      <c r="AD26" s="82" t="n"/>
-      <c r="AE26" s="82" t="n"/>
-      <c r="AF26" s="82" t="n"/>
-      <c r="AG26" s="82" t="n"/>
-      <c r="AH26" s="82" t="n"/>
-      <c r="AI26" s="82" t="n"/>
-      <c r="AJ26" s="82" t="n"/>
-      <c r="AK26" s="82" t="n"/>
-      <c r="AL26" s="82" t="n"/>
-      <c r="AM26" s="82" t="n"/>
-      <c r="AN26" s="82" t="n"/>
-      <c r="AO26" s="82" t="n"/>
-      <c r="AP26" s="82" t="n"/>
-      <c r="AQ26" s="82" t="n"/>
-      <c r="AR26" s="82" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1">
       <c r="A27" s="66" t="n">
@@ -17556,35 +16267,6 @@
       <c r="M27" s="73" t="n"/>
       <c r="N27" s="73" t="n"/>
       <c r="O27" s="73" t="n"/>
-      <c r="P27" s="73" t="n"/>
-      <c r="Q27" s="73" t="n"/>
-      <c r="R27" s="73" t="n"/>
-      <c r="S27" s="73" t="n"/>
-      <c r="T27" s="73" t="n"/>
-      <c r="U27" s="73" t="n"/>
-      <c r="V27" s="73" t="n"/>
-      <c r="W27" s="73" t="n"/>
-      <c r="X27" s="73" t="n"/>
-      <c r="Y27" s="73" t="n"/>
-      <c r="Z27" s="73" t="n"/>
-      <c r="AA27" s="73" t="n"/>
-      <c r="AB27" s="73" t="n"/>
-      <c r="AC27" s="73" t="n"/>
-      <c r="AD27" s="73" t="n"/>
-      <c r="AE27" s="73" t="n"/>
-      <c r="AF27" s="73" t="n"/>
-      <c r="AG27" s="73" t="n"/>
-      <c r="AH27" s="73" t="n"/>
-      <c r="AI27" s="73" t="n"/>
-      <c r="AJ27" s="73" t="n"/>
-      <c r="AK27" s="73" t="n"/>
-      <c r="AL27" s="73" t="n"/>
-      <c r="AM27" s="73" t="n"/>
-      <c r="AN27" s="73" t="n"/>
-      <c r="AO27" s="73" t="n"/>
-      <c r="AP27" s="73" t="n"/>
-      <c r="AQ27" s="73" t="n"/>
-      <c r="AR27" s="73" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1">
       <c r="A28" s="75" t="n">
@@ -17628,35 +16310,6 @@
       <c r="M28" s="82" t="n"/>
       <c r="N28" s="82" t="n"/>
       <c r="O28" s="82" t="n"/>
-      <c r="P28" s="82" t="n"/>
-      <c r="Q28" s="82" t="n"/>
-      <c r="R28" s="82" t="n"/>
-      <c r="S28" s="82" t="n"/>
-      <c r="T28" s="82" t="n"/>
-      <c r="U28" s="82" t="n"/>
-      <c r="V28" s="82" t="n"/>
-      <c r="W28" s="82" t="n"/>
-      <c r="X28" s="82" t="n"/>
-      <c r="Y28" s="82" t="n"/>
-      <c r="Z28" s="82" t="n"/>
-      <c r="AA28" s="82" t="n"/>
-      <c r="AB28" s="82" t="n"/>
-      <c r="AC28" s="82" t="n"/>
-      <c r="AD28" s="82" t="n"/>
-      <c r="AE28" s="82" t="n"/>
-      <c r="AF28" s="82" t="n"/>
-      <c r="AG28" s="82" t="n"/>
-      <c r="AH28" s="82" t="n"/>
-      <c r="AI28" s="82" t="n"/>
-      <c r="AJ28" s="82" t="n"/>
-      <c r="AK28" s="82" t="n"/>
-      <c r="AL28" s="82" t="n"/>
-      <c r="AM28" s="82" t="n"/>
-      <c r="AN28" s="82" t="n"/>
-      <c r="AO28" s="82" t="n"/>
-      <c r="AP28" s="82" t="n"/>
-      <c r="AQ28" s="82" t="n"/>
-      <c r="AR28" s="82" t="n"/>
     </row>
     <row r="29" ht="22.05" customHeight="1">
       <c r="A29" s="66" t="n">
@@ -17700,35 +16353,6 @@
       <c r="M29" s="73" t="n"/>
       <c r="N29" s="73" t="n"/>
       <c r="O29" s="73" t="n"/>
-      <c r="P29" s="73" t="n"/>
-      <c r="Q29" s="73" t="n"/>
-      <c r="R29" s="73" t="n"/>
-      <c r="S29" s="73" t="n"/>
-      <c r="T29" s="73" t="n"/>
-      <c r="U29" s="73" t="n"/>
-      <c r="V29" s="73" t="n"/>
-      <c r="W29" s="73" t="n"/>
-      <c r="X29" s="73" t="n"/>
-      <c r="Y29" s="73" t="n"/>
-      <c r="Z29" s="73" t="n"/>
-      <c r="AA29" s="73" t="n"/>
-      <c r="AB29" s="73" t="n"/>
-      <c r="AC29" s="73" t="n"/>
-      <c r="AD29" s="73" t="n"/>
-      <c r="AE29" s="73" t="n"/>
-      <c r="AF29" s="73" t="n"/>
-      <c r="AG29" s="73" t="n"/>
-      <c r="AH29" s="73" t="n"/>
-      <c r="AI29" s="73" t="n"/>
-      <c r="AJ29" s="73" t="n"/>
-      <c r="AK29" s="73" t="n"/>
-      <c r="AL29" s="73" t="n"/>
-      <c r="AM29" s="73" t="n"/>
-      <c r="AN29" s="73" t="n"/>
-      <c r="AO29" s="73" t="n"/>
-      <c r="AP29" s="73" t="n"/>
-      <c r="AQ29" s="73" t="n"/>
-      <c r="AR29" s="73" t="n"/>
     </row>
     <row r="30" ht="22.05" customHeight="1">
       <c r="A30" s="75" t="n">
@@ -17772,35 +16396,6 @@
       <c r="M30" s="82" t="n"/>
       <c r="N30" s="82" t="n"/>
       <c r="O30" s="82" t="n"/>
-      <c r="P30" s="82" t="n"/>
-      <c r="Q30" s="82" t="n"/>
-      <c r="R30" s="82" t="n"/>
-      <c r="S30" s="82" t="n"/>
-      <c r="T30" s="82" t="n"/>
-      <c r="U30" s="82" t="n"/>
-      <c r="V30" s="82" t="n"/>
-      <c r="W30" s="82" t="n"/>
-      <c r="X30" s="82" t="n"/>
-      <c r="Y30" s="82" t="n"/>
-      <c r="Z30" s="82" t="n"/>
-      <c r="AA30" s="82" t="n"/>
-      <c r="AB30" s="82" t="n"/>
-      <c r="AC30" s="82" t="n"/>
-      <c r="AD30" s="82" t="n"/>
-      <c r="AE30" s="82" t="n"/>
-      <c r="AF30" s="82" t="n"/>
-      <c r="AG30" s="82" t="n"/>
-      <c r="AH30" s="82" t="n"/>
-      <c r="AI30" s="82" t="n"/>
-      <c r="AJ30" s="82" t="n"/>
-      <c r="AK30" s="82" t="n"/>
-      <c r="AL30" s="82" t="n"/>
-      <c r="AM30" s="82" t="n"/>
-      <c r="AN30" s="82" t="n"/>
-      <c r="AO30" s="82" t="n"/>
-      <c r="AP30" s="82" t="n"/>
-      <c r="AQ30" s="82" t="n"/>
-      <c r="AR30" s="82" t="n"/>
     </row>
     <row r="31" ht="22.05" customHeight="1">
       <c r="A31" s="66" t="n">
@@ -17844,35 +16439,6 @@
       <c r="M31" s="73" t="n"/>
       <c r="N31" s="73" t="n"/>
       <c r="O31" s="73" t="n"/>
-      <c r="P31" s="73" t="n"/>
-      <c r="Q31" s="73" t="n"/>
-      <c r="R31" s="73" t="n"/>
-      <c r="S31" s="73" t="n"/>
-      <c r="T31" s="73" t="n"/>
-      <c r="U31" s="73" t="n"/>
-      <c r="V31" s="73" t="n"/>
-      <c r="W31" s="73" t="n"/>
-      <c r="X31" s="73" t="n"/>
-      <c r="Y31" s="73" t="n"/>
-      <c r="Z31" s="73" t="n"/>
-      <c r="AA31" s="73" t="n"/>
-      <c r="AB31" s="73" t="n"/>
-      <c r="AC31" s="73" t="n"/>
-      <c r="AD31" s="73" t="n"/>
-      <c r="AE31" s="73" t="n"/>
-      <c r="AF31" s="73" t="n"/>
-      <c r="AG31" s="73" t="n"/>
-      <c r="AH31" s="73" t="n"/>
-      <c r="AI31" s="73" t="n"/>
-      <c r="AJ31" s="73" t="n"/>
-      <c r="AK31" s="73" t="n"/>
-      <c r="AL31" s="73" t="n"/>
-      <c r="AM31" s="73" t="n"/>
-      <c r="AN31" s="73" t="n"/>
-      <c r="AO31" s="73" t="n"/>
-      <c r="AP31" s="73" t="n"/>
-      <c r="AQ31" s="73" t="n"/>
-      <c r="AR31" s="73" t="n"/>
     </row>
     <row r="32" ht="22.05" customHeight="1">
       <c r="A32" s="75" t="n">
@@ -17916,35 +16482,6 @@
       <c r="M32" s="82" t="n"/>
       <c r="N32" s="82" t="n"/>
       <c r="O32" s="82" t="n"/>
-      <c r="P32" s="82" t="n"/>
-      <c r="Q32" s="82" t="n"/>
-      <c r="R32" s="82" t="n"/>
-      <c r="S32" s="82" t="n"/>
-      <c r="T32" s="82" t="n"/>
-      <c r="U32" s="82" t="n"/>
-      <c r="V32" s="82" t="n"/>
-      <c r="W32" s="82" t="n"/>
-      <c r="X32" s="82" t="n"/>
-      <c r="Y32" s="82" t="n"/>
-      <c r="Z32" s="82" t="n"/>
-      <c r="AA32" s="82" t="n"/>
-      <c r="AB32" s="82" t="n"/>
-      <c r="AC32" s="82" t="n"/>
-      <c r="AD32" s="82" t="n"/>
-      <c r="AE32" s="82" t="n"/>
-      <c r="AF32" s="82" t="n"/>
-      <c r="AG32" s="82" t="n"/>
-      <c r="AH32" s="82" t="n"/>
-      <c r="AI32" s="82" t="n"/>
-      <c r="AJ32" s="82" t="n"/>
-      <c r="AK32" s="82" t="n"/>
-      <c r="AL32" s="82" t="n"/>
-      <c r="AM32" s="82" t="n"/>
-      <c r="AN32" s="82" t="n"/>
-      <c r="AO32" s="82" t="n"/>
-      <c r="AP32" s="82" t="n"/>
-      <c r="AQ32" s="82" t="n"/>
-      <c r="AR32" s="82" t="n"/>
     </row>
     <row r="33" ht="22.05" customHeight="1">
       <c r="A33" s="66" t="n">
@@ -17988,35 +16525,6 @@
       <c r="M33" s="73" t="n"/>
       <c r="N33" s="73" t="n"/>
       <c r="O33" s="73" t="n"/>
-      <c r="P33" s="73" t="n"/>
-      <c r="Q33" s="73" t="n"/>
-      <c r="R33" s="73" t="n"/>
-      <c r="S33" s="73" t="n"/>
-      <c r="T33" s="73" t="n"/>
-      <c r="U33" s="73" t="n"/>
-      <c r="V33" s="73" t="n"/>
-      <c r="W33" s="73" t="n"/>
-      <c r="X33" s="73" t="n"/>
-      <c r="Y33" s="73" t="n"/>
-      <c r="Z33" s="73" t="n"/>
-      <c r="AA33" s="73" t="n"/>
-      <c r="AB33" s="73" t="n"/>
-      <c r="AC33" s="73" t="n"/>
-      <c r="AD33" s="73" t="n"/>
-      <c r="AE33" s="73" t="n"/>
-      <c r="AF33" s="73" t="n"/>
-      <c r="AG33" s="73" t="n"/>
-      <c r="AH33" s="73" t="n"/>
-      <c r="AI33" s="73" t="n"/>
-      <c r="AJ33" s="73" t="n"/>
-      <c r="AK33" s="73" t="n"/>
-      <c r="AL33" s="73" t="n"/>
-      <c r="AM33" s="73" t="n"/>
-      <c r="AN33" s="73" t="n"/>
-      <c r="AO33" s="73" t="n"/>
-      <c r="AP33" s="73" t="n"/>
-      <c r="AQ33" s="73" t="n"/>
-      <c r="AR33" s="73" t="n"/>
     </row>
     <row r="34" ht="22.05" customHeight="1">
       <c r="A34" s="75" t="n">
@@ -18060,35 +16568,6 @@
       <c r="M34" s="82" t="n"/>
       <c r="N34" s="82" t="n"/>
       <c r="O34" s="82" t="n"/>
-      <c r="P34" s="82" t="n"/>
-      <c r="Q34" s="82" t="n"/>
-      <c r="R34" s="82" t="n"/>
-      <c r="S34" s="82" t="n"/>
-      <c r="T34" s="82" t="n"/>
-      <c r="U34" s="82" t="n"/>
-      <c r="V34" s="82" t="n"/>
-      <c r="W34" s="82" t="n"/>
-      <c r="X34" s="82" t="n"/>
-      <c r="Y34" s="82" t="n"/>
-      <c r="Z34" s="82" t="n"/>
-      <c r="AA34" s="82" t="n"/>
-      <c r="AB34" s="82" t="n"/>
-      <c r="AC34" s="82" t="n"/>
-      <c r="AD34" s="82" t="n"/>
-      <c r="AE34" s="82" t="n"/>
-      <c r="AF34" s="82" t="n"/>
-      <c r="AG34" s="82" t="n"/>
-      <c r="AH34" s="82" t="n"/>
-      <c r="AI34" s="82" t="n"/>
-      <c r="AJ34" s="82" t="n"/>
-      <c r="AK34" s="82" t="n"/>
-      <c r="AL34" s="82" t="n"/>
-      <c r="AM34" s="82" t="n"/>
-      <c r="AN34" s="82" t="n"/>
-      <c r="AO34" s="82" t="n"/>
-      <c r="AP34" s="82" t="n"/>
-      <c r="AQ34" s="82" t="n"/>
-      <c r="AR34" s="82" t="n"/>
     </row>
     <row r="35" ht="22.05" customHeight="1">
       <c r="A35" s="66" t="n">
@@ -18132,35 +16611,6 @@
       <c r="M35" s="73" t="n"/>
       <c r="N35" s="73" t="n"/>
       <c r="O35" s="73" t="n"/>
-      <c r="P35" s="73" t="n"/>
-      <c r="Q35" s="73" t="n"/>
-      <c r="R35" s="73" t="n"/>
-      <c r="S35" s="73" t="n"/>
-      <c r="T35" s="73" t="n"/>
-      <c r="U35" s="73" t="n"/>
-      <c r="V35" s="73" t="n"/>
-      <c r="W35" s="73" t="n"/>
-      <c r="X35" s="73" t="n"/>
-      <c r="Y35" s="73" t="n"/>
-      <c r="Z35" s="73" t="n"/>
-      <c r="AA35" s="73" t="n"/>
-      <c r="AB35" s="73" t="n"/>
-      <c r="AC35" s="73" t="n"/>
-      <c r="AD35" s="73" t="n"/>
-      <c r="AE35" s="73" t="n"/>
-      <c r="AF35" s="73" t="n"/>
-      <c r="AG35" s="73" t="n"/>
-      <c r="AH35" s="73" t="n"/>
-      <c r="AI35" s="73" t="n"/>
-      <c r="AJ35" s="73" t="n"/>
-      <c r="AK35" s="73" t="n"/>
-      <c r="AL35" s="73" t="n"/>
-      <c r="AM35" s="73" t="n"/>
-      <c r="AN35" s="73" t="n"/>
-      <c r="AO35" s="73" t="n"/>
-      <c r="AP35" s="73" t="n"/>
-      <c r="AQ35" s="73" t="n"/>
-      <c r="AR35" s="73" t="n"/>
     </row>
     <row r="36" ht="22.05" customHeight="1">
       <c r="A36" s="75" t="n">
@@ -18204,35 +16654,6 @@
       <c r="M36" s="82" t="n"/>
       <c r="N36" s="82" t="n"/>
       <c r="O36" s="82" t="n"/>
-      <c r="P36" s="82" t="n"/>
-      <c r="Q36" s="82" t="n"/>
-      <c r="R36" s="82" t="n"/>
-      <c r="S36" s="82" t="n"/>
-      <c r="T36" s="82" t="n"/>
-      <c r="U36" s="82" t="n"/>
-      <c r="V36" s="82" t="n"/>
-      <c r="W36" s="82" t="n"/>
-      <c r="X36" s="82" t="n"/>
-      <c r="Y36" s="82" t="n"/>
-      <c r="Z36" s="82" t="n"/>
-      <c r="AA36" s="82" t="n"/>
-      <c r="AB36" s="82" t="n"/>
-      <c r="AC36" s="82" t="n"/>
-      <c r="AD36" s="82" t="n"/>
-      <c r="AE36" s="82" t="n"/>
-      <c r="AF36" s="82" t="n"/>
-      <c r="AG36" s="82" t="n"/>
-      <c r="AH36" s="82" t="n"/>
-      <c r="AI36" s="82" t="n"/>
-      <c r="AJ36" s="82" t="n"/>
-      <c r="AK36" s="82" t="n"/>
-      <c r="AL36" s="82" t="n"/>
-      <c r="AM36" s="82" t="n"/>
-      <c r="AN36" s="82" t="n"/>
-      <c r="AO36" s="82" t="n"/>
-      <c r="AP36" s="82" t="n"/>
-      <c r="AQ36" s="82" t="n"/>
-      <c r="AR36" s="82" t="n"/>
     </row>
     <row r="37" ht="22.05" customHeight="1">
       <c r="A37" s="66" t="n">
@@ -18276,35 +16697,6 @@
       <c r="M37" s="73" t="n"/>
       <c r="N37" s="73" t="n"/>
       <c r="O37" s="73" t="n"/>
-      <c r="P37" s="73" t="n"/>
-      <c r="Q37" s="73" t="n"/>
-      <c r="R37" s="73" t="n"/>
-      <c r="S37" s="73" t="n"/>
-      <c r="T37" s="73" t="n"/>
-      <c r="U37" s="73" t="n"/>
-      <c r="V37" s="73" t="n"/>
-      <c r="W37" s="73" t="n"/>
-      <c r="X37" s="73" t="n"/>
-      <c r="Y37" s="73" t="n"/>
-      <c r="Z37" s="73" t="n"/>
-      <c r="AA37" s="73" t="n"/>
-      <c r="AB37" s="73" t="n"/>
-      <c r="AC37" s="73" t="n"/>
-      <c r="AD37" s="73" t="n"/>
-      <c r="AE37" s="73" t="n"/>
-      <c r="AF37" s="73" t="n"/>
-      <c r="AG37" s="73" t="n"/>
-      <c r="AH37" s="73" t="n"/>
-      <c r="AI37" s="73" t="n"/>
-      <c r="AJ37" s="73" t="n"/>
-      <c r="AK37" s="73" t="n"/>
-      <c r="AL37" s="73" t="n"/>
-      <c r="AM37" s="73" t="n"/>
-      <c r="AN37" s="73" t="n"/>
-      <c r="AO37" s="73" t="n"/>
-      <c r="AP37" s="73" t="n"/>
-      <c r="AQ37" s="73" t="n"/>
-      <c r="AR37" s="73" t="n"/>
     </row>
     <row r="38" ht="22.05" customHeight="1">
       <c r="A38" s="75" t="n">
@@ -18348,35 +16740,6 @@
       <c r="M38" s="82" t="n"/>
       <c r="N38" s="82" t="n"/>
       <c r="O38" s="82" t="n"/>
-      <c r="P38" s="82" t="n"/>
-      <c r="Q38" s="82" t="n"/>
-      <c r="R38" s="82" t="n"/>
-      <c r="S38" s="82" t="n"/>
-      <c r="T38" s="82" t="n"/>
-      <c r="U38" s="82" t="n"/>
-      <c r="V38" s="82" t="n"/>
-      <c r="W38" s="82" t="n"/>
-      <c r="X38" s="82" t="n"/>
-      <c r="Y38" s="82" t="n"/>
-      <c r="Z38" s="82" t="n"/>
-      <c r="AA38" s="82" t="n"/>
-      <c r="AB38" s="82" t="n"/>
-      <c r="AC38" s="82" t="n"/>
-      <c r="AD38" s="82" t="n"/>
-      <c r="AE38" s="82" t="n"/>
-      <c r="AF38" s="82" t="n"/>
-      <c r="AG38" s="82" t="n"/>
-      <c r="AH38" s="82" t="n"/>
-      <c r="AI38" s="82" t="n"/>
-      <c r="AJ38" s="82" t="n"/>
-      <c r="AK38" s="82" t="n"/>
-      <c r="AL38" s="82" t="n"/>
-      <c r="AM38" s="82" t="n"/>
-      <c r="AN38" s="82" t="n"/>
-      <c r="AO38" s="82" t="n"/>
-      <c r="AP38" s="82" t="n"/>
-      <c r="AQ38" s="82" t="n"/>
-      <c r="AR38" s="82" t="n"/>
     </row>
     <row r="39" ht="22.05" customHeight="1">
       <c r="A39" s="66" t="n">
@@ -18420,35 +16783,6 @@
       <c r="M39" s="73" t="n"/>
       <c r="N39" s="73" t="n"/>
       <c r="O39" s="73" t="n"/>
-      <c r="P39" s="73" t="n"/>
-      <c r="Q39" s="73" t="n"/>
-      <c r="R39" s="73" t="n"/>
-      <c r="S39" s="73" t="n"/>
-      <c r="T39" s="73" t="n"/>
-      <c r="U39" s="73" t="n"/>
-      <c r="V39" s="73" t="n"/>
-      <c r="W39" s="73" t="n"/>
-      <c r="X39" s="73" t="n"/>
-      <c r="Y39" s="73" t="n"/>
-      <c r="Z39" s="73" t="n"/>
-      <c r="AA39" s="73" t="n"/>
-      <c r="AB39" s="73" t="n"/>
-      <c r="AC39" s="73" t="n"/>
-      <c r="AD39" s="73" t="n"/>
-      <c r="AE39" s="73" t="n"/>
-      <c r="AF39" s="73" t="n"/>
-      <c r="AG39" s="73" t="n"/>
-      <c r="AH39" s="73" t="n"/>
-      <c r="AI39" s="73" t="n"/>
-      <c r="AJ39" s="73" t="n"/>
-      <c r="AK39" s="73" t="n"/>
-      <c r="AL39" s="73" t="n"/>
-      <c r="AM39" s="73" t="n"/>
-      <c r="AN39" s="73" t="n"/>
-      <c r="AO39" s="73" t="n"/>
-      <c r="AP39" s="73" t="n"/>
-      <c r="AQ39" s="73" t="n"/>
-      <c r="AR39" s="73" t="n"/>
     </row>
     <row r="40" ht="22.05" customHeight="1">
       <c r="A40" s="75" t="n">
@@ -18492,35 +16826,6 @@
       <c r="M40" s="82" t="n"/>
       <c r="N40" s="82" t="n"/>
       <c r="O40" s="82" t="n"/>
-      <c r="P40" s="82" t="n"/>
-      <c r="Q40" s="82" t="n"/>
-      <c r="R40" s="82" t="n"/>
-      <c r="S40" s="82" t="n"/>
-      <c r="T40" s="82" t="n"/>
-      <c r="U40" s="82" t="n"/>
-      <c r="V40" s="82" t="n"/>
-      <c r="W40" s="82" t="n"/>
-      <c r="X40" s="82" t="n"/>
-      <c r="Y40" s="82" t="n"/>
-      <c r="Z40" s="82" t="n"/>
-      <c r="AA40" s="82" t="n"/>
-      <c r="AB40" s="82" t="n"/>
-      <c r="AC40" s="82" t="n"/>
-      <c r="AD40" s="82" t="n"/>
-      <c r="AE40" s="82" t="n"/>
-      <c r="AF40" s="82" t="n"/>
-      <c r="AG40" s="82" t="n"/>
-      <c r="AH40" s="82" t="n"/>
-      <c r="AI40" s="82" t="n"/>
-      <c r="AJ40" s="82" t="n"/>
-      <c r="AK40" s="82" t="n"/>
-      <c r="AL40" s="82" t="n"/>
-      <c r="AM40" s="82" t="n"/>
-      <c r="AN40" s="82" t="n"/>
-      <c r="AO40" s="82" t="n"/>
-      <c r="AP40" s="82" t="n"/>
-      <c r="AQ40" s="82" t="n"/>
-      <c r="AR40" s="82" t="n"/>
     </row>
     <row r="41" ht="22.05" customHeight="1">
       <c r="A41" s="66" t="n">
@@ -18564,35 +16869,6 @@
       <c r="M41" s="73" t="n"/>
       <c r="N41" s="73" t="n"/>
       <c r="O41" s="73" t="n"/>
-      <c r="P41" s="73" t="n"/>
-      <c r="Q41" s="73" t="n"/>
-      <c r="R41" s="73" t="n"/>
-      <c r="S41" s="73" t="n"/>
-      <c r="T41" s="73" t="n"/>
-      <c r="U41" s="73" t="n"/>
-      <c r="V41" s="73" t="n"/>
-      <c r="W41" s="73" t="n"/>
-      <c r="X41" s="73" t="n"/>
-      <c r="Y41" s="73" t="n"/>
-      <c r="Z41" s="73" t="n"/>
-      <c r="AA41" s="73" t="n"/>
-      <c r="AB41" s="73" t="n"/>
-      <c r="AC41" s="73" t="n"/>
-      <c r="AD41" s="73" t="n"/>
-      <c r="AE41" s="73" t="n"/>
-      <c r="AF41" s="73" t="n"/>
-      <c r="AG41" s="73" t="n"/>
-      <c r="AH41" s="73" t="n"/>
-      <c r="AI41" s="73" t="n"/>
-      <c r="AJ41" s="73" t="n"/>
-      <c r="AK41" s="73" t="n"/>
-      <c r="AL41" s="73" t="n"/>
-      <c r="AM41" s="73" t="n"/>
-      <c r="AN41" s="73" t="n"/>
-      <c r="AO41" s="73" t="n"/>
-      <c r="AP41" s="73" t="n"/>
-      <c r="AQ41" s="73" t="n"/>
-      <c r="AR41" s="73" t="n"/>
     </row>
     <row r="42" ht="22.05" customHeight="1">
       <c r="A42" s="75" t="n">
@@ -18636,35 +16912,6 @@
       <c r="M42" s="82" t="n"/>
       <c r="N42" s="82" t="n"/>
       <c r="O42" s="82" t="n"/>
-      <c r="P42" s="82" t="n"/>
-      <c r="Q42" s="82" t="n"/>
-      <c r="R42" s="82" t="n"/>
-      <c r="S42" s="82" t="n"/>
-      <c r="T42" s="82" t="n"/>
-      <c r="U42" s="82" t="n"/>
-      <c r="V42" s="82" t="n"/>
-      <c r="W42" s="82" t="n"/>
-      <c r="X42" s="82" t="n"/>
-      <c r="Y42" s="82" t="n"/>
-      <c r="Z42" s="82" t="n"/>
-      <c r="AA42" s="82" t="n"/>
-      <c r="AB42" s="82" t="n"/>
-      <c r="AC42" s="82" t="n"/>
-      <c r="AD42" s="82" t="n"/>
-      <c r="AE42" s="82" t="n"/>
-      <c r="AF42" s="82" t="n"/>
-      <c r="AG42" s="82" t="n"/>
-      <c r="AH42" s="82" t="n"/>
-      <c r="AI42" s="82" t="n"/>
-      <c r="AJ42" s="82" t="n"/>
-      <c r="AK42" s="82" t="n"/>
-      <c r="AL42" s="82" t="n"/>
-      <c r="AM42" s="82" t="n"/>
-      <c r="AN42" s="82" t="n"/>
-      <c r="AO42" s="82" t="n"/>
-      <c r="AP42" s="82" t="n"/>
-      <c r="AQ42" s="82" t="n"/>
-      <c r="AR42" s="82" t="n"/>
     </row>
     <row r="43" ht="22.05" customHeight="1">
       <c r="A43" s="66" t="n">
@@ -18708,35 +16955,6 @@
       <c r="M43" s="73" t="n"/>
       <c r="N43" s="73" t="n"/>
       <c r="O43" s="73" t="n"/>
-      <c r="P43" s="73" t="n"/>
-      <c r="Q43" s="73" t="n"/>
-      <c r="R43" s="73" t="n"/>
-      <c r="S43" s="73" t="n"/>
-      <c r="T43" s="73" t="n"/>
-      <c r="U43" s="73" t="n"/>
-      <c r="V43" s="73" t="n"/>
-      <c r="W43" s="73" t="n"/>
-      <c r="X43" s="73" t="n"/>
-      <c r="Y43" s="73" t="n"/>
-      <c r="Z43" s="73" t="n"/>
-      <c r="AA43" s="73" t="n"/>
-      <c r="AB43" s="73" t="n"/>
-      <c r="AC43" s="73" t="n"/>
-      <c r="AD43" s="73" t="n"/>
-      <c r="AE43" s="73" t="n"/>
-      <c r="AF43" s="73" t="n"/>
-      <c r="AG43" s="73" t="n"/>
-      <c r="AH43" s="73" t="n"/>
-      <c r="AI43" s="73" t="n"/>
-      <c r="AJ43" s="73" t="n"/>
-      <c r="AK43" s="73" t="n"/>
-      <c r="AL43" s="73" t="n"/>
-      <c r="AM43" s="73" t="n"/>
-      <c r="AN43" s="73" t="n"/>
-      <c r="AO43" s="73" t="n"/>
-      <c r="AP43" s="73" t="n"/>
-      <c r="AQ43" s="73" t="n"/>
-      <c r="AR43" s="73" t="n"/>
     </row>
     <row r="44" ht="22.05" customHeight="1">
       <c r="A44" s="75" t="n">
@@ -18780,35 +16998,6 @@
       <c r="M44" s="82" t="n"/>
       <c r="N44" s="82" t="n"/>
       <c r="O44" s="82" t="n"/>
-      <c r="P44" s="82" t="n"/>
-      <c r="Q44" s="82" t="n"/>
-      <c r="R44" s="82" t="n"/>
-      <c r="S44" s="82" t="n"/>
-      <c r="T44" s="82" t="n"/>
-      <c r="U44" s="82" t="n"/>
-      <c r="V44" s="82" t="n"/>
-      <c r="W44" s="82" t="n"/>
-      <c r="X44" s="82" t="n"/>
-      <c r="Y44" s="82" t="n"/>
-      <c r="Z44" s="82" t="n"/>
-      <c r="AA44" s="82" t="n"/>
-      <c r="AB44" s="82" t="n"/>
-      <c r="AC44" s="82" t="n"/>
-      <c r="AD44" s="82" t="n"/>
-      <c r="AE44" s="82" t="n"/>
-      <c r="AF44" s="82" t="n"/>
-      <c r="AG44" s="82" t="n"/>
-      <c r="AH44" s="82" t="n"/>
-      <c r="AI44" s="82" t="n"/>
-      <c r="AJ44" s="82" t="n"/>
-      <c r="AK44" s="82" t="n"/>
-      <c r="AL44" s="82" t="n"/>
-      <c r="AM44" s="82" t="n"/>
-      <c r="AN44" s="82" t="n"/>
-      <c r="AO44" s="82" t="n"/>
-      <c r="AP44" s="82" t="n"/>
-      <c r="AQ44" s="82" t="n"/>
-      <c r="AR44" s="82" t="n"/>
     </row>
     <row r="45" ht="22.05" customHeight="1">
       <c r="A45" s="66" t="n">
@@ -18852,35 +17041,6 @@
       <c r="M45" s="73" t="n"/>
       <c r="N45" s="73" t="n"/>
       <c r="O45" s="73" t="n"/>
-      <c r="P45" s="73" t="n"/>
-      <c r="Q45" s="73" t="n"/>
-      <c r="R45" s="73" t="n"/>
-      <c r="S45" s="73" t="n"/>
-      <c r="T45" s="73" t="n"/>
-      <c r="U45" s="73" t="n"/>
-      <c r="V45" s="73" t="n"/>
-      <c r="W45" s="73" t="n"/>
-      <c r="X45" s="73" t="n"/>
-      <c r="Y45" s="73" t="n"/>
-      <c r="Z45" s="73" t="n"/>
-      <c r="AA45" s="73" t="n"/>
-      <c r="AB45" s="73" t="n"/>
-      <c r="AC45" s="73" t="n"/>
-      <c r="AD45" s="73" t="n"/>
-      <c r="AE45" s="73" t="n"/>
-      <c r="AF45" s="73" t="n"/>
-      <c r="AG45" s="73" t="n"/>
-      <c r="AH45" s="73" t="n"/>
-      <c r="AI45" s="73" t="n"/>
-      <c r="AJ45" s="73" t="n"/>
-      <c r="AK45" s="73" t="n"/>
-      <c r="AL45" s="73" t="n"/>
-      <c r="AM45" s="73" t="n"/>
-      <c r="AN45" s="73" t="n"/>
-      <c r="AO45" s="73" t="n"/>
-      <c r="AP45" s="73" t="n"/>
-      <c r="AQ45" s="73" t="n"/>
-      <c r="AR45" s="73" t="n"/>
     </row>
     <row r="46" ht="22.05" customHeight="1">
       <c r="A46" s="75" t="n">
@@ -18924,35 +17084,6 @@
       <c r="M46" s="82" t="n"/>
       <c r="N46" s="82" t="n"/>
       <c r="O46" s="82" t="n"/>
-      <c r="P46" s="82" t="n"/>
-      <c r="Q46" s="82" t="n"/>
-      <c r="R46" s="82" t="n"/>
-      <c r="S46" s="82" t="n"/>
-      <c r="T46" s="82" t="n"/>
-      <c r="U46" s="82" t="n"/>
-      <c r="V46" s="82" t="n"/>
-      <c r="W46" s="82" t="n"/>
-      <c r="X46" s="82" t="n"/>
-      <c r="Y46" s="82" t="n"/>
-      <c r="Z46" s="82" t="n"/>
-      <c r="AA46" s="82" t="n"/>
-      <c r="AB46" s="82" t="n"/>
-      <c r="AC46" s="82" t="n"/>
-      <c r="AD46" s="82" t="n"/>
-      <c r="AE46" s="82" t="n"/>
-      <c r="AF46" s="82" t="n"/>
-      <c r="AG46" s="82" t="n"/>
-      <c r="AH46" s="82" t="n"/>
-      <c r="AI46" s="82" t="n"/>
-      <c r="AJ46" s="82" t="n"/>
-      <c r="AK46" s="82" t="n"/>
-      <c r="AL46" s="82" t="n"/>
-      <c r="AM46" s="82" t="n"/>
-      <c r="AN46" s="82" t="n"/>
-      <c r="AO46" s="82" t="n"/>
-      <c r="AP46" s="82" t="n"/>
-      <c r="AQ46" s="82" t="n"/>
-      <c r="AR46" s="82" t="n"/>
     </row>
     <row r="47" ht="22.05" customHeight="1">
       <c r="A47" s="66" t="n">
@@ -18996,35 +17127,6 @@
       <c r="M47" s="73" t="n"/>
       <c r="N47" s="73" t="n"/>
       <c r="O47" s="73" t="n"/>
-      <c r="P47" s="73" t="n"/>
-      <c r="Q47" s="73" t="n"/>
-      <c r="R47" s="73" t="n"/>
-      <c r="S47" s="73" t="n"/>
-      <c r="T47" s="73" t="n"/>
-      <c r="U47" s="73" t="n"/>
-      <c r="V47" s="73" t="n"/>
-      <c r="W47" s="73" t="n"/>
-      <c r="X47" s="73" t="n"/>
-      <c r="Y47" s="73" t="n"/>
-      <c r="Z47" s="73" t="n"/>
-      <c r="AA47" s="73" t="n"/>
-      <c r="AB47" s="73" t="n"/>
-      <c r="AC47" s="73" t="n"/>
-      <c r="AD47" s="73" t="n"/>
-      <c r="AE47" s="73" t="n"/>
-      <c r="AF47" s="73" t="n"/>
-      <c r="AG47" s="73" t="n"/>
-      <c r="AH47" s="73" t="n"/>
-      <c r="AI47" s="73" t="n"/>
-      <c r="AJ47" s="73" t="n"/>
-      <c r="AK47" s="73" t="n"/>
-      <c r="AL47" s="73" t="n"/>
-      <c r="AM47" s="73" t="n"/>
-      <c r="AN47" s="73" t="n"/>
-      <c r="AO47" s="73" t="n"/>
-      <c r="AP47" s="73" t="n"/>
-      <c r="AQ47" s="73" t="n"/>
-      <c r="AR47" s="73" t="n"/>
     </row>
     <row r="48" ht="22.05" customHeight="1">
       <c r="A48" s="75" t="n">
@@ -19068,35 +17170,6 @@
       <c r="M48" s="82" t="n"/>
       <c r="N48" s="82" t="n"/>
       <c r="O48" s="82" t="n"/>
-      <c r="P48" s="82" t="n"/>
-      <c r="Q48" s="82" t="n"/>
-      <c r="R48" s="82" t="n"/>
-      <c r="S48" s="82" t="n"/>
-      <c r="T48" s="82" t="n"/>
-      <c r="U48" s="82" t="n"/>
-      <c r="V48" s="82" t="n"/>
-      <c r="W48" s="82" t="n"/>
-      <c r="X48" s="82" t="n"/>
-      <c r="Y48" s="82" t="n"/>
-      <c r="Z48" s="82" t="n"/>
-      <c r="AA48" s="82" t="n"/>
-      <c r="AB48" s="82" t="n"/>
-      <c r="AC48" s="82" t="n"/>
-      <c r="AD48" s="82" t="n"/>
-      <c r="AE48" s="82" t="n"/>
-      <c r="AF48" s="82" t="n"/>
-      <c r="AG48" s="82" t="n"/>
-      <c r="AH48" s="82" t="n"/>
-      <c r="AI48" s="82" t="n"/>
-      <c r="AJ48" s="82" t="n"/>
-      <c r="AK48" s="82" t="n"/>
-      <c r="AL48" s="82" t="n"/>
-      <c r="AM48" s="82" t="n"/>
-      <c r="AN48" s="82" t="n"/>
-      <c r="AO48" s="82" t="n"/>
-      <c r="AP48" s="82" t="n"/>
-      <c r="AQ48" s="82" t="n"/>
-      <c r="AR48" s="82" t="n"/>
     </row>
     <row r="49" ht="22.05" customHeight="1">
       <c r="A49" s="66" t="n">
@@ -19140,35 +17213,6 @@
       <c r="M49" s="73" t="n"/>
       <c r="N49" s="73" t="n"/>
       <c r="O49" s="73" t="n"/>
-      <c r="P49" s="73" t="n"/>
-      <c r="Q49" s="73" t="n"/>
-      <c r="R49" s="73" t="n"/>
-      <c r="S49" s="73" t="n"/>
-      <c r="T49" s="73" t="n"/>
-      <c r="U49" s="73" t="n"/>
-      <c r="V49" s="73" t="n"/>
-      <c r="W49" s="73" t="n"/>
-      <c r="X49" s="73" t="n"/>
-      <c r="Y49" s="73" t="n"/>
-      <c r="Z49" s="73" t="n"/>
-      <c r="AA49" s="73" t="n"/>
-      <c r="AB49" s="73" t="n"/>
-      <c r="AC49" s="73" t="n"/>
-      <c r="AD49" s="73" t="n"/>
-      <c r="AE49" s="73" t="n"/>
-      <c r="AF49" s="73" t="n"/>
-      <c r="AG49" s="73" t="n"/>
-      <c r="AH49" s="73" t="n"/>
-      <c r="AI49" s="73" t="n"/>
-      <c r="AJ49" s="73" t="n"/>
-      <c r="AK49" s="73" t="n"/>
-      <c r="AL49" s="73" t="n"/>
-      <c r="AM49" s="73" t="n"/>
-      <c r="AN49" s="73" t="n"/>
-      <c r="AO49" s="73" t="n"/>
-      <c r="AP49" s="73" t="n"/>
-      <c r="AQ49" s="73" t="n"/>
-      <c r="AR49" s="73" t="n"/>
     </row>
     <row r="50" ht="22.05" customHeight="1">
       <c r="A50" s="75" t="n">
@@ -19212,35 +17256,6 @@
       <c r="M50" s="82" t="n"/>
       <c r="N50" s="82" t="n"/>
       <c r="O50" s="82" t="n"/>
-      <c r="P50" s="82" t="n"/>
-      <c r="Q50" s="82" t="n"/>
-      <c r="R50" s="82" t="n"/>
-      <c r="S50" s="82" t="n"/>
-      <c r="T50" s="82" t="n"/>
-      <c r="U50" s="82" t="n"/>
-      <c r="V50" s="82" t="n"/>
-      <c r="W50" s="82" t="n"/>
-      <c r="X50" s="82" t="n"/>
-      <c r="Y50" s="82" t="n"/>
-      <c r="Z50" s="82" t="n"/>
-      <c r="AA50" s="82" t="n"/>
-      <c r="AB50" s="82" t="n"/>
-      <c r="AC50" s="82" t="n"/>
-      <c r="AD50" s="82" t="n"/>
-      <c r="AE50" s="82" t="n"/>
-      <c r="AF50" s="82" t="n"/>
-      <c r="AG50" s="82" t="n"/>
-      <c r="AH50" s="82" t="n"/>
-      <c r="AI50" s="82" t="n"/>
-      <c r="AJ50" s="82" t="n"/>
-      <c r="AK50" s="82" t="n"/>
-      <c r="AL50" s="82" t="n"/>
-      <c r="AM50" s="82" t="n"/>
-      <c r="AN50" s="82" t="n"/>
-      <c r="AO50" s="82" t="n"/>
-      <c r="AP50" s="82" t="n"/>
-      <c r="AQ50" s="82" t="n"/>
-      <c r="AR50" s="82" t="n"/>
     </row>
     <row r="51" ht="22.05" customHeight="1">
       <c r="A51" s="66" t="n">
@@ -19284,35 +17299,6 @@
       <c r="M51" s="73" t="n"/>
       <c r="N51" s="73" t="n"/>
       <c r="O51" s="73" t="n"/>
-      <c r="P51" s="73" t="n"/>
-      <c r="Q51" s="73" t="n"/>
-      <c r="R51" s="73" t="n"/>
-      <c r="S51" s="73" t="n"/>
-      <c r="T51" s="73" t="n"/>
-      <c r="U51" s="73" t="n"/>
-      <c r="V51" s="73" t="n"/>
-      <c r="W51" s="73" t="n"/>
-      <c r="X51" s="73" t="n"/>
-      <c r="Y51" s="73" t="n"/>
-      <c r="Z51" s="73" t="n"/>
-      <c r="AA51" s="73" t="n"/>
-      <c r="AB51" s="73" t="n"/>
-      <c r="AC51" s="73" t="n"/>
-      <c r="AD51" s="73" t="n"/>
-      <c r="AE51" s="73" t="n"/>
-      <c r="AF51" s="73" t="n"/>
-      <c r="AG51" s="73" t="n"/>
-      <c r="AH51" s="73" t="n"/>
-      <c r="AI51" s="73" t="n"/>
-      <c r="AJ51" s="73" t="n"/>
-      <c r="AK51" s="73" t="n"/>
-      <c r="AL51" s="73" t="n"/>
-      <c r="AM51" s="73" t="n"/>
-      <c r="AN51" s="73" t="n"/>
-      <c r="AO51" s="73" t="n"/>
-      <c r="AP51" s="73" t="n"/>
-      <c r="AQ51" s="73" t="n"/>
-      <c r="AR51" s="73" t="n"/>
     </row>
     <row r="52" ht="22.05" customHeight="1">
       <c r="A52" s="75" t="n">
@@ -19356,35 +17342,6 @@
       <c r="M52" s="82" t="n"/>
       <c r="N52" s="82" t="n"/>
       <c r="O52" s="82" t="n"/>
-      <c r="P52" s="82" t="n"/>
-      <c r="Q52" s="82" t="n"/>
-      <c r="R52" s="82" t="n"/>
-      <c r="S52" s="82" t="n"/>
-      <c r="T52" s="82" t="n"/>
-      <c r="U52" s="82" t="n"/>
-      <c r="V52" s="82" t="n"/>
-      <c r="W52" s="82" t="n"/>
-      <c r="X52" s="82" t="n"/>
-      <c r="Y52" s="82" t="n"/>
-      <c r="Z52" s="82" t="n"/>
-      <c r="AA52" s="82" t="n"/>
-      <c r="AB52" s="82" t="n"/>
-      <c r="AC52" s="82" t="n"/>
-      <c r="AD52" s="82" t="n"/>
-      <c r="AE52" s="82" t="n"/>
-      <c r="AF52" s="82" t="n"/>
-      <c r="AG52" s="82" t="n"/>
-      <c r="AH52" s="82" t="n"/>
-      <c r="AI52" s="82" t="n"/>
-      <c r="AJ52" s="82" t="n"/>
-      <c r="AK52" s="82" t="n"/>
-      <c r="AL52" s="82" t="n"/>
-      <c r="AM52" s="82" t="n"/>
-      <c r="AN52" s="82" t="n"/>
-      <c r="AO52" s="82" t="n"/>
-      <c r="AP52" s="82" t="n"/>
-      <c r="AQ52" s="82" t="n"/>
-      <c r="AR52" s="82" t="n"/>
     </row>
     <row r="53" ht="22.05" customHeight="1">
       <c r="A53" s="66" t="n">
@@ -19428,35 +17385,6 @@
       <c r="M53" s="73" t="n"/>
       <c r="N53" s="73" t="n"/>
       <c r="O53" s="73" t="n"/>
-      <c r="P53" s="73" t="n"/>
-      <c r="Q53" s="73" t="n"/>
-      <c r="R53" s="73" t="n"/>
-      <c r="S53" s="73" t="n"/>
-      <c r="T53" s="73" t="n"/>
-      <c r="U53" s="73" t="n"/>
-      <c r="V53" s="73" t="n"/>
-      <c r="W53" s="73" t="n"/>
-      <c r="X53" s="73" t="n"/>
-      <c r="Y53" s="73" t="n"/>
-      <c r="Z53" s="73" t="n"/>
-      <c r="AA53" s="73" t="n"/>
-      <c r="AB53" s="73" t="n"/>
-      <c r="AC53" s="73" t="n"/>
-      <c r="AD53" s="73" t="n"/>
-      <c r="AE53" s="73" t="n"/>
-      <c r="AF53" s="73" t="n"/>
-      <c r="AG53" s="73" t="n"/>
-      <c r="AH53" s="73" t="n"/>
-      <c r="AI53" s="73" t="n"/>
-      <c r="AJ53" s="73" t="n"/>
-      <c r="AK53" s="73" t="n"/>
-      <c r="AL53" s="73" t="n"/>
-      <c r="AM53" s="73" t="n"/>
-      <c r="AN53" s="73" t="n"/>
-      <c r="AO53" s="73" t="n"/>
-      <c r="AP53" s="73" t="n"/>
-      <c r="AQ53" s="73" t="n"/>
-      <c r="AR53" s="73" t="n"/>
     </row>
     <row r="54" ht="22.05" customHeight="1">
       <c r="A54" s="75" t="n">
@@ -19500,35 +17428,6 @@
       <c r="M54" s="82" t="n"/>
       <c r="N54" s="82" t="n"/>
       <c r="O54" s="82" t="n"/>
-      <c r="P54" s="82" t="n"/>
-      <c r="Q54" s="82" t="n"/>
-      <c r="R54" s="82" t="n"/>
-      <c r="S54" s="82" t="n"/>
-      <c r="T54" s="82" t="n"/>
-      <c r="U54" s="82" t="n"/>
-      <c r="V54" s="82" t="n"/>
-      <c r="W54" s="82" t="n"/>
-      <c r="X54" s="82" t="n"/>
-      <c r="Y54" s="82" t="n"/>
-      <c r="Z54" s="82" t="n"/>
-      <c r="AA54" s="82" t="n"/>
-      <c r="AB54" s="82" t="n"/>
-      <c r="AC54" s="82" t="n"/>
-      <c r="AD54" s="82" t="n"/>
-      <c r="AE54" s="82" t="n"/>
-      <c r="AF54" s="82" t="n"/>
-      <c r="AG54" s="82" t="n"/>
-      <c r="AH54" s="82" t="n"/>
-      <c r="AI54" s="82" t="n"/>
-      <c r="AJ54" s="82" t="n"/>
-      <c r="AK54" s="82" t="n"/>
-      <c r="AL54" s="82" t="n"/>
-      <c r="AM54" s="82" t="n"/>
-      <c r="AN54" s="82" t="n"/>
-      <c r="AO54" s="82" t="n"/>
-      <c r="AP54" s="82" t="n"/>
-      <c r="AQ54" s="82" t="n"/>
-      <c r="AR54" s="82" t="n"/>
     </row>
     <row r="55" ht="22.05" customHeight="1">
       <c r="A55" s="66" t="n">
@@ -19572,35 +17471,6 @@
       <c r="M55" s="73" t="n"/>
       <c r="N55" s="73" t="n"/>
       <c r="O55" s="73" t="n"/>
-      <c r="P55" s="73" t="n"/>
-      <c r="Q55" s="73" t="n"/>
-      <c r="R55" s="73" t="n"/>
-      <c r="S55" s="73" t="n"/>
-      <c r="T55" s="73" t="n"/>
-      <c r="U55" s="73" t="n"/>
-      <c r="V55" s="73" t="n"/>
-      <c r="W55" s="73" t="n"/>
-      <c r="X55" s="73" t="n"/>
-      <c r="Y55" s="73" t="n"/>
-      <c r="Z55" s="73" t="n"/>
-      <c r="AA55" s="73" t="n"/>
-      <c r="AB55" s="73" t="n"/>
-      <c r="AC55" s="73" t="n"/>
-      <c r="AD55" s="73" t="n"/>
-      <c r="AE55" s="73" t="n"/>
-      <c r="AF55" s="73" t="n"/>
-      <c r="AG55" s="73" t="n"/>
-      <c r="AH55" s="73" t="n"/>
-      <c r="AI55" s="73" t="n"/>
-      <c r="AJ55" s="73" t="n"/>
-      <c r="AK55" s="73" t="n"/>
-      <c r="AL55" s="73" t="n"/>
-      <c r="AM55" s="73" t="n"/>
-      <c r="AN55" s="73" t="n"/>
-      <c r="AO55" s="73" t="n"/>
-      <c r="AP55" s="73" t="n"/>
-      <c r="AQ55" s="73" t="n"/>
-      <c r="AR55" s="73" t="n"/>
     </row>
     <row r="56" ht="22.05" customHeight="1">
       <c r="A56" s="75" t="n">
@@ -19644,35 +17514,6 @@
       <c r="M56" s="82" t="n"/>
       <c r="N56" s="82" t="n"/>
       <c r="O56" s="82" t="n"/>
-      <c r="P56" s="82" t="n"/>
-      <c r="Q56" s="82" t="n"/>
-      <c r="R56" s="82" t="n"/>
-      <c r="S56" s="82" t="n"/>
-      <c r="T56" s="82" t="n"/>
-      <c r="U56" s="82" t="n"/>
-      <c r="V56" s="82" t="n"/>
-      <c r="W56" s="82" t="n"/>
-      <c r="X56" s="82" t="n"/>
-      <c r="Y56" s="82" t="n"/>
-      <c r="Z56" s="82" t="n"/>
-      <c r="AA56" s="82" t="n"/>
-      <c r="AB56" s="82" t="n"/>
-      <c r="AC56" s="82" t="n"/>
-      <c r="AD56" s="82" t="n"/>
-      <c r="AE56" s="82" t="n"/>
-      <c r="AF56" s="82" t="n"/>
-      <c r="AG56" s="82" t="n"/>
-      <c r="AH56" s="82" t="n"/>
-      <c r="AI56" s="82" t="n"/>
-      <c r="AJ56" s="82" t="n"/>
-      <c r="AK56" s="82" t="n"/>
-      <c r="AL56" s="82" t="n"/>
-      <c r="AM56" s="82" t="n"/>
-      <c r="AN56" s="82" t="n"/>
-      <c r="AO56" s="82" t="n"/>
-      <c r="AP56" s="82" t="n"/>
-      <c r="AQ56" s="82" t="n"/>
-      <c r="AR56" s="82" t="n"/>
     </row>
     <row r="57" ht="22.05" customHeight="1">
       <c r="A57" s="66" t="n">
@@ -19716,35 +17557,6 @@
       <c r="M57" s="73" t="n"/>
       <c r="N57" s="73" t="n"/>
       <c r="O57" s="73" t="n"/>
-      <c r="P57" s="73" t="n"/>
-      <c r="Q57" s="73" t="n"/>
-      <c r="R57" s="73" t="n"/>
-      <c r="S57" s="73" t="n"/>
-      <c r="T57" s="73" t="n"/>
-      <c r="U57" s="73" t="n"/>
-      <c r="V57" s="73" t="n"/>
-      <c r="W57" s="73" t="n"/>
-      <c r="X57" s="73" t="n"/>
-      <c r="Y57" s="73" t="n"/>
-      <c r="Z57" s="73" t="n"/>
-      <c r="AA57" s="73" t="n"/>
-      <c r="AB57" s="73" t="n"/>
-      <c r="AC57" s="73" t="n"/>
-      <c r="AD57" s="73" t="n"/>
-      <c r="AE57" s="73" t="n"/>
-      <c r="AF57" s="73" t="n"/>
-      <c r="AG57" s="73" t="n"/>
-      <c r="AH57" s="73" t="n"/>
-      <c r="AI57" s="73" t="n"/>
-      <c r="AJ57" s="73" t="n"/>
-      <c r="AK57" s="73" t="n"/>
-      <c r="AL57" s="73" t="n"/>
-      <c r="AM57" s="73" t="n"/>
-      <c r="AN57" s="73" t="n"/>
-      <c r="AO57" s="73" t="n"/>
-      <c r="AP57" s="73" t="n"/>
-      <c r="AQ57" s="73" t="n"/>
-      <c r="AR57" s="73" t="n"/>
     </row>
     <row r="58" ht="22.05" customHeight="1">
       <c r="A58" s="75" t="n">
@@ -19788,35 +17600,6 @@
       <c r="M58" s="82" t="n"/>
       <c r="N58" s="82" t="n"/>
       <c r="O58" s="82" t="n"/>
-      <c r="P58" s="82" t="n"/>
-      <c r="Q58" s="82" t="n"/>
-      <c r="R58" s="82" t="n"/>
-      <c r="S58" s="82" t="n"/>
-      <c r="T58" s="82" t="n"/>
-      <c r="U58" s="82" t="n"/>
-      <c r="V58" s="82" t="n"/>
-      <c r="W58" s="82" t="n"/>
-      <c r="X58" s="82" t="n"/>
-      <c r="Y58" s="82" t="n"/>
-      <c r="Z58" s="82" t="n"/>
-      <c r="AA58" s="82" t="n"/>
-      <c r="AB58" s="82" t="n"/>
-      <c r="AC58" s="82" t="n"/>
-      <c r="AD58" s="82" t="n"/>
-      <c r="AE58" s="82" t="n"/>
-      <c r="AF58" s="82" t="n"/>
-      <c r="AG58" s="82" t="n"/>
-      <c r="AH58" s="82" t="n"/>
-      <c r="AI58" s="82" t="n"/>
-      <c r="AJ58" s="82" t="n"/>
-      <c r="AK58" s="82" t="n"/>
-      <c r="AL58" s="82" t="n"/>
-      <c r="AM58" s="82" t="n"/>
-      <c r="AN58" s="82" t="n"/>
-      <c r="AO58" s="82" t="n"/>
-      <c r="AP58" s="82" t="n"/>
-      <c r="AQ58" s="82" t="n"/>
-      <c r="AR58" s="82" t="n"/>
     </row>
     <row r="59" ht="22.05" customHeight="1">
       <c r="A59" s="66" t="n">
@@ -19860,35 +17643,6 @@
       <c r="M59" s="73" t="n"/>
       <c r="N59" s="73" t="n"/>
       <c r="O59" s="73" t="n"/>
-      <c r="P59" s="73" t="n"/>
-      <c r="Q59" s="73" t="n"/>
-      <c r="R59" s="73" t="n"/>
-      <c r="S59" s="73" t="n"/>
-      <c r="T59" s="73" t="n"/>
-      <c r="U59" s="73" t="n"/>
-      <c r="V59" s="73" t="n"/>
-      <c r="W59" s="73" t="n"/>
-      <c r="X59" s="73" t="n"/>
-      <c r="Y59" s="73" t="n"/>
-      <c r="Z59" s="73" t="n"/>
-      <c r="AA59" s="73" t="n"/>
-      <c r="AB59" s="73" t="n"/>
-      <c r="AC59" s="73" t="n"/>
-      <c r="AD59" s="73" t="n"/>
-      <c r="AE59" s="73" t="n"/>
-      <c r="AF59" s="73" t="n"/>
-      <c r="AG59" s="73" t="n"/>
-      <c r="AH59" s="73" t="n"/>
-      <c r="AI59" s="73" t="n"/>
-      <c r="AJ59" s="73" t="n"/>
-      <c r="AK59" s="73" t="n"/>
-      <c r="AL59" s="73" t="n"/>
-      <c r="AM59" s="73" t="n"/>
-      <c r="AN59" s="73" t="n"/>
-      <c r="AO59" s="73" t="n"/>
-      <c r="AP59" s="73" t="n"/>
-      <c r="AQ59" s="73" t="n"/>
-      <c r="AR59" s="73" t="n"/>
     </row>
     <row r="60" ht="22.05" customHeight="1">
       <c r="A60" s="75" t="n">
@@ -19932,35 +17686,6 @@
       <c r="M60" s="82" t="n"/>
       <c r="N60" s="82" t="n"/>
       <c r="O60" s="82" t="n"/>
-      <c r="P60" s="82" t="n"/>
-      <c r="Q60" s="82" t="n"/>
-      <c r="R60" s="82" t="n"/>
-      <c r="S60" s="82" t="n"/>
-      <c r="T60" s="82" t="n"/>
-      <c r="U60" s="82" t="n"/>
-      <c r="V60" s="82" t="n"/>
-      <c r="W60" s="82" t="n"/>
-      <c r="X60" s="82" t="n"/>
-      <c r="Y60" s="82" t="n"/>
-      <c r="Z60" s="82" t="n"/>
-      <c r="AA60" s="82" t="n"/>
-      <c r="AB60" s="82" t="n"/>
-      <c r="AC60" s="82" t="n"/>
-      <c r="AD60" s="82" t="n"/>
-      <c r="AE60" s="82" t="n"/>
-      <c r="AF60" s="82" t="n"/>
-      <c r="AG60" s="82" t="n"/>
-      <c r="AH60" s="82" t="n"/>
-      <c r="AI60" s="82" t="n"/>
-      <c r="AJ60" s="82" t="n"/>
-      <c r="AK60" s="82" t="n"/>
-      <c r="AL60" s="82" t="n"/>
-      <c r="AM60" s="82" t="n"/>
-      <c r="AN60" s="82" t="n"/>
-      <c r="AO60" s="82" t="n"/>
-      <c r="AP60" s="82" t="n"/>
-      <c r="AQ60" s="82" t="n"/>
-      <c r="AR60" s="82" t="n"/>
     </row>
     <row r="61" ht="22.05" customHeight="1">
       <c r="A61" s="66" t="n">
@@ -20004,35 +17729,6 @@
       <c r="M61" s="73" t="n"/>
       <c r="N61" s="73" t="n"/>
       <c r="O61" s="73" t="n"/>
-      <c r="P61" s="73" t="n"/>
-      <c r="Q61" s="73" t="n"/>
-      <c r="R61" s="73" t="n"/>
-      <c r="S61" s="73" t="n"/>
-      <c r="T61" s="73" t="n"/>
-      <c r="U61" s="73" t="n"/>
-      <c r="V61" s="73" t="n"/>
-      <c r="W61" s="73" t="n"/>
-      <c r="X61" s="73" t="n"/>
-      <c r="Y61" s="73" t="n"/>
-      <c r="Z61" s="73" t="n"/>
-      <c r="AA61" s="73" t="n"/>
-      <c r="AB61" s="73" t="n"/>
-      <c r="AC61" s="73" t="n"/>
-      <c r="AD61" s="73" t="n"/>
-      <c r="AE61" s="73" t="n"/>
-      <c r="AF61" s="73" t="n"/>
-      <c r="AG61" s="73" t="n"/>
-      <c r="AH61" s="73" t="n"/>
-      <c r="AI61" s="73" t="n"/>
-      <c r="AJ61" s="73" t="n"/>
-      <c r="AK61" s="73" t="n"/>
-      <c r="AL61" s="73" t="n"/>
-      <c r="AM61" s="73" t="n"/>
-      <c r="AN61" s="73" t="n"/>
-      <c r="AO61" s="73" t="n"/>
-      <c r="AP61" s="73" t="n"/>
-      <c r="AQ61" s="73" t="n"/>
-      <c r="AR61" s="73" t="n"/>
     </row>
     <row r="62" ht="22.05" customHeight="1">
       <c r="A62" s="75" t="n">
@@ -20076,35 +17772,6 @@
       <c r="M62" s="82" t="n"/>
       <c r="N62" s="82" t="n"/>
       <c r="O62" s="82" t="n"/>
-      <c r="P62" s="82" t="n"/>
-      <c r="Q62" s="82" t="n"/>
-      <c r="R62" s="82" t="n"/>
-      <c r="S62" s="82" t="n"/>
-      <c r="T62" s="82" t="n"/>
-      <c r="U62" s="82" t="n"/>
-      <c r="V62" s="82" t="n"/>
-      <c r="W62" s="82" t="n"/>
-      <c r="X62" s="82" t="n"/>
-      <c r="Y62" s="82" t="n"/>
-      <c r="Z62" s="82" t="n"/>
-      <c r="AA62" s="82" t="n"/>
-      <c r="AB62" s="82" t="n"/>
-      <c r="AC62" s="82" t="n"/>
-      <c r="AD62" s="82" t="n"/>
-      <c r="AE62" s="82" t="n"/>
-      <c r="AF62" s="82" t="n"/>
-      <c r="AG62" s="82" t="n"/>
-      <c r="AH62" s="82" t="n"/>
-      <c r="AI62" s="82" t="n"/>
-      <c r="AJ62" s="82" t="n"/>
-      <c r="AK62" s="82" t="n"/>
-      <c r="AL62" s="82" t="n"/>
-      <c r="AM62" s="82" t="n"/>
-      <c r="AN62" s="82" t="n"/>
-      <c r="AO62" s="82" t="n"/>
-      <c r="AP62" s="82" t="n"/>
-      <c r="AQ62" s="82" t="n"/>
-      <c r="AR62" s="82" t="n"/>
     </row>
     <row r="63" ht="22.05" customHeight="1">
       <c r="A63" s="66" t="n">
@@ -20148,35 +17815,6 @@
       <c r="M63" s="73" t="n"/>
       <c r="N63" s="73" t="n"/>
       <c r="O63" s="73" t="n"/>
-      <c r="P63" s="73" t="n"/>
-      <c r="Q63" s="73" t="n"/>
-      <c r="R63" s="73" t="n"/>
-      <c r="S63" s="73" t="n"/>
-      <c r="T63" s="73" t="n"/>
-      <c r="U63" s="73" t="n"/>
-      <c r="V63" s="73" t="n"/>
-      <c r="W63" s="73" t="n"/>
-      <c r="X63" s="73" t="n"/>
-      <c r="Y63" s="73" t="n"/>
-      <c r="Z63" s="73" t="n"/>
-      <c r="AA63" s="73" t="n"/>
-      <c r="AB63" s="73" t="n"/>
-      <c r="AC63" s="73" t="n"/>
-      <c r="AD63" s="73" t="n"/>
-      <c r="AE63" s="73" t="n"/>
-      <c r="AF63" s="73" t="n"/>
-      <c r="AG63" s="73" t="n"/>
-      <c r="AH63" s="73" t="n"/>
-      <c r="AI63" s="73" t="n"/>
-      <c r="AJ63" s="73" t="n"/>
-      <c r="AK63" s="73" t="n"/>
-      <c r="AL63" s="73" t="n"/>
-      <c r="AM63" s="73" t="n"/>
-      <c r="AN63" s="73" t="n"/>
-      <c r="AO63" s="73" t="n"/>
-      <c r="AP63" s="73" t="n"/>
-      <c r="AQ63" s="73" t="n"/>
-      <c r="AR63" s="73" t="n"/>
     </row>
     <row r="64" ht="22.05" customHeight="1">
       <c r="A64" s="75" t="n">
@@ -20220,35 +17858,6 @@
       <c r="M64" s="82" t="n"/>
       <c r="N64" s="82" t="n"/>
       <c r="O64" s="82" t="n"/>
-      <c r="P64" s="82" t="n"/>
-      <c r="Q64" s="82" t="n"/>
-      <c r="R64" s="82" t="n"/>
-      <c r="S64" s="82" t="n"/>
-      <c r="T64" s="82" t="n"/>
-      <c r="U64" s="82" t="n"/>
-      <c r="V64" s="82" t="n"/>
-      <c r="W64" s="82" t="n"/>
-      <c r="X64" s="82" t="n"/>
-      <c r="Y64" s="82" t="n"/>
-      <c r="Z64" s="82" t="n"/>
-      <c r="AA64" s="82" t="n"/>
-      <c r="AB64" s="82" t="n"/>
-      <c r="AC64" s="82" t="n"/>
-      <c r="AD64" s="82" t="n"/>
-      <c r="AE64" s="82" t="n"/>
-      <c r="AF64" s="82" t="n"/>
-      <c r="AG64" s="82" t="n"/>
-      <c r="AH64" s="82" t="n"/>
-      <c r="AI64" s="82" t="n"/>
-      <c r="AJ64" s="82" t="n"/>
-      <c r="AK64" s="82" t="n"/>
-      <c r="AL64" s="82" t="n"/>
-      <c r="AM64" s="82" t="n"/>
-      <c r="AN64" s="82" t="n"/>
-      <c r="AO64" s="82" t="n"/>
-      <c r="AP64" s="82" t="n"/>
-      <c r="AQ64" s="82" t="n"/>
-      <c r="AR64" s="82" t="n"/>
     </row>
     <row r="65" ht="22.05" customHeight="1">
       <c r="A65" s="66" t="n">
@@ -20292,35 +17901,6 @@
       <c r="M65" s="73" t="n"/>
       <c r="N65" s="73" t="n"/>
       <c r="O65" s="73" t="n"/>
-      <c r="P65" s="73" t="n"/>
-      <c r="Q65" s="73" t="n"/>
-      <c r="R65" s="73" t="n"/>
-      <c r="S65" s="73" t="n"/>
-      <c r="T65" s="73" t="n"/>
-      <c r="U65" s="73" t="n"/>
-      <c r="V65" s="73" t="n"/>
-      <c r="W65" s="73" t="n"/>
-      <c r="X65" s="73" t="n"/>
-      <c r="Y65" s="73" t="n"/>
-      <c r="Z65" s="73" t="n"/>
-      <c r="AA65" s="73" t="n"/>
-      <c r="AB65" s="73" t="n"/>
-      <c r="AC65" s="73" t="n"/>
-      <c r="AD65" s="73" t="n"/>
-      <c r="AE65" s="73" t="n"/>
-      <c r="AF65" s="73" t="n"/>
-      <c r="AG65" s="73" t="n"/>
-      <c r="AH65" s="73" t="n"/>
-      <c r="AI65" s="73" t="n"/>
-      <c r="AJ65" s="73" t="n"/>
-      <c r="AK65" s="73" t="n"/>
-      <c r="AL65" s="73" t="n"/>
-      <c r="AM65" s="73" t="n"/>
-      <c r="AN65" s="73" t="n"/>
-      <c r="AO65" s="73" t="n"/>
-      <c r="AP65" s="73" t="n"/>
-      <c r="AQ65" s="73" t="n"/>
-      <c r="AR65" s="73" t="n"/>
     </row>
     <row r="66" ht="22.05" customHeight="1">
       <c r="A66" s="75" t="n">
@@ -20364,35 +17944,6 @@
       <c r="M66" s="82" t="n"/>
       <c r="N66" s="82" t="n"/>
       <c r="O66" s="82" t="n"/>
-      <c r="P66" s="82" t="n"/>
-      <c r="Q66" s="82" t="n"/>
-      <c r="R66" s="82" t="n"/>
-      <c r="S66" s="82" t="n"/>
-      <c r="T66" s="82" t="n"/>
-      <c r="U66" s="82" t="n"/>
-      <c r="V66" s="82" t="n"/>
-      <c r="W66" s="82" t="n"/>
-      <c r="X66" s="82" t="n"/>
-      <c r="Y66" s="82" t="n"/>
-      <c r="Z66" s="82" t="n"/>
-      <c r="AA66" s="82" t="n"/>
-      <c r="AB66" s="82" t="n"/>
-      <c r="AC66" s="82" t="n"/>
-      <c r="AD66" s="82" t="n"/>
-      <c r="AE66" s="82" t="n"/>
-      <c r="AF66" s="82" t="n"/>
-      <c r="AG66" s="82" t="n"/>
-      <c r="AH66" s="82" t="n"/>
-      <c r="AI66" s="82" t="n"/>
-      <c r="AJ66" s="82" t="n"/>
-      <c r="AK66" s="82" t="n"/>
-      <c r="AL66" s="82" t="n"/>
-      <c r="AM66" s="82" t="n"/>
-      <c r="AN66" s="82" t="n"/>
-      <c r="AO66" s="82" t="n"/>
-      <c r="AP66" s="82" t="n"/>
-      <c r="AQ66" s="82" t="n"/>
-      <c r="AR66" s="82" t="n"/>
     </row>
     <row r="67" ht="22.05" customHeight="1">
       <c r="A67" s="66" t="n">
@@ -20436,35 +17987,6 @@
       <c r="M67" s="73" t="n"/>
       <c r="N67" s="73" t="n"/>
       <c r="O67" s="73" t="n"/>
-      <c r="P67" s="73" t="n"/>
-      <c r="Q67" s="73" t="n"/>
-      <c r="R67" s="73" t="n"/>
-      <c r="S67" s="73" t="n"/>
-      <c r="T67" s="73" t="n"/>
-      <c r="U67" s="73" t="n"/>
-      <c r="V67" s="73" t="n"/>
-      <c r="W67" s="73" t="n"/>
-      <c r="X67" s="73" t="n"/>
-      <c r="Y67" s="73" t="n"/>
-      <c r="Z67" s="73" t="n"/>
-      <c r="AA67" s="73" t="n"/>
-      <c r="AB67" s="73" t="n"/>
-      <c r="AC67" s="73" t="n"/>
-      <c r="AD67" s="73" t="n"/>
-      <c r="AE67" s="73" t="n"/>
-      <c r="AF67" s="73" t="n"/>
-      <c r="AG67" s="73" t="n"/>
-      <c r="AH67" s="73" t="n"/>
-      <c r="AI67" s="73" t="n"/>
-      <c r="AJ67" s="73" t="n"/>
-      <c r="AK67" s="73" t="n"/>
-      <c r="AL67" s="73" t="n"/>
-      <c r="AM67" s="73" t="n"/>
-      <c r="AN67" s="73" t="n"/>
-      <c r="AO67" s="73" t="n"/>
-      <c r="AP67" s="73" t="n"/>
-      <c r="AQ67" s="73" t="n"/>
-      <c r="AR67" s="73" t="n"/>
     </row>
     <row r="68" ht="22.05" customHeight="1">
       <c r="A68" s="75" t="n">
@@ -20508,35 +18030,6 @@
       <c r="M68" s="82" t="n"/>
       <c r="N68" s="82" t="n"/>
       <c r="O68" s="82" t="n"/>
-      <c r="P68" s="82" t="n"/>
-      <c r="Q68" s="82" t="n"/>
-      <c r="R68" s="82" t="n"/>
-      <c r="S68" s="82" t="n"/>
-      <c r="T68" s="82" t="n"/>
-      <c r="U68" s="82" t="n"/>
-      <c r="V68" s="82" t="n"/>
-      <c r="W68" s="82" t="n"/>
-      <c r="X68" s="82" t="n"/>
-      <c r="Y68" s="82" t="n"/>
-      <c r="Z68" s="82" t="n"/>
-      <c r="AA68" s="82" t="n"/>
-      <c r="AB68" s="82" t="n"/>
-      <c r="AC68" s="82" t="n"/>
-      <c r="AD68" s="82" t="n"/>
-      <c r="AE68" s="82" t="n"/>
-      <c r="AF68" s="82" t="n"/>
-      <c r="AG68" s="82" t="n"/>
-      <c r="AH68" s="82" t="n"/>
-      <c r="AI68" s="82" t="n"/>
-      <c r="AJ68" s="82" t="n"/>
-      <c r="AK68" s="82" t="n"/>
-      <c r="AL68" s="82" t="n"/>
-      <c r="AM68" s="82" t="n"/>
-      <c r="AN68" s="82" t="n"/>
-      <c r="AO68" s="82" t="n"/>
-      <c r="AP68" s="82" t="n"/>
-      <c r="AQ68" s="82" t="n"/>
-      <c r="AR68" s="82" t="n"/>
     </row>
     <row r="69" ht="22.05" customHeight="1">
       <c r="A69" s="66" t="n">
@@ -20580,35 +18073,6 @@
       <c r="M69" s="73" t="n"/>
       <c r="N69" s="73" t="n"/>
       <c r="O69" s="73" t="n"/>
-      <c r="P69" s="73" t="n"/>
-      <c r="Q69" s="73" t="n"/>
-      <c r="R69" s="73" t="n"/>
-      <c r="S69" s="73" t="n"/>
-      <c r="T69" s="73" t="n"/>
-      <c r="U69" s="73" t="n"/>
-      <c r="V69" s="73" t="n"/>
-      <c r="W69" s="73" t="n"/>
-      <c r="X69" s="73" t="n"/>
-      <c r="Y69" s="73" t="n"/>
-      <c r="Z69" s="73" t="n"/>
-      <c r="AA69" s="73" t="n"/>
-      <c r="AB69" s="73" t="n"/>
-      <c r="AC69" s="73" t="n"/>
-      <c r="AD69" s="73" t="n"/>
-      <c r="AE69" s="73" t="n"/>
-      <c r="AF69" s="73" t="n"/>
-      <c r="AG69" s="73" t="n"/>
-      <c r="AH69" s="73" t="n"/>
-      <c r="AI69" s="73" t="n"/>
-      <c r="AJ69" s="73" t="n"/>
-      <c r="AK69" s="73" t="n"/>
-      <c r="AL69" s="73" t="n"/>
-      <c r="AM69" s="73" t="n"/>
-      <c r="AN69" s="73" t="n"/>
-      <c r="AO69" s="73" t="n"/>
-      <c r="AP69" s="73" t="n"/>
-      <c r="AQ69" s="73" t="n"/>
-      <c r="AR69" s="73" t="n"/>
     </row>
     <row r="70" ht="22.05" customHeight="1">
       <c r="A70" s="75" t="n">
@@ -20652,35 +18116,6 @@
       <c r="M70" s="82" t="n"/>
       <c r="N70" s="82" t="n"/>
       <c r="O70" s="82" t="n"/>
-      <c r="P70" s="82" t="n"/>
-      <c r="Q70" s="82" t="n"/>
-      <c r="R70" s="82" t="n"/>
-      <c r="S70" s="82" t="n"/>
-      <c r="T70" s="82" t="n"/>
-      <c r="U70" s="82" t="n"/>
-      <c r="V70" s="82" t="n"/>
-      <c r="W70" s="82" t="n"/>
-      <c r="X70" s="82" t="n"/>
-      <c r="Y70" s="82" t="n"/>
-      <c r="Z70" s="82" t="n"/>
-      <c r="AA70" s="82" t="n"/>
-      <c r="AB70" s="82" t="n"/>
-      <c r="AC70" s="82" t="n"/>
-      <c r="AD70" s="82" t="n"/>
-      <c r="AE70" s="82" t="n"/>
-      <c r="AF70" s="82" t="n"/>
-      <c r="AG70" s="82" t="n"/>
-      <c r="AH70" s="82" t="n"/>
-      <c r="AI70" s="82" t="n"/>
-      <c r="AJ70" s="82" t="n"/>
-      <c r="AK70" s="82" t="n"/>
-      <c r="AL70" s="82" t="n"/>
-      <c r="AM70" s="82" t="n"/>
-      <c r="AN70" s="82" t="n"/>
-      <c r="AO70" s="82" t="n"/>
-      <c r="AP70" s="82" t="n"/>
-      <c r="AQ70" s="82" t="n"/>
-      <c r="AR70" s="82" t="n"/>
     </row>
     <row r="71" ht="22.05" customHeight="1">
       <c r="A71" s="66" t="n">
@@ -20724,35 +18159,6 @@
       <c r="M71" s="73" t="n"/>
       <c r="N71" s="73" t="n"/>
       <c r="O71" s="73" t="n"/>
-      <c r="P71" s="73" t="n"/>
-      <c r="Q71" s="73" t="n"/>
-      <c r="R71" s="73" t="n"/>
-      <c r="S71" s="73" t="n"/>
-      <c r="T71" s="73" t="n"/>
-      <c r="U71" s="73" t="n"/>
-      <c r="V71" s="73" t="n"/>
-      <c r="W71" s="73" t="n"/>
-      <c r="X71" s="73" t="n"/>
-      <c r="Y71" s="73" t="n"/>
-      <c r="Z71" s="73" t="n"/>
-      <c r="AA71" s="73" t="n"/>
-      <c r="AB71" s="73" t="n"/>
-      <c r="AC71" s="73" t="n"/>
-      <c r="AD71" s="73" t="n"/>
-      <c r="AE71" s="73" t="n"/>
-      <c r="AF71" s="73" t="n"/>
-      <c r="AG71" s="73" t="n"/>
-      <c r="AH71" s="73" t="n"/>
-      <c r="AI71" s="73" t="n"/>
-      <c r="AJ71" s="73" t="n"/>
-      <c r="AK71" s="73" t="n"/>
-      <c r="AL71" s="73" t="n"/>
-      <c r="AM71" s="73" t="n"/>
-      <c r="AN71" s="73" t="n"/>
-      <c r="AO71" s="73" t="n"/>
-      <c r="AP71" s="73" t="n"/>
-      <c r="AQ71" s="73" t="n"/>
-      <c r="AR71" s="73" t="n"/>
     </row>
     <row r="72" ht="22.05" customHeight="1">
       <c r="A72" s="75" t="n">
@@ -20796,35 +18202,6 @@
       <c r="M72" s="82" t="n"/>
       <c r="N72" s="82" t="n"/>
       <c r="O72" s="82" t="n"/>
-      <c r="P72" s="82" t="n"/>
-      <c r="Q72" s="82" t="n"/>
-      <c r="R72" s="82" t="n"/>
-      <c r="S72" s="82" t="n"/>
-      <c r="T72" s="82" t="n"/>
-      <c r="U72" s="82" t="n"/>
-      <c r="V72" s="82" t="n"/>
-      <c r="W72" s="82" t="n"/>
-      <c r="X72" s="82" t="n"/>
-      <c r="Y72" s="82" t="n"/>
-      <c r="Z72" s="82" t="n"/>
-      <c r="AA72" s="82" t="n"/>
-      <c r="AB72" s="82" t="n"/>
-      <c r="AC72" s="82" t="n"/>
-      <c r="AD72" s="82" t="n"/>
-      <c r="AE72" s="82" t="n"/>
-      <c r="AF72" s="82" t="n"/>
-      <c r="AG72" s="82" t="n"/>
-      <c r="AH72" s="82" t="n"/>
-      <c r="AI72" s="82" t="n"/>
-      <c r="AJ72" s="82" t="n"/>
-      <c r="AK72" s="82" t="n"/>
-      <c r="AL72" s="82" t="n"/>
-      <c r="AM72" s="82" t="n"/>
-      <c r="AN72" s="82" t="n"/>
-      <c r="AO72" s="82" t="n"/>
-      <c r="AP72" s="82" t="n"/>
-      <c r="AQ72" s="82" t="n"/>
-      <c r="AR72" s="82" t="n"/>
     </row>
     <row r="73" ht="22.05" customHeight="1">
       <c r="A73" s="66" t="n">
@@ -20868,35 +18245,6 @@
       <c r="M73" s="73" t="n"/>
       <c r="N73" s="73" t="n"/>
       <c r="O73" s="73" t="n"/>
-      <c r="P73" s="73" t="n"/>
-      <c r="Q73" s="73" t="n"/>
-      <c r="R73" s="73" t="n"/>
-      <c r="S73" s="73" t="n"/>
-      <c r="T73" s="73" t="n"/>
-      <c r="U73" s="73" t="n"/>
-      <c r="V73" s="73" t="n"/>
-      <c r="W73" s="73" t="n"/>
-      <c r="X73" s="73" t="n"/>
-      <c r="Y73" s="73" t="n"/>
-      <c r="Z73" s="73" t="n"/>
-      <c r="AA73" s="73" t="n"/>
-      <c r="AB73" s="73" t="n"/>
-      <c r="AC73" s="73" t="n"/>
-      <c r="AD73" s="73" t="n"/>
-      <c r="AE73" s="73" t="n"/>
-      <c r="AF73" s="73" t="n"/>
-      <c r="AG73" s="73" t="n"/>
-      <c r="AH73" s="73" t="n"/>
-      <c r="AI73" s="73" t="n"/>
-      <c r="AJ73" s="73" t="n"/>
-      <c r="AK73" s="73" t="n"/>
-      <c r="AL73" s="73" t="n"/>
-      <c r="AM73" s="73" t="n"/>
-      <c r="AN73" s="73" t="n"/>
-      <c r="AO73" s="73" t="n"/>
-      <c r="AP73" s="73" t="n"/>
-      <c r="AQ73" s="73" t="n"/>
-      <c r="AR73" s="73" t="n"/>
     </row>
     <row r="74" ht="22.05" customHeight="1">
       <c r="A74" s="75" t="n">
@@ -20940,35 +18288,6 @@
       <c r="M74" s="82" t="n"/>
       <c r="N74" s="82" t="n"/>
       <c r="O74" s="82" t="n"/>
-      <c r="P74" s="82" t="n"/>
-      <c r="Q74" s="82" t="n"/>
-      <c r="R74" s="82" t="n"/>
-      <c r="S74" s="82" t="n"/>
-      <c r="T74" s="82" t="n"/>
-      <c r="U74" s="82" t="n"/>
-      <c r="V74" s="82" t="n"/>
-      <c r="W74" s="82" t="n"/>
-      <c r="X74" s="82" t="n"/>
-      <c r="Y74" s="82" t="n"/>
-      <c r="Z74" s="82" t="n"/>
-      <c r="AA74" s="82" t="n"/>
-      <c r="AB74" s="82" t="n"/>
-      <c r="AC74" s="82" t="n"/>
-      <c r="AD74" s="82" t="n"/>
-      <c r="AE74" s="82" t="n"/>
-      <c r="AF74" s="82" t="n"/>
-      <c r="AG74" s="82" t="n"/>
-      <c r="AH74" s="82" t="n"/>
-      <c r="AI74" s="82" t="n"/>
-      <c r="AJ74" s="82" t="n"/>
-      <c r="AK74" s="82" t="n"/>
-      <c r="AL74" s="82" t="n"/>
-      <c r="AM74" s="82" t="n"/>
-      <c r="AN74" s="82" t="n"/>
-      <c r="AO74" s="82" t="n"/>
-      <c r="AP74" s="82" t="n"/>
-      <c r="AQ74" s="82" t="n"/>
-      <c r="AR74" s="82" t="n"/>
     </row>
     <row r="75" ht="22.05" customHeight="1">
       <c r="A75" s="66" t="n">
@@ -21012,35 +18331,6 @@
       <c r="M75" s="73" t="n"/>
       <c r="N75" s="73" t="n"/>
       <c r="O75" s="73" t="n"/>
-      <c r="P75" s="73" t="n"/>
-      <c r="Q75" s="73" t="n"/>
-      <c r="R75" s="73" t="n"/>
-      <c r="S75" s="73" t="n"/>
-      <c r="T75" s="73" t="n"/>
-      <c r="U75" s="73" t="n"/>
-      <c r="V75" s="73" t="n"/>
-      <c r="W75" s="73" t="n"/>
-      <c r="X75" s="73" t="n"/>
-      <c r="Y75" s="73" t="n"/>
-      <c r="Z75" s="73" t="n"/>
-      <c r="AA75" s="73" t="n"/>
-      <c r="AB75" s="73" t="n"/>
-      <c r="AC75" s="73" t="n"/>
-      <c r="AD75" s="73" t="n"/>
-      <c r="AE75" s="73" t="n"/>
-      <c r="AF75" s="73" t="n"/>
-      <c r="AG75" s="73" t="n"/>
-      <c r="AH75" s="73" t="n"/>
-      <c r="AI75" s="73" t="n"/>
-      <c r="AJ75" s="73" t="n"/>
-      <c r="AK75" s="73" t="n"/>
-      <c r="AL75" s="73" t="n"/>
-      <c r="AM75" s="73" t="n"/>
-      <c r="AN75" s="73" t="n"/>
-      <c r="AO75" s="73" t="n"/>
-      <c r="AP75" s="73" t="n"/>
-      <c r="AQ75" s="73" t="n"/>
-      <c r="AR75" s="73" t="n"/>
     </row>
     <row r="76" ht="22.05" customHeight="1">
       <c r="A76" s="75" t="n">
@@ -21084,35 +18374,6 @@
       <c r="M76" s="82" t="n"/>
       <c r="N76" s="82" t="n"/>
       <c r="O76" s="82" t="n"/>
-      <c r="P76" s="82" t="n"/>
-      <c r="Q76" s="82" t="n"/>
-      <c r="R76" s="82" t="n"/>
-      <c r="S76" s="82" t="n"/>
-      <c r="T76" s="82" t="n"/>
-      <c r="U76" s="82" t="n"/>
-      <c r="V76" s="82" t="n"/>
-      <c r="W76" s="82" t="n"/>
-      <c r="X76" s="82" t="n"/>
-      <c r="Y76" s="82" t="n"/>
-      <c r="Z76" s="82" t="n"/>
-      <c r="AA76" s="82" t="n"/>
-      <c r="AB76" s="82" t="n"/>
-      <c r="AC76" s="82" t="n"/>
-      <c r="AD76" s="82" t="n"/>
-      <c r="AE76" s="82" t="n"/>
-      <c r="AF76" s="82" t="n"/>
-      <c r="AG76" s="82" t="n"/>
-      <c r="AH76" s="82" t="n"/>
-      <c r="AI76" s="82" t="n"/>
-      <c r="AJ76" s="82" t="n"/>
-      <c r="AK76" s="82" t="n"/>
-      <c r="AL76" s="82" t="n"/>
-      <c r="AM76" s="82" t="n"/>
-      <c r="AN76" s="82" t="n"/>
-      <c r="AO76" s="82" t="n"/>
-      <c r="AP76" s="82" t="n"/>
-      <c r="AQ76" s="82" t="n"/>
-      <c r="AR76" s="82" t="n"/>
     </row>
     <row r="77" ht="22.05" customHeight="1">
       <c r="A77" s="66" t="n">
@@ -21156,35 +18417,6 @@
       <c r="M77" s="73" t="n"/>
       <c r="N77" s="73" t="n"/>
       <c r="O77" s="73" t="n"/>
-      <c r="P77" s="73" t="n"/>
-      <c r="Q77" s="73" t="n"/>
-      <c r="R77" s="73" t="n"/>
-      <c r="S77" s="73" t="n"/>
-      <c r="T77" s="73" t="n"/>
-      <c r="U77" s="73" t="n"/>
-      <c r="V77" s="73" t="n"/>
-      <c r="W77" s="73" t="n"/>
-      <c r="X77" s="73" t="n"/>
-      <c r="Y77" s="73" t="n"/>
-      <c r="Z77" s="73" t="n"/>
-      <c r="AA77" s="73" t="n"/>
-      <c r="AB77" s="73" t="n"/>
-      <c r="AC77" s="73" t="n"/>
-      <c r="AD77" s="73" t="n"/>
-      <c r="AE77" s="73" t="n"/>
-      <c r="AF77" s="73" t="n"/>
-      <c r="AG77" s="73" t="n"/>
-      <c r="AH77" s="73" t="n"/>
-      <c r="AI77" s="73" t="n"/>
-      <c r="AJ77" s="73" t="n"/>
-      <c r="AK77" s="73" t="n"/>
-      <c r="AL77" s="73" t="n"/>
-      <c r="AM77" s="73" t="n"/>
-      <c r="AN77" s="73" t="n"/>
-      <c r="AO77" s="73" t="n"/>
-      <c r="AP77" s="73" t="n"/>
-      <c r="AQ77" s="73" t="n"/>
-      <c r="AR77" s="73" t="n"/>
     </row>
     <row r="78" ht="22.05" customHeight="1">
       <c r="A78" s="75" t="n">
@@ -21228,35 +18460,6 @@
       <c r="M78" s="82" t="n"/>
       <c r="N78" s="82" t="n"/>
       <c r="O78" s="82" t="n"/>
-      <c r="P78" s="82" t="n"/>
-      <c r="Q78" s="82" t="n"/>
-      <c r="R78" s="82" t="n"/>
-      <c r="S78" s="82" t="n"/>
-      <c r="T78" s="82" t="n"/>
-      <c r="U78" s="82" t="n"/>
-      <c r="V78" s="82" t="n"/>
-      <c r="W78" s="82" t="n"/>
-      <c r="X78" s="82" t="n"/>
-      <c r="Y78" s="82" t="n"/>
-      <c r="Z78" s="82" t="n"/>
-      <c r="AA78" s="82" t="n"/>
-      <c r="AB78" s="82" t="n"/>
-      <c r="AC78" s="82" t="n"/>
-      <c r="AD78" s="82" t="n"/>
-      <c r="AE78" s="82" t="n"/>
-      <c r="AF78" s="82" t="n"/>
-      <c r="AG78" s="82" t="n"/>
-      <c r="AH78" s="82" t="n"/>
-      <c r="AI78" s="82" t="n"/>
-      <c r="AJ78" s="82" t="n"/>
-      <c r="AK78" s="82" t="n"/>
-      <c r="AL78" s="82" t="n"/>
-      <c r="AM78" s="82" t="n"/>
-      <c r="AN78" s="82" t="n"/>
-      <c r="AO78" s="82" t="n"/>
-      <c r="AP78" s="82" t="n"/>
-      <c r="AQ78" s="82" t="n"/>
-      <c r="AR78" s="82" t="n"/>
     </row>
     <row r="79" ht="22.05" customHeight="1">
       <c r="A79" s="66" t="n">
@@ -21300,35 +18503,6 @@
       <c r="M79" s="73" t="n"/>
       <c r="N79" s="73" t="n"/>
       <c r="O79" s="73" t="n"/>
-      <c r="P79" s="73" t="n"/>
-      <c r="Q79" s="73" t="n"/>
-      <c r="R79" s="73" t="n"/>
-      <c r="S79" s="73" t="n"/>
-      <c r="T79" s="73" t="n"/>
-      <c r="U79" s="73" t="n"/>
-      <c r="V79" s="73" t="n"/>
-      <c r="W79" s="73" t="n"/>
-      <c r="X79" s="73" t="n"/>
-      <c r="Y79" s="73" t="n"/>
-      <c r="Z79" s="73" t="n"/>
-      <c r="AA79" s="73" t="n"/>
-      <c r="AB79" s="73" t="n"/>
-      <c r="AC79" s="73" t="n"/>
-      <c r="AD79" s="73" t="n"/>
-      <c r="AE79" s="73" t="n"/>
-      <c r="AF79" s="73" t="n"/>
-      <c r="AG79" s="73" t="n"/>
-      <c r="AH79" s="73" t="n"/>
-      <c r="AI79" s="73" t="n"/>
-      <c r="AJ79" s="73" t="n"/>
-      <c r="AK79" s="73" t="n"/>
-      <c r="AL79" s="73" t="n"/>
-      <c r="AM79" s="73" t="n"/>
-      <c r="AN79" s="73" t="n"/>
-      <c r="AO79" s="73" t="n"/>
-      <c r="AP79" s="73" t="n"/>
-      <c r="AQ79" s="73" t="n"/>
-      <c r="AR79" s="73" t="n"/>
     </row>
     <row r="80" ht="22.05" customHeight="1">
       <c r="A80" s="75" t="n">
@@ -21372,35 +18546,6 @@
       <c r="M80" s="82" t="n"/>
       <c r="N80" s="82" t="n"/>
       <c r="O80" s="82" t="n"/>
-      <c r="P80" s="82" t="n"/>
-      <c r="Q80" s="82" t="n"/>
-      <c r="R80" s="82" t="n"/>
-      <c r="S80" s="82" t="n"/>
-      <c r="T80" s="82" t="n"/>
-      <c r="U80" s="82" t="n"/>
-      <c r="V80" s="82" t="n"/>
-      <c r="W80" s="82" t="n"/>
-      <c r="X80" s="82" t="n"/>
-      <c r="Y80" s="82" t="n"/>
-      <c r="Z80" s="82" t="n"/>
-      <c r="AA80" s="82" t="n"/>
-      <c r="AB80" s="82" t="n"/>
-      <c r="AC80" s="82" t="n"/>
-      <c r="AD80" s="82" t="n"/>
-      <c r="AE80" s="82" t="n"/>
-      <c r="AF80" s="82" t="n"/>
-      <c r="AG80" s="82" t="n"/>
-      <c r="AH80" s="82" t="n"/>
-      <c r="AI80" s="82" t="n"/>
-      <c r="AJ80" s="82" t="n"/>
-      <c r="AK80" s="82" t="n"/>
-      <c r="AL80" s="82" t="n"/>
-      <c r="AM80" s="82" t="n"/>
-      <c r="AN80" s="82" t="n"/>
-      <c r="AO80" s="82" t="n"/>
-      <c r="AP80" s="82" t="n"/>
-      <c r="AQ80" s="82" t="n"/>
-      <c r="AR80" s="82" t="n"/>
     </row>
     <row r="81" ht="22.05" customHeight="1">
       <c r="A81" s="66" t="n">
@@ -21444,35 +18589,6 @@
       <c r="M81" s="73" t="n"/>
       <c r="N81" s="73" t="n"/>
       <c r="O81" s="73" t="n"/>
-      <c r="P81" s="73" t="n"/>
-      <c r="Q81" s="73" t="n"/>
-      <c r="R81" s="73" t="n"/>
-      <c r="S81" s="73" t="n"/>
-      <c r="T81" s="73" t="n"/>
-      <c r="U81" s="73" t="n"/>
-      <c r="V81" s="73" t="n"/>
-      <c r="W81" s="73" t="n"/>
-      <c r="X81" s="73" t="n"/>
-      <c r="Y81" s="73" t="n"/>
-      <c r="Z81" s="73" t="n"/>
-      <c r="AA81" s="73" t="n"/>
-      <c r="AB81" s="73" t="n"/>
-      <c r="AC81" s="73" t="n"/>
-      <c r="AD81" s="73" t="n"/>
-      <c r="AE81" s="73" t="n"/>
-      <c r="AF81" s="73" t="n"/>
-      <c r="AG81" s="73" t="n"/>
-      <c r="AH81" s="73" t="n"/>
-      <c r="AI81" s="73" t="n"/>
-      <c r="AJ81" s="73" t="n"/>
-      <c r="AK81" s="73" t="n"/>
-      <c r="AL81" s="73" t="n"/>
-      <c r="AM81" s="73" t="n"/>
-      <c r="AN81" s="73" t="n"/>
-      <c r="AO81" s="73" t="n"/>
-      <c r="AP81" s="73" t="n"/>
-      <c r="AQ81" s="73" t="n"/>
-      <c r="AR81" s="73" t="n"/>
     </row>
     <row r="82" ht="22.05" customHeight="1">
       <c r="A82" s="75" t="n">
@@ -21516,35 +18632,6 @@
       <c r="M82" s="82" t="n"/>
       <c r="N82" s="82" t="n"/>
       <c r="O82" s="82" t="n"/>
-      <c r="P82" s="82" t="n"/>
-      <c r="Q82" s="82" t="n"/>
-      <c r="R82" s="82" t="n"/>
-      <c r="S82" s="82" t="n"/>
-      <c r="T82" s="82" t="n"/>
-      <c r="U82" s="82" t="n"/>
-      <c r="V82" s="82" t="n"/>
-      <c r="W82" s="82" t="n"/>
-      <c r="X82" s="82" t="n"/>
-      <c r="Y82" s="82" t="n"/>
-      <c r="Z82" s="82" t="n"/>
-      <c r="AA82" s="82" t="n"/>
-      <c r="AB82" s="82" t="n"/>
-      <c r="AC82" s="82" t="n"/>
-      <c r="AD82" s="82" t="n"/>
-      <c r="AE82" s="82" t="n"/>
-      <c r="AF82" s="82" t="n"/>
-      <c r="AG82" s="82" t="n"/>
-      <c r="AH82" s="82" t="n"/>
-      <c r="AI82" s="82" t="n"/>
-      <c r="AJ82" s="82" t="n"/>
-      <c r="AK82" s="82" t="n"/>
-      <c r="AL82" s="82" t="n"/>
-      <c r="AM82" s="82" t="n"/>
-      <c r="AN82" s="82" t="n"/>
-      <c r="AO82" s="82" t="n"/>
-      <c r="AP82" s="82" t="n"/>
-      <c r="AQ82" s="82" t="n"/>
-      <c r="AR82" s="82" t="n"/>
     </row>
     <row r="83" ht="22.05" customHeight="1">
       <c r="A83" s="66" t="n">
@@ -21588,35 +18675,6 @@
       <c r="M83" s="73" t="n"/>
       <c r="N83" s="73" t="n"/>
       <c r="O83" s="73" t="n"/>
-      <c r="P83" s="73" t="n"/>
-      <c r="Q83" s="73" t="n"/>
-      <c r="R83" s="73" t="n"/>
-      <c r="S83" s="73" t="n"/>
-      <c r="T83" s="73" t="n"/>
-      <c r="U83" s="73" t="n"/>
-      <c r="V83" s="73" t="n"/>
-      <c r="W83" s="73" t="n"/>
-      <c r="X83" s="73" t="n"/>
-      <c r="Y83" s="73" t="n"/>
-      <c r="Z83" s="73" t="n"/>
-      <c r="AA83" s="73" t="n"/>
-      <c r="AB83" s="73" t="n"/>
-      <c r="AC83" s="73" t="n"/>
-      <c r="AD83" s="73" t="n"/>
-      <c r="AE83" s="73" t="n"/>
-      <c r="AF83" s="73" t="n"/>
-      <c r="AG83" s="73" t="n"/>
-      <c r="AH83" s="73" t="n"/>
-      <c r="AI83" s="73" t="n"/>
-      <c r="AJ83" s="73" t="n"/>
-      <c r="AK83" s="73" t="n"/>
-      <c r="AL83" s="73" t="n"/>
-      <c r="AM83" s="73" t="n"/>
-      <c r="AN83" s="73" t="n"/>
-      <c r="AO83" s="73" t="n"/>
-      <c r="AP83" s="73" t="n"/>
-      <c r="AQ83" s="73" t="n"/>
-      <c r="AR83" s="73" t="n"/>
     </row>
     <row r="84" ht="22.05" customHeight="1">
       <c r="A84" s="75" t="n">
@@ -21660,35 +18718,6 @@
       <c r="M84" s="82" t="n"/>
       <c r="N84" s="82" t="n"/>
       <c r="O84" s="82" t="n"/>
-      <c r="P84" s="82" t="n"/>
-      <c r="Q84" s="82" t="n"/>
-      <c r="R84" s="82" t="n"/>
-      <c r="S84" s="82" t="n"/>
-      <c r="T84" s="82" t="n"/>
-      <c r="U84" s="82" t="n"/>
-      <c r="V84" s="82" t="n"/>
-      <c r="W84" s="82" t="n"/>
-      <c r="X84" s="82" t="n"/>
-      <c r="Y84" s="82" t="n"/>
-      <c r="Z84" s="82" t="n"/>
-      <c r="AA84" s="82" t="n"/>
-      <c r="AB84" s="82" t="n"/>
-      <c r="AC84" s="82" t="n"/>
-      <c r="AD84" s="82" t="n"/>
-      <c r="AE84" s="82" t="n"/>
-      <c r="AF84" s="82" t="n"/>
-      <c r="AG84" s="82" t="n"/>
-      <c r="AH84" s="82" t="n"/>
-      <c r="AI84" s="82" t="n"/>
-      <c r="AJ84" s="82" t="n"/>
-      <c r="AK84" s="82" t="n"/>
-      <c r="AL84" s="82" t="n"/>
-      <c r="AM84" s="82" t="n"/>
-      <c r="AN84" s="82" t="n"/>
-      <c r="AO84" s="82" t="n"/>
-      <c r="AP84" s="82" t="n"/>
-      <c r="AQ84" s="82" t="n"/>
-      <c r="AR84" s="82" t="n"/>
     </row>
     <row r="85" ht="22.05" customHeight="1">
       <c r="A85" s="66" t="n">
@@ -21732,35 +18761,6 @@
       <c r="M85" s="73" t="n"/>
       <c r="N85" s="73" t="n"/>
       <c r="O85" s="73" t="n"/>
-      <c r="P85" s="73" t="n"/>
-      <c r="Q85" s="73" t="n"/>
-      <c r="R85" s="73" t="n"/>
-      <c r="S85" s="73" t="n"/>
-      <c r="T85" s="73" t="n"/>
-      <c r="U85" s="73" t="n"/>
-      <c r="V85" s="73" t="n"/>
-      <c r="W85" s="73" t="n"/>
-      <c r="X85" s="73" t="n"/>
-      <c r="Y85" s="73" t="n"/>
-      <c r="Z85" s="73" t="n"/>
-      <c r="AA85" s="73" t="n"/>
-      <c r="AB85" s="73" t="n"/>
-      <c r="AC85" s="73" t="n"/>
-      <c r="AD85" s="73" t="n"/>
-      <c r="AE85" s="73" t="n"/>
-      <c r="AF85" s="73" t="n"/>
-      <c r="AG85" s="73" t="n"/>
-      <c r="AH85" s="73" t="n"/>
-      <c r="AI85" s="73" t="n"/>
-      <c r="AJ85" s="73" t="n"/>
-      <c r="AK85" s="73" t="n"/>
-      <c r="AL85" s="73" t="n"/>
-      <c r="AM85" s="73" t="n"/>
-      <c r="AN85" s="73" t="n"/>
-      <c r="AO85" s="73" t="n"/>
-      <c r="AP85" s="73" t="n"/>
-      <c r="AQ85" s="73" t="n"/>
-      <c r="AR85" s="73" t="n"/>
     </row>
     <row r="86" ht="22.05" customHeight="1">
       <c r="A86" s="75" t="n">
@@ -21804,35 +18804,6 @@
       <c r="M86" s="82" t="n"/>
       <c r="N86" s="82" t="n"/>
       <c r="O86" s="82" t="n"/>
-      <c r="P86" s="82" t="n"/>
-      <c r="Q86" s="82" t="n"/>
-      <c r="R86" s="82" t="n"/>
-      <c r="S86" s="82" t="n"/>
-      <c r="T86" s="82" t="n"/>
-      <c r="U86" s="82" t="n"/>
-      <c r="V86" s="82" t="n"/>
-      <c r="W86" s="82" t="n"/>
-      <c r="X86" s="82" t="n"/>
-      <c r="Y86" s="82" t="n"/>
-      <c r="Z86" s="82" t="n"/>
-      <c r="AA86" s="82" t="n"/>
-      <c r="AB86" s="82" t="n"/>
-      <c r="AC86" s="82" t="n"/>
-      <c r="AD86" s="82" t="n"/>
-      <c r="AE86" s="82" t="n"/>
-      <c r="AF86" s="82" t="n"/>
-      <c r="AG86" s="82" t="n"/>
-      <c r="AH86" s="82" t="n"/>
-      <c r="AI86" s="82" t="n"/>
-      <c r="AJ86" s="82" t="n"/>
-      <c r="AK86" s="82" t="n"/>
-      <c r="AL86" s="82" t="n"/>
-      <c r="AM86" s="82" t="n"/>
-      <c r="AN86" s="82" t="n"/>
-      <c r="AO86" s="82" t="n"/>
-      <c r="AP86" s="82" t="n"/>
-      <c r="AQ86" s="82" t="n"/>
-      <c r="AR86" s="82" t="n"/>
     </row>
     <row r="87" ht="22.05" customHeight="1">
       <c r="A87" s="66" t="n">
@@ -21876,35 +18847,6 @@
       <c r="M87" s="73" t="n"/>
       <c r="N87" s="73" t="n"/>
       <c r="O87" s="73" t="n"/>
-      <c r="P87" s="73" t="n"/>
-      <c r="Q87" s="73" t="n"/>
-      <c r="R87" s="73" t="n"/>
-      <c r="S87" s="73" t="n"/>
-      <c r="T87" s="73" t="n"/>
-      <c r="U87" s="73" t="n"/>
-      <c r="V87" s="73" t="n"/>
-      <c r="W87" s="73" t="n"/>
-      <c r="X87" s="73" t="n"/>
-      <c r="Y87" s="73" t="n"/>
-      <c r="Z87" s="73" t="n"/>
-      <c r="AA87" s="73" t="n"/>
-      <c r="AB87" s="73" t="n"/>
-      <c r="AC87" s="73" t="n"/>
-      <c r="AD87" s="73" t="n"/>
-      <c r="AE87" s="73" t="n"/>
-      <c r="AF87" s="73" t="n"/>
-      <c r="AG87" s="73" t="n"/>
-      <c r="AH87" s="73" t="n"/>
-      <c r="AI87" s="73" t="n"/>
-      <c r="AJ87" s="73" t="n"/>
-      <c r="AK87" s="73" t="n"/>
-      <c r="AL87" s="73" t="n"/>
-      <c r="AM87" s="73" t="n"/>
-      <c r="AN87" s="73" t="n"/>
-      <c r="AO87" s="73" t="n"/>
-      <c r="AP87" s="73" t="n"/>
-      <c r="AQ87" s="73" t="n"/>
-      <c r="AR87" s="73" t="n"/>
     </row>
     <row r="88" ht="22.05" customHeight="1">
       <c r="A88" s="75" t="n">
@@ -21948,35 +18890,6 @@
       <c r="M88" s="82" t="n"/>
       <c r="N88" s="82" t="n"/>
       <c r="O88" s="82" t="n"/>
-      <c r="P88" s="82" t="n"/>
-      <c r="Q88" s="82" t="n"/>
-      <c r="R88" s="82" t="n"/>
-      <c r="S88" s="82" t="n"/>
-      <c r="T88" s="82" t="n"/>
-      <c r="U88" s="82" t="n"/>
-      <c r="V88" s="82" t="n"/>
-      <c r="W88" s="82" t="n"/>
-      <c r="X88" s="82" t="n"/>
-      <c r="Y88" s="82" t="n"/>
-      <c r="Z88" s="82" t="n"/>
-      <c r="AA88" s="82" t="n"/>
-      <c r="AB88" s="82" t="n"/>
-      <c r="AC88" s="82" t="n"/>
-      <c r="AD88" s="82" t="n"/>
-      <c r="AE88" s="82" t="n"/>
-      <c r="AF88" s="82" t="n"/>
-      <c r="AG88" s="82" t="n"/>
-      <c r="AH88" s="82" t="n"/>
-      <c r="AI88" s="82" t="n"/>
-      <c r="AJ88" s="82" t="n"/>
-      <c r="AK88" s="82" t="n"/>
-      <c r="AL88" s="82" t="n"/>
-      <c r="AM88" s="82" t="n"/>
-      <c r="AN88" s="82" t="n"/>
-      <c r="AO88" s="82" t="n"/>
-      <c r="AP88" s="82" t="n"/>
-      <c r="AQ88" s="82" t="n"/>
-      <c r="AR88" s="82" t="n"/>
     </row>
     <row r="89" ht="22.05" customHeight="1">
       <c r="A89" s="66" t="n">
@@ -22020,35 +18933,6 @@
       <c r="M89" s="73" t="n"/>
       <c r="N89" s="73" t="n"/>
       <c r="O89" s="73" t="n"/>
-      <c r="P89" s="73" t="n"/>
-      <c r="Q89" s="73" t="n"/>
-      <c r="R89" s="73" t="n"/>
-      <c r="S89" s="73" t="n"/>
-      <c r="T89" s="73" t="n"/>
-      <c r="U89" s="73" t="n"/>
-      <c r="V89" s="73" t="n"/>
-      <c r="W89" s="73" t="n"/>
-      <c r="X89" s="73" t="n"/>
-      <c r="Y89" s="73" t="n"/>
-      <c r="Z89" s="73" t="n"/>
-      <c r="AA89" s="73" t="n"/>
-      <c r="AB89" s="73" t="n"/>
-      <c r="AC89" s="73" t="n"/>
-      <c r="AD89" s="73" t="n"/>
-      <c r="AE89" s="73" t="n"/>
-      <c r="AF89" s="73" t="n"/>
-      <c r="AG89" s="73" t="n"/>
-      <c r="AH89" s="73" t="n"/>
-      <c r="AI89" s="73" t="n"/>
-      <c r="AJ89" s="73" t="n"/>
-      <c r="AK89" s="73" t="n"/>
-      <c r="AL89" s="73" t="n"/>
-      <c r="AM89" s="73" t="n"/>
-      <c r="AN89" s="73" t="n"/>
-      <c r="AO89" s="73" t="n"/>
-      <c r="AP89" s="73" t="n"/>
-      <c r="AQ89" s="73" t="n"/>
-      <c r="AR89" s="73" t="n"/>
     </row>
     <row r="90" ht="22.05" customHeight="1">
       <c r="A90" s="75" t="n">
@@ -22092,35 +18976,6 @@
       <c r="M90" s="82" t="n"/>
       <c r="N90" s="82" t="n"/>
       <c r="O90" s="82" t="n"/>
-      <c r="P90" s="82" t="n"/>
-      <c r="Q90" s="82" t="n"/>
-      <c r="R90" s="82" t="n"/>
-      <c r="S90" s="82" t="n"/>
-      <c r="T90" s="82" t="n"/>
-      <c r="U90" s="82" t="n"/>
-      <c r="V90" s="82" t="n"/>
-      <c r="W90" s="82" t="n"/>
-      <c r="X90" s="82" t="n"/>
-      <c r="Y90" s="82" t="n"/>
-      <c r="Z90" s="82" t="n"/>
-      <c r="AA90" s="82" t="n"/>
-      <c r="AB90" s="82" t="n"/>
-      <c r="AC90" s="82" t="n"/>
-      <c r="AD90" s="82" t="n"/>
-      <c r="AE90" s="82" t="n"/>
-      <c r="AF90" s="82" t="n"/>
-      <c r="AG90" s="82" t="n"/>
-      <c r="AH90" s="82" t="n"/>
-      <c r="AI90" s="82" t="n"/>
-      <c r="AJ90" s="82" t="n"/>
-      <c r="AK90" s="82" t="n"/>
-      <c r="AL90" s="82" t="n"/>
-      <c r="AM90" s="82" t="n"/>
-      <c r="AN90" s="82" t="n"/>
-      <c r="AO90" s="82" t="n"/>
-      <c r="AP90" s="82" t="n"/>
-      <c r="AQ90" s="82" t="n"/>
-      <c r="AR90" s="82" t="n"/>
     </row>
     <row r="91" ht="22.05" customHeight="1">
       <c r="A91" s="66" t="n">
@@ -22164,35 +19019,6 @@
       <c r="M91" s="73" t="n"/>
       <c r="N91" s="73" t="n"/>
       <c r="O91" s="73" t="n"/>
-      <c r="P91" s="73" t="n"/>
-      <c r="Q91" s="73" t="n"/>
-      <c r="R91" s="73" t="n"/>
-      <c r="S91" s="73" t="n"/>
-      <c r="T91" s="73" t="n"/>
-      <c r="U91" s="73" t="n"/>
-      <c r="V91" s="73" t="n"/>
-      <c r="W91" s="73" t="n"/>
-      <c r="X91" s="73" t="n"/>
-      <c r="Y91" s="73" t="n"/>
-      <c r="Z91" s="73" t="n"/>
-      <c r="AA91" s="73" t="n"/>
-      <c r="AB91" s="73" t="n"/>
-      <c r="AC91" s="73" t="n"/>
-      <c r="AD91" s="73" t="n"/>
-      <c r="AE91" s="73" t="n"/>
-      <c r="AF91" s="73" t="n"/>
-      <c r="AG91" s="73" t="n"/>
-      <c r="AH91" s="73" t="n"/>
-      <c r="AI91" s="73" t="n"/>
-      <c r="AJ91" s="73" t="n"/>
-      <c r="AK91" s="73" t="n"/>
-      <c r="AL91" s="73" t="n"/>
-      <c r="AM91" s="73" t="n"/>
-      <c r="AN91" s="73" t="n"/>
-      <c r="AO91" s="73" t="n"/>
-      <c r="AP91" s="73" t="n"/>
-      <c r="AQ91" s="73" t="n"/>
-      <c r="AR91" s="73" t="n"/>
     </row>
     <row r="92" ht="22.05" customHeight="1">
       <c r="A92" s="75" t="n">
@@ -22236,35 +19062,6 @@
       <c r="M92" s="82" t="n"/>
       <c r="N92" s="82" t="n"/>
       <c r="O92" s="82" t="n"/>
-      <c r="P92" s="82" t="n"/>
-      <c r="Q92" s="82" t="n"/>
-      <c r="R92" s="82" t="n"/>
-      <c r="S92" s="82" t="n"/>
-      <c r="T92" s="82" t="n"/>
-      <c r="U92" s="82" t="n"/>
-      <c r="V92" s="82" t="n"/>
-      <c r="W92" s="82" t="n"/>
-      <c r="X92" s="82" t="n"/>
-      <c r="Y92" s="82" t="n"/>
-      <c r="Z92" s="82" t="n"/>
-      <c r="AA92" s="82" t="n"/>
-      <c r="AB92" s="82" t="n"/>
-      <c r="AC92" s="82" t="n"/>
-      <c r="AD92" s="82" t="n"/>
-      <c r="AE92" s="82" t="n"/>
-      <c r="AF92" s="82" t="n"/>
-      <c r="AG92" s="82" t="n"/>
-      <c r="AH92" s="82" t="n"/>
-      <c r="AI92" s="82" t="n"/>
-      <c r="AJ92" s="82" t="n"/>
-      <c r="AK92" s="82" t="n"/>
-      <c r="AL92" s="82" t="n"/>
-      <c r="AM92" s="82" t="n"/>
-      <c r="AN92" s="82" t="n"/>
-      <c r="AO92" s="82" t="n"/>
-      <c r="AP92" s="82" t="n"/>
-      <c r="AQ92" s="82" t="n"/>
-      <c r="AR92" s="82" t="n"/>
     </row>
     <row r="93" ht="22.05" customHeight="1">
       <c r="A93" s="66" t="n">
@@ -22308,35 +19105,6 @@
       <c r="M93" s="73" t="n"/>
       <c r="N93" s="73" t="n"/>
       <c r="O93" s="73" t="n"/>
-      <c r="P93" s="73" t="n"/>
-      <c r="Q93" s="73" t="n"/>
-      <c r="R93" s="73" t="n"/>
-      <c r="S93" s="73" t="n"/>
-      <c r="T93" s="73" t="n"/>
-      <c r="U93" s="73" t="n"/>
-      <c r="V93" s="73" t="n"/>
-      <c r="W93" s="73" t="n"/>
-      <c r="X93" s="73" t="n"/>
-      <c r="Y93" s="73" t="n"/>
-      <c r="Z93" s="73" t="n"/>
-      <c r="AA93" s="73" t="n"/>
-      <c r="AB93" s="73" t="n"/>
-      <c r="AC93" s="73" t="n"/>
-      <c r="AD93" s="73" t="n"/>
-      <c r="AE93" s="73" t="n"/>
-      <c r="AF93" s="73" t="n"/>
-      <c r="AG93" s="73" t="n"/>
-      <c r="AH93" s="73" t="n"/>
-      <c r="AI93" s="73" t="n"/>
-      <c r="AJ93" s="73" t="n"/>
-      <c r="AK93" s="73" t="n"/>
-      <c r="AL93" s="73" t="n"/>
-      <c r="AM93" s="73" t="n"/>
-      <c r="AN93" s="73" t="n"/>
-      <c r="AO93" s="73" t="n"/>
-      <c r="AP93" s="73" t="n"/>
-      <c r="AQ93" s="73" t="n"/>
-      <c r="AR93" s="73" t="n"/>
     </row>
     <row r="94" ht="22.05" customHeight="1">
       <c r="A94" s="75" t="n">
@@ -22380,35 +19148,6 @@
       <c r="M94" s="82" t="n"/>
       <c r="N94" s="82" t="n"/>
       <c r="O94" s="82" t="n"/>
-      <c r="P94" s="82" t="n"/>
-      <c r="Q94" s="82" t="n"/>
-      <c r="R94" s="82" t="n"/>
-      <c r="S94" s="82" t="n"/>
-      <c r="T94" s="82" t="n"/>
-      <c r="U94" s="82" t="n"/>
-      <c r="V94" s="82" t="n"/>
-      <c r="W94" s="82" t="n"/>
-      <c r="X94" s="82" t="n"/>
-      <c r="Y94" s="82" t="n"/>
-      <c r="Z94" s="82" t="n"/>
-      <c r="AA94" s="82" t="n"/>
-      <c r="AB94" s="82" t="n"/>
-      <c r="AC94" s="82" t="n"/>
-      <c r="AD94" s="82" t="n"/>
-      <c r="AE94" s="82" t="n"/>
-      <c r="AF94" s="82" t="n"/>
-      <c r="AG94" s="82" t="n"/>
-      <c r="AH94" s="82" t="n"/>
-      <c r="AI94" s="82" t="n"/>
-      <c r="AJ94" s="82" t="n"/>
-      <c r="AK94" s="82" t="n"/>
-      <c r="AL94" s="82" t="n"/>
-      <c r="AM94" s="82" t="n"/>
-      <c r="AN94" s="82" t="n"/>
-      <c r="AO94" s="82" t="n"/>
-      <c r="AP94" s="82" t="n"/>
-      <c r="AQ94" s="82" t="n"/>
-      <c r="AR94" s="82" t="n"/>
     </row>
     <row r="95" ht="22.05" customHeight="1">
       <c r="A95" s="66" t="n">
@@ -22452,35 +19191,6 @@
       <c r="M95" s="73" t="n"/>
       <c r="N95" s="73" t="n"/>
       <c r="O95" s="73" t="n"/>
-      <c r="P95" s="73" t="n"/>
-      <c r="Q95" s="73" t="n"/>
-      <c r="R95" s="73" t="n"/>
-      <c r="S95" s="73" t="n"/>
-      <c r="T95" s="73" t="n"/>
-      <c r="U95" s="73" t="n"/>
-      <c r="V95" s="73" t="n"/>
-      <c r="W95" s="73" t="n"/>
-      <c r="X95" s="73" t="n"/>
-      <c r="Y95" s="73" t="n"/>
-      <c r="Z95" s="73" t="n"/>
-      <c r="AA95" s="73" t="n"/>
-      <c r="AB95" s="73" t="n"/>
-      <c r="AC95" s="73" t="n"/>
-      <c r="AD95" s="73" t="n"/>
-      <c r="AE95" s="73" t="n"/>
-      <c r="AF95" s="73" t="n"/>
-      <c r="AG95" s="73" t="n"/>
-      <c r="AH95" s="73" t="n"/>
-      <c r="AI95" s="73" t="n"/>
-      <c r="AJ95" s="73" t="n"/>
-      <c r="AK95" s="73" t="n"/>
-      <c r="AL95" s="73" t="n"/>
-      <c r="AM95" s="73" t="n"/>
-      <c r="AN95" s="73" t="n"/>
-      <c r="AO95" s="73" t="n"/>
-      <c r="AP95" s="73" t="n"/>
-      <c r="AQ95" s="73" t="n"/>
-      <c r="AR95" s="73" t="n"/>
     </row>
     <row r="96" ht="22.05" customHeight="1">
       <c r="A96" s="75" t="n">
@@ -22524,35 +19234,6 @@
       <c r="M96" s="82" t="n"/>
       <c r="N96" s="82" t="n"/>
       <c r="O96" s="82" t="n"/>
-      <c r="P96" s="82" t="n"/>
-      <c r="Q96" s="82" t="n"/>
-      <c r="R96" s="82" t="n"/>
-      <c r="S96" s="82" t="n"/>
-      <c r="T96" s="82" t="n"/>
-      <c r="U96" s="82" t="n"/>
-      <c r="V96" s="82" t="n"/>
-      <c r="W96" s="82" t="n"/>
-      <c r="X96" s="82" t="n"/>
-      <c r="Y96" s="82" t="n"/>
-      <c r="Z96" s="82" t="n"/>
-      <c r="AA96" s="82" t="n"/>
-      <c r="AB96" s="82" t="n"/>
-      <c r="AC96" s="82" t="n"/>
-      <c r="AD96" s="82" t="n"/>
-      <c r="AE96" s="82" t="n"/>
-      <c r="AF96" s="82" t="n"/>
-      <c r="AG96" s="82" t="n"/>
-      <c r="AH96" s="82" t="n"/>
-      <c r="AI96" s="82" t="n"/>
-      <c r="AJ96" s="82" t="n"/>
-      <c r="AK96" s="82" t="n"/>
-      <c r="AL96" s="82" t="n"/>
-      <c r="AM96" s="82" t="n"/>
-      <c r="AN96" s="82" t="n"/>
-      <c r="AO96" s="82" t="n"/>
-      <c r="AP96" s="82" t="n"/>
-      <c r="AQ96" s="82" t="n"/>
-      <c r="AR96" s="82" t="n"/>
     </row>
     <row r="97" ht="22.05" customHeight="1">
       <c r="A97" s="66" t="n">
@@ -22596,35 +19277,6 @@
       <c r="M97" s="73" t="n"/>
       <c r="N97" s="73" t="n"/>
       <c r="O97" s="73" t="n"/>
-      <c r="P97" s="73" t="n"/>
-      <c r="Q97" s="73" t="n"/>
-      <c r="R97" s="73" t="n"/>
-      <c r="S97" s="73" t="n"/>
-      <c r="T97" s="73" t="n"/>
-      <c r="U97" s="73" t="n"/>
-      <c r="V97" s="73" t="n"/>
-      <c r="W97" s="73" t="n"/>
-      <c r="X97" s="73" t="n"/>
-      <c r="Y97" s="73" t="n"/>
-      <c r="Z97" s="73" t="n"/>
-      <c r="AA97" s="73" t="n"/>
-      <c r="AB97" s="73" t="n"/>
-      <c r="AC97" s="73" t="n"/>
-      <c r="AD97" s="73" t="n"/>
-      <c r="AE97" s="73" t="n"/>
-      <c r="AF97" s="73" t="n"/>
-      <c r="AG97" s="73" t="n"/>
-      <c r="AH97" s="73" t="n"/>
-      <c r="AI97" s="73" t="n"/>
-      <c r="AJ97" s="73" t="n"/>
-      <c r="AK97" s="73" t="n"/>
-      <c r="AL97" s="73" t="n"/>
-      <c r="AM97" s="73" t="n"/>
-      <c r="AN97" s="73" t="n"/>
-      <c r="AO97" s="73" t="n"/>
-      <c r="AP97" s="73" t="n"/>
-      <c r="AQ97" s="73" t="n"/>
-      <c r="AR97" s="73" t="n"/>
     </row>
     <row r="98" ht="22.05" customHeight="1">
       <c r="A98" s="75" t="n">
@@ -22668,35 +19320,6 @@
       <c r="M98" s="82" t="n"/>
       <c r="N98" s="82" t="n"/>
       <c r="O98" s="82" t="n"/>
-      <c r="P98" s="82" t="n"/>
-      <c r="Q98" s="82" t="n"/>
-      <c r="R98" s="82" t="n"/>
-      <c r="S98" s="82" t="n"/>
-      <c r="T98" s="82" t="n"/>
-      <c r="U98" s="82" t="n"/>
-      <c r="V98" s="82" t="n"/>
-      <c r="W98" s="82" t="n"/>
-      <c r="X98" s="82" t="n"/>
-      <c r="Y98" s="82" t="n"/>
-      <c r="Z98" s="82" t="n"/>
-      <c r="AA98" s="82" t="n"/>
-      <c r="AB98" s="82" t="n"/>
-      <c r="AC98" s="82" t="n"/>
-      <c r="AD98" s="82" t="n"/>
-      <c r="AE98" s="82" t="n"/>
-      <c r="AF98" s="82" t="n"/>
-      <c r="AG98" s="82" t="n"/>
-      <c r="AH98" s="82" t="n"/>
-      <c r="AI98" s="82" t="n"/>
-      <c r="AJ98" s="82" t="n"/>
-      <c r="AK98" s="82" t="n"/>
-      <c r="AL98" s="82" t="n"/>
-      <c r="AM98" s="82" t="n"/>
-      <c r="AN98" s="82" t="n"/>
-      <c r="AO98" s="82" t="n"/>
-      <c r="AP98" s="82" t="n"/>
-      <c r="AQ98" s="82" t="n"/>
-      <c r="AR98" s="82" t="n"/>
     </row>
     <row r="99" ht="22.05" customHeight="1">
       <c r="A99" s="66" t="n">
@@ -22740,35 +19363,6 @@
       <c r="M99" s="73" t="n"/>
       <c r="N99" s="73" t="n"/>
       <c r="O99" s="73" t="n"/>
-      <c r="P99" s="73" t="n"/>
-      <c r="Q99" s="73" t="n"/>
-      <c r="R99" s="73" t="n"/>
-      <c r="S99" s="73" t="n"/>
-      <c r="T99" s="73" t="n"/>
-      <c r="U99" s="73" t="n"/>
-      <c r="V99" s="73" t="n"/>
-      <c r="W99" s="73" t="n"/>
-      <c r="X99" s="73" t="n"/>
-      <c r="Y99" s="73" t="n"/>
-      <c r="Z99" s="73" t="n"/>
-      <c r="AA99" s="73" t="n"/>
-      <c r="AB99" s="73" t="n"/>
-      <c r="AC99" s="73" t="n"/>
-      <c r="AD99" s="73" t="n"/>
-      <c r="AE99" s="73" t="n"/>
-      <c r="AF99" s="73" t="n"/>
-      <c r="AG99" s="73" t="n"/>
-      <c r="AH99" s="73" t="n"/>
-      <c r="AI99" s="73" t="n"/>
-      <c r="AJ99" s="73" t="n"/>
-      <c r="AK99" s="73" t="n"/>
-      <c r="AL99" s="73" t="n"/>
-      <c r="AM99" s="73" t="n"/>
-      <c r="AN99" s="73" t="n"/>
-      <c r="AO99" s="73" t="n"/>
-      <c r="AP99" s="73" t="n"/>
-      <c r="AQ99" s="73" t="n"/>
-      <c r="AR99" s="73" t="n"/>
     </row>
     <row r="100" ht="22.05" customHeight="1">
       <c r="A100" s="75" t="n">
@@ -22812,35 +19406,6 @@
       <c r="M100" s="82" t="n"/>
       <c r="N100" s="82" t="n"/>
       <c r="O100" s="82" t="n"/>
-      <c r="P100" s="82" t="n"/>
-      <c r="Q100" s="82" t="n"/>
-      <c r="R100" s="82" t="n"/>
-      <c r="S100" s="82" t="n"/>
-      <c r="T100" s="82" t="n"/>
-      <c r="U100" s="82" t="n"/>
-      <c r="V100" s="82" t="n"/>
-      <c r="W100" s="82" t="n"/>
-      <c r="X100" s="82" t="n"/>
-      <c r="Y100" s="82" t="n"/>
-      <c r="Z100" s="82" t="n"/>
-      <c r="AA100" s="82" t="n"/>
-      <c r="AB100" s="82" t="n"/>
-      <c r="AC100" s="82" t="n"/>
-      <c r="AD100" s="82" t="n"/>
-      <c r="AE100" s="82" t="n"/>
-      <c r="AF100" s="82" t="n"/>
-      <c r="AG100" s="82" t="n"/>
-      <c r="AH100" s="82" t="n"/>
-      <c r="AI100" s="82" t="n"/>
-      <c r="AJ100" s="82" t="n"/>
-      <c r="AK100" s="82" t="n"/>
-      <c r="AL100" s="82" t="n"/>
-      <c r="AM100" s="82" t="n"/>
-      <c r="AN100" s="82" t="n"/>
-      <c r="AO100" s="82" t="n"/>
-      <c r="AP100" s="82" t="n"/>
-      <c r="AQ100" s="82" t="n"/>
-      <c r="AR100" s="82" t="n"/>
     </row>
     <row r="101" ht="22.05" customHeight="1">
       <c r="A101" s="66" t="n">
@@ -22884,35 +19449,6 @@
       <c r="M101" s="73" t="n"/>
       <c r="N101" s="73" t="n"/>
       <c r="O101" s="73" t="n"/>
-      <c r="P101" s="73" t="n"/>
-      <c r="Q101" s="73" t="n"/>
-      <c r="R101" s="73" t="n"/>
-      <c r="S101" s="73" t="n"/>
-      <c r="T101" s="73" t="n"/>
-      <c r="U101" s="73" t="n"/>
-      <c r="V101" s="73" t="n"/>
-      <c r="W101" s="73" t="n"/>
-      <c r="X101" s="73" t="n"/>
-      <c r="Y101" s="73" t="n"/>
-      <c r="Z101" s="73" t="n"/>
-      <c r="AA101" s="73" t="n"/>
-      <c r="AB101" s="73" t="n"/>
-      <c r="AC101" s="73" t="n"/>
-      <c r="AD101" s="73" t="n"/>
-      <c r="AE101" s="73" t="n"/>
-      <c r="AF101" s="73" t="n"/>
-      <c r="AG101" s="73" t="n"/>
-      <c r="AH101" s="73" t="n"/>
-      <c r="AI101" s="73" t="n"/>
-      <c r="AJ101" s="73" t="n"/>
-      <c r="AK101" s="73" t="n"/>
-      <c r="AL101" s="73" t="n"/>
-      <c r="AM101" s="73" t="n"/>
-      <c r="AN101" s="73" t="n"/>
-      <c r="AO101" s="73" t="n"/>
-      <c r="AP101" s="73" t="n"/>
-      <c r="AQ101" s="73" t="n"/>
-      <c r="AR101" s="73" t="n"/>
     </row>
     <row r="102" ht="22.05" customHeight="1">
       <c r="A102" s="75" t="n">
@@ -22956,35 +19492,6 @@
       <c r="M102" s="82" t="n"/>
       <c r="N102" s="82" t="n"/>
       <c r="O102" s="82" t="n"/>
-      <c r="P102" s="82" t="n"/>
-      <c r="Q102" s="82" t="n"/>
-      <c r="R102" s="82" t="n"/>
-      <c r="S102" s="82" t="n"/>
-      <c r="T102" s="82" t="n"/>
-      <c r="U102" s="82" t="n"/>
-      <c r="V102" s="82" t="n"/>
-      <c r="W102" s="82" t="n"/>
-      <c r="X102" s="82" t="n"/>
-      <c r="Y102" s="82" t="n"/>
-      <c r="Z102" s="82" t="n"/>
-      <c r="AA102" s="82" t="n"/>
-      <c r="AB102" s="82" t="n"/>
-      <c r="AC102" s="82" t="n"/>
-      <c r="AD102" s="82" t="n"/>
-      <c r="AE102" s="82" t="n"/>
-      <c r="AF102" s="82" t="n"/>
-      <c r="AG102" s="82" t="n"/>
-      <c r="AH102" s="82" t="n"/>
-      <c r="AI102" s="82" t="n"/>
-      <c r="AJ102" s="82" t="n"/>
-      <c r="AK102" s="82" t="n"/>
-      <c r="AL102" s="82" t="n"/>
-      <c r="AM102" s="82" t="n"/>
-      <c r="AN102" s="82" t="n"/>
-      <c r="AO102" s="82" t="n"/>
-      <c r="AP102" s="82" t="n"/>
-      <c r="AQ102" s="82" t="n"/>
-      <c r="AR102" s="82" t="n"/>
     </row>
     <row r="103" ht="22.05" customHeight="1">
       <c r="A103" s="66" t="n">
@@ -23028,35 +19535,6 @@
       <c r="M103" s="73" t="n"/>
       <c r="N103" s="73" t="n"/>
       <c r="O103" s="73" t="n"/>
-      <c r="P103" s="73" t="n"/>
-      <c r="Q103" s="73" t="n"/>
-      <c r="R103" s="73" t="n"/>
-      <c r="S103" s="73" t="n"/>
-      <c r="T103" s="73" t="n"/>
-      <c r="U103" s="73" t="n"/>
-      <c r="V103" s="73" t="n"/>
-      <c r="W103" s="73" t="n"/>
-      <c r="X103" s="73" t="n"/>
-      <c r="Y103" s="73" t="n"/>
-      <c r="Z103" s="73" t="n"/>
-      <c r="AA103" s="73" t="n"/>
-      <c r="AB103" s="73" t="n"/>
-      <c r="AC103" s="73" t="n"/>
-      <c r="AD103" s="73" t="n"/>
-      <c r="AE103" s="73" t="n"/>
-      <c r="AF103" s="73" t="n"/>
-      <c r="AG103" s="73" t="n"/>
-      <c r="AH103" s="73" t="n"/>
-      <c r="AI103" s="73" t="n"/>
-      <c r="AJ103" s="73" t="n"/>
-      <c r="AK103" s="73" t="n"/>
-      <c r="AL103" s="73" t="n"/>
-      <c r="AM103" s="73" t="n"/>
-      <c r="AN103" s="73" t="n"/>
-      <c r="AO103" s="73" t="n"/>
-      <c r="AP103" s="73" t="n"/>
-      <c r="AQ103" s="73" t="n"/>
-      <c r="AR103" s="73" t="n"/>
     </row>
     <row r="104" ht="22.05" customHeight="1">
       <c r="A104" s="75" t="n">
@@ -23100,35 +19578,6 @@
       <c r="M104" s="82" t="n"/>
       <c r="N104" s="82" t="n"/>
       <c r="O104" s="82" t="n"/>
-      <c r="P104" s="82" t="n"/>
-      <c r="Q104" s="82" t="n"/>
-      <c r="R104" s="82" t="n"/>
-      <c r="S104" s="82" t="n"/>
-      <c r="T104" s="82" t="n"/>
-      <c r="U104" s="82" t="n"/>
-      <c r="V104" s="82" t="n"/>
-      <c r="W104" s="82" t="n"/>
-      <c r="X104" s="82" t="n"/>
-      <c r="Y104" s="82" t="n"/>
-      <c r="Z104" s="82" t="n"/>
-      <c r="AA104" s="82" t="n"/>
-      <c r="AB104" s="82" t="n"/>
-      <c r="AC104" s="82" t="n"/>
-      <c r="AD104" s="82" t="n"/>
-      <c r="AE104" s="82" t="n"/>
-      <c r="AF104" s="82" t="n"/>
-      <c r="AG104" s="82" t="n"/>
-      <c r="AH104" s="82" t="n"/>
-      <c r="AI104" s="82" t="n"/>
-      <c r="AJ104" s="82" t="n"/>
-      <c r="AK104" s="82" t="n"/>
-      <c r="AL104" s="82" t="n"/>
-      <c r="AM104" s="82" t="n"/>
-      <c r="AN104" s="82" t="n"/>
-      <c r="AO104" s="82" t="n"/>
-      <c r="AP104" s="82" t="n"/>
-      <c r="AQ104" s="82" t="n"/>
-      <c r="AR104" s="82" t="n"/>
     </row>
     <row r="105" ht="22.05" customHeight="1">
       <c r="A105" s="66" t="n">
@@ -23172,35 +19621,6 @@
       <c r="M105" s="73" t="n"/>
       <c r="N105" s="73" t="n"/>
       <c r="O105" s="73" t="n"/>
-      <c r="P105" s="73" t="n"/>
-      <c r="Q105" s="73" t="n"/>
-      <c r="R105" s="73" t="n"/>
-      <c r="S105" s="73" t="n"/>
-      <c r="T105" s="73" t="n"/>
-      <c r="U105" s="73" t="n"/>
-      <c r="V105" s="73" t="n"/>
-      <c r="W105" s="73" t="n"/>
-      <c r="X105" s="73" t="n"/>
-      <c r="Y105" s="73" t="n"/>
-      <c r="Z105" s="73" t="n"/>
-      <c r="AA105" s="73" t="n"/>
-      <c r="AB105" s="73" t="n"/>
-      <c r="AC105" s="73" t="n"/>
-      <c r="AD105" s="73" t="n"/>
-      <c r="AE105" s="73" t="n"/>
-      <c r="AF105" s="73" t="n"/>
-      <c r="AG105" s="73" t="n"/>
-      <c r="AH105" s="73" t="n"/>
-      <c r="AI105" s="73" t="n"/>
-      <c r="AJ105" s="73" t="n"/>
-      <c r="AK105" s="73" t="n"/>
-      <c r="AL105" s="73" t="n"/>
-      <c r="AM105" s="73" t="n"/>
-      <c r="AN105" s="73" t="n"/>
-      <c r="AO105" s="73" t="n"/>
-      <c r="AP105" s="73" t="n"/>
-      <c r="AQ105" s="73" t="n"/>
-      <c r="AR105" s="73" t="n"/>
     </row>
     <row r="106" ht="22.05" customHeight="1">
       <c r="A106" s="75" t="n">
@@ -23244,35 +19664,6 @@
       <c r="M106" s="82" t="n"/>
       <c r="N106" s="82" t="n"/>
       <c r="O106" s="82" t="n"/>
-      <c r="P106" s="82" t="n"/>
-      <c r="Q106" s="82" t="n"/>
-      <c r="R106" s="82" t="n"/>
-      <c r="S106" s="82" t="n"/>
-      <c r="T106" s="82" t="n"/>
-      <c r="U106" s="82" t="n"/>
-      <c r="V106" s="82" t="n"/>
-      <c r="W106" s="82" t="n"/>
-      <c r="X106" s="82" t="n"/>
-      <c r="Y106" s="82" t="n"/>
-      <c r="Z106" s="82" t="n"/>
-      <c r="AA106" s="82" t="n"/>
-      <c r="AB106" s="82" t="n"/>
-      <c r="AC106" s="82" t="n"/>
-      <c r="AD106" s="82" t="n"/>
-      <c r="AE106" s="82" t="n"/>
-      <c r="AF106" s="82" t="n"/>
-      <c r="AG106" s="82" t="n"/>
-      <c r="AH106" s="82" t="n"/>
-      <c r="AI106" s="82" t="n"/>
-      <c r="AJ106" s="82" t="n"/>
-      <c r="AK106" s="82" t="n"/>
-      <c r="AL106" s="82" t="n"/>
-      <c r="AM106" s="82" t="n"/>
-      <c r="AN106" s="82" t="n"/>
-      <c r="AO106" s="82" t="n"/>
-      <c r="AP106" s="82" t="n"/>
-      <c r="AQ106" s="82" t="n"/>
-      <c r="AR106" s="82" t="n"/>
     </row>
     <row r="107" ht="22.05" customHeight="1">
       <c r="A107" s="66" t="n">
@@ -23316,35 +19707,6 @@
       <c r="M107" s="73" t="n"/>
       <c r="N107" s="73" t="n"/>
       <c r="O107" s="73" t="n"/>
-      <c r="P107" s="73" t="n"/>
-      <c r="Q107" s="73" t="n"/>
-      <c r="R107" s="73" t="n"/>
-      <c r="S107" s="73" t="n"/>
-      <c r="T107" s="73" t="n"/>
-      <c r="U107" s="73" t="n"/>
-      <c r="V107" s="73" t="n"/>
-      <c r="W107" s="73" t="n"/>
-      <c r="X107" s="73" t="n"/>
-      <c r="Y107" s="73" t="n"/>
-      <c r="Z107" s="73" t="n"/>
-      <c r="AA107" s="73" t="n"/>
-      <c r="AB107" s="73" t="n"/>
-      <c r="AC107" s="73" t="n"/>
-      <c r="AD107" s="73" t="n"/>
-      <c r="AE107" s="73" t="n"/>
-      <c r="AF107" s="73" t="n"/>
-      <c r="AG107" s="73" t="n"/>
-      <c r="AH107" s="73" t="n"/>
-      <c r="AI107" s="73" t="n"/>
-      <c r="AJ107" s="73" t="n"/>
-      <c r="AK107" s="73" t="n"/>
-      <c r="AL107" s="73" t="n"/>
-      <c r="AM107" s="73" t="n"/>
-      <c r="AN107" s="73" t="n"/>
-      <c r="AO107" s="73" t="n"/>
-      <c r="AP107" s="73" t="n"/>
-      <c r="AQ107" s="73" t="n"/>
-      <c r="AR107" s="73" t="n"/>
     </row>
     <row r="108" ht="22.05" customHeight="1">
       <c r="A108" s="75" t="n">
@@ -23388,35 +19750,6 @@
       <c r="M108" s="82" t="n"/>
       <c r="N108" s="82" t="n"/>
       <c r="O108" s="82" t="n"/>
-      <c r="P108" s="82" t="n"/>
-      <c r="Q108" s="82" t="n"/>
-      <c r="R108" s="82" t="n"/>
-      <c r="S108" s="82" t="n"/>
-      <c r="T108" s="82" t="n"/>
-      <c r="U108" s="82" t="n"/>
-      <c r="V108" s="82" t="n"/>
-      <c r="W108" s="82" t="n"/>
-      <c r="X108" s="82" t="n"/>
-      <c r="Y108" s="82" t="n"/>
-      <c r="Z108" s="82" t="n"/>
-      <c r="AA108" s="82" t="n"/>
-      <c r="AB108" s="82" t="n"/>
-      <c r="AC108" s="82" t="n"/>
-      <c r="AD108" s="82" t="n"/>
-      <c r="AE108" s="82" t="n"/>
-      <c r="AF108" s="82" t="n"/>
-      <c r="AG108" s="82" t="n"/>
-      <c r="AH108" s="82" t="n"/>
-      <c r="AI108" s="82" t="n"/>
-      <c r="AJ108" s="82" t="n"/>
-      <c r="AK108" s="82" t="n"/>
-      <c r="AL108" s="82" t="n"/>
-      <c r="AM108" s="82" t="n"/>
-      <c r="AN108" s="82" t="n"/>
-      <c r="AO108" s="82" t="n"/>
-      <c r="AP108" s="82" t="n"/>
-      <c r="AQ108" s="82" t="n"/>
-      <c r="AR108" s="82" t="n"/>
     </row>
     <row r="109" ht="22.05" customHeight="1">
       <c r="A109" s="66" t="n">
@@ -23456,35 +19789,6 @@
       <c r="M109" s="73" t="n"/>
       <c r="N109" s="73" t="n"/>
       <c r="O109" s="73" t="n"/>
-      <c r="P109" s="73" t="n"/>
-      <c r="Q109" s="73" t="n"/>
-      <c r="R109" s="73" t="n"/>
-      <c r="S109" s="73" t="n"/>
-      <c r="T109" s="73" t="n"/>
-      <c r="U109" s="73" t="n"/>
-      <c r="V109" s="73" t="n"/>
-      <c r="W109" s="73" t="n"/>
-      <c r="X109" s="73" t="n"/>
-      <c r="Y109" s="73" t="n"/>
-      <c r="Z109" s="73" t="n"/>
-      <c r="AA109" s="73" t="n"/>
-      <c r="AB109" s="73" t="n"/>
-      <c r="AC109" s="73" t="n"/>
-      <c r="AD109" s="73" t="n"/>
-      <c r="AE109" s="73" t="n"/>
-      <c r="AF109" s="73" t="n"/>
-      <c r="AG109" s="73" t="n"/>
-      <c r="AH109" s="73" t="n"/>
-      <c r="AI109" s="73" t="n"/>
-      <c r="AJ109" s="73" t="n"/>
-      <c r="AK109" s="73" t="n"/>
-      <c r="AL109" s="73" t="n"/>
-      <c r="AM109" s="73" t="n"/>
-      <c r="AN109" s="73" t="n"/>
-      <c r="AO109" s="73" t="n"/>
-      <c r="AP109" s="73" t="n"/>
-      <c r="AQ109" s="73" t="n"/>
-      <c r="AR109" s="73" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="75" t="n">
@@ -23524,35 +19828,6 @@
       <c r="M110" s="82" t="n"/>
       <c r="N110" s="82" t="n"/>
       <c r="O110" s="82" t="n"/>
-      <c r="P110" s="82" t="n"/>
-      <c r="Q110" s="82" t="n"/>
-      <c r="R110" s="82" t="n"/>
-      <c r="S110" s="82" t="n"/>
-      <c r="T110" s="82" t="n"/>
-      <c r="U110" s="82" t="n"/>
-      <c r="V110" s="82" t="n"/>
-      <c r="W110" s="82" t="n"/>
-      <c r="X110" s="82" t="n"/>
-      <c r="Y110" s="82" t="n"/>
-      <c r="Z110" s="82" t="n"/>
-      <c r="AA110" s="82" t="n"/>
-      <c r="AB110" s="82" t="n"/>
-      <c r="AC110" s="82" t="n"/>
-      <c r="AD110" s="82" t="n"/>
-      <c r="AE110" s="82" t="n"/>
-      <c r="AF110" s="82" t="n"/>
-      <c r="AG110" s="82" t="n"/>
-      <c r="AH110" s="82" t="n"/>
-      <c r="AI110" s="82" t="n"/>
-      <c r="AJ110" s="82" t="n"/>
-      <c r="AK110" s="82" t="n"/>
-      <c r="AL110" s="82" t="n"/>
-      <c r="AM110" s="82" t="n"/>
-      <c r="AN110" s="82" t="n"/>
-      <c r="AO110" s="82" t="n"/>
-      <c r="AP110" s="82" t="n"/>
-      <c r="AQ110" s="82" t="n"/>
-      <c r="AR110" s="82" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="66" t="n"/>
@@ -23570,35 +19845,6 @@
       <c r="M111" s="66" t="n"/>
       <c r="N111" s="66" t="n"/>
       <c r="O111" s="66" t="n"/>
-      <c r="P111" s="66" t="n"/>
-      <c r="Q111" s="66" t="n"/>
-      <c r="R111" s="66" t="n"/>
-      <c r="S111" s="66" t="n"/>
-      <c r="T111" s="66" t="n"/>
-      <c r="U111" s="66" t="n"/>
-      <c r="V111" s="66" t="n"/>
-      <c r="W111" s="66" t="n"/>
-      <c r="X111" s="66" t="n"/>
-      <c r="Y111" s="66" t="n"/>
-      <c r="Z111" s="66" t="n"/>
-      <c r="AA111" s="66" t="n"/>
-      <c r="AB111" s="66" t="n"/>
-      <c r="AC111" s="66" t="n"/>
-      <c r="AD111" s="66" t="n"/>
-      <c r="AE111" s="66" t="n"/>
-      <c r="AF111" s="66" t="n"/>
-      <c r="AG111" s="66" t="n"/>
-      <c r="AH111" s="66" t="n"/>
-      <c r="AI111" s="66" t="n"/>
-      <c r="AJ111" s="66" t="n"/>
-      <c r="AK111" s="66" t="n"/>
-      <c r="AL111" s="66" t="n"/>
-      <c r="AM111" s="66" t="n"/>
-      <c r="AN111" s="66" t="n"/>
-      <c r="AO111" s="66" t="n"/>
-      <c r="AP111" s="66" t="n"/>
-      <c r="AQ111" s="66" t="n"/>
-      <c r="AR111" s="66" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="75" t="n"/>
@@ -23616,35 +19862,6 @@
       <c r="M112" s="75" t="n"/>
       <c r="N112" s="75" t="n"/>
       <c r="O112" s="75" t="n"/>
-      <c r="P112" s="75" t="n"/>
-      <c r="Q112" s="75" t="n"/>
-      <c r="R112" s="75" t="n"/>
-      <c r="S112" s="75" t="n"/>
-      <c r="T112" s="75" t="n"/>
-      <c r="U112" s="75" t="n"/>
-      <c r="V112" s="75" t="n"/>
-      <c r="W112" s="75" t="n"/>
-      <c r="X112" s="75" t="n"/>
-      <c r="Y112" s="75" t="n"/>
-      <c r="Z112" s="75" t="n"/>
-      <c r="AA112" s="75" t="n"/>
-      <c r="AB112" s="75" t="n"/>
-      <c r="AC112" s="75" t="n"/>
-      <c r="AD112" s="75" t="n"/>
-      <c r="AE112" s="75" t="n"/>
-      <c r="AF112" s="75" t="n"/>
-      <c r="AG112" s="75" t="n"/>
-      <c r="AH112" s="75" t="n"/>
-      <c r="AI112" s="75" t="n"/>
-      <c r="AJ112" s="75" t="n"/>
-      <c r="AK112" s="75" t="n"/>
-      <c r="AL112" s="75" t="n"/>
-      <c r="AM112" s="75" t="n"/>
-      <c r="AN112" s="75" t="n"/>
-      <c r="AO112" s="75" t="n"/>
-      <c r="AP112" s="75" t="n"/>
-      <c r="AQ112" s="75" t="n"/>
-      <c r="AR112" s="75" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="66" t="n"/>
@@ -23662,35 +19879,6 @@
       <c r="M113" s="66" t="n"/>
       <c r="N113" s="66" t="n"/>
       <c r="O113" s="66" t="n"/>
-      <c r="P113" s="66" t="n"/>
-      <c r="Q113" s="66" t="n"/>
-      <c r="R113" s="66" t="n"/>
-      <c r="S113" s="66" t="n"/>
-      <c r="T113" s="66" t="n"/>
-      <c r="U113" s="66" t="n"/>
-      <c r="V113" s="66" t="n"/>
-      <c r="W113" s="66" t="n"/>
-      <c r="X113" s="66" t="n"/>
-      <c r="Y113" s="66" t="n"/>
-      <c r="Z113" s="66" t="n"/>
-      <c r="AA113" s="66" t="n"/>
-      <c r="AB113" s="66" t="n"/>
-      <c r="AC113" s="66" t="n"/>
-      <c r="AD113" s="66" t="n"/>
-      <c r="AE113" s="66" t="n"/>
-      <c r="AF113" s="66" t="n"/>
-      <c r="AG113" s="66" t="n"/>
-      <c r="AH113" s="66" t="n"/>
-      <c r="AI113" s="66" t="n"/>
-      <c r="AJ113" s="66" t="n"/>
-      <c r="AK113" s="66" t="n"/>
-      <c r="AL113" s="66" t="n"/>
-      <c r="AM113" s="66" t="n"/>
-      <c r="AN113" s="66" t="n"/>
-      <c r="AO113" s="66" t="n"/>
-      <c r="AP113" s="66" t="n"/>
-      <c r="AQ113" s="66" t="n"/>
-      <c r="AR113" s="66" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="75" t="n"/>
@@ -23708,35 +19896,6 @@
       <c r="M114" s="75" t="n"/>
       <c r="N114" s="75" t="n"/>
       <c r="O114" s="75" t="n"/>
-      <c r="P114" s="75" t="n"/>
-      <c r="Q114" s="75" t="n"/>
-      <c r="R114" s="75" t="n"/>
-      <c r="S114" s="75" t="n"/>
-      <c r="T114" s="75" t="n"/>
-      <c r="U114" s="75" t="n"/>
-      <c r="V114" s="75" t="n"/>
-      <c r="W114" s="75" t="n"/>
-      <c r="X114" s="75" t="n"/>
-      <c r="Y114" s="75" t="n"/>
-      <c r="Z114" s="75" t="n"/>
-      <c r="AA114" s="75" t="n"/>
-      <c r="AB114" s="75" t="n"/>
-      <c r="AC114" s="75" t="n"/>
-      <c r="AD114" s="75" t="n"/>
-      <c r="AE114" s="75" t="n"/>
-      <c r="AF114" s="75" t="n"/>
-      <c r="AG114" s="75" t="n"/>
-      <c r="AH114" s="75" t="n"/>
-      <c r="AI114" s="75" t="n"/>
-      <c r="AJ114" s="75" t="n"/>
-      <c r="AK114" s="75" t="n"/>
-      <c r="AL114" s="75" t="n"/>
-      <c r="AM114" s="75" t="n"/>
-      <c r="AN114" s="75" t="n"/>
-      <c r="AO114" s="75" t="n"/>
-      <c r="AP114" s="75" t="n"/>
-      <c r="AQ114" s="75" t="n"/>
-      <c r="AR114" s="75" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="66" t="n"/>
@@ -23754,35 +19913,6 @@
       <c r="M115" s="66" t="n"/>
       <c r="N115" s="66" t="n"/>
       <c r="O115" s="66" t="n"/>
-      <c r="P115" s="66" t="n"/>
-      <c r="Q115" s="66" t="n"/>
-      <c r="R115" s="66" t="n"/>
-      <c r="S115" s="66" t="n"/>
-      <c r="T115" s="66" t="n"/>
-      <c r="U115" s="66" t="n"/>
-      <c r="V115" s="66" t="n"/>
-      <c r="W115" s="66" t="n"/>
-      <c r="X115" s="66" t="n"/>
-      <c r="Y115" s="66" t="n"/>
-      <c r="Z115" s="66" t="n"/>
-      <c r="AA115" s="66" t="n"/>
-      <c r="AB115" s="66" t="n"/>
-      <c r="AC115" s="66" t="n"/>
-      <c r="AD115" s="66" t="n"/>
-      <c r="AE115" s="66" t="n"/>
-      <c r="AF115" s="66" t="n"/>
-      <c r="AG115" s="66" t="n"/>
-      <c r="AH115" s="66" t="n"/>
-      <c r="AI115" s="66" t="n"/>
-      <c r="AJ115" s="66" t="n"/>
-      <c r="AK115" s="66" t="n"/>
-      <c r="AL115" s="66" t="n"/>
-      <c r="AM115" s="66" t="n"/>
-      <c r="AN115" s="66" t="n"/>
-      <c r="AO115" s="66" t="n"/>
-      <c r="AP115" s="66" t="n"/>
-      <c r="AQ115" s="66" t="n"/>
-      <c r="AR115" s="66" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="75" t="n"/>
@@ -23800,35 +19930,6 @@
       <c r="M116" s="75" t="n"/>
       <c r="N116" s="75" t="n"/>
       <c r="O116" s="75" t="n"/>
-      <c r="P116" s="75" t="n"/>
-      <c r="Q116" s="75" t="n"/>
-      <c r="R116" s="75" t="n"/>
-      <c r="S116" s="75" t="n"/>
-      <c r="T116" s="75" t="n"/>
-      <c r="U116" s="75" t="n"/>
-      <c r="V116" s="75" t="n"/>
-      <c r="W116" s="75" t="n"/>
-      <c r="X116" s="75" t="n"/>
-      <c r="Y116" s="75" t="n"/>
-      <c r="Z116" s="75" t="n"/>
-      <c r="AA116" s="75" t="n"/>
-      <c r="AB116" s="75" t="n"/>
-      <c r="AC116" s="75" t="n"/>
-      <c r="AD116" s="75" t="n"/>
-      <c r="AE116" s="75" t="n"/>
-      <c r="AF116" s="75" t="n"/>
-      <c r="AG116" s="75" t="n"/>
-      <c r="AH116" s="75" t="n"/>
-      <c r="AI116" s="75" t="n"/>
-      <c r="AJ116" s="75" t="n"/>
-      <c r="AK116" s="75" t="n"/>
-      <c r="AL116" s="75" t="n"/>
-      <c r="AM116" s="75" t="n"/>
-      <c r="AN116" s="75" t="n"/>
-      <c r="AO116" s="75" t="n"/>
-      <c r="AP116" s="75" t="n"/>
-      <c r="AQ116" s="75" t="n"/>
-      <c r="AR116" s="75" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="66" t="n"/>
@@ -23846,35 +19947,6 @@
       <c r="M117" s="66" t="n"/>
       <c r="N117" s="66" t="n"/>
       <c r="O117" s="66" t="n"/>
-      <c r="P117" s="66" t="n"/>
-      <c r="Q117" s="66" t="n"/>
-      <c r="R117" s="66" t="n"/>
-      <c r="S117" s="66" t="n"/>
-      <c r="T117" s="66" t="n"/>
-      <c r="U117" s="66" t="n"/>
-      <c r="V117" s="66" t="n"/>
-      <c r="W117" s="66" t="n"/>
-      <c r="X117" s="66" t="n"/>
-      <c r="Y117" s="66" t="n"/>
-      <c r="Z117" s="66" t="n"/>
-      <c r="AA117" s="66" t="n"/>
-      <c r="AB117" s="66" t="n"/>
-      <c r="AC117" s="66" t="n"/>
-      <c r="AD117" s="66" t="n"/>
-      <c r="AE117" s="66" t="n"/>
-      <c r="AF117" s="66" t="n"/>
-      <c r="AG117" s="66" t="n"/>
-      <c r="AH117" s="66" t="n"/>
-      <c r="AI117" s="66" t="n"/>
-      <c r="AJ117" s="66" t="n"/>
-      <c r="AK117" s="66" t="n"/>
-      <c r="AL117" s="66" t="n"/>
-      <c r="AM117" s="66" t="n"/>
-      <c r="AN117" s="66" t="n"/>
-      <c r="AO117" s="66" t="n"/>
-      <c r="AP117" s="66" t="n"/>
-      <c r="AQ117" s="66" t="n"/>
-      <c r="AR117" s="66" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="75" t="n"/>
@@ -23892,35 +19964,6 @@
       <c r="M118" s="75" t="n"/>
       <c r="N118" s="75" t="n"/>
       <c r="O118" s="75" t="n"/>
-      <c r="P118" s="75" t="n"/>
-      <c r="Q118" s="75" t="n"/>
-      <c r="R118" s="75" t="n"/>
-      <c r="S118" s="75" t="n"/>
-      <c r="T118" s="75" t="n"/>
-      <c r="U118" s="75" t="n"/>
-      <c r="V118" s="75" t="n"/>
-      <c r="W118" s="75" t="n"/>
-      <c r="X118" s="75" t="n"/>
-      <c r="Y118" s="75" t="n"/>
-      <c r="Z118" s="75" t="n"/>
-      <c r="AA118" s="75" t="n"/>
-      <c r="AB118" s="75" t="n"/>
-      <c r="AC118" s="75" t="n"/>
-      <c r="AD118" s="75" t="n"/>
-      <c r="AE118" s="75" t="n"/>
-      <c r="AF118" s="75" t="n"/>
-      <c r="AG118" s="75" t="n"/>
-      <c r="AH118" s="75" t="n"/>
-      <c r="AI118" s="75" t="n"/>
-      <c r="AJ118" s="75" t="n"/>
-      <c r="AK118" s="75" t="n"/>
-      <c r="AL118" s="75" t="n"/>
-      <c r="AM118" s="75" t="n"/>
-      <c r="AN118" s="75" t="n"/>
-      <c r="AO118" s="75" t="n"/>
-      <c r="AP118" s="75" t="n"/>
-      <c r="AQ118" s="75" t="n"/>
-      <c r="AR118" s="75" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="66" t="n"/>
@@ -23938,35 +19981,6 @@
       <c r="M119" s="66" t="n"/>
       <c r="N119" s="66" t="n"/>
       <c r="O119" s="66" t="n"/>
-      <c r="P119" s="66" t="n"/>
-      <c r="Q119" s="66" t="n"/>
-      <c r="R119" s="66" t="n"/>
-      <c r="S119" s="66" t="n"/>
-      <c r="T119" s="66" t="n"/>
-      <c r="U119" s="66" t="n"/>
-      <c r="V119" s="66" t="n"/>
-      <c r="W119" s="66" t="n"/>
-      <c r="X119" s="66" t="n"/>
-      <c r="Y119" s="66" t="n"/>
-      <c r="Z119" s="66" t="n"/>
-      <c r="AA119" s="66" t="n"/>
-      <c r="AB119" s="66" t="n"/>
-      <c r="AC119" s="66" t="n"/>
-      <c r="AD119" s="66" t="n"/>
-      <c r="AE119" s="66" t="n"/>
-      <c r="AF119" s="66" t="n"/>
-      <c r="AG119" s="66" t="n"/>
-      <c r="AH119" s="66" t="n"/>
-      <c r="AI119" s="66" t="n"/>
-      <c r="AJ119" s="66" t="n"/>
-      <c r="AK119" s="66" t="n"/>
-      <c r="AL119" s="66" t="n"/>
-      <c r="AM119" s="66" t="n"/>
-      <c r="AN119" s="66" t="n"/>
-      <c r="AO119" s="66" t="n"/>
-      <c r="AP119" s="66" t="n"/>
-      <c r="AQ119" s="66" t="n"/>
-      <c r="AR119" s="66" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="75" t="n"/>
@@ -23984,35 +19998,6 @@
       <c r="M120" s="75" t="n"/>
       <c r="N120" s="75" t="n"/>
       <c r="O120" s="75" t="n"/>
-      <c r="P120" s="75" t="n"/>
-      <c r="Q120" s="75" t="n"/>
-      <c r="R120" s="75" t="n"/>
-      <c r="S120" s="75" t="n"/>
-      <c r="T120" s="75" t="n"/>
-      <c r="U120" s="75" t="n"/>
-      <c r="V120" s="75" t="n"/>
-      <c r="W120" s="75" t="n"/>
-      <c r="X120" s="75" t="n"/>
-      <c r="Y120" s="75" t="n"/>
-      <c r="Z120" s="75" t="n"/>
-      <c r="AA120" s="75" t="n"/>
-      <c r="AB120" s="75" t="n"/>
-      <c r="AC120" s="75" t="n"/>
-      <c r="AD120" s="75" t="n"/>
-      <c r="AE120" s="75" t="n"/>
-      <c r="AF120" s="75" t="n"/>
-      <c r="AG120" s="75" t="n"/>
-      <c r="AH120" s="75" t="n"/>
-      <c r="AI120" s="75" t="n"/>
-      <c r="AJ120" s="75" t="n"/>
-      <c r="AK120" s="75" t="n"/>
-      <c r="AL120" s="75" t="n"/>
-      <c r="AM120" s="75" t="n"/>
-      <c r="AN120" s="75" t="n"/>
-      <c r="AO120" s="75" t="n"/>
-      <c r="AP120" s="75" t="n"/>
-      <c r="AQ120" s="75" t="n"/>
-      <c r="AR120" s="75" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="66" t="n"/>
@@ -24030,35 +20015,6 @@
       <c r="M121" s="66" t="n"/>
       <c r="N121" s="66" t="n"/>
       <c r="O121" s="66" t="n"/>
-      <c r="P121" s="66" t="n"/>
-      <c r="Q121" s="66" t="n"/>
-      <c r="R121" s="66" t="n"/>
-      <c r="S121" s="66" t="n"/>
-      <c r="T121" s="66" t="n"/>
-      <c r="U121" s="66" t="n"/>
-      <c r="V121" s="66" t="n"/>
-      <c r="W121" s="66" t="n"/>
-      <c r="X121" s="66" t="n"/>
-      <c r="Y121" s="66" t="n"/>
-      <c r="Z121" s="66" t="n"/>
-      <c r="AA121" s="66" t="n"/>
-      <c r="AB121" s="66" t="n"/>
-      <c r="AC121" s="66" t="n"/>
-      <c r="AD121" s="66" t="n"/>
-      <c r="AE121" s="66" t="n"/>
-      <c r="AF121" s="66" t="n"/>
-      <c r="AG121" s="66" t="n"/>
-      <c r="AH121" s="66" t="n"/>
-      <c r="AI121" s="66" t="n"/>
-      <c r="AJ121" s="66" t="n"/>
-      <c r="AK121" s="66" t="n"/>
-      <c r="AL121" s="66" t="n"/>
-      <c r="AM121" s="66" t="n"/>
-      <c r="AN121" s="66" t="n"/>
-      <c r="AO121" s="66" t="n"/>
-      <c r="AP121" s="66" t="n"/>
-      <c r="AQ121" s="66" t="n"/>
-      <c r="AR121" s="66" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="75" t="n"/>
@@ -24076,35 +20032,6 @@
       <c r="M122" s="75" t="n"/>
       <c r="N122" s="75" t="n"/>
       <c r="O122" s="75" t="n"/>
-      <c r="P122" s="75" t="n"/>
-      <c r="Q122" s="75" t="n"/>
-      <c r="R122" s="75" t="n"/>
-      <c r="S122" s="75" t="n"/>
-      <c r="T122" s="75" t="n"/>
-      <c r="U122" s="75" t="n"/>
-      <c r="V122" s="75" t="n"/>
-      <c r="W122" s="75" t="n"/>
-      <c r="X122" s="75" t="n"/>
-      <c r="Y122" s="75" t="n"/>
-      <c r="Z122" s="75" t="n"/>
-      <c r="AA122" s="75" t="n"/>
-      <c r="AB122" s="75" t="n"/>
-      <c r="AC122" s="75" t="n"/>
-      <c r="AD122" s="75" t="n"/>
-      <c r="AE122" s="75" t="n"/>
-      <c r="AF122" s="75" t="n"/>
-      <c r="AG122" s="75" t="n"/>
-      <c r="AH122" s="75" t="n"/>
-      <c r="AI122" s="75" t="n"/>
-      <c r="AJ122" s="75" t="n"/>
-      <c r="AK122" s="75" t="n"/>
-      <c r="AL122" s="75" t="n"/>
-      <c r="AM122" s="75" t="n"/>
-      <c r="AN122" s="75" t="n"/>
-      <c r="AO122" s="75" t="n"/>
-      <c r="AP122" s="75" t="n"/>
-      <c r="AQ122" s="75" t="n"/>
-      <c r="AR122" s="75" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="66" t="n"/>
@@ -24122,35 +20049,6 @@
       <c r="M123" s="66" t="n"/>
       <c r="N123" s="66" t="n"/>
       <c r="O123" s="66" t="n"/>
-      <c r="P123" s="66" t="n"/>
-      <c r="Q123" s="66" t="n"/>
-      <c r="R123" s="66" t="n"/>
-      <c r="S123" s="66" t="n"/>
-      <c r="T123" s="66" t="n"/>
-      <c r="U123" s="66" t="n"/>
-      <c r="V123" s="66" t="n"/>
-      <c r="W123" s="66" t="n"/>
-      <c r="X123" s="66" t="n"/>
-      <c r="Y123" s="66" t="n"/>
-      <c r="Z123" s="66" t="n"/>
-      <c r="AA123" s="66" t="n"/>
-      <c r="AB123" s="66" t="n"/>
-      <c r="AC123" s="66" t="n"/>
-      <c r="AD123" s="66" t="n"/>
-      <c r="AE123" s="66" t="n"/>
-      <c r="AF123" s="66" t="n"/>
-      <c r="AG123" s="66" t="n"/>
-      <c r="AH123" s="66" t="n"/>
-      <c r="AI123" s="66" t="n"/>
-      <c r="AJ123" s="66" t="n"/>
-      <c r="AK123" s="66" t="n"/>
-      <c r="AL123" s="66" t="n"/>
-      <c r="AM123" s="66" t="n"/>
-      <c r="AN123" s="66" t="n"/>
-      <c r="AO123" s="66" t="n"/>
-      <c r="AP123" s="66" t="n"/>
-      <c r="AQ123" s="66" t="n"/>
-      <c r="AR123" s="66" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="75" t="n"/>
@@ -24168,35 +20066,6 @@
       <c r="M124" s="75" t="n"/>
       <c r="N124" s="75" t="n"/>
       <c r="O124" s="75" t="n"/>
-      <c r="P124" s="75" t="n"/>
-      <c r="Q124" s="75" t="n"/>
-      <c r="R124" s="75" t="n"/>
-      <c r="S124" s="75" t="n"/>
-      <c r="T124" s="75" t="n"/>
-      <c r="U124" s="75" t="n"/>
-      <c r="V124" s="75" t="n"/>
-      <c r="W124" s="75" t="n"/>
-      <c r="X124" s="75" t="n"/>
-      <c r="Y124" s="75" t="n"/>
-      <c r="Z124" s="75" t="n"/>
-      <c r="AA124" s="75" t="n"/>
-      <c r="AB124" s="75" t="n"/>
-      <c r="AC124" s="75" t="n"/>
-      <c r="AD124" s="75" t="n"/>
-      <c r="AE124" s="75" t="n"/>
-      <c r="AF124" s="75" t="n"/>
-      <c r="AG124" s="75" t="n"/>
-      <c r="AH124" s="75" t="n"/>
-      <c r="AI124" s="75" t="n"/>
-      <c r="AJ124" s="75" t="n"/>
-      <c r="AK124" s="75" t="n"/>
-      <c r="AL124" s="75" t="n"/>
-      <c r="AM124" s="75" t="n"/>
-      <c r="AN124" s="75" t="n"/>
-      <c r="AO124" s="75" t="n"/>
-      <c r="AP124" s="75" t="n"/>
-      <c r="AQ124" s="75" t="n"/>
-      <c r="AR124" s="75" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="66" t="n"/>
@@ -24214,35 +20083,6 @@
       <c r="M125" s="66" t="n"/>
       <c r="N125" s="66" t="n"/>
       <c r="O125" s="66" t="n"/>
-      <c r="P125" s="66" t="n"/>
-      <c r="Q125" s="66" t="n"/>
-      <c r="R125" s="66" t="n"/>
-      <c r="S125" s="66" t="n"/>
-      <c r="T125" s="66" t="n"/>
-      <c r="U125" s="66" t="n"/>
-      <c r="V125" s="66" t="n"/>
-      <c r="W125" s="66" t="n"/>
-      <c r="X125" s="66" t="n"/>
-      <c r="Y125" s="66" t="n"/>
-      <c r="Z125" s="66" t="n"/>
-      <c r="AA125" s="66" t="n"/>
-      <c r="AB125" s="66" t="n"/>
-      <c r="AC125" s="66" t="n"/>
-      <c r="AD125" s="66" t="n"/>
-      <c r="AE125" s="66" t="n"/>
-      <c r="AF125" s="66" t="n"/>
-      <c r="AG125" s="66" t="n"/>
-      <c r="AH125" s="66" t="n"/>
-      <c r="AI125" s="66" t="n"/>
-      <c r="AJ125" s="66" t="n"/>
-      <c r="AK125" s="66" t="n"/>
-      <c r="AL125" s="66" t="n"/>
-      <c r="AM125" s="66" t="n"/>
-      <c r="AN125" s="66" t="n"/>
-      <c r="AO125" s="66" t="n"/>
-      <c r="AP125" s="66" t="n"/>
-      <c r="AQ125" s="66" t="n"/>
-      <c r="AR125" s="66" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="75" t="n"/>
@@ -24260,35 +20100,6 @@
       <c r="M126" s="75" t="n"/>
       <c r="N126" s="75" t="n"/>
       <c r="O126" s="75" t="n"/>
-      <c r="P126" s="75" t="n"/>
-      <c r="Q126" s="75" t="n"/>
-      <c r="R126" s="75" t="n"/>
-      <c r="S126" s="75" t="n"/>
-      <c r="T126" s="75" t="n"/>
-      <c r="U126" s="75" t="n"/>
-      <c r="V126" s="75" t="n"/>
-      <c r="W126" s="75" t="n"/>
-      <c r="X126" s="75" t="n"/>
-      <c r="Y126" s="75" t="n"/>
-      <c r="Z126" s="75" t="n"/>
-      <c r="AA126" s="75" t="n"/>
-      <c r="AB126" s="75" t="n"/>
-      <c r="AC126" s="75" t="n"/>
-      <c r="AD126" s="75" t="n"/>
-      <c r="AE126" s="75" t="n"/>
-      <c r="AF126" s="75" t="n"/>
-      <c r="AG126" s="75" t="n"/>
-      <c r="AH126" s="75" t="n"/>
-      <c r="AI126" s="75" t="n"/>
-      <c r="AJ126" s="75" t="n"/>
-      <c r="AK126" s="75" t="n"/>
-      <c r="AL126" s="75" t="n"/>
-      <c r="AM126" s="75" t="n"/>
-      <c r="AN126" s="75" t="n"/>
-      <c r="AO126" s="75" t="n"/>
-      <c r="AP126" s="75" t="n"/>
-      <c r="AQ126" s="75" t="n"/>
-      <c r="AR126" s="75" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="66" t="n"/>
@@ -24306,35 +20117,6 @@
       <c r="M127" s="66" t="n"/>
       <c r="N127" s="66" t="n"/>
       <c r="O127" s="66" t="n"/>
-      <c r="P127" s="66" t="n"/>
-      <c r="Q127" s="66" t="n"/>
-      <c r="R127" s="66" t="n"/>
-      <c r="S127" s="66" t="n"/>
-      <c r="T127" s="66" t="n"/>
-      <c r="U127" s="66" t="n"/>
-      <c r="V127" s="66" t="n"/>
-      <c r="W127" s="66" t="n"/>
-      <c r="X127" s="66" t="n"/>
-      <c r="Y127" s="66" t="n"/>
-      <c r="Z127" s="66" t="n"/>
-      <c r="AA127" s="66" t="n"/>
-      <c r="AB127" s="66" t="n"/>
-      <c r="AC127" s="66" t="n"/>
-      <c r="AD127" s="66" t="n"/>
-      <c r="AE127" s="66" t="n"/>
-      <c r="AF127" s="66" t="n"/>
-      <c r="AG127" s="66" t="n"/>
-      <c r="AH127" s="66" t="n"/>
-      <c r="AI127" s="66" t="n"/>
-      <c r="AJ127" s="66" t="n"/>
-      <c r="AK127" s="66" t="n"/>
-      <c r="AL127" s="66" t="n"/>
-      <c r="AM127" s="66" t="n"/>
-      <c r="AN127" s="66" t="n"/>
-      <c r="AO127" s="66" t="n"/>
-      <c r="AP127" s="66" t="n"/>
-      <c r="AQ127" s="66" t="n"/>
-      <c r="AR127" s="66" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="75" t="n"/>
@@ -24352,35 +20134,6 @@
       <c r="M128" s="75" t="n"/>
       <c r="N128" s="75" t="n"/>
       <c r="O128" s="75" t="n"/>
-      <c r="P128" s="75" t="n"/>
-      <c r="Q128" s="75" t="n"/>
-      <c r="R128" s="75" t="n"/>
-      <c r="S128" s="75" t="n"/>
-      <c r="T128" s="75" t="n"/>
-      <c r="U128" s="75" t="n"/>
-      <c r="V128" s="75" t="n"/>
-      <c r="W128" s="75" t="n"/>
-      <c r="X128" s="75" t="n"/>
-      <c r="Y128" s="75" t="n"/>
-      <c r="Z128" s="75" t="n"/>
-      <c r="AA128" s="75" t="n"/>
-      <c r="AB128" s="75" t="n"/>
-      <c r="AC128" s="75" t="n"/>
-      <c r="AD128" s="75" t="n"/>
-      <c r="AE128" s="75" t="n"/>
-      <c r="AF128" s="75" t="n"/>
-      <c r="AG128" s="75" t="n"/>
-      <c r="AH128" s="75" t="n"/>
-      <c r="AI128" s="75" t="n"/>
-      <c r="AJ128" s="75" t="n"/>
-      <c r="AK128" s="75" t="n"/>
-      <c r="AL128" s="75" t="n"/>
-      <c r="AM128" s="75" t="n"/>
-      <c r="AN128" s="75" t="n"/>
-      <c r="AO128" s="75" t="n"/>
-      <c r="AP128" s="75" t="n"/>
-      <c r="AQ128" s="75" t="n"/>
-      <c r="AR128" s="75" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="66" t="n"/>
@@ -24398,35 +20151,6 @@
       <c r="M129" s="66" t="n"/>
       <c r="N129" s="66" t="n"/>
       <c r="O129" s="66" t="n"/>
-      <c r="P129" s="66" t="n"/>
-      <c r="Q129" s="66" t="n"/>
-      <c r="R129" s="66" t="n"/>
-      <c r="S129" s="66" t="n"/>
-      <c r="T129" s="66" t="n"/>
-      <c r="U129" s="66" t="n"/>
-      <c r="V129" s="66" t="n"/>
-      <c r="W129" s="66" t="n"/>
-      <c r="X129" s="66" t="n"/>
-      <c r="Y129" s="66" t="n"/>
-      <c r="Z129" s="66" t="n"/>
-      <c r="AA129" s="66" t="n"/>
-      <c r="AB129" s="66" t="n"/>
-      <c r="AC129" s="66" t="n"/>
-      <c r="AD129" s="66" t="n"/>
-      <c r="AE129" s="66" t="n"/>
-      <c r="AF129" s="66" t="n"/>
-      <c r="AG129" s="66" t="n"/>
-      <c r="AH129" s="66" t="n"/>
-      <c r="AI129" s="66" t="n"/>
-      <c r="AJ129" s="66" t="n"/>
-      <c r="AK129" s="66" t="n"/>
-      <c r="AL129" s="66" t="n"/>
-      <c r="AM129" s="66" t="n"/>
-      <c r="AN129" s="66" t="n"/>
-      <c r="AO129" s="66" t="n"/>
-      <c r="AP129" s="66" t="n"/>
-      <c r="AQ129" s="66" t="n"/>
-      <c r="AR129" s="66" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="75" t="n"/>
@@ -24444,35 +20168,6 @@
       <c r="M130" s="75" t="n"/>
       <c r="N130" s="75" t="n"/>
       <c r="O130" s="75" t="n"/>
-      <c r="P130" s="75" t="n"/>
-      <c r="Q130" s="75" t="n"/>
-      <c r="R130" s="75" t="n"/>
-      <c r="S130" s="75" t="n"/>
-      <c r="T130" s="75" t="n"/>
-      <c r="U130" s="75" t="n"/>
-      <c r="V130" s="75" t="n"/>
-      <c r="W130" s="75" t="n"/>
-      <c r="X130" s="75" t="n"/>
-      <c r="Y130" s="75" t="n"/>
-      <c r="Z130" s="75" t="n"/>
-      <c r="AA130" s="75" t="n"/>
-      <c r="AB130" s="75" t="n"/>
-      <c r="AC130" s="75" t="n"/>
-      <c r="AD130" s="75" t="n"/>
-      <c r="AE130" s="75" t="n"/>
-      <c r="AF130" s="75" t="n"/>
-      <c r="AG130" s="75" t="n"/>
-      <c r="AH130" s="75" t="n"/>
-      <c r="AI130" s="75" t="n"/>
-      <c r="AJ130" s="75" t="n"/>
-      <c r="AK130" s="75" t="n"/>
-      <c r="AL130" s="75" t="n"/>
-      <c r="AM130" s="75" t="n"/>
-      <c r="AN130" s="75" t="n"/>
-      <c r="AO130" s="75" t="n"/>
-      <c r="AP130" s="75" t="n"/>
-      <c r="AQ130" s="75" t="n"/>
-      <c r="AR130" s="75" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="66" t="n"/>
@@ -24490,35 +20185,6 @@
       <c r="M131" s="66" t="n"/>
       <c r="N131" s="66" t="n"/>
       <c r="O131" s="66" t="n"/>
-      <c r="P131" s="66" t="n"/>
-      <c r="Q131" s="66" t="n"/>
-      <c r="R131" s="66" t="n"/>
-      <c r="S131" s="66" t="n"/>
-      <c r="T131" s="66" t="n"/>
-      <c r="U131" s="66" t="n"/>
-      <c r="V131" s="66" t="n"/>
-      <c r="W131" s="66" t="n"/>
-      <c r="X131" s="66" t="n"/>
-      <c r="Y131" s="66" t="n"/>
-      <c r="Z131" s="66" t="n"/>
-      <c r="AA131" s="66" t="n"/>
-      <c r="AB131" s="66" t="n"/>
-      <c r="AC131" s="66" t="n"/>
-      <c r="AD131" s="66" t="n"/>
-      <c r="AE131" s="66" t="n"/>
-      <c r="AF131" s="66" t="n"/>
-      <c r="AG131" s="66" t="n"/>
-      <c r="AH131" s="66" t="n"/>
-      <c r="AI131" s="66" t="n"/>
-      <c r="AJ131" s="66" t="n"/>
-      <c r="AK131" s="66" t="n"/>
-      <c r="AL131" s="66" t="n"/>
-      <c r="AM131" s="66" t="n"/>
-      <c r="AN131" s="66" t="n"/>
-      <c r="AO131" s="66" t="n"/>
-      <c r="AP131" s="66" t="n"/>
-      <c r="AQ131" s="66" t="n"/>
-      <c r="AR131" s="66" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="75" t="n"/>
@@ -24536,35 +20202,6 @@
       <c r="M132" s="75" t="n"/>
       <c r="N132" s="75" t="n"/>
       <c r="O132" s="75" t="n"/>
-      <c r="P132" s="75" t="n"/>
-      <c r="Q132" s="75" t="n"/>
-      <c r="R132" s="75" t="n"/>
-      <c r="S132" s="75" t="n"/>
-      <c r="T132" s="75" t="n"/>
-      <c r="U132" s="75" t="n"/>
-      <c r="V132" s="75" t="n"/>
-      <c r="W132" s="75" t="n"/>
-      <c r="X132" s="75" t="n"/>
-      <c r="Y132" s="75" t="n"/>
-      <c r="Z132" s="75" t="n"/>
-      <c r="AA132" s="75" t="n"/>
-      <c r="AB132" s="75" t="n"/>
-      <c r="AC132" s="75" t="n"/>
-      <c r="AD132" s="75" t="n"/>
-      <c r="AE132" s="75" t="n"/>
-      <c r="AF132" s="75" t="n"/>
-      <c r="AG132" s="75" t="n"/>
-      <c r="AH132" s="75" t="n"/>
-      <c r="AI132" s="75" t="n"/>
-      <c r="AJ132" s="75" t="n"/>
-      <c r="AK132" s="75" t="n"/>
-      <c r="AL132" s="75" t="n"/>
-      <c r="AM132" s="75" t="n"/>
-      <c r="AN132" s="75" t="n"/>
-      <c r="AO132" s="75" t="n"/>
-      <c r="AP132" s="75" t="n"/>
-      <c r="AQ132" s="75" t="n"/>
-      <c r="AR132" s="75" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="66" t="n"/>
@@ -24582,35 +20219,6 @@
       <c r="M133" s="66" t="n"/>
       <c r="N133" s="66" t="n"/>
       <c r="O133" s="66" t="n"/>
-      <c r="P133" s="66" t="n"/>
-      <c r="Q133" s="66" t="n"/>
-      <c r="R133" s="66" t="n"/>
-      <c r="S133" s="66" t="n"/>
-      <c r="T133" s="66" t="n"/>
-      <c r="U133" s="66" t="n"/>
-      <c r="V133" s="66" t="n"/>
-      <c r="W133" s="66" t="n"/>
-      <c r="X133" s="66" t="n"/>
-      <c r="Y133" s="66" t="n"/>
-      <c r="Z133" s="66" t="n"/>
-      <c r="AA133" s="66" t="n"/>
-      <c r="AB133" s="66" t="n"/>
-      <c r="AC133" s="66" t="n"/>
-      <c r="AD133" s="66" t="n"/>
-      <c r="AE133" s="66" t="n"/>
-      <c r="AF133" s="66" t="n"/>
-      <c r="AG133" s="66" t="n"/>
-      <c r="AH133" s="66" t="n"/>
-      <c r="AI133" s="66" t="n"/>
-      <c r="AJ133" s="66" t="n"/>
-      <c r="AK133" s="66" t="n"/>
-      <c r="AL133" s="66" t="n"/>
-      <c r="AM133" s="66" t="n"/>
-      <c r="AN133" s="66" t="n"/>
-      <c r="AO133" s="66" t="n"/>
-      <c r="AP133" s="66" t="n"/>
-      <c r="AQ133" s="66" t="n"/>
-      <c r="AR133" s="66" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="75" t="n"/>
@@ -24628,35 +20236,6 @@
       <c r="M134" s="75" t="n"/>
       <c r="N134" s="75" t="n"/>
       <c r="O134" s="75" t="n"/>
-      <c r="P134" s="75" t="n"/>
-      <c r="Q134" s="75" t="n"/>
-      <c r="R134" s="75" t="n"/>
-      <c r="S134" s="75" t="n"/>
-      <c r="T134" s="75" t="n"/>
-      <c r="U134" s="75" t="n"/>
-      <c r="V134" s="75" t="n"/>
-      <c r="W134" s="75" t="n"/>
-      <c r="X134" s="75" t="n"/>
-      <c r="Y134" s="75" t="n"/>
-      <c r="Z134" s="75" t="n"/>
-      <c r="AA134" s="75" t="n"/>
-      <c r="AB134" s="75" t="n"/>
-      <c r="AC134" s="75" t="n"/>
-      <c r="AD134" s="75" t="n"/>
-      <c r="AE134" s="75" t="n"/>
-      <c r="AF134" s="75" t="n"/>
-      <c r="AG134" s="75" t="n"/>
-      <c r="AH134" s="75" t="n"/>
-      <c r="AI134" s="75" t="n"/>
-      <c r="AJ134" s="75" t="n"/>
-      <c r="AK134" s="75" t="n"/>
-      <c r="AL134" s="75" t="n"/>
-      <c r="AM134" s="75" t="n"/>
-      <c r="AN134" s="75" t="n"/>
-      <c r="AO134" s="75" t="n"/>
-      <c r="AP134" s="75" t="n"/>
-      <c r="AQ134" s="75" t="n"/>
-      <c r="AR134" s="75" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="66" t="n"/>
@@ -24674,35 +20253,6 @@
       <c r="M135" s="66" t="n"/>
       <c r="N135" s="66" t="n"/>
       <c r="O135" s="66" t="n"/>
-      <c r="P135" s="66" t="n"/>
-      <c r="Q135" s="66" t="n"/>
-      <c r="R135" s="66" t="n"/>
-      <c r="S135" s="66" t="n"/>
-      <c r="T135" s="66" t="n"/>
-      <c r="U135" s="66" t="n"/>
-      <c r="V135" s="66" t="n"/>
-      <c r="W135" s="66" t="n"/>
-      <c r="X135" s="66" t="n"/>
-      <c r="Y135" s="66" t="n"/>
-      <c r="Z135" s="66" t="n"/>
-      <c r="AA135" s="66" t="n"/>
-      <c r="AB135" s="66" t="n"/>
-      <c r="AC135" s="66" t="n"/>
-      <c r="AD135" s="66" t="n"/>
-      <c r="AE135" s="66" t="n"/>
-      <c r="AF135" s="66" t="n"/>
-      <c r="AG135" s="66" t="n"/>
-      <c r="AH135" s="66" t="n"/>
-      <c r="AI135" s="66" t="n"/>
-      <c r="AJ135" s="66" t="n"/>
-      <c r="AK135" s="66" t="n"/>
-      <c r="AL135" s="66" t="n"/>
-      <c r="AM135" s="66" t="n"/>
-      <c r="AN135" s="66" t="n"/>
-      <c r="AO135" s="66" t="n"/>
-      <c r="AP135" s="66" t="n"/>
-      <c r="AQ135" s="66" t="n"/>
-      <c r="AR135" s="66" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="75" t="n"/>
@@ -24720,35 +20270,6 @@
       <c r="M136" s="75" t="n"/>
       <c r="N136" s="75" t="n"/>
       <c r="O136" s="75" t="n"/>
-      <c r="P136" s="75" t="n"/>
-      <c r="Q136" s="75" t="n"/>
-      <c r="R136" s="75" t="n"/>
-      <c r="S136" s="75" t="n"/>
-      <c r="T136" s="75" t="n"/>
-      <c r="U136" s="75" t="n"/>
-      <c r="V136" s="75" t="n"/>
-      <c r="W136" s="75" t="n"/>
-      <c r="X136" s="75" t="n"/>
-      <c r="Y136" s="75" t="n"/>
-      <c r="Z136" s="75" t="n"/>
-      <c r="AA136" s="75" t="n"/>
-      <c r="AB136" s="75" t="n"/>
-      <c r="AC136" s="75" t="n"/>
-      <c r="AD136" s="75" t="n"/>
-      <c r="AE136" s="75" t="n"/>
-      <c r="AF136" s="75" t="n"/>
-      <c r="AG136" s="75" t="n"/>
-      <c r="AH136" s="75" t="n"/>
-      <c r="AI136" s="75" t="n"/>
-      <c r="AJ136" s="75" t="n"/>
-      <c r="AK136" s="75" t="n"/>
-      <c r="AL136" s="75" t="n"/>
-      <c r="AM136" s="75" t="n"/>
-      <c r="AN136" s="75" t="n"/>
-      <c r="AO136" s="75" t="n"/>
-      <c r="AP136" s="75" t="n"/>
-      <c r="AQ136" s="75" t="n"/>
-      <c r="AR136" s="75" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="66" t="n"/>
@@ -24766,35 +20287,6 @@
       <c r="M137" s="66" t="n"/>
       <c r="N137" s="66" t="n"/>
       <c r="O137" s="66" t="n"/>
-      <c r="P137" s="66" t="n"/>
-      <c r="Q137" s="66" t="n"/>
-      <c r="R137" s="66" t="n"/>
-      <c r="S137" s="66" t="n"/>
-      <c r="T137" s="66" t="n"/>
-      <c r="U137" s="66" t="n"/>
-      <c r="V137" s="66" t="n"/>
-      <c r="W137" s="66" t="n"/>
-      <c r="X137" s="66" t="n"/>
-      <c r="Y137" s="66" t="n"/>
-      <c r="Z137" s="66" t="n"/>
-      <c r="AA137" s="66" t="n"/>
-      <c r="AB137" s="66" t="n"/>
-      <c r="AC137" s="66" t="n"/>
-      <c r="AD137" s="66" t="n"/>
-      <c r="AE137" s="66" t="n"/>
-      <c r="AF137" s="66" t="n"/>
-      <c r="AG137" s="66" t="n"/>
-      <c r="AH137" s="66" t="n"/>
-      <c r="AI137" s="66" t="n"/>
-      <c r="AJ137" s="66" t="n"/>
-      <c r="AK137" s="66" t="n"/>
-      <c r="AL137" s="66" t="n"/>
-      <c r="AM137" s="66" t="n"/>
-      <c r="AN137" s="66" t="n"/>
-      <c r="AO137" s="66" t="n"/>
-      <c r="AP137" s="66" t="n"/>
-      <c r="AQ137" s="66" t="n"/>
-      <c r="AR137" s="66" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="75" t="n"/>
@@ -24812,35 +20304,6 @@
       <c r="M138" s="75" t="n"/>
       <c r="N138" s="75" t="n"/>
       <c r="O138" s="75" t="n"/>
-      <c r="P138" s="75" t="n"/>
-      <c r="Q138" s="75" t="n"/>
-      <c r="R138" s="75" t="n"/>
-      <c r="S138" s="75" t="n"/>
-      <c r="T138" s="75" t="n"/>
-      <c r="U138" s="75" t="n"/>
-      <c r="V138" s="75" t="n"/>
-      <c r="W138" s="75" t="n"/>
-      <c r="X138" s="75" t="n"/>
-      <c r="Y138" s="75" t="n"/>
-      <c r="Z138" s="75" t="n"/>
-      <c r="AA138" s="75" t="n"/>
-      <c r="AB138" s="75" t="n"/>
-      <c r="AC138" s="75" t="n"/>
-      <c r="AD138" s="75" t="n"/>
-      <c r="AE138" s="75" t="n"/>
-      <c r="AF138" s="75" t="n"/>
-      <c r="AG138" s="75" t="n"/>
-      <c r="AH138" s="75" t="n"/>
-      <c r="AI138" s="75" t="n"/>
-      <c r="AJ138" s="75" t="n"/>
-      <c r="AK138" s="75" t="n"/>
-      <c r="AL138" s="75" t="n"/>
-      <c r="AM138" s="75" t="n"/>
-      <c r="AN138" s="75" t="n"/>
-      <c r="AO138" s="75" t="n"/>
-      <c r="AP138" s="75" t="n"/>
-      <c r="AQ138" s="75" t="n"/>
-      <c r="AR138" s="75" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="66" t="n"/>
@@ -24858,35 +20321,6 @@
       <c r="M139" s="66" t="n"/>
       <c r="N139" s="66" t="n"/>
       <c r="O139" s="66" t="n"/>
-      <c r="P139" s="66" t="n"/>
-      <c r="Q139" s="66" t="n"/>
-      <c r="R139" s="66" t="n"/>
-      <c r="S139" s="66" t="n"/>
-      <c r="T139" s="66" t="n"/>
-      <c r="U139" s="66" t="n"/>
-      <c r="V139" s="66" t="n"/>
-      <c r="W139" s="66" t="n"/>
-      <c r="X139" s="66" t="n"/>
-      <c r="Y139" s="66" t="n"/>
-      <c r="Z139" s="66" t="n"/>
-      <c r="AA139" s="66" t="n"/>
-      <c r="AB139" s="66" t="n"/>
-      <c r="AC139" s="66" t="n"/>
-      <c r="AD139" s="66" t="n"/>
-      <c r="AE139" s="66" t="n"/>
-      <c r="AF139" s="66" t="n"/>
-      <c r="AG139" s="66" t="n"/>
-      <c r="AH139" s="66" t="n"/>
-      <c r="AI139" s="66" t="n"/>
-      <c r="AJ139" s="66" t="n"/>
-      <c r="AK139" s="66" t="n"/>
-      <c r="AL139" s="66" t="n"/>
-      <c r="AM139" s="66" t="n"/>
-      <c r="AN139" s="66" t="n"/>
-      <c r="AO139" s="66" t="n"/>
-      <c r="AP139" s="66" t="n"/>
-      <c r="AQ139" s="66" t="n"/>
-      <c r="AR139" s="66" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="75" t="n"/>
@@ -24904,41 +20338,12 @@
       <c r="M140" s="75" t="n"/>
       <c r="N140" s="75" t="n"/>
       <c r="O140" s="75" t="n"/>
-      <c r="P140" s="75" t="n"/>
-      <c r="Q140" s="75" t="n"/>
-      <c r="R140" s="75" t="n"/>
-      <c r="S140" s="75" t="n"/>
-      <c r="T140" s="75" t="n"/>
-      <c r="U140" s="75" t="n"/>
-      <c r="V140" s="75" t="n"/>
-      <c r="W140" s="75" t="n"/>
-      <c r="X140" s="75" t="n"/>
-      <c r="Y140" s="75" t="n"/>
-      <c r="Z140" s="75" t="n"/>
-      <c r="AA140" s="75" t="n"/>
-      <c r="AB140" s="75" t="n"/>
-      <c r="AC140" s="75" t="n"/>
-      <c r="AD140" s="75" t="n"/>
-      <c r="AE140" s="75" t="n"/>
-      <c r="AF140" s="75" t="n"/>
-      <c r="AG140" s="75" t="n"/>
-      <c r="AH140" s="75" t="n"/>
-      <c r="AI140" s="75" t="n"/>
-      <c r="AJ140" s="75" t="n"/>
-      <c r="AK140" s="75" t="n"/>
-      <c r="AL140" s="75" t="n"/>
-      <c r="AM140" s="75" t="n"/>
-      <c r="AN140" s="75" t="n"/>
-      <c r="AO140" s="75" t="n"/>
-      <c r="AP140" s="75" t="n"/>
-      <c r="AQ140" s="75" t="n"/>
-      <c r="AR140" s="75" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:AN2"/>
-    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -24981,7 +20386,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -25010,7 +20415,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -25036,9 +20441,9 @@
       <c r="T2" s="91" t="n"/>
       <c r="U2" s="91" t="n"/>
       <c r="V2" s="92" t="n"/>
-      <c r="W2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="W2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -26088,7 +21493,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -26126,7 +21531,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -26161,9 +21566,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="AF2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -33983,7 +29388,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -33997,7 +29402,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -34008,9 +29413,9 @@
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="91" t="n"/>
       <c r="G2" s="92" t="n"/>
-      <c r="H2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="H2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -41341,7 +36746,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -41354,7 +36759,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -41364,9 +36769,9 @@
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="92" t="n"/>
-      <c r="G2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="G2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -45454,7 +40859,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -45466,7 +40871,7 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -45475,9 +40880,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="F2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -49021,7 +44426,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -49059,7 +44464,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -49094,9 +44499,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="117" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="AF2" s="129" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -838,6 +838,15 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1115,11 +1124,16 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -1654,11 +1668,16 @@
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
@@ -1951,11 +1970,16 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -2199,11 +2223,16 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -2789,11 +2818,16 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -3257,7 +3291,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3295,7 +3329,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3330,9 +3364,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="AF2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3759,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="71" t="n">
+      <c r="P5" s="95" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -3784,12 +3818,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="98" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="77" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -3821,7 +3855,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="P6" s="96" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -3917,7 +3951,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="71" t="n">
+      <c r="P7" s="95" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -3981,7 +4015,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="77" t="inlineStr">
+      <c r="H8" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4013,7 +4047,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="80" t="n">
+      <c r="P8" s="96" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -4077,7 +4111,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4109,7 +4143,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="71" t="n">
+      <c r="P9" s="95" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -4168,12 +4202,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="77" t="inlineStr">
+      <c r="G10" s="98" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="77" t="inlineStr">
+      <c r="H10" s="98" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -4205,7 +4239,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="80" t="n">
+      <c r="P10" s="96" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -4301,7 +4335,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="71" t="n">
+      <c r="P11" s="95" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -4397,7 +4431,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="80" t="n">
+      <c r="P12" s="96" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -4493,7 +4527,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="71" t="n">
+      <c r="P13" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -4589,7 +4623,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="80" t="n">
+      <c r="P14" s="96" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -4781,7 +4815,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="80" t="n">
+      <c r="P16" s="96" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -4977,7 +5011,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="80" t="n">
+      <c r="P18" s="96" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -5036,12 +5070,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="68" t="inlineStr">
+      <c r="G19" s="98" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="68" t="inlineStr">
+      <c r="H19" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5073,7 +5107,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="71" t="n">
+      <c r="P19" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -5137,7 +5171,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="77" t="inlineStr">
+      <c r="H20" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5169,7 +5203,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="80" t="n">
+      <c r="P20" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -5228,12 +5262,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="68" t="inlineStr">
+      <c r="G21" s="98" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="68" t="inlineStr">
+      <c r="H21" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5265,7 +5299,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="71" t="n">
+      <c r="P21" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -5329,7 +5363,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5361,7 +5395,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="80" t="n">
+      <c r="P22" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -5425,7 +5459,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="68" t="inlineStr">
+      <c r="H23" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5457,7 +5491,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="71" t="n">
+      <c r="P23" s="95" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -5553,7 +5587,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="80" t="n">
+      <c r="P24" s="96" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -5649,7 +5683,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="71" t="n">
+      <c r="P25" s="95" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -5745,7 +5779,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="80" t="n">
+      <c r="P26" s="96" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -5841,7 +5875,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="71" t="n">
+      <c r="P27" s="95" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -5941,7 +5975,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="80" t="n">
+      <c r="P28" s="96" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -6037,7 +6071,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="71" t="n">
+      <c r="P29" s="95" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -6133,7 +6167,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="80" t="n">
+      <c r="P30" s="96" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -6229,7 +6263,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="71" t="n">
+      <c r="P31" s="95" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -6325,7 +6359,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="80" t="n">
+      <c r="P32" s="96" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -6421,7 +6455,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="71" t="n">
+      <c r="P33" s="95" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -6517,7 +6551,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="80" t="n">
+      <c r="P34" s="96" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -6613,7 +6647,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="71" t="n">
+      <c r="P35" s="95" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -6709,7 +6743,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="80" t="n">
+      <c r="P36" s="96" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -6805,7 +6839,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="71" t="n">
+      <c r="P37" s="95" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -6864,12 +6898,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="77" t="inlineStr">
+      <c r="G38" s="98" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="77" t="inlineStr">
+      <c r="H38" s="98" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -6901,7 +6935,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="80" t="n">
+      <c r="P38" s="96" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -6997,7 +7031,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="71" t="n">
+      <c r="P39" s="95" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -7056,12 +7090,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="77" t="inlineStr">
+      <c r="G40" s="98" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="77" t="inlineStr">
+      <c r="H40" s="98" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -7093,7 +7127,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="80" t="n">
+      <c r="P40" s="96" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -7156,12 +7190,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="68" t="inlineStr">
+      <c r="G41" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="68" t="inlineStr">
+      <c r="H41" s="98" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -7193,7 +7227,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="71" t="n">
+      <c r="P41" s="95" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -7256,12 +7290,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="G42" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="H42" s="98" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -7293,7 +7327,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="80" t="n">
+      <c r="P42" s="96" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -7393,7 +7427,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="71" t="n">
+      <c r="P43" s="95" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -7493,7 +7527,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="80" t="n">
+      <c r="P44" s="96" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -7556,7 +7590,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="68" t="inlineStr">
+      <c r="G45" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7593,7 +7627,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="71" t="n">
+      <c r="P45" s="95" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -7656,7 +7690,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="77" t="inlineStr">
+      <c r="G46" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7693,7 +7727,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="80" t="n">
+      <c r="P46" s="96" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -7752,12 +7786,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="68" t="inlineStr">
+      <c r="G47" s="98" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="68" t="inlineStr">
+      <c r="H47" s="98" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -7789,7 +7823,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="71" t="n">
+      <c r="P47" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -7889,7 +7923,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="80" t="n">
+      <c r="P48" s="96" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -7989,7 +8023,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="71" t="n">
+      <c r="P49" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -8089,7 +8123,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="80" t="n">
+      <c r="P50" s="96" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -8189,7 +8223,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="71" t="n">
+      <c r="P51" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -8285,7 +8319,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="80" t="n">
+      <c r="P52" s="96" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -8381,7 +8415,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="71" t="n">
+      <c r="P53" s="95" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -8477,7 +8511,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="80" t="n">
+      <c r="P54" s="96" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -8573,7 +8607,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="71" t="n">
+      <c r="P55" s="95" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -8673,7 +8707,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="80" t="n">
+      <c r="P56" s="96" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -8769,7 +8803,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="71" t="n">
+      <c r="P57" s="95" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -8865,7 +8899,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="80" t="n">
+      <c r="P58" s="96" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -8961,7 +8995,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="71" t="n">
+      <c r="P59" s="95" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -9057,7 +9091,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="80" t="n">
+      <c r="P60" s="96" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -9116,12 +9150,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="68" t="inlineStr">
+      <c r="G61" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="68" t="inlineStr">
+      <c r="H61" s="98" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -9153,7 +9187,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="71" t="n">
+      <c r="P61" s="95" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -9217,7 +9251,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="77" t="inlineStr">
+      <c r="H62" s="97" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -9312,12 +9346,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="68" t="inlineStr">
+      <c r="G63" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="68" t="inlineStr">
+      <c r="H63" s="98" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -9349,7 +9383,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="71" t="n">
+      <c r="P63" s="95" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -9413,7 +9447,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="77" t="inlineStr">
+      <c r="H64" s="97" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -9549,7 +9583,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="71" t="n">
+      <c r="P65" s="95" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -9649,7 +9683,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="80" t="n">
+      <c r="P66" s="96" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -9749,7 +9783,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="71" t="n">
+      <c r="P67" s="95" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -9812,7 +9846,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="77" t="inlineStr">
+      <c r="G68" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9849,7 +9883,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="80" t="n">
+      <c r="P68" s="96" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -9912,7 +9946,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="68" t="inlineStr">
+      <c r="G69" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9949,7 +9983,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="71" t="n">
+      <c r="P69" s="95" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -10045,7 +10079,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="80" t="n">
+      <c r="P70" s="96" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -10109,7 +10143,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="68" t="inlineStr">
+      <c r="H71" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -10141,7 +10175,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="71" t="n">
+      <c r="P71" s="95" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -10237,7 +10271,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="80" t="n">
+      <c r="P72" s="96" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -10333,7 +10367,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="71" t="n">
+      <c r="P73" s="95" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -10397,7 +10431,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="77" t="inlineStr">
+      <c r="H74" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -10429,7 +10463,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="80" t="n">
+      <c r="P74" s="96" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -10525,7 +10559,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="71" t="n">
+      <c r="P75" s="95" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -10621,7 +10655,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="80" t="n">
+      <c r="P76" s="96" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -10717,7 +10751,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="71" t="n">
+      <c r="P77" s="95" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -10817,7 +10851,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="80" t="n">
+      <c r="P78" s="96" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -10913,7 +10947,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="71" t="n">
+      <c r="P79" s="95" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -11013,7 +11047,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="80" t="n">
+      <c r="P80" s="96" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -11113,7 +11147,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="71" t="n">
+      <c r="P81" s="95" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -11213,7 +11247,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="80" t="n">
+      <c r="P82" s="96" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -11309,7 +11343,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="71" t="n">
+      <c r="P83" s="95" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -11405,7 +11439,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="80" t="n">
+      <c r="P84" s="96" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -11501,7 +11535,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="71" t="n">
+      <c r="P85" s="95" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -11597,7 +11631,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="80" t="n">
+      <c r="P86" s="96" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -11697,7 +11731,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="71" t="n">
+      <c r="P87" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -11793,7 +11827,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="80" t="n">
+      <c r="P88" s="96" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -11889,7 +11923,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="71" t="n">
+      <c r="P89" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -11985,7 +12019,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="80" t="n">
+      <c r="P90" s="96" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -12085,7 +12119,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="71" t="n">
+      <c r="P91" s="95" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -12181,7 +12215,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="80" t="n">
+      <c r="P92" s="96" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -12277,7 +12311,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="71" t="n">
+      <c r="P93" s="95" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -12377,7 +12411,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="80" t="n">
+      <c r="P94" s="96" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -12477,7 +12511,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="71" t="n">
+      <c r="P95" s="95" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -12577,7 +12611,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="80" t="n">
+      <c r="P96" s="96" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -12677,7 +12711,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="71" t="n">
+      <c r="P97" s="95" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -12773,7 +12807,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="80" t="n">
+      <c r="P98" s="96" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -12832,7 +12866,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="68" t="inlineStr">
+      <c r="G99" s="97" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -12869,7 +12903,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="71" t="n">
+      <c r="P99" s="95" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -12969,7 +13003,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="80" t="n">
+      <c r="P100" s="96" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -13065,7 +13099,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="71" t="n">
+      <c r="P101" s="95" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -13161,7 +13195,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="80" t="n">
+      <c r="P102" s="96" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -13257,7 +13291,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="71" t="n">
+      <c r="P103" s="95" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -13316,12 +13350,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="77" t="inlineStr">
+      <c r="G104" s="97" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="77" t="inlineStr">
+      <c r="H104" s="97" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -13353,7 +13387,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="80" t="n">
+      <c r="P104" s="96" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -13449,7 +13483,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="71" t="n">
+      <c r="P105" s="95" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -13543,7 +13577,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="80" t="n">
+      <c r="P106" s="96" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -13637,7 +13671,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="71" t="n">
+      <c r="P107" s="95" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -13731,7 +13765,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="80" t="n">
+      <c r="P108" s="96" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -13829,7 +13863,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="71" t="n">
+      <c r="P109" s="95" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -13913,7 +13947,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="80" t="n">
+      <c r="P110" s="96" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -15072,7 +15106,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -15093,7 +15127,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15111,9 +15145,9 @@
       <c r="L2" s="91" t="n"/>
       <c r="M2" s="91" t="n"/>
       <c r="N2" s="92" t="n"/>
-      <c r="O2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="O2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20420,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -20415,7 +20449,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -20441,9 +20475,9 @@
       <c r="T2" s="91" t="n"/>
       <c r="U2" s="91" t="n"/>
       <c r="V2" s="92" t="n"/>
-      <c r="W2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="W2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -21493,7 +21527,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -21531,7 +21565,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -21566,9 +21600,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="AF2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29422,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -29402,7 +29436,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -29413,9 +29447,9 @@
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="91" t="n"/>
       <c r="G2" s="92" t="n"/>
-      <c r="H2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="H2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -36746,7 +36780,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -36759,7 +36793,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -36769,9 +36803,9 @@
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="92" t="n"/>
-      <c r="G2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="G2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -40859,7 +40893,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -40871,7 +40905,7 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -40880,9 +40914,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="F2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:43</t>
         </is>
       </c>
     </row>
@@ -44426,7 +44460,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="127" t="inlineStr">
+      <c r="A1" s="130" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -44464,7 +44498,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="128" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -44499,9 +44533,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="129" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="AF2" s="132" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:44</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -436,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -847,6 +847,24 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -931,15 +949,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -953,65 +986,121 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제품구분 (검사기 분류)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1022,11 +1111,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1041,90 +1138,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1134,116 +1311,204 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -1251,337 +1516,650 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G6" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R6)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R6)
 관리코드 005T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R6)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R6)
 관리코드 005T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H8" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 005T2603 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 005T2603 품명 불일치
 권위(R6): ARRAY 기능 검사기 (전용케이스)
 현재(R8): ARRAY 기능 검사기 (전용케이스) Modify
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 005T2603 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 005T2603 품명 불일치
 권위(R6): ARRAY 기능 검사기 (전용케이스)
 현재(R9): ARRAY 기능 검사기 (전용케이스) Modify
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G10" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R10)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R10)
 관리코드 003T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H10" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R10)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R10)
 관리코드 003T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G19" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R19)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R19)
 관리코드 005T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H19" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R19)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R19)
 관리코드 005T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H20" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 005T2604 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 005T2604 품명 불일치
 권위(R19): 기능검사기(UK3S)
 현재(R20): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G21" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R21)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R21)
 관리코드 006T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H21" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R21)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R21)
 관리코드 006T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H22" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 006T2604 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 006T2604 품명 불일치
 권위(R21): 기능검사기(UK3S)
 현재(R22): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 006T2604 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 006T2604 품명 불일치
 권위(R21): 기능검사기(UK3S)
 현재(R23): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G38" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R38)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R38)
 관리코드 017T2602의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H38" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R38)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R38)
 관리코드 017T2602의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G40" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R40)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R40)
 관리코드 005T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H40" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R40)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R40)
 관리코드 005T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G41" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R41)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R41)
 관리코드 028T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H41" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R41)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R41)
 관리코드 028T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G42" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R42)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R42)
 관리코드 029T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H42" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R42)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R42)
 관리코드 029T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G45" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 028T2601 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 028T2601 모델 불일치
 권위(R41): SM-A27B USB PBA
 현재(R45): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G46" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 029T2601 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 029T2601 모델 불일치
 권위(R42): SM-A27B USB PBA
 현재(R46): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G47" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R47)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R47)
 관리코드 002T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H47" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R47)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R47)
 관리코드 002T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G61" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R61)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R61)
 관리코드 022T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H61" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R61)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R61)
 관리코드 022T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H62" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 022T2603 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 022T2603 품명 불일치
 권위(R61): OS검사기_케이스포함
 현재(R62): OS검사기_MODIFY
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G63" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R63)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R63)
 관리코드 024T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H63" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R63)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R63)
 관리코드 024T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="H64" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 024T2603 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 024T2603 품명 불일치
 권위(R63): TDR+IL검사기_케이스포함
 현재(R64): TDR+IL검사기_MODIFY
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G68" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 028T2601 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 028T2601 모델 불일치
 권위(R41): SM-A27B USB PBA
 현재(R68): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G69" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 029T2601 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 029T2601 모델 불일치
 권위(R42): SM-A27B USB PBA
 현재(R69): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 017T2602 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 017T2602 품명 불일치
 권위(R38): 기능검사기 (UK4S)
 현재(R71): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H74" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003T2601 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003T2601 품명 불일치
 권위(R10): 기능검사기 MODIFY
 현재(R74): 기능검사기(UK4)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G99" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 005T2601 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 005T2601 모델 불일치
 권위(R40): SM-L716 BAROMETER
 현재(R99): SM-L715 BAROMETER
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G104" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 002T2604 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 002T2604 모델 불일치
 권위(R47): VMF0971-0125003
 현재(R104): ZNB-400
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H104" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 002T2604 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 002T2604 품명 불일치
 권위(R47): VSWR 검사기- CASE 재활용
 현재(R104): 모듈검사기_케이스 제외
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1596,15 +2174,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1618,57 +2211,105 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1678,82 +2319,139 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1768,26 +2466,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ INV번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ INV번호
 (출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -1795,11 +2516,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1813,164 +2542,292 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1980,11 +2837,19 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고
 완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -1992,11 +2857,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하
 완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2004,11 +2877,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조달
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조달
 진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2016,6 +2897,7 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2030,15 +2912,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2052,65 +2949,121 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제품구분 (검사기 분류)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2121,11 +3074,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2140,90 +3101,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2233,116 +3274,204 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2350,17 +3479,26 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2375,15 +3513,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2397,61 +3550,110 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2466,15 +3668,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2488,55 +3705,96 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2551,26 +3809,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2584,33 +3865,58 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2625,15 +3931,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2647,65 +3968,121 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제품구분 (검사기 분류)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2716,11 +4093,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2735,90 +4120,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2828,116 +4293,204 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2945,17 +4498,26 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -3291,7 +4853,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3329,7 +4891,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3364,9 +4926,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="AF2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:32</t>
         </is>
       </c>
     </row>
@@ -3759,7 +5321,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="95" t="n">
+      <c r="P5" s="71" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -3818,12 +5380,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="98" t="inlineStr">
+      <c r="G6" s="77" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -3855,7 +5417,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="96" t="n">
+      <c r="P6" s="80" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -3951,7 +5513,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="95" t="n">
+      <c r="P7" s="71" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -4015,7 +5577,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="97" t="inlineStr">
+      <c r="H8" s="77" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4047,7 +5609,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="96" t="n">
+      <c r="P8" s="80" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -4111,7 +5673,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="97" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -4143,7 +5705,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="95" t="n">
+      <c r="P9" s="71" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -4202,12 +5764,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="98" t="inlineStr">
+      <c r="G10" s="77" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="98" t="inlineStr">
+      <c r="H10" s="77" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -4239,7 +5801,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="96" t="n">
+      <c r="P10" s="80" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -4335,7 +5897,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="95" t="n">
+      <c r="P11" s="71" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -4431,7 +5993,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="96" t="n">
+      <c r="P12" s="80" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -4527,7 +6089,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="95" t="n">
+      <c r="P13" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -4623,7 +6185,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="96" t="n">
+      <c r="P14" s="80" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -4815,7 +6377,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="96" t="n">
+      <c r="P16" s="80" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -5011,7 +6573,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="96" t="n">
+      <c r="P18" s="80" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -5070,12 +6632,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="98" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="98" t="inlineStr">
+      <c r="H19" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5107,7 +6669,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="95" t="n">
+      <c r="P19" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -5171,7 +6733,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="97" t="inlineStr">
+      <c r="H20" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5203,7 +6765,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="96" t="n">
+      <c r="P20" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -5262,12 +6824,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="98" t="inlineStr">
+      <c r="G21" s="68" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="98" t="inlineStr">
+      <c r="H21" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -5299,7 +6861,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="95" t="n">
+      <c r="P21" s="71" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -5363,7 +6925,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="97" t="inlineStr">
+      <c r="H22" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5395,7 +6957,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="96" t="n">
+      <c r="P22" s="80" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -5459,7 +7021,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="97" t="inlineStr">
+      <c r="H23" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -5491,7 +7053,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="95" t="n">
+      <c r="P23" s="71" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -5587,7 +7149,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="96" t="n">
+      <c r="P24" s="80" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -5683,7 +7245,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="95" t="n">
+      <c r="P25" s="71" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -5779,7 +7341,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="96" t="n">
+      <c r="P26" s="80" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -5875,7 +7437,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="95" t="n">
+      <c r="P27" s="71" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -5975,7 +7537,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="96" t="n">
+      <c r="P28" s="80" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -6071,7 +7633,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="95" t="n">
+      <c r="P29" s="71" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -6167,7 +7729,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="96" t="n">
+      <c r="P30" s="80" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -6263,7 +7825,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="95" t="n">
+      <c r="P31" s="71" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -6359,7 +7921,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="96" t="n">
+      <c r="P32" s="80" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -6455,7 +8017,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="95" t="n">
+      <c r="P33" s="71" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -6551,7 +8113,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="96" t="n">
+      <c r="P34" s="80" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -6647,7 +8209,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="95" t="n">
+      <c r="P35" s="71" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -6743,7 +8305,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="96" t="n">
+      <c r="P36" s="80" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -6839,7 +8401,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="95" t="n">
+      <c r="P37" s="71" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -6898,12 +8460,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="98" t="inlineStr">
+      <c r="G38" s="77" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="98" t="inlineStr">
+      <c r="H38" s="77" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -6935,7 +8497,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="96" t="n">
+      <c r="P38" s="80" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -7031,7 +8593,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="95" t="n">
+      <c r="P39" s="71" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -7090,12 +8652,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="98" t="inlineStr">
+      <c r="G40" s="77" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="98" t="inlineStr">
+      <c r="H40" s="77" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -7127,7 +8689,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="96" t="n">
+      <c r="P40" s="80" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -7190,12 +8752,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="98" t="inlineStr">
+      <c r="G41" s="68" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="98" t="inlineStr">
+      <c r="H41" s="68" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -7227,7 +8789,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="95" t="n">
+      <c r="P41" s="71" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -7290,12 +8852,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="98" t="inlineStr">
+      <c r="G42" s="77" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="98" t="inlineStr">
+      <c r="H42" s="77" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -7327,7 +8889,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="96" t="n">
+      <c r="P42" s="80" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -7427,7 +8989,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="95" t="n">
+      <c r="P43" s="71" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -7527,7 +9089,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="96" t="n">
+      <c r="P44" s="80" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -7590,7 +9152,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="97" t="inlineStr">
+      <c r="G45" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7627,7 +9189,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="95" t="n">
+      <c r="P45" s="71" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -7690,7 +9252,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="97" t="inlineStr">
+      <c r="G46" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -7727,7 +9289,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="96" t="n">
+      <c r="P46" s="80" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -7786,12 +9348,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="98" t="inlineStr">
+      <c r="G47" s="68" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="98" t="inlineStr">
+      <c r="H47" s="68" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -7823,7 +9385,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="95" t="n">
+      <c r="P47" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -7923,7 +9485,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="96" t="n">
+      <c r="P48" s="80" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -8023,7 +9585,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="95" t="n">
+      <c r="P49" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -8123,7 +9685,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="96" t="n">
+      <c r="P50" s="80" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -8223,7 +9785,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="95" t="n">
+      <c r="P51" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -8319,7 +9881,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="96" t="n">
+      <c r="P52" s="80" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -8415,7 +9977,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="95" t="n">
+      <c r="P53" s="71" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -8511,7 +10073,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="96" t="n">
+      <c r="P54" s="80" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -8607,7 +10169,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="95" t="n">
+      <c r="P55" s="71" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -8707,7 +10269,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="96" t="n">
+      <c r="P56" s="80" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -8803,7 +10365,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="95" t="n">
+      <c r="P57" s="71" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -8899,7 +10461,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="96" t="n">
+      <c r="P58" s="80" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -8995,7 +10557,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="95" t="n">
+      <c r="P59" s="71" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -9091,7 +10653,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="96" t="n">
+      <c r="P60" s="80" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -9150,12 +10712,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="98" t="inlineStr">
+      <c r="G61" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="98" t="inlineStr">
+      <c r="H61" s="68" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -9187,7 +10749,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="95" t="n">
+      <c r="P61" s="71" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -9251,7 +10813,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="97" t="inlineStr">
+      <c r="H62" s="77" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -9346,12 +10908,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="98" t="inlineStr">
+      <c r="G63" s="68" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="98" t="inlineStr">
+      <c r="H63" s="68" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -9383,7 +10945,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="95" t="n">
+      <c r="P63" s="71" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -9447,7 +11009,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="97" t="inlineStr">
+      <c r="H64" s="77" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -9583,7 +11145,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="95" t="n">
+      <c r="P65" s="71" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -9683,7 +11245,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="96" t="n">
+      <c r="P66" s="80" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -9783,7 +11345,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="95" t="n">
+      <c r="P67" s="71" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -9846,7 +11408,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="97" t="inlineStr">
+      <c r="G68" s="77" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9883,7 +11445,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="96" t="n">
+      <c r="P68" s="80" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -9946,7 +11508,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="97" t="inlineStr">
+      <c r="G69" s="68" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9983,7 +11545,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="95" t="n">
+      <c r="P69" s="71" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -10079,7 +11641,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="96" t="n">
+      <c r="P70" s="80" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -10143,7 +11705,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="97" t="inlineStr">
+      <c r="H71" s="68" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -10175,7 +11737,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="95" t="n">
+      <c r="P71" s="71" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -10271,7 +11833,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="96" t="n">
+      <c r="P72" s="80" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -10367,7 +11929,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="95" t="n">
+      <c r="P73" s="71" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -10431,7 +11993,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="97" t="inlineStr">
+      <c r="H74" s="77" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -10463,7 +12025,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="96" t="n">
+      <c r="P74" s="80" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -10559,7 +12121,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="95" t="n">
+      <c r="P75" s="71" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -10655,7 +12217,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="96" t="n">
+      <c r="P76" s="80" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -10751,7 +12313,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="95" t="n">
+      <c r="P77" s="71" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -10851,7 +12413,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="96" t="n">
+      <c r="P78" s="80" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -10947,7 +12509,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="95" t="n">
+      <c r="P79" s="71" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -11047,7 +12609,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="96" t="n">
+      <c r="P80" s="80" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -11147,7 +12709,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="95" t="n">
+      <c r="P81" s="71" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -11247,7 +12809,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="96" t="n">
+      <c r="P82" s="80" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -11343,7 +12905,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="95" t="n">
+      <c r="P83" s="71" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -11439,7 +13001,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="96" t="n">
+      <c r="P84" s="80" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -11535,7 +13097,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="95" t="n">
+      <c r="P85" s="71" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -11631,7 +13193,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="96" t="n">
+      <c r="P86" s="80" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -11731,7 +13293,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="95" t="n">
+      <c r="P87" s="71" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -11827,7 +13389,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="96" t="n">
+      <c r="P88" s="80" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -11923,7 +13485,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="95" t="n">
+      <c r="P89" s="71" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -12019,7 +13581,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="96" t="n">
+      <c r="P90" s="80" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -12119,7 +13681,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="95" t="n">
+      <c r="P91" s="71" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -12215,7 +13777,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="96" t="n">
+      <c r="P92" s="80" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -12311,7 +13873,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="95" t="n">
+      <c r="P93" s="71" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -12411,7 +13973,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="96" t="n">
+      <c r="P94" s="80" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -12511,7 +14073,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="95" t="n">
+      <c r="P95" s="71" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -12611,7 +14173,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="96" t="n">
+      <c r="P96" s="80" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -12711,7 +14273,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="95" t="n">
+      <c r="P97" s="71" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -12807,7 +14369,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="96" t="n">
+      <c r="P98" s="80" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -12866,7 +14428,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="97" t="inlineStr">
+      <c r="G99" s="68" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -12903,7 +14465,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="95" t="n">
+      <c r="P99" s="71" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -13003,7 +14565,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="96" t="n">
+      <c r="P100" s="80" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -13099,7 +14661,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="95" t="n">
+      <c r="P101" s="71" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -13195,7 +14757,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="96" t="n">
+      <c r="P102" s="80" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -13291,7 +14853,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="95" t="n">
+      <c r="P103" s="71" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -13350,12 +14912,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="97" t="inlineStr">
+      <c r="G104" s="77" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="97" t="inlineStr">
+      <c r="H104" s="77" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -13387,7 +14949,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="96" t="n">
+      <c r="P104" s="80" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -13483,7 +15045,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="95" t="n">
+      <c r="P105" s="71" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -13577,7 +15139,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="96" t="n">
+      <c r="P106" s="80" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -13671,7 +15233,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="95" t="n">
+      <c r="P107" s="71" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -13765,7 +15327,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="96" t="n">
+      <c r="P108" s="80" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -13863,7 +15425,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="95" t="n">
+      <c r="P109" s="71" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -13947,7 +15509,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="96" t="n">
+      <c r="P110" s="80" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -15106,7 +16668,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -15127,7 +16689,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15145,9 +16707,9 @@
       <c r="L2" s="91" t="n"/>
       <c r="M2" s="91" t="n"/>
       <c r="N2" s="92" t="n"/>
-      <c r="O2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="O2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:32</t>
         </is>
       </c>
     </row>
@@ -20420,7 +21982,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -20449,7 +22011,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -20475,9 +22037,9 @@
       <c r="T2" s="91" t="n"/>
       <c r="U2" s="91" t="n"/>
       <c r="V2" s="92" t="n"/>
-      <c r="W2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="W2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:32</t>
         </is>
       </c>
     </row>
@@ -21527,7 +23089,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -21565,7 +23127,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -21600,9 +23162,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="AF2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -29422,7 +30984,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -29436,7 +30998,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -29447,9 +31009,9 @@
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="91" t="n"/>
       <c r="G2" s="92" t="n"/>
-      <c r="H2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="H2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -36780,7 +38342,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -36793,7 +38355,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -36803,9 +38365,9 @@
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="91" t="n"/>
       <c r="F2" s="92" t="n"/>
-      <c r="G2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="G2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -40893,7 +42455,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -40905,7 +42467,7 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -40914,9 +42476,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:43</t>
+      <c r="F2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -44460,7 +46022,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -44498,7 +46060,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -44533,9 +46095,9 @@
       <c r="AC2" s="91" t="n"/>
       <c r="AD2" s="91" t="n"/>
       <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="132" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:44</t>
+      <c r="AF2" s="138" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -293,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -432,11 +432,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -865,6 +894,17 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4840,20 +4880,20 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" style="34" min="23" max="23"/>
-    <col width="8" customWidth="1" style="34" min="24" max="24"/>
-    <col width="10" customWidth="1" style="34" min="25" max="25"/>
-    <col width="12" customWidth="1" style="34" min="26" max="26"/>
-    <col width="8" customWidth="1" style="34" min="27" max="27"/>
-    <col width="13" customWidth="1" style="34" min="28" max="28"/>
-    <col width="8" customWidth="1" style="34" min="29" max="31"/>
-    <col width="8" customWidth="1" style="34" min="30" max="30"/>
+    <col width="7" customWidth="1" style="34" min="24" max="24"/>
+    <col width="7" customWidth="1" style="34" min="25" max="25"/>
+    <col width="7" customWidth="1" style="34" min="26" max="26"/>
+    <col width="7" customWidth="1" style="34" min="27" max="27"/>
+    <col width="7" customWidth="1" style="34" min="28" max="28"/>
+    <col width="7" customWidth="1" style="34" min="29" max="31"/>
+    <col width="7" customWidth="1" style="34" min="30" max="30"/>
     <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -4891,7 +4931,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -4923,14 +4963,14 @@
       <c r="Z2" s="91" t="n"/>
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
-      <c r="AC2" s="91" t="n"/>
-      <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:32</t>
-        </is>
-      </c>
+      <c r="AC2" s="92" t="n"/>
+      <c r="AD2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="AE2" s="142" t="n"/>
+      <c r="AF2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -5224,7 +5264,8 @@
       </c>
       <c r="Z4" s="64" t="inlineStr">
         <is>
-          <t>개발혁신팀</t>
+          <t>개발혁신
+팀</t>
         </is>
       </c>
       <c r="AA4" s="64" t="inlineStr">
@@ -5234,7 +5275,8 @@
       </c>
       <c r="AB4" s="64" t="inlineStr">
         <is>
-          <t>제조기술1팀</t>
+          <t>제조기술
+1팀</t>
         </is>
       </c>
       <c r="AC4" s="64" t="inlineStr">
@@ -16561,9 +16603,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="I5:I140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
@@ -16629,13 +16672,13 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="19"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="19"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -16668,7 +16711,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -16689,7 +16732,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16704,14 +16747,14 @@
       <c r="I2" s="91" t="n"/>
       <c r="J2" s="91" t="n"/>
       <c r="K2" s="91" t="n"/>
-      <c r="L2" s="91" t="n"/>
-      <c r="M2" s="91" t="n"/>
-      <c r="N2" s="92" t="n"/>
-      <c r="O2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:32</t>
-        </is>
-      </c>
+      <c r="L2" s="92" t="n"/>
+      <c r="M2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="N2" s="142" t="n"/>
+      <c r="O2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -16846,7 +16889,8 @@
       </c>
       <c r="K4" s="64" t="inlineStr">
         <is>
-          <t>개발혁신팀
+          <t>개발혁신
+팀
 완료일</t>
         </is>
       </c>
@@ -16858,7 +16902,8 @@
       </c>
       <c r="M4" s="64" t="inlineStr">
         <is>
-          <t>제조기술1팀
+          <t>제조기술
+1팀
 완료일</t>
         </is>
       </c>
@@ -21937,9 +21982,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -21982,7 +22028,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -22011,7 +22057,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -22034,14 +22080,14 @@
       <c r="Q2" s="91" t="n"/>
       <c r="R2" s="91" t="n"/>
       <c r="S2" s="91" t="n"/>
-      <c r="T2" s="91" t="n"/>
-      <c r="U2" s="91" t="n"/>
-      <c r="V2" s="92" t="n"/>
-      <c r="W2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:32</t>
-        </is>
-      </c>
+      <c r="T2" s="92" t="n"/>
+      <c r="U2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="V2" s="142" t="n"/>
+      <c r="W2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -23034,9 +23080,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
+  <mergeCells count="3">
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -23076,20 +23123,20 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" style="34" min="23" max="23"/>
-    <col width="8" customWidth="1" style="34" min="24" max="24"/>
-    <col width="10" customWidth="1" style="34" min="25" max="25"/>
-    <col width="12" customWidth="1" style="34" min="26" max="26"/>
-    <col width="8" customWidth="1" style="34" min="27" max="27"/>
-    <col width="13" customWidth="1" style="34" min="28" max="28"/>
-    <col width="8" customWidth="1" style="34" min="29" max="31"/>
-    <col width="8" customWidth="1" style="34" min="30" max="30"/>
+    <col width="7" customWidth="1" style="34" min="24" max="24"/>
+    <col width="7" customWidth="1" style="34" min="25" max="25"/>
+    <col width="7" customWidth="1" style="34" min="26" max="26"/>
+    <col width="7" customWidth="1" style="34" min="27" max="27"/>
+    <col width="7" customWidth="1" style="34" min="28" max="28"/>
+    <col width="7" customWidth="1" style="34" min="29" max="31"/>
+    <col width="7" customWidth="1" style="34" min="30" max="30"/>
     <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -23127,7 +23174,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -23159,14 +23206,14 @@
       <c r="Z2" s="91" t="n"/>
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
-      <c r="AC2" s="91" t="n"/>
-      <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="AC2" s="92" t="n"/>
+      <c r="AD2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="AE2" s="142" t="n"/>
+      <c r="AF2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -23460,7 +23507,8 @@
       </c>
       <c r="Z4" s="64" t="inlineStr">
         <is>
-          <t>개발혁신팀</t>
+          <t>개발혁신
+팀</t>
         </is>
       </c>
       <c r="AA4" s="64" t="inlineStr">
@@ -23470,7 +23518,8 @@
       </c>
       <c r="AB4" s="64" t="inlineStr">
         <is>
-          <t>제조기술1팀</t>
+          <t>제조기술
+1팀</t>
         </is>
       </c>
       <c r="AC4" s="64" t="inlineStr">
@@ -30913,9 +30962,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="I5:I103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
@@ -30984,7 +31034,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -30998,7 +31048,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -31006,14 +31056,14 @@
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
-      <c r="E2" s="91" t="n"/>
-      <c r="F2" s="91" t="n"/>
-      <c r="G2" s="92" t="n"/>
-      <c r="H2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="E2" s="92" t="n"/>
+      <c r="F2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="G2" s="142" t="n"/>
+      <c r="H2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -38313,8 +38363,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38342,7 +38393,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -38355,21 +38406,21 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
-      <c r="D2" s="91" t="n"/>
-      <c r="E2" s="91" t="n"/>
-      <c r="F2" s="92" t="n"/>
-      <c r="G2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="D2" s="92" t="n"/>
+      <c r="E2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="F2" s="142" t="n"/>
+      <c r="G2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -42427,9 +42478,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -42455,7 +42507,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -42467,20 +42519,20 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
-      <c r="C2" s="91" t="n"/>
-      <c r="D2" s="91" t="n"/>
-      <c r="E2" s="92" t="n"/>
-      <c r="F2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="C2" s="92" t="n"/>
+      <c r="D2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="E2" s="142" t="n"/>
+      <c r="F2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -45968,9 +46020,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="3">
+    <mergeCell ref="D2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -46009,20 +46062,20 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" style="34" min="23" max="23"/>
-    <col width="8" customWidth="1" style="34" min="24" max="24"/>
-    <col width="10" customWidth="1" style="34" min="25" max="25"/>
-    <col width="12" customWidth="1" style="34" min="26" max="26"/>
-    <col width="8" customWidth="1" style="34" min="27" max="27"/>
-    <col width="13" customWidth="1" style="34" min="28" max="28"/>
-    <col width="8" customWidth="1" style="34" min="29" max="31"/>
-    <col width="8" customWidth="1" style="34" min="30" max="30"/>
+    <col width="7" customWidth="1" style="34" min="24" max="24"/>
+    <col width="7" customWidth="1" style="34" min="25" max="25"/>
+    <col width="7" customWidth="1" style="34" min="26" max="26"/>
+    <col width="7" customWidth="1" style="34" min="27" max="27"/>
+    <col width="7" customWidth="1" style="34" min="28" max="28"/>
+    <col width="7" customWidth="1" style="34" min="29" max="31"/>
+    <col width="7" customWidth="1" style="34" min="30" max="30"/>
     <col width="12" customWidth="1" style="34" min="31" max="31"/>
     <col width="12" customWidth="1" style="34" min="32" max="33"/>
     <col width="12" customWidth="1" style="34" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="136" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -46060,7 +46113,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="140" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -46092,14 +46145,14 @@
       <c r="Z2" s="91" t="n"/>
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
-      <c r="AC2" s="91" t="n"/>
-      <c r="AD2" s="91" t="n"/>
-      <c r="AE2" s="92" t="n"/>
-      <c r="AF2" s="138" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="AC2" s="92" t="n"/>
+      <c r="AD2" s="141" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:57</t>
+        </is>
+      </c>
+      <c r="AE2" s="142" t="n"/>
+      <c r="AF2" s="143" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -46393,7 +46446,8 @@
       </c>
       <c r="Z4" s="64" t="inlineStr">
         <is>
-          <t>개발혁신팀</t>
+          <t>개발혁신
+팀</t>
         </is>
       </c>
       <c r="AA4" s="64" t="inlineStr">
@@ -46403,7 +46457,8 @@
       </c>
       <c r="AB4" s="64" t="inlineStr">
         <is>
-          <t>제조기술1팀</t>
+          <t>제조기술
+1팀</t>
         </is>
       </c>
       <c r="AC4" s="64" t="inlineStr">
@@ -47450,9 +47505,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="I5:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -465,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -905,6 +905,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1548,14 +1557,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -1570,11 +1583,16 @@
           </rPr>
           <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2531,11 +2549,16 @@
           </rPr>
           <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2548,14 +2571,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ INV번호
-(출하코드) (세부항목 진척률)
+          <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2647,11 +2674,16 @@
           </rPr>
           <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2666,11 +2698,16 @@
           </rPr>
           <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2685,11 +2722,16 @@
           </rPr>
           <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2704,11 +2746,16 @@
           </rPr>
           <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2741,11 +2788,16 @@
           </rPr>
           <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2776,11 +2828,16 @@
           </rPr>
           <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2812,11 +2869,16 @@
           </rPr>
           <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2850,11 +2912,16 @@
           </rPr>
           <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2889,14 +2956,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 입고
-완료 (세부항목 진척률)
+          <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2909,14 +2980,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 출하
-완료 (세부항목 진척률)
+          <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -2929,14 +3004,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 조달
-진행률 (세부항목 진척률)
+          <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -3511,14 +3590,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -3533,11 +3616,16 @@
           </rPr>
           <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -3810,11 +3898,16 @@
           </rPr>
           <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -3829,11 +3922,16 @@
           </rPr>
           <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -3951,11 +4049,16 @@
           </rPr>
           <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -4530,14 +4633,18 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -4552,11 +4659,16 @@
           </rPr>
           <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
         </r>
       </text>
     </comment>
@@ -4893,7 +5005,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -4931,7 +5043,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -4964,13 +5076,13 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="AE2" s="142" t="n"/>
-      <c r="AF2" s="143" t="n"/>
+      <c r="AD2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:25</t>
+        </is>
+      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -16711,7 +16823,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -16732,7 +16844,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16748,13 +16860,13 @@
       <c r="J2" s="91" t="n"/>
       <c r="K2" s="91" t="n"/>
       <c r="L2" s="92" t="n"/>
-      <c r="M2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="N2" s="142" t="n"/>
-      <c r="O2" s="143" t="n"/>
+      <c r="M2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:25</t>
+        </is>
+      </c>
+      <c r="N2" s="91" t="n"/>
+      <c r="O2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -22028,7 +22140,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -22057,7 +22169,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -22081,13 +22193,13 @@
       <c r="R2" s="91" t="n"/>
       <c r="S2" s="91" t="n"/>
       <c r="T2" s="92" t="n"/>
-      <c r="U2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="V2" s="142" t="n"/>
-      <c r="W2" s="143" t="n"/>
+      <c r="U2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:25</t>
+        </is>
+      </c>
+      <c r="V2" s="91" t="n"/>
+      <c r="W2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -23136,7 +23248,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -23174,7 +23286,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -23207,13 +23319,13 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="AE2" s="142" t="n"/>
-      <c r="AF2" s="143" t="n"/>
+      <c r="AD2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -31034,7 +31146,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -31048,7 +31160,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -31057,13 +31169,13 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="G2" s="142" t="n"/>
-      <c r="H2" s="143" t="n"/>
+      <c r="F2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="G2" s="91" t="n"/>
+      <c r="H2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -38393,7 +38505,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -38406,7 +38518,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -38414,13 +38526,13 @@
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="92" t="n"/>
-      <c r="E2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="F2" s="142" t="n"/>
-      <c r="G2" s="143" t="n"/>
+      <c r="E2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="F2" s="91" t="n"/>
+      <c r="G2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -42507,7 +42619,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -42519,20 +42631,20 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="92" t="n"/>
-      <c r="D2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="E2" s="142" t="n"/>
-      <c r="F2" s="143" t="n"/>
+      <c r="D2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="E2" s="91" t="n"/>
+      <c r="F2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">
@@ -46075,7 +46187,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="139" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -46113,7 +46225,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="140" t="inlineStr">
+      <c r="A2" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -46146,13 +46258,13 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="141" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:57</t>
-        </is>
-      </c>
-      <c r="AE2" s="142" t="n"/>
-      <c r="AF2" s="143" t="n"/>
+      <c r="AD2" s="146" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="AE2" s="91" t="n"/>
+      <c r="AF2" s="92" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="57" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -465,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -905,6 +905,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5005,7 +5014,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5043,7 +5052,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5076,9 +5085,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:25</t>
+      <c r="AD2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -16823,7 +16832,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -16844,7 +16853,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16860,9 +16869,9 @@
       <c r="J2" s="91" t="n"/>
       <c r="K2" s="91" t="n"/>
       <c r="L2" s="92" t="n"/>
-      <c r="M2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:25</t>
+      <c r="M2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="N2" s="91" t="n"/>
@@ -22140,7 +22149,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -22169,7 +22178,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -22193,9 +22202,9 @@
       <c r="R2" s="91" t="n"/>
       <c r="S2" s="91" t="n"/>
       <c r="T2" s="92" t="n"/>
-      <c r="U2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:25</t>
+      <c r="U2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="V2" s="91" t="n"/>
@@ -23248,7 +23257,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -23286,7 +23295,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -23319,9 +23328,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="AD2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -31146,7 +31155,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -31160,7 +31169,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -31169,9 +31178,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="F2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="G2" s="91" t="n"/>
@@ -38505,7 +38514,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -38518,7 +38527,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -38526,9 +38535,9 @@
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="92" t="n"/>
-      <c r="E2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="E2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="F2" s="91" t="n"/>
@@ -42619,7 +42628,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -42631,16 +42640,16 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="92" t="n"/>
-      <c r="D2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="D2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="E2" s="91" t="n"/>
@@ -46187,7 +46196,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="144" t="inlineStr">
+      <c r="A1" s="147" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -46225,7 +46234,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="145" t="inlineStr">
+      <c r="A2" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -46258,9 +46267,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="146" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="AD2" s="149" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -465,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -905,6 +905,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5014,7 +5023,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5052,7 +5061,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5085,9 +5094,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="AD2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -16832,7 +16841,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -16853,7 +16862,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16869,9 +16878,9 @@
       <c r="J2" s="91" t="n"/>
       <c r="K2" s="91" t="n"/>
       <c r="L2" s="92" t="n"/>
-      <c r="M2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="M2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="N2" s="91" t="n"/>
@@ -22149,7 +22158,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -22178,7 +22187,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -22202,9 +22211,9 @@
       <c r="R2" s="91" t="n"/>
       <c r="S2" s="91" t="n"/>
       <c r="T2" s="92" t="n"/>
-      <c r="U2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="U2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="V2" s="91" t="n"/>
@@ -23257,7 +23266,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -23295,7 +23304,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -23328,9 +23337,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="AD2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -31155,7 +31164,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -31169,7 +31178,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -31178,9 +31187,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="F2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="G2" s="91" t="n"/>
@@ -38514,7 +38523,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -38527,7 +38536,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -38535,9 +38544,9 @@
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="92" t="n"/>
-      <c r="E2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="E2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="F2" s="91" t="n"/>
@@ -42628,7 +42637,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -42640,16 +42649,16 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="92" t="n"/>
-      <c r="D2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="D2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="E2" s="91" t="n"/>
@@ -46196,7 +46205,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="147" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -46234,7 +46243,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="148" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -46267,9 +46276,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="149" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="AD2" s="152" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -465,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -905,6 +905,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5023,7 +5032,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5061,7 +5070,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5094,9 +5103,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="AD2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -5493,7 +5502,7 @@
       <c r="O5" s="70" t="n">
         <v>380000</v>
       </c>
-      <c r="P5" s="71" t="n">
+      <c r="P5" s="95" t="n">
         <v>3040000</v>
       </c>
       <c r="Q5" s="72" t="inlineStr">
@@ -5552,12 +5561,12 @@
         </is>
       </c>
       <c r="F6" s="76" t="n"/>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="98" t="inlineStr">
         <is>
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H6" s="77" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스)</t>
         </is>
@@ -5589,7 +5598,7 @@
       <c r="O6" s="79" t="n">
         <v>21800000</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="P6" s="96" t="n">
         <v>21800000</v>
       </c>
       <c r="Q6" s="81" t="inlineStr">
@@ -5685,7 +5694,7 @@
       <c r="O7" s="70" t="n">
         <v>19040000</v>
       </c>
-      <c r="P7" s="71" t="n">
+      <c r="P7" s="95" t="n">
         <v>19040000</v>
       </c>
       <c r="Q7" s="72" t="inlineStr">
@@ -5749,7 +5758,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H8" s="77" t="inlineStr">
+      <c r="H8" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -5781,7 +5790,7 @@
       <c r="O8" s="79" t="n">
         <v>2730000</v>
       </c>
-      <c r="P8" s="80" t="n">
+      <c r="P8" s="96" t="n">
         <v>2730000</v>
       </c>
       <c r="Q8" s="81" t="inlineStr">
@@ -5845,7 +5854,7 @@
           <t>SM-F976 GND PCB</t>
         </is>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="97" t="inlineStr">
         <is>
           <t>ARRAY 기능 검사기 (전용케이스) Modify</t>
         </is>
@@ -5877,7 +5886,7 @@
       <c r="O9" s="70" t="n">
         <v>712000</v>
       </c>
-      <c r="P9" s="71" t="n">
+      <c r="P9" s="95" t="n">
         <v>712000</v>
       </c>
       <c r="Q9" s="72" t="inlineStr">
@@ -5936,12 +5945,12 @@
         </is>
       </c>
       <c r="F10" s="76" t="n"/>
-      <c r="G10" s="77" t="inlineStr">
+      <c r="G10" s="98" t="inlineStr">
         <is>
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H10" s="77" t="inlineStr">
+      <c r="H10" s="98" t="inlineStr">
         <is>
           <t>기능검사기 MODIFY</t>
         </is>
@@ -5973,7 +5982,7 @@
       <c r="O10" s="79" t="n">
         <v>769000</v>
       </c>
-      <c r="P10" s="80" t="n">
+      <c r="P10" s="96" t="n">
         <v>769000</v>
       </c>
       <c r="Q10" s="81" t="inlineStr">
@@ -6069,7 +6078,7 @@
       <c r="O11" s="70" t="n">
         <v>152000</v>
       </c>
-      <c r="P11" s="71" t="n">
+      <c r="P11" s="95" t="n">
         <v>1824000</v>
       </c>
       <c r="Q11" s="72" t="inlineStr">
@@ -6165,7 +6174,7 @@
       <c r="O12" s="79" t="n">
         <v>313000</v>
       </c>
-      <c r="P12" s="80" t="n">
+      <c r="P12" s="96" t="n">
         <v>313000</v>
       </c>
       <c r="Q12" s="81" t="inlineStr">
@@ -6261,7 +6270,7 @@
       <c r="O13" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P13" s="71" t="n">
+      <c r="P13" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q13" s="72" t="inlineStr">
@@ -6357,7 +6366,7 @@
       <c r="O14" s="79" t="n">
         <v>680</v>
       </c>
-      <c r="P14" s="80" t="n">
+      <c r="P14" s="96" t="n">
         <v>2720</v>
       </c>
       <c r="Q14" s="81" t="inlineStr">
@@ -6549,7 +6558,7 @@
       <c r="O16" s="79" t="n">
         <v>600</v>
       </c>
-      <c r="P16" s="80" t="n">
+      <c r="P16" s="96" t="n">
         <v>3000</v>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -6745,7 +6754,7 @@
       <c r="O18" s="79" t="n">
         <v>2394000</v>
       </c>
-      <c r="P18" s="80" t="n">
+      <c r="P18" s="96" t="n">
         <v>4788000</v>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -6804,12 +6813,12 @@
         </is>
       </c>
       <c r="F19" s="67" t="n"/>
-      <c r="G19" s="68" t="inlineStr">
+      <c r="G19" s="98" t="inlineStr">
         <is>
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H19" s="68" t="inlineStr">
+      <c r="H19" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -6841,7 +6850,7 @@
       <c r="O19" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P19" s="71" t="n">
+      <c r="P19" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q19" s="72" t="inlineStr">
@@ -6905,7 +6914,7 @@
           <t>SM-L345 ECG KEY</t>
         </is>
       </c>
-      <c r="H20" s="77" t="inlineStr">
+      <c r="H20" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -6937,7 +6946,7 @@
       <c r="O20" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P20" s="80" t="n">
+      <c r="P20" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q20" s="81" t="inlineStr">
@@ -6996,12 +7005,12 @@
         </is>
       </c>
       <c r="F21" s="67" t="n"/>
-      <c r="G21" s="68" t="inlineStr">
+      <c r="G21" s="98" t="inlineStr">
         <is>
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H21" s="68" t="inlineStr">
+      <c r="H21" s="98" t="inlineStr">
         <is>
           <t>기능검사기(UK3S)</t>
         </is>
@@ -7033,7 +7042,7 @@
       <c r="O21" s="70" t="n">
         <v>3705000</v>
       </c>
-      <c r="P21" s="71" t="n">
+      <c r="P21" s="95" t="n">
         <v>3705000</v>
       </c>
       <c r="Q21" s="72" t="inlineStr">
@@ -7097,7 +7106,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -7129,7 +7138,7 @@
       <c r="O22" s="79" t="n">
         <v>3205000</v>
       </c>
-      <c r="P22" s="80" t="n">
+      <c r="P22" s="96" t="n">
         <v>3205000</v>
       </c>
       <c r="Q22" s="81" t="inlineStr">
@@ -7193,7 +7202,7 @@
           <t>SM-L715 MIC KEY</t>
         </is>
       </c>
-      <c r="H23" s="68" t="inlineStr">
+      <c r="H23" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -7225,7 +7234,7 @@
       <c r="O23" s="70" t="n">
         <v>3105000</v>
       </c>
-      <c r="P23" s="71" t="n">
+      <c r="P23" s="95" t="n">
         <v>3105000</v>
       </c>
       <c r="Q23" s="72" t="inlineStr">
@@ -7321,7 +7330,7 @@
       <c r="O24" s="79" t="n">
         <v>8900000</v>
       </c>
-      <c r="P24" s="80" t="n">
+      <c r="P24" s="96" t="n">
         <v>8900000</v>
       </c>
       <c r="Q24" s="81" t="inlineStr">
@@ -7417,7 +7426,7 @@
       <c r="O25" s="70" t="n">
         <v>5780000</v>
       </c>
-      <c r="P25" s="71" t="n">
+      <c r="P25" s="95" t="n">
         <v>5780000</v>
       </c>
       <c r="Q25" s="72" t="inlineStr">
@@ -7513,7 +7522,7 @@
       <c r="O26" s="79" t="n">
         <v>9230000</v>
       </c>
-      <c r="P26" s="80" t="n">
+      <c r="P26" s="96" t="n">
         <v>9230000</v>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -7609,7 +7618,7 @@
       <c r="O27" s="70" t="n">
         <v>5210000</v>
       </c>
-      <c r="P27" s="71" t="n">
+      <c r="P27" s="95" t="n">
         <v>5210000</v>
       </c>
       <c r="Q27" s="72" t="inlineStr">
@@ -7709,7 +7718,7 @@
       <c r="O28" s="79" t="n">
         <v>7640000</v>
       </c>
-      <c r="P28" s="80" t="n">
+      <c r="P28" s="96" t="n">
         <v>7640000</v>
       </c>
       <c r="Q28" s="81" t="inlineStr">
@@ -7805,7 +7814,7 @@
       <c r="O29" s="70" t="n">
         <v>8550000</v>
       </c>
-      <c r="P29" s="71" t="n">
+      <c r="P29" s="95" t="n">
         <v>8550000</v>
       </c>
       <c r="Q29" s="72" t="inlineStr">
@@ -7901,7 +7910,7 @@
       <c r="O30" s="79" t="n">
         <v>7550000</v>
       </c>
-      <c r="P30" s="80" t="n">
+      <c r="P30" s="96" t="n">
         <v>7550000</v>
       </c>
       <c r="Q30" s="81" t="inlineStr">
@@ -7997,7 +8006,7 @@
       <c r="O31" s="70" t="n">
         <v>7860000</v>
       </c>
-      <c r="P31" s="71" t="n">
+      <c r="P31" s="95" t="n">
         <v>7860000</v>
       </c>
       <c r="Q31" s="72" t="inlineStr">
@@ -8093,7 +8102,7 @@
       <c r="O32" s="79" t="n">
         <v>6850000</v>
       </c>
-      <c r="P32" s="80" t="n">
+      <c r="P32" s="96" t="n">
         <v>6850000</v>
       </c>
       <c r="Q32" s="81" t="inlineStr">
@@ -8189,7 +8198,7 @@
       <c r="O33" s="70" t="n">
         <v>7550000</v>
       </c>
-      <c r="P33" s="71" t="n">
+      <c r="P33" s="95" t="n">
         <v>7550000</v>
       </c>
       <c r="Q33" s="72" t="inlineStr">
@@ -8285,7 +8294,7 @@
       <c r="O34" s="79" t="n">
         <v>7270000</v>
       </c>
-      <c r="P34" s="80" t="n">
+      <c r="P34" s="96" t="n">
         <v>7270000</v>
       </c>
       <c r="Q34" s="81" t="inlineStr">
@@ -8381,7 +8390,7 @@
       <c r="O35" s="70" t="n">
         <v>1770000</v>
       </c>
-      <c r="P35" s="71" t="n">
+      <c r="P35" s="95" t="n">
         <v>5310000</v>
       </c>
       <c r="Q35" s="72" t="inlineStr">
@@ -8477,7 +8486,7 @@
       <c r="O36" s="79" t="n">
         <v>400000</v>
       </c>
-      <c r="P36" s="80" t="n">
+      <c r="P36" s="96" t="n">
         <v>400000</v>
       </c>
       <c r="Q36" s="81" t="inlineStr">
@@ -8573,7 +8582,7 @@
       <c r="O37" s="70" t="n">
         <v>3800000</v>
       </c>
-      <c r="P37" s="71" t="n">
+      <c r="P37" s="95" t="n">
         <v>3800000</v>
       </c>
       <c r="Q37" s="72" t="inlineStr">
@@ -8632,12 +8641,12 @@
         </is>
       </c>
       <c r="F38" s="76" t="n"/>
-      <c r="G38" s="77" t="inlineStr">
+      <c r="G38" s="98" t="inlineStr">
         <is>
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H38" s="77" t="inlineStr">
+      <c r="H38" s="98" t="inlineStr">
         <is>
           <t>기능검사기 (UK4S)</t>
         </is>
@@ -8669,7 +8678,7 @@
       <c r="O38" s="79" t="n">
         <v>5020000</v>
       </c>
-      <c r="P38" s="80" t="n">
+      <c r="P38" s="96" t="n">
         <v>5020000</v>
       </c>
       <c r="Q38" s="81" t="inlineStr">
@@ -8765,7 +8774,7 @@
       <c r="O39" s="70" t="n">
         <v>247000</v>
       </c>
-      <c r="P39" s="71" t="n">
+      <c r="P39" s="95" t="n">
         <v>247000</v>
       </c>
       <c r="Q39" s="72" t="inlineStr">
@@ -8824,12 +8833,12 @@
         </is>
       </c>
       <c r="F40" s="76" t="n"/>
-      <c r="G40" s="77" t="inlineStr">
+      <c r="G40" s="98" t="inlineStr">
         <is>
           <t>SM-L716 BAROMETER</t>
         </is>
       </c>
-      <c r="H40" s="77" t="inlineStr">
+      <c r="H40" s="98" t="inlineStr">
         <is>
           <t>10기압 기능검사기(UK3S)</t>
         </is>
@@ -8861,7 +8870,7 @@
       <c r="O40" s="79" t="n">
         <v>6020000</v>
       </c>
-      <c r="P40" s="80" t="n">
+      <c r="P40" s="96" t="n">
         <v>6020000</v>
       </c>
       <c r="Q40" s="81" t="inlineStr">
@@ -8924,12 +8933,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G41" s="68" t="inlineStr">
+      <c r="G41" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H41" s="68" t="inlineStr">
+      <c r="H41" s="98" t="inlineStr">
         <is>
           <t>성능검사기_케이스 제외</t>
         </is>
@@ -8961,7 +8970,7 @@
       <c r="O41" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P41" s="71" t="n">
+      <c r="P41" s="95" t="n">
         <v>6973600</v>
       </c>
       <c r="Q41" s="72" t="inlineStr">
@@ -9024,12 +9033,12 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="G42" s="98" t="inlineStr">
         <is>
           <t>SM-A27B USB PBA</t>
         </is>
       </c>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="H42" s="98" t="inlineStr">
         <is>
           <t>VSWR검사기_케이스 제외</t>
         </is>
@@ -9061,7 +9070,7 @@
       <c r="O42" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P42" s="80" t="n">
+      <c r="P42" s="96" t="n">
         <v>4342400</v>
       </c>
       <c r="Q42" s="81" t="inlineStr">
@@ -9161,7 +9170,7 @@
       <c r="O43" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P43" s="71" t="n">
+      <c r="P43" s="95" t="n">
         <v>34868000</v>
       </c>
       <c r="Q43" s="72" t="inlineStr">
@@ -9261,7 +9270,7 @@
       <c r="O44" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P44" s="80" t="n">
+      <c r="P44" s="96" t="n">
         <v>13027200</v>
       </c>
       <c r="Q44" s="81" t="inlineStr">
@@ -9324,7 +9333,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G45" s="68" t="inlineStr">
+      <c r="G45" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9361,7 +9370,7 @@
       <c r="O45" s="70" t="n">
         <v>3486800</v>
       </c>
-      <c r="P45" s="71" t="n">
+      <c r="P45" s="95" t="n">
         <v>38354800</v>
       </c>
       <c r="Q45" s="72" t="inlineStr">
@@ -9424,7 +9433,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G46" s="77" t="inlineStr">
+      <c r="G46" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -9461,7 +9470,7 @@
       <c r="O46" s="79" t="n">
         <v>2171200</v>
       </c>
-      <c r="P46" s="80" t="n">
+      <c r="P46" s="96" t="n">
         <v>15198400</v>
       </c>
       <c r="Q46" s="81" t="inlineStr">
@@ -9520,12 +9529,12 @@
         </is>
       </c>
       <c r="F47" s="67" t="n"/>
-      <c r="G47" s="68" t="inlineStr">
+      <c r="G47" s="98" t="inlineStr">
         <is>
           <t>VMF0971-0125003</t>
         </is>
       </c>
-      <c r="H47" s="68" t="inlineStr">
+      <c r="H47" s="98" t="inlineStr">
         <is>
           <t>VSWR 검사기- CASE 재활용</t>
         </is>
@@ -9557,7 +9566,7 @@
       <c r="O47" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P47" s="71" t="n">
+      <c r="P47" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q47" s="72" t="inlineStr">
@@ -9657,7 +9666,7 @@
       <c r="O48" s="79" t="n">
         <v>2080000</v>
       </c>
-      <c r="P48" s="80" t="n">
+      <c r="P48" s="96" t="n">
         <v>2080000</v>
       </c>
       <c r="Q48" s="81" t="inlineStr">
@@ -9757,7 +9766,7 @@
       <c r="O49" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P49" s="71" t="n">
+      <c r="P49" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q49" s="72" t="inlineStr">
@@ -9857,7 +9866,7 @@
       <c r="O50" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P50" s="80" t="n">
+      <c r="P50" s="96" t="n">
         <v>2140000</v>
       </c>
       <c r="Q50" s="81" t="inlineStr">
@@ -9957,7 +9966,7 @@
       <c r="O51" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P51" s="71" t="n">
+      <c r="P51" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q51" s="72" t="inlineStr">
@@ -10053,7 +10062,7 @@
       <c r="O52" s="79" t="n">
         <v>3420000</v>
       </c>
-      <c r="P52" s="80" t="n">
+      <c r="P52" s="96" t="n">
         <v>3420000</v>
       </c>
       <c r="Q52" s="81" t="inlineStr">
@@ -10149,7 +10158,7 @@
       <c r="O53" s="70" t="n">
         <v>5790000</v>
       </c>
-      <c r="P53" s="71" t="n">
+      <c r="P53" s="95" t="n">
         <v>5790000</v>
       </c>
       <c r="Q53" s="72" t="inlineStr">
@@ -10245,7 +10254,7 @@
       <c r="O54" s="79" t="n">
         <v>5690000</v>
       </c>
-      <c r="P54" s="80" t="n">
+      <c r="P54" s="96" t="n">
         <v>5690000</v>
       </c>
       <c r="Q54" s="81" t="inlineStr">
@@ -10341,7 +10350,7 @@
       <c r="O55" s="70" t="n">
         <v>5590000</v>
       </c>
-      <c r="P55" s="71" t="n">
+      <c r="P55" s="95" t="n">
         <v>5590000</v>
       </c>
       <c r="Q55" s="72" t="inlineStr">
@@ -10441,7 +10450,7 @@
       <c r="O56" s="79" t="n">
         <v>3400000</v>
       </c>
-      <c r="P56" s="80" t="n">
+      <c r="P56" s="96" t="n">
         <v>3400000</v>
       </c>
       <c r="Q56" s="81" t="inlineStr">
@@ -10537,7 +10546,7 @@
       <c r="O57" s="70" t="n">
         <v>3714000</v>
       </c>
-      <c r="P57" s="71" t="n">
+      <c r="P57" s="95" t="n">
         <v>3714000</v>
       </c>
       <c r="Q57" s="72" t="inlineStr">
@@ -10633,7 +10642,7 @@
       <c r="O58" s="79" t="n">
         <v>3614000</v>
       </c>
-      <c r="P58" s="80" t="n">
+      <c r="P58" s="96" t="n">
         <v>3614000</v>
       </c>
       <c r="Q58" s="81" t="inlineStr">
@@ -10729,7 +10738,7 @@
       <c r="O59" s="70" t="n">
         <v>3514000</v>
       </c>
-      <c r="P59" s="71" t="n">
+      <c r="P59" s="95" t="n">
         <v>3514000</v>
       </c>
       <c r="Q59" s="72" t="inlineStr">
@@ -10825,7 +10834,7 @@
       <c r="O60" s="79" t="n">
         <v>5590000</v>
       </c>
-      <c r="P60" s="80" t="n">
+      <c r="P60" s="96" t="n">
         <v>5590000</v>
       </c>
       <c r="Q60" s="81" t="inlineStr">
@@ -10884,12 +10893,12 @@
         </is>
       </c>
       <c r="F61" s="67" t="n"/>
-      <c r="G61" s="68" t="inlineStr">
+      <c r="G61" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H61" s="68" t="inlineStr">
+      <c r="H61" s="98" t="inlineStr">
         <is>
           <t>OS검사기_케이스포함</t>
         </is>
@@ -10921,7 +10930,7 @@
       <c r="O61" s="70" t="n">
         <v>5955000</v>
       </c>
-      <c r="P61" s="71" t="n">
+      <c r="P61" s="95" t="n">
         <v>5955000</v>
       </c>
       <c r="Q61" s="72" t="inlineStr">
@@ -10985,7 +10994,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H62" s="77" t="inlineStr">
+      <c r="H62" s="97" t="inlineStr">
         <is>
           <t>OS검사기_MODIFY</t>
         </is>
@@ -11080,12 +11089,12 @@
         </is>
       </c>
       <c r="F63" s="67" t="n"/>
-      <c r="G63" s="68" t="inlineStr">
+      <c r="G63" s="98" t="inlineStr">
         <is>
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H63" s="68" t="inlineStr">
+      <c r="H63" s="98" t="inlineStr">
         <is>
           <t>TDR+IL검사기_케이스포함</t>
         </is>
@@ -11117,7 +11126,7 @@
       <c r="O63" s="70" t="n">
         <v>8625000</v>
       </c>
-      <c r="P63" s="71" t="n">
+      <c r="P63" s="95" t="n">
         <v>8625000</v>
       </c>
       <c r="Q63" s="72" t="inlineStr">
@@ -11181,7 +11190,7 @@
           <t>SM-F976U MAIN FRC</t>
         </is>
       </c>
-      <c r="H64" s="77" t="inlineStr">
+      <c r="H64" s="97" t="inlineStr">
         <is>
           <t>TDR+IL검사기_MODIFY</t>
         </is>
@@ -11317,7 +11326,7 @@
       <c r="O65" s="70" t="n">
         <v>2650000</v>
       </c>
-      <c r="P65" s="71" t="n">
+      <c r="P65" s="95" t="n">
         <v>5300000</v>
       </c>
       <c r="Q65" s="72" t="inlineStr">
@@ -11417,7 +11426,7 @@
       <c r="O66" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P66" s="80" t="n">
+      <c r="P66" s="96" t="n">
         <v>20920800</v>
       </c>
       <c r="Q66" s="81" t="inlineStr">
@@ -11517,7 +11526,7 @@
       <c r="O67" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P67" s="71" t="n">
+      <c r="P67" s="95" t="n">
         <v>6513600</v>
       </c>
       <c r="Q67" s="72" t="inlineStr">
@@ -11580,7 +11589,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G68" s="77" t="inlineStr">
+      <c r="G68" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -11617,7 +11626,7 @@
       <c r="O68" s="79" t="n">
         <v>3486800</v>
       </c>
-      <c r="P68" s="80" t="n">
+      <c r="P68" s="96" t="n">
         <v>10460400</v>
       </c>
       <c r="Q68" s="81" t="inlineStr">
@@ -11680,7 +11689,7 @@
           <t>PBA</t>
         </is>
       </c>
-      <c r="G69" s="68" t="inlineStr">
+      <c r="G69" s="97" t="inlineStr">
         <is>
           <t>SM-A27BE USB PBA</t>
         </is>
@@ -11717,7 +11726,7 @@
       <c r="O69" s="70" t="n">
         <v>2171200</v>
       </c>
-      <c r="P69" s="71" t="n">
+      <c r="P69" s="95" t="n">
         <v>4342400</v>
       </c>
       <c r="Q69" s="72" t="inlineStr">
@@ -11813,7 +11822,7 @@
       <c r="O70" s="79" t="n">
         <v>4120000</v>
       </c>
-      <c r="P70" s="80" t="n">
+      <c r="P70" s="96" t="n">
         <v>12360000</v>
       </c>
       <c r="Q70" s="81" t="inlineStr">
@@ -11877,7 +11886,7 @@
           <t>SM-F971U MAIN LOWER HPCB</t>
         </is>
       </c>
-      <c r="H71" s="68" t="inlineStr">
+      <c r="H71" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4S)</t>
         </is>
@@ -11909,7 +11918,7 @@
       <c r="O71" s="70" t="n">
         <v>5390000</v>
       </c>
-      <c r="P71" s="71" t="n">
+      <c r="P71" s="95" t="n">
         <v>64680000</v>
       </c>
       <c r="Q71" s="72" t="inlineStr">
@@ -12005,7 +12014,7 @@
       <c r="O72" s="79" t="n">
         <v>5270000</v>
       </c>
-      <c r="P72" s="80" t="n">
+      <c r="P72" s="96" t="n">
         <v>52700000</v>
       </c>
       <c r="Q72" s="81" t="inlineStr">
@@ -12101,7 +12110,7 @@
       <c r="O73" s="70" t="n">
         <v>4220000</v>
       </c>
-      <c r="P73" s="71" t="n">
+      <c r="P73" s="95" t="n">
         <v>8440000</v>
       </c>
       <c r="Q73" s="72" t="inlineStr">
@@ -12165,7 +12174,7 @@
           <t>SM-F776U PROXIMITY</t>
         </is>
       </c>
-      <c r="H74" s="77" t="inlineStr">
+      <c r="H74" s="97" t="inlineStr">
         <is>
           <t>기능검사기(UK4)</t>
         </is>
@@ -12197,7 +12206,7 @@
       <c r="O74" s="79" t="n">
         <v>6250000</v>
       </c>
-      <c r="P74" s="80" t="n">
+      <c r="P74" s="96" t="n">
         <v>50000000</v>
       </c>
       <c r="Q74" s="81" t="inlineStr">
@@ -12293,7 +12302,7 @@
       <c r="O75" s="70" t="n">
         <v>21600000</v>
       </c>
-      <c r="P75" s="71" t="n">
+      <c r="P75" s="95" t="n">
         <v>21600000</v>
       </c>
       <c r="Q75" s="72" t="inlineStr">
@@ -12389,7 +12398,7 @@
       <c r="O76" s="79" t="n">
         <v>8625000</v>
       </c>
-      <c r="P76" s="80" t="n">
+      <c r="P76" s="96" t="n">
         <v>8625000</v>
       </c>
       <c r="Q76" s="81" t="inlineStr">
@@ -12485,7 +12494,7 @@
       <c r="O77" s="70" t="n">
         <v>5235000</v>
       </c>
-      <c r="P77" s="71" t="n">
+      <c r="P77" s="95" t="n">
         <v>5235000</v>
       </c>
       <c r="Q77" s="72" t="inlineStr">
@@ -12585,7 +12594,7 @@
       <c r="O78" s="79" t="n">
         <v>6335000</v>
       </c>
-      <c r="P78" s="80" t="n">
+      <c r="P78" s="96" t="n">
         <v>6335000</v>
       </c>
       <c r="Q78" s="81" t="inlineStr">
@@ -12681,7 +12690,7 @@
       <c r="O79" s="70" t="n">
         <v>4295000</v>
       </c>
-      <c r="P79" s="71" t="n">
+      <c r="P79" s="95" t="n">
         <v>4295000</v>
       </c>
       <c r="Q79" s="72" t="inlineStr">
@@ -12781,7 +12790,7 @@
       <c r="O80" s="79" t="n">
         <v>5235000</v>
       </c>
-      <c r="P80" s="80" t="n">
+      <c r="P80" s="96" t="n">
         <v>5235000</v>
       </c>
       <c r="Q80" s="81" t="inlineStr">
@@ -12881,7 +12890,7 @@
       <c r="O81" s="70" t="n">
         <v>6335000</v>
       </c>
-      <c r="P81" s="71" t="n">
+      <c r="P81" s="95" t="n">
         <v>6335000</v>
       </c>
       <c r="Q81" s="72" t="inlineStr">
@@ -12981,7 +12990,7 @@
       <c r="O82" s="79" t="n">
         <v>4295000</v>
       </c>
-      <c r="P82" s="80" t="n">
+      <c r="P82" s="96" t="n">
         <v>4295000</v>
       </c>
       <c r="Q82" s="81" t="inlineStr">
@@ -13077,7 +13086,7 @@
       <c r="O83" s="70" t="n">
         <v>4850000</v>
       </c>
-      <c r="P83" s="71" t="n">
+      <c r="P83" s="95" t="n">
         <v>4850000</v>
       </c>
       <c r="Q83" s="72" t="inlineStr">
@@ -13173,7 +13182,7 @@
       <c r="O84" s="79" t="n">
         <v>7761000</v>
       </c>
-      <c r="P84" s="80" t="n">
+      <c r="P84" s="96" t="n">
         <v>7761000</v>
       </c>
       <c r="Q84" s="81" t="inlineStr">
@@ -13269,7 +13278,7 @@
       <c r="O85" s="70" t="n">
         <v>400000</v>
       </c>
-      <c r="P85" s="71" t="n">
+      <c r="P85" s="95" t="n">
         <v>3200000</v>
       </c>
       <c r="Q85" s="72" t="inlineStr">
@@ -13365,7 +13374,7 @@
       <c r="O86" s="79" t="n">
         <v>5265000</v>
       </c>
-      <c r="P86" s="80" t="n">
+      <c r="P86" s="96" t="n">
         <v>5265000</v>
       </c>
       <c r="Q86" s="81" t="inlineStr">
@@ -13465,7 +13474,7 @@
       <c r="O87" s="70" t="n">
         <v>2490000</v>
       </c>
-      <c r="P87" s="71" t="n">
+      <c r="P87" s="95" t="n">
         <v>2490000</v>
       </c>
       <c r="Q87" s="72" t="inlineStr">
@@ -13561,7 +13570,7 @@
       <c r="O88" s="79" t="n">
         <v>2410000</v>
       </c>
-      <c r="P88" s="80" t="n">
+      <c r="P88" s="96" t="n">
         <v>2410000</v>
       </c>
       <c r="Q88" s="81" t="inlineStr">
@@ -13657,7 +13666,7 @@
       <c r="O89" s="70" t="n">
         <v>2210000</v>
       </c>
-      <c r="P89" s="71" t="n">
+      <c r="P89" s="95" t="n">
         <v>2210000</v>
       </c>
       <c r="Q89" s="72" t="inlineStr">
@@ -13753,7 +13762,7 @@
       <c r="O90" s="79" t="n">
         <v>7820000</v>
       </c>
-      <c r="P90" s="80" t="n">
+      <c r="P90" s="96" t="n">
         <v>15640000</v>
       </c>
       <c r="Q90" s="81" t="inlineStr">
@@ -13853,7 +13862,7 @@
       <c r="O91" s="70" t="n">
         <v>2880000</v>
       </c>
-      <c r="P91" s="71" t="n">
+      <c r="P91" s="95" t="n">
         <v>2880000</v>
       </c>
       <c r="Q91" s="72" t="inlineStr">
@@ -13949,7 +13958,7 @@
       <c r="O92" s="79" t="n">
         <v>2210000</v>
       </c>
-      <c r="P92" s="80" t="n">
+      <c r="P92" s="96" t="n">
         <v>2210000</v>
       </c>
       <c r="Q92" s="81" t="inlineStr">
@@ -14045,7 +14054,7 @@
       <c r="O93" s="70" t="n">
         <v>5850000</v>
       </c>
-      <c r="P93" s="71" t="n">
+      <c r="P93" s="95" t="n">
         <v>5850000</v>
       </c>
       <c r="Q93" s="72" t="inlineStr">
@@ -14145,7 +14154,7 @@
       <c r="O94" s="79" t="n">
         <v>2140000</v>
       </c>
-      <c r="P94" s="80" t="n">
+      <c r="P94" s="96" t="n">
         <v>8560000</v>
       </c>
       <c r="Q94" s="81" t="inlineStr">
@@ -14245,7 +14254,7 @@
       <c r="O95" s="70" t="n">
         <v>2040000</v>
       </c>
-      <c r="P95" s="71" t="n">
+      <c r="P95" s="95" t="n">
         <v>4080000</v>
       </c>
       <c r="Q95" s="72" t="inlineStr">
@@ -14345,7 +14354,7 @@
       <c r="O96" s="79" t="n">
         <v>2780000</v>
       </c>
-      <c r="P96" s="80" t="n">
+      <c r="P96" s="96" t="n">
         <v>8340000</v>
       </c>
       <c r="Q96" s="81" t="inlineStr">
@@ -14445,7 +14454,7 @@
       <c r="O97" s="70" t="n">
         <v>2680000</v>
       </c>
-      <c r="P97" s="71" t="n">
+      <c r="P97" s="95" t="n">
         <v>8040000</v>
       </c>
       <c r="Q97" s="72" t="inlineStr">
@@ -14541,7 +14550,7 @@
       <c r="O98" s="79" t="n">
         <v>3161</v>
       </c>
-      <c r="P98" s="80" t="n">
+      <c r="P98" s="96" t="n">
         <v>37932</v>
       </c>
       <c r="Q98" s="81" t="inlineStr">
@@ -14600,7 +14609,7 @@
         </is>
       </c>
       <c r="F99" s="67" t="n"/>
-      <c r="G99" s="68" t="inlineStr">
+      <c r="G99" s="97" t="inlineStr">
         <is>
           <t>SM-L715 BAROMETER</t>
         </is>
@@ -14637,7 +14646,7 @@
       <c r="O99" s="70" t="n">
         <v>4540</v>
       </c>
-      <c r="P99" s="71" t="n">
+      <c r="P99" s="95" t="n">
         <v>54480</v>
       </c>
       <c r="Q99" s="72" t="inlineStr">
@@ -14737,7 +14746,7 @@
       <c r="O100" s="79" t="n">
         <v>7000000</v>
       </c>
-      <c r="P100" s="80" t="n">
+      <c r="P100" s="96" t="n">
         <v>7000000</v>
       </c>
       <c r="Q100" s="81" t="inlineStr">
@@ -14833,7 +14842,7 @@
       <c r="O101" s="70" t="n">
         <v>8300000</v>
       </c>
-      <c r="P101" s="71" t="n">
+      <c r="P101" s="95" t="n">
         <v>8300000</v>
       </c>
       <c r="Q101" s="72" t="inlineStr">
@@ -14929,7 +14938,7 @@
       <c r="O102" s="79" t="n">
         <v>6440000</v>
       </c>
-      <c r="P102" s="80" t="n">
+      <c r="P102" s="96" t="n">
         <v>6440000</v>
       </c>
       <c r="Q102" s="81" t="inlineStr">
@@ -15025,7 +15034,7 @@
       <c r="O103" s="70" t="n">
         <v>6440000</v>
       </c>
-      <c r="P103" s="71" t="n">
+      <c r="P103" s="95" t="n">
         <v>6440000</v>
       </c>
       <c r="Q103" s="72" t="inlineStr">
@@ -15084,12 +15093,12 @@
         </is>
       </c>
       <c r="F104" s="76" t="n"/>
-      <c r="G104" s="77" t="inlineStr">
+      <c r="G104" s="97" t="inlineStr">
         <is>
           <t>ZNB-400</t>
         </is>
       </c>
-      <c r="H104" s="77" t="inlineStr">
+      <c r="H104" s="97" t="inlineStr">
         <is>
           <t>모듈검사기_케이스 제외</t>
         </is>
@@ -15121,7 +15130,7 @@
       <c r="O104" s="79" t="n">
         <v>4807000</v>
       </c>
-      <c r="P104" s="80" t="n">
+      <c r="P104" s="96" t="n">
         <v>4807000</v>
       </c>
       <c r="Q104" s="81" t="inlineStr">
@@ -15217,7 +15226,7 @@
       <c r="O105" s="70" t="n">
         <v>3648000</v>
       </c>
-      <c r="P105" s="71" t="n">
+      <c r="P105" s="95" t="n">
         <v>3648000</v>
       </c>
       <c r="Q105" s="72" t="inlineStr">
@@ -15311,7 +15320,7 @@
       <c r="O106" s="79" t="n">
         <v>3548000</v>
       </c>
-      <c r="P106" s="80" t="n">
+      <c r="P106" s="96" t="n">
         <v>3548000</v>
       </c>
       <c r="Q106" s="81" t="inlineStr">
@@ -15405,7 +15414,7 @@
       <c r="O107" s="70" t="n">
         <v>110000000</v>
       </c>
-      <c r="P107" s="71" t="n">
+      <c r="P107" s="95" t="n">
         <v>110000000</v>
       </c>
       <c r="Q107" s="72" t="inlineStr">
@@ -15499,7 +15508,7 @@
       <c r="O108" s="79" t="n">
         <v>23000000</v>
       </c>
-      <c r="P108" s="80" t="n">
+      <c r="P108" s="96" t="n">
         <v>23000000</v>
       </c>
       <c r="Q108" s="81" t="inlineStr">
@@ -15597,7 +15606,7 @@
       <c r="O109" s="70" t="n">
         <v>6000000</v>
       </c>
-      <c r="P109" s="71" t="n">
+      <c r="P109" s="95" t="n">
         <v>12000000</v>
       </c>
       <c r="Q109" s="72" t="inlineStr">
@@ -15681,7 +15690,7 @@
       <c r="O110" s="79" t="n">
         <v>6000000</v>
       </c>
-      <c r="P110" s="80" t="n">
+      <c r="P110" s="96" t="n">
         <v>12000000</v>
       </c>
       <c r="Q110" s="81" t="inlineStr">
@@ -16841,7 +16850,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -16862,7 +16871,7 @@
       <c r="O1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 진행현황 (v3.1 부서별 완료일)  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16878,9 +16887,9 @@
       <c r="J2" s="91" t="n"/>
       <c r="K2" s="91" t="n"/>
       <c r="L2" s="92" t="n"/>
-      <c r="M2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="M2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="N2" s="91" t="n"/>
@@ -22158,7 +22167,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -22187,7 +22196,7 @@
       <c r="W1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -22211,9 +22220,9 @@
       <c r="R2" s="91" t="n"/>
       <c r="S2" s="91" t="n"/>
       <c r="T2" s="92" t="n"/>
-      <c r="U2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="U2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="V2" s="91" t="n"/>
@@ -23266,7 +23275,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -23304,7 +23313,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -23337,9 +23346,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="AD2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>
@@ -31164,7 +31173,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -31178,7 +31187,7 @@
       <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -31187,9 +31196,9 @@
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="91" t="n"/>
       <c r="E2" s="92" t="n"/>
-      <c r="F2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="F2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="G2" s="91" t="n"/>
@@ -38523,7 +38532,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -38536,7 +38545,7 @@
       <c r="G1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -38544,9 +38553,9 @@
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="91" t="n"/>
       <c r="D2" s="92" t="n"/>
-      <c r="E2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="E2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="F2" s="91" t="n"/>
@@ -42637,7 +42646,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -42649,16 +42658,16 @@
       <c r="F1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="91" t="n"/>
       <c r="C2" s="92" t="n"/>
-      <c r="D2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="D2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="E2" s="91" t="n"/>
@@ -46205,7 +46214,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -46243,7 +46252,7 @@
       <c r="AF1" s="92" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="151" t="inlineStr">
+      <c r="A2" s="154" t="inlineStr">
         <is>
           <t>㈜케이엔케이 검사기 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -46276,9 +46285,9 @@
       <c r="AA2" s="91" t="n"/>
       <c r="AB2" s="91" t="n"/>
       <c r="AC2" s="92" t="n"/>
-      <c r="AD2" s="152" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="AD2" s="155" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:57</t>
         </is>
       </c>
       <c r="AE2" s="91" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_PMS_2026.xlsx
@@ -1025,30 +1025,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1062,121 +1047,65 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제품구분 (검사기 분류)
+        <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1187,19 +1116,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1214,170 +1135,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1387,204 +1228,116 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1596,19 +1349,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1620,631 +1365,326 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="G6" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R6)
+        <t>★ 권위 행 (R6)
 관리코드 005T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R6)
+        <t>★ 권위 행 (R6)
 관리코드 005T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H8" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 005T2603 품명 불일치
+        <t>⚠️ 관리코드 005T2603 품명 불일치
 권위(R6): ARRAY 기능 검사기 (전용케이스)
 현재(R8): ARRAY 기능 검사기 (전용케이스) Modify
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 005T2603 품명 불일치
+        <t>⚠️ 관리코드 005T2603 품명 불일치
 권위(R6): ARRAY 기능 검사기 (전용케이스)
 현재(R9): ARRAY 기능 검사기 (전용케이스) Modify
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G10" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R10)
+        <t>★ 권위 행 (R10)
 관리코드 003T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H10" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R10)
+        <t>★ 권위 행 (R10)
 관리코드 003T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G19" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R19)
+        <t>★ 권위 행 (R19)
 관리코드 005T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H19" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R19)
+        <t>★ 권위 행 (R19)
 관리코드 005T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H20" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 005T2604 품명 불일치
+        <t>⚠️ 관리코드 005T2604 품명 불일치
 권위(R19): 기능검사기(UK3S)
 현재(R20): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G21" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R21)
+        <t>★ 권위 행 (R21)
 관리코드 006T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H21" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R21)
+        <t>★ 권위 행 (R21)
 관리코드 006T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H22" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 006T2604 품명 불일치
+        <t>⚠️ 관리코드 006T2604 품명 불일치
 권위(R21): 기능검사기(UK3S)
 현재(R22): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H23" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 006T2604 품명 불일치
+        <t>⚠️ 관리코드 006T2604 품명 불일치
 권위(R21): 기능검사기(UK3S)
 현재(R23): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G38" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R38)
+        <t>★ 권위 행 (R38)
 관리코드 017T2602의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H38" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R38)
+        <t>★ 권위 행 (R38)
 관리코드 017T2602의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G40" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R40)
+        <t>★ 권위 행 (R40)
 관리코드 005T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H40" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R40)
+        <t>★ 권위 행 (R40)
 관리코드 005T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G41" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R41)
+        <t>★ 권위 행 (R41)
 관리코드 028T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H41" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R41)
+        <t>★ 권위 행 (R41)
 관리코드 028T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G42" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R42)
+        <t>★ 권위 행 (R42)
 관리코드 029T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H42" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R42)
+        <t>★ 권위 행 (R42)
 관리코드 029T2601의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G45" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 028T2601 모델 불일치
+        <t>⚠️ 관리코드 028T2601 모델 불일치
 권위(R41): SM-A27B USB PBA
 현재(R45): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G46" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 029T2601 모델 불일치
+        <t>⚠️ 관리코드 029T2601 모델 불일치
 권위(R42): SM-A27B USB PBA
 현재(R46): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G47" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R47)
+        <t>★ 권위 행 (R47)
 관리코드 002T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H47" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R47)
+        <t>★ 권위 행 (R47)
 관리코드 002T2604의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G61" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R61)
+        <t>★ 권위 행 (R61)
 관리코드 022T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H61" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R61)
+        <t>★ 권위 행 (R61)
 관리코드 022T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H62" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 022T2603 품명 불일치
+        <t>⚠️ 관리코드 022T2603 품명 불일치
 권위(R61): OS검사기_케이스포함
 현재(R62): OS검사기_MODIFY
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G63" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R63)
+        <t>★ 권위 행 (R63)
 관리코드 024T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H63" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R63)
+        <t>★ 권위 행 (R63)
 관리코드 024T2603의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="H64" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 024T2603 품명 불일치
+        <t>⚠️ 관리코드 024T2603 품명 불일치
 권위(R63): TDR+IL검사기_케이스포함
 현재(R64): TDR+IL검사기_MODIFY
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G68" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 028T2601 모델 불일치
+        <t>⚠️ 관리코드 028T2601 모델 불일치
 권위(R41): SM-A27B USB PBA
 현재(R68): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G69" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 029T2601 모델 불일치
+        <t>⚠️ 관리코드 029T2601 모델 불일치
 권위(R42): SM-A27B USB PBA
 현재(R69): SM-A27BE USB PBA
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 017T2602 품명 불일치
+        <t>⚠️ 관리코드 017T2602 품명 불일치
 권위(R38): 기능검사기 (UK4S)
 현재(R71): 기능검사기(UK4S)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H74" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003T2601 품명 불일치
+        <t>⚠️ 관리코드 003T2601 품명 불일치
 권위(R10): 기능검사기 MODIFY
 현재(R74): 기능검사기(UK4)
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G99" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 005T2601 모델 불일치
+        <t>⚠️ 관리코드 005T2601 모델 불일치
 권위(R40): SM-L716 BAROMETER
 현재(R99): SM-L715 BAROMETER
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G104" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 002T2604 모델 불일치
+        <t>⚠️ 관리코드 002T2604 모델 불일치
 권위(R47): VMF0971-0125003
 현재(R104): ZNB-400
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H104" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 002T2604 품명 불일치
+        <t>⚠️ 관리코드 002T2604 품명 불일치
 권위(R47): VSWR 검사기- CASE 재활용
 현재(R104): 모듈검사기_케이스 제외
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2259,30 +1699,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2296,105 +1721,57 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2404,139 +1781,82 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2551,30 +1871,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하구분 (세부항목 진척률)
+        <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2586,19 +1891,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ INV번호(출하코드) (세부항목 진척률)
+        <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2610,19 +1907,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2636,70 +1925,38 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 차수/경로 (세부항목 진척률)
+        <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2711,19 +1968,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 거래유형 (세부항목 진척률)
+        <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2735,19 +1984,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통관분류 (세부항목 진척률)
+        <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2759,19 +2000,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하일 (세부항목 진척률)
+        <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2783,37 +2016,21 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 환율 (세부항목 진척률)
+        <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2825,35 +2042,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOX수 (세부항목 진척률)
+        <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2865,36 +2066,20 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 인보이스(USD) (세부항목 진척률)
+        <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2906,38 +2091,22 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ VN입고일 (세부항목 진척률)
+        <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2949,19 +2118,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2971,19 +2132,11 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입고완료 (세부항목 진척률)
+        <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2995,19 +2148,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하완료 (세부항목 진척률)
+        <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3019,19 +2164,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 조달진행률 (세부항목 진척률)
+        <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3043,7 +2180,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3058,30 +2194,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3095,121 +2216,65 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제품구분 (검사기 분류)
+        <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -3220,19 +2285,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -3247,170 +2304,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -3420,204 +2397,116 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3629,19 +2518,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3653,7 +2534,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3668,30 +2548,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3705,110 +2570,61 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3823,30 +2639,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3860,70 +2661,38 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행일 (세부항목 진척률)
+        <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3935,19 +2704,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행사유 (세부항목 진척률)
+        <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3959,7 +2720,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3974,49 +2734,26 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -4030,51 +2767,27 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 생성일 (세부항목 진척률)
+        <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4086,7 +2799,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -4101,30 +2813,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -4138,121 +2835,65 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제품구분 (검사기 분류)
+        <t>▣ 제품구분 (검사기 분류)
 • 드롭다운 선택:
   PBA    — PCB Board Assembly 검사기
   TSP    — Touch Screen Panel 검사기
   SENSOR — 센서 검사기
   기타   — 위에 해당되지 않는 검사기
 • 대시보드 제품군별 집계에 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -4263,19 +2904,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -4290,170 +2923,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -4463,204 +3016,116 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4672,19 +3137,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4696,7 +3153,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -5451,7 +3907,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="67" t="inlineStr">
@@ -5643,7 +4099,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="67" t="inlineStr">
@@ -5835,7 +4291,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="67" t="inlineStr">
@@ -5931,7 +4387,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="76" t="inlineStr">
@@ -6027,7 +4483,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="67" t="inlineStr">
@@ -6123,7 +4579,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="76" t="inlineStr">
@@ -6219,7 +4675,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="67" t="inlineStr">
@@ -6315,7 +4771,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="76" t="inlineStr">
@@ -6411,7 +4867,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="67" t="inlineStr">
@@ -6507,7 +4963,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="76" t="inlineStr">
@@ -6603,7 +5059,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="67" t="inlineStr">
@@ -6699,7 +5155,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="76" t="inlineStr">
@@ -6799,7 +5255,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="67" t="inlineStr">
@@ -6895,7 +5351,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="76" t="inlineStr">
@@ -6991,7 +5447,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="67" t="inlineStr">
@@ -7087,7 +5543,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="76" t="inlineStr">
@@ -7183,7 +5639,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="67" t="inlineStr">
@@ -7279,7 +5735,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="76" t="inlineStr">
@@ -7375,7 +5831,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="67" t="inlineStr">
@@ -7471,7 +5927,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="76" t="inlineStr">
@@ -7567,7 +6023,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="67" t="inlineStr">
@@ -7859,7 +6315,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="76" t="inlineStr">
@@ -7955,7 +6411,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="67" t="inlineStr">
@@ -8051,7 +6507,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="76" t="inlineStr">
@@ -8147,7 +6603,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="67" t="inlineStr">
@@ -8243,7 +6699,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="76" t="inlineStr">
@@ -8339,7 +6795,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="67" t="inlineStr">
@@ -8531,7 +6987,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="67" t="inlineStr">
@@ -8627,7 +7083,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="76" t="inlineStr">
@@ -8723,7 +7179,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="67" t="inlineStr">
@@ -9015,7 +7471,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="76" t="inlineStr">
@@ -9115,7 +7571,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="67" t="inlineStr">
@@ -9215,7 +7671,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="76" t="inlineStr">
@@ -9315,7 +7771,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
@@ -9415,7 +7871,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="76" t="inlineStr">
@@ -9515,7 +7971,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="67" t="inlineStr">
@@ -9711,7 +8167,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="67" t="inlineStr">
@@ -9811,7 +8267,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="76" t="inlineStr">
@@ -9911,7 +8367,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="67" t="inlineStr">
@@ -10011,7 +8467,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="76" t="inlineStr">
@@ -10107,7 +8563,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="67" t="inlineStr">
@@ -10203,7 +8659,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="76" t="inlineStr">
@@ -10299,7 +8755,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="67" t="inlineStr">
@@ -10395,7 +8851,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="76" t="inlineStr">
@@ -10495,7 +8951,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="67" t="inlineStr">
@@ -10591,7 +9047,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="76" t="inlineStr">
@@ -10687,7 +9143,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="67" t="inlineStr">
@@ -10879,7 +9335,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="67" t="inlineStr">
@@ -10975,7 +9431,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="76" t="inlineStr">
@@ -11075,7 +9531,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="67" t="inlineStr">
@@ -11171,7 +9627,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="76" t="inlineStr">
@@ -11371,7 +9827,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="76" t="inlineStr">
@@ -11471,7 +9927,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="67" t="inlineStr">
@@ -11571,7 +10027,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="76" t="inlineStr">
@@ -11671,7 +10127,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="67" t="inlineStr">
@@ -11771,7 +10227,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="76" t="inlineStr">
@@ -11867,7 +10323,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="67" t="inlineStr">
@@ -11963,7 +10419,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="76" t="inlineStr">
@@ -12059,7 +10515,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="67" t="inlineStr">
@@ -12155,7 +10611,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="76" t="inlineStr">
@@ -12347,7 +10803,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="76" t="inlineStr">
@@ -12443,7 +10899,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="67" t="inlineStr">
@@ -12539,7 +10995,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="76" t="inlineStr">
@@ -12639,7 +11095,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="67" t="inlineStr">
@@ -12735,7 +11191,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="76" t="inlineStr">
@@ -12835,7 +11291,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="67" t="inlineStr">
@@ -12935,7 +11391,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="76" t="inlineStr">
@@ -13035,7 +11491,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="67" t="inlineStr">
@@ -13323,7 +11779,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="76" t="inlineStr">
@@ -13419,7 +11875,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="67" t="inlineStr">
@@ -13519,7 +11975,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="76" t="inlineStr">
@@ -13615,7 +12071,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="67" t="inlineStr">
@@ -13711,7 +12167,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="76" t="inlineStr">
@@ -13907,7 +12363,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="76" t="inlineStr">
@@ -14003,7 +12459,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="67" t="inlineStr">
@@ -14099,7 +12555,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="76" t="inlineStr">
@@ -14199,7 +12655,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="67" t="inlineStr">
@@ -14299,7 +12755,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="76" t="inlineStr">
@@ -14399,7 +12855,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="67" t="inlineStr">
@@ -14499,7 +12955,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="76" t="inlineStr">
@@ -14595,7 +13051,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="67" t="inlineStr">
@@ -14791,7 +13247,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="67" t="inlineStr">
@@ -14887,7 +13343,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="76" t="inlineStr">
@@ -14983,7 +13439,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="67" t="inlineStr">
@@ -15079,7 +13535,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="76" t="inlineStr">
@@ -15175,7 +13631,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="67" t="inlineStr">
@@ -15269,7 +13725,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="76" t="inlineStr">
@@ -15457,7 +13913,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="76" t="inlineStr">
@@ -15647,7 +14103,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="76" t="inlineStr">
@@ -17070,7 +15526,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -17156,7 +15612,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -17242,7 +15698,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -17285,7 +15741,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="75" t="inlineStr">
@@ -17328,7 +15784,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -17371,7 +15827,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -17414,7 +15870,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -17457,7 +15913,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -17500,7 +15956,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -17543,7 +15999,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -17586,7 +16042,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -17629,7 +16085,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
@@ -17672,7 +16128,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -17715,7 +16171,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -17758,7 +16214,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -17801,7 +16257,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -17844,7 +16300,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -17887,7 +16343,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -17930,7 +16386,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -17973,7 +16429,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -18016,7 +16472,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="66" t="inlineStr">
@@ -18145,7 +16601,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -18188,7 +16644,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -18231,7 +16687,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -18274,7 +16730,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -18317,7 +16773,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -18360,7 +16816,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -18446,7 +16902,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -18489,7 +16945,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -18532,7 +16988,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -18661,7 +17117,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -18704,7 +17160,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -18747,7 +17203,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -18790,7 +17246,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -18833,7 +17289,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -18876,7 +17332,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -18962,7 +17418,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -19005,7 +17461,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -19048,7 +17504,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -19091,7 +17547,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -19134,7 +17590,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="66" t="inlineStr">
@@ -19177,7 +17633,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -19220,7 +17676,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -19263,7 +17719,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -19306,7 +17762,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -19349,7 +17805,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -19392,7 +17848,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="66" t="inlineStr">
@@ -19478,7 +17934,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -19521,7 +17977,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="75" t="inlineStr">
@@ -19564,7 +18020,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -19607,7 +18063,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="75" t="inlineStr">
@@ -19693,7 +18149,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -19736,7 +18192,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="66" t="inlineStr">
@@ -19779,7 +18235,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -19822,7 +18278,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -19865,7 +18321,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -19908,7 +18364,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -19951,7 +18407,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -19994,7 +18450,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -20037,7 +18493,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="75" t="inlineStr">
@@ -20123,7 +18579,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -20166,7 +18622,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -20209,7 +18665,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -20252,7 +18708,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -20295,7 +18751,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="75" t="inlineStr">
@@ -20338,7 +18794,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -20381,7 +18837,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -20424,7 +18880,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -20553,7 +19009,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -20596,7 +19052,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -20639,7 +19095,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -20682,7 +19138,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -20725,7 +19181,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -20811,7 +19267,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -20854,7 +19310,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -20897,7 +19353,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -20940,7 +19396,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -20983,7 +19439,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -21026,7 +19482,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -21069,7 +19525,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="75" t="inlineStr">
@@ -21112,7 +19568,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -21198,7 +19654,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -21241,7 +19697,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -21284,7 +19740,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -21327,7 +19783,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -21370,7 +19826,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -21413,7 +19869,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -21499,7 +19955,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -21581,7 +20037,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -24344,7 +22800,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260324-2</t>
+          <t>T-260324-1</t>
         </is>
       </c>
       <c r="D12" s="76" t="inlineStr">
@@ -24896,7 +23352,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260324-3</t>
+          <t>T-260324-2</t>
         </is>
       </c>
       <c r="D18" s="76" t="inlineStr">
@@ -24988,7 +23444,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260324-4</t>
+          <t>T-260324-3</t>
         </is>
       </c>
       <c r="D19" s="67" t="inlineStr">
@@ -25172,7 +23628,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260326-2</t>
+          <t>T-260326-1</t>
         </is>
       </c>
       <c r="D21" s="67" t="inlineStr">
@@ -25264,7 +23720,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260326-3</t>
+          <t>T-260326-2</t>
         </is>
       </c>
       <c r="D22" s="76" t="inlineStr">
@@ -25356,7 +23812,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260326-4</t>
+          <t>T-260326-3</t>
         </is>
       </c>
       <c r="D23" s="67" t="inlineStr">
@@ -25540,7 +23996,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260324-6</t>
+          <t>T-260324-5</t>
         </is>
       </c>
       <c r="D25" s="67" t="inlineStr">
@@ -25632,7 +24088,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260324-7</t>
+          <t>T-260324-6</t>
         </is>
       </c>
       <c r="D26" s="76" t="inlineStr">
@@ -25724,7 +24180,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260401-2</t>
+          <t>T-260401-1</t>
         </is>
       </c>
       <c r="D27" s="67" t="inlineStr">
@@ -25816,7 +24272,7 @@
       </c>
       <c r="C28" s="75" t="inlineStr">
         <is>
-          <t>T-260401-3</t>
+          <t>T-260401-2</t>
         </is>
       </c>
       <c r="D28" s="76" t="inlineStr">
@@ -26092,7 +24548,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260330-2</t>
+          <t>T-260330-1</t>
         </is>
       </c>
       <c r="D31" s="67" t="inlineStr">
@@ -26184,7 +24640,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260330-3</t>
+          <t>T-260330-2</t>
         </is>
       </c>
       <c r="D32" s="76" t="inlineStr">
@@ -26276,7 +24732,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260330-4</t>
+          <t>T-260330-3</t>
         </is>
       </c>
       <c r="D33" s="67" t="inlineStr">
@@ -26460,7 +24916,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260403-2</t>
+          <t>T-260403-1</t>
         </is>
       </c>
       <c r="D35" s="67" t="inlineStr">
@@ -26552,7 +25008,7 @@
       </c>
       <c r="C36" s="75" t="inlineStr">
         <is>
-          <t>T-260403-3</t>
+          <t>T-260403-2</t>
         </is>
       </c>
       <c r="D36" s="76" t="inlineStr">
@@ -26644,7 +25100,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260403-4</t>
+          <t>T-260403-3</t>
         </is>
       </c>
       <c r="D37" s="67" t="inlineStr">
@@ -26736,7 +25192,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260403-5</t>
+          <t>T-260403-4</t>
         </is>
       </c>
       <c r="D38" s="76" t="inlineStr">
@@ -26828,7 +25284,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260312-2</t>
+          <t>T-260312-1</t>
         </is>
       </c>
       <c r="D39" s="67" t="inlineStr">
@@ -26924,7 +25380,7 @@
       </c>
       <c r="C40" s="75" t="inlineStr">
         <is>
-          <t>T-260312-3</t>
+          <t>T-260312-2</t>
         </is>
       </c>
       <c r="D40" s="76" t="inlineStr">
@@ -27020,7 +25476,7 @@
       </c>
       <c r="C41" s="66" t="inlineStr">
         <is>
-          <t>T-260312-4</t>
+          <t>T-260312-3</t>
         </is>
       </c>
       <c r="D41" s="67" t="inlineStr">
@@ -27392,7 +25848,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260318-2</t>
+          <t>T-260318-1</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
@@ -27484,7 +25940,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260324-11</t>
+          <t>T-260324-10</t>
         </is>
       </c>
       <c r="D46" s="76" t="inlineStr">
@@ -27576,7 +26032,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260325-2</t>
+          <t>T-260325-1</t>
         </is>
       </c>
       <c r="D47" s="67" t="inlineStr">
@@ -27668,7 +26124,7 @@
       </c>
       <c r="C48" s="75" t="inlineStr">
         <is>
-          <t>T-260319-2</t>
+          <t>T-260319-1</t>
         </is>
       </c>
       <c r="D48" s="76" t="inlineStr">
@@ -27760,7 +26216,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260319-3</t>
+          <t>T-260319-2</t>
         </is>
       </c>
       <c r="D49" s="67" t="inlineStr">
@@ -27852,7 +26308,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260325-3</t>
+          <t>T-260325-2</t>
         </is>
       </c>
       <c r="D50" s="76" t="inlineStr">
@@ -27944,7 +26400,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260401-5</t>
+          <t>T-260401-4</t>
         </is>
       </c>
       <c r="D51" s="67" t="inlineStr">
@@ -28036,7 +26492,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260331-4</t>
+          <t>T-260331-3</t>
         </is>
       </c>
       <c r="D52" s="76" t="inlineStr">
@@ -28132,7 +26588,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260331-5</t>
+          <t>T-260331-4</t>
         </is>
       </c>
       <c r="D53" s="67" t="inlineStr">
@@ -28228,7 +26684,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260331-6</t>
+          <t>T-260331-5</t>
         </is>
       </c>
       <c r="D54" s="76" t="inlineStr">
@@ -28324,7 +26780,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260331-7</t>
+          <t>T-260331-6</t>
         </is>
       </c>
       <c r="D55" s="67" t="inlineStr">
@@ -28420,7 +26876,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260324-12</t>
+          <t>T-260324-11</t>
         </is>
       </c>
       <c r="D56" s="76" t="inlineStr">
@@ -28516,7 +26972,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260313-2</t>
+          <t>T-260313-1</t>
         </is>
       </c>
       <c r="D57" s="67" t="inlineStr">
@@ -28608,7 +27064,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260326-5</t>
+          <t>T-260326-4</t>
         </is>
       </c>
       <c r="D58" s="76" t="inlineStr">
@@ -28800,7 +27256,7 @@
       </c>
       <c r="C60" s="75" t="inlineStr">
         <is>
-          <t>T-260331-8</t>
+          <t>T-260331-7</t>
         </is>
       </c>
       <c r="D60" s="76" t="inlineStr">
@@ -28892,7 +27348,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260331-9</t>
+          <t>T-260331-8</t>
         </is>
       </c>
       <c r="D61" s="67" t="inlineStr">
@@ -28984,7 +27440,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260331-10</t>
+          <t>T-260331-9</t>
         </is>
       </c>
       <c r="D62" s="76" t="inlineStr">
@@ -29076,7 +27532,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260318-3</t>
+          <t>T-260318-2</t>
         </is>
       </c>
       <c r="D63" s="67" t="inlineStr">
@@ -29168,7 +27624,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260325-4</t>
+          <t>T-260325-3</t>
         </is>
       </c>
       <c r="D64" s="76" t="inlineStr">
@@ -29260,7 +27716,7 @@
       </c>
       <c r="C65" s="66" t="inlineStr">
         <is>
-          <t>T-260325-5</t>
+          <t>T-260325-4</t>
         </is>
       </c>
       <c r="D65" s="67" t="inlineStr">
@@ -29352,7 +27808,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260316-2</t>
+          <t>T-260316-1</t>
         </is>
       </c>
       <c r="D66" s="76" t="inlineStr">
@@ -29444,7 +27900,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260318-4</t>
+          <t>T-260318-3</t>
         </is>
       </c>
       <c r="D67" s="67" t="inlineStr">
@@ -29536,7 +27992,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260318-5</t>
+          <t>T-260318-4</t>
         </is>
       </c>
       <c r="D68" s="76" t="inlineStr">
@@ -29628,7 +28084,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260325-6</t>
+          <t>T-260325-5</t>
         </is>
       </c>
       <c r="D69" s="67" t="inlineStr">
@@ -29720,7 +28176,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260327-8</t>
+          <t>T-260327-7</t>
         </is>
       </c>
       <c r="D70" s="76" t="inlineStr">
@@ -29812,7 +28268,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260331-11</t>
+          <t>T-260331-10</t>
         </is>
       </c>
       <c r="D71" s="67" t="inlineStr">
@@ -29904,7 +28360,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260303-3</t>
+          <t>T-260303-2</t>
         </is>
       </c>
       <c r="D72" s="76" t="inlineStr">
@@ -29996,7 +28452,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260310-2</t>
+          <t>T-260310-1</t>
         </is>
       </c>
       <c r="D73" s="67" t="inlineStr">
@@ -31299,7 +29755,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -31379,7 +29835,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -31459,7 +29915,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -31499,7 +29955,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="75" t="inlineStr">
@@ -31539,7 +29995,7 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="66" t="inlineStr">
@@ -31579,7 +30035,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -31619,7 +30075,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -31659,7 +30115,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -31699,7 +30155,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -31739,7 +30195,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -31779,7 +30235,7 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="66" t="inlineStr">
@@ -31819,7 +30275,7 @@
       </c>
       <c r="C18" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
@@ -31859,7 +30315,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -31899,7 +30355,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -31939,7 +30395,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -31979,7 +30435,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -32019,7 +30475,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -32059,7 +30515,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -32099,7 +30555,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -32139,7 +30595,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -32179,7 +30635,7 @@
       </c>
       <c r="C27" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="66" t="inlineStr">
@@ -32299,7 +30755,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -32339,7 +30795,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -32379,7 +30835,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -32419,7 +30875,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -32459,7 +30915,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -32499,7 +30955,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -32579,7 +31035,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -32619,7 +31075,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -32659,7 +31115,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -32779,7 +31235,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -32819,7 +31275,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -32859,7 +31315,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -32899,7 +31355,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -32939,7 +31395,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -32979,7 +31435,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -33059,7 +31515,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -33099,7 +31555,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -33139,7 +31595,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -33179,7 +31635,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -33219,7 +31675,7 @@
       </c>
       <c r="C53" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="66" t="inlineStr">
@@ -33259,7 +31715,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -33299,7 +31755,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -33339,7 +31795,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -33379,7 +31835,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -33419,7 +31875,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -33459,7 +31915,7 @@
       </c>
       <c r="C59" s="66" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="66" t="inlineStr">
@@ -33539,7 +31995,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -33579,7 +32035,7 @@
       </c>
       <c r="C62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="75" t="inlineStr">
@@ -33619,7 +32075,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -33659,7 +32115,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="75" t="inlineStr">
@@ -33739,7 +32195,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -33779,7 +32235,7 @@
       </c>
       <c r="C67" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="66" t="inlineStr">
@@ -33819,7 +32275,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -33859,7 +32315,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -33899,7 +32355,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -33939,7 +32395,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -33979,7 +32435,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -34019,7 +32475,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -34059,7 +32515,7 @@
       </c>
       <c r="C74" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="75" t="inlineStr">
@@ -34139,7 +32595,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -34179,7 +32635,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -34219,7 +32675,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -34259,7 +32715,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -34299,7 +32755,7 @@
       </c>
       <c r="C80" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="75" t="inlineStr">
@@ -34339,7 +32795,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -34379,7 +32835,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -34419,7 +32875,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -34539,7 +32995,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -34579,7 +33035,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -34619,7 +33075,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -34659,7 +33115,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -34699,7 +33155,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -34779,7 +33235,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -34819,7 +33275,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -34859,7 +33315,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -34899,7 +33355,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -34939,7 +33395,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -34979,7 +33435,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -35019,7 +33475,7 @@
       </c>
       <c r="C98" s="75" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="75" t="inlineStr">
@@ -35059,7 +33515,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -35139,7 +33595,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -35179,7 +33635,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -35219,7 +33675,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -35259,7 +33715,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -35299,7 +33755,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -35339,7 +33795,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -35419,7 +33875,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -35495,7 +33951,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -35571,7 +34027,7 @@
       </c>
       <c r="C112" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D112" s="75" t="inlineStr">
@@ -35611,7 +34067,7 @@
       </c>
       <c r="C113" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D113" s="66" t="inlineStr">
@@ -35651,7 +34107,7 @@
       </c>
       <c r="C114" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D114" s="75" t="inlineStr">
@@ -35691,7 +34147,7 @@
       </c>
       <c r="C115" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D115" s="66" t="inlineStr">
@@ -35771,7 +34227,7 @@
       </c>
       <c r="C117" s="66" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D117" s="66" t="inlineStr">
@@ -35811,7 +34267,7 @@
       </c>
       <c r="C118" s="75" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D118" s="75" t="inlineStr">
@@ -35851,7 +34307,7 @@
       </c>
       <c r="C119" s="66" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D119" s="66" t="inlineStr">
@@ -35891,7 +34347,7 @@
       </c>
       <c r="C120" s="75" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D120" s="75" t="inlineStr">
@@ -35931,7 +34387,7 @@
       </c>
       <c r="C121" s="66" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D121" s="66" t="inlineStr">
@@ -36011,7 +34467,7 @@
       </c>
       <c r="C123" s="66" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D123" s="66" t="inlineStr">
@@ -36051,7 +34507,7 @@
       </c>
       <c r="C124" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D124" s="75" t="inlineStr">
@@ -36091,7 +34547,7 @@
       </c>
       <c r="C125" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D125" s="66" t="inlineStr">
@@ -36131,7 +34587,7 @@
       </c>
       <c r="C126" s="75" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D126" s="75" t="inlineStr">
@@ -36171,7 +34627,7 @@
       </c>
       <c r="C127" s="66" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D127" s="66" t="inlineStr">
@@ -36211,7 +34667,7 @@
       </c>
       <c r="C128" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D128" s="75" t="inlineStr">
@@ -36251,7 +34707,7 @@
       </c>
       <c r="C129" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D129" s="66" t="inlineStr">
@@ -36291,7 +34747,7 @@
       </c>
       <c r="C130" s="75" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D130" s="75" t="inlineStr">
@@ -36331,7 +34787,7 @@
       </c>
       <c r="C131" s="66" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D131" s="66" t="inlineStr">
@@ -36371,7 +34827,7 @@
       </c>
       <c r="C132" s="75" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D132" s="75" t="inlineStr">
@@ -36411,7 +34867,7 @@
       </c>
       <c r="C133" s="66" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D133" s="66" t="inlineStr">
@@ -36451,7 +34907,7 @@
       </c>
       <c r="C134" s="75" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D134" s="75" t="inlineStr">
@@ -36491,7 +34947,7 @@
       </c>
       <c r="C135" s="66" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D135" s="66" t="inlineStr">
@@ -36531,7 +34987,7 @@
       </c>
       <c r="C136" s="75" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D136" s="75" t="inlineStr">
@@ -36571,7 +35027,7 @@
       </c>
       <c r="C137" s="66" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D137" s="66" t="inlineStr">
@@ -36611,7 +35067,7 @@
       </c>
       <c r="C138" s="75" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D138" s="75" t="inlineStr">
@@ -36651,7 +35107,7 @@
       </c>
       <c r="C139" s="66" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D139" s="66" t="inlineStr">
@@ -36691,7 +35147,7 @@
       </c>
       <c r="C140" s="75" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D140" s="75" t="inlineStr">
@@ -36731,7 +35187,7 @@
       </c>
       <c r="C141" s="66" t="inlineStr">
         <is>
-          <t>T-260331-8</t>
+          <t>T-260331-7</t>
         </is>
       </c>
       <c r="D141" s="66" t="inlineStr">
@@ -36771,7 +35227,7 @@
       </c>
       <c r="C142" s="75" t="inlineStr">
         <is>
-          <t>T-260331-9</t>
+          <t>T-260331-8</t>
         </is>
       </c>
       <c r="D142" s="75" t="inlineStr">
@@ -36811,7 +35267,7 @@
       </c>
       <c r="C143" s="66" t="inlineStr">
         <is>
-          <t>T-260331-10</t>
+          <t>T-260331-9</t>
         </is>
       </c>
       <c r="D143" s="66" t="inlineStr">
@@ -36851,7 +35307,7 @@
       </c>
       <c r="C144" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D144" s="75" t="inlineStr">
@@ -36891,7 +35347,7 @@
       </c>
       <c r="C145" s="66" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D145" s="66" t="inlineStr">
@@ -36931,7 +35387,7 @@
       </c>
       <c r="C146" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D146" s="75" t="inlineStr">
@@ -36971,7 +35427,7 @@
       </c>
       <c r="C147" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D147" s="66" t="inlineStr">
@@ -37011,7 +35467,7 @@
       </c>
       <c r="C148" s="75" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D148" s="75" t="inlineStr">
@@ -37051,7 +35507,7 @@
       </c>
       <c r="C149" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D149" s="66" t="inlineStr">
@@ -37091,7 +35547,7 @@
       </c>
       <c r="C150" s="75" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D150" s="75" t="inlineStr">
@@ -37131,7 +35587,7 @@
       </c>
       <c r="C151" s="66" t="inlineStr">
         <is>
-          <t>T-260318-3</t>
+          <t>T-260318-2</t>
         </is>
       </c>
       <c r="D151" s="66" t="inlineStr">
@@ -37171,7 +35627,7 @@
       </c>
       <c r="C152" s="75" t="inlineStr">
         <is>
-          <t>T-260325-4</t>
+          <t>T-260325-3</t>
         </is>
       </c>
       <c r="D152" s="75" t="inlineStr">
@@ -37211,7 +35667,7 @@
       </c>
       <c r="C153" s="66" t="inlineStr">
         <is>
-          <t>T-260325-5</t>
+          <t>T-260325-4</t>
         </is>
       </c>
       <c r="D153" s="66" t="inlineStr">
@@ -37251,7 +35707,7 @@
       </c>
       <c r="C154" s="75" t="inlineStr">
         <is>
-          <t>T-260316-2</t>
+          <t>T-260316-1</t>
         </is>
       </c>
       <c r="D154" s="75" t="inlineStr">
@@ -37291,7 +35747,7 @@
       </c>
       <c r="C155" s="66" t="inlineStr">
         <is>
-          <t>T-260318-4</t>
+          <t>T-260318-3</t>
         </is>
       </c>
       <c r="D155" s="66" t="inlineStr">
@@ -37331,7 +35787,7 @@
       </c>
       <c r="C156" s="75" t="inlineStr">
         <is>
-          <t>T-260318-5</t>
+          <t>T-260318-4</t>
         </is>
       </c>
       <c r="D156" s="75" t="inlineStr">
@@ -37371,7 +35827,7 @@
       </c>
       <c r="C157" s="66" t="inlineStr">
         <is>
-          <t>T-260325-6</t>
+          <t>T-260325-5</t>
         </is>
       </c>
       <c r="D157" s="66" t="inlineStr">
@@ -37411,7 +35867,7 @@
       </c>
       <c r="C158" s="75" t="inlineStr">
         <is>
-          <t>T-260327-8</t>
+          <t>T-260327-7</t>
         </is>
       </c>
       <c r="D158" s="75" t="inlineStr">
@@ -37451,7 +35907,7 @@
       </c>
       <c r="C159" s="66" t="inlineStr">
         <is>
-          <t>T-260331-11</t>
+          <t>T-260331-10</t>
         </is>
       </c>
       <c r="D159" s="66" t="inlineStr">
@@ -37491,7 +35947,7 @@
       </c>
       <c r="C160" s="75" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D160" s="75" t="inlineStr">
@@ -37531,7 +35987,7 @@
       </c>
       <c r="C161" s="66" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D161" s="66" t="inlineStr">
@@ -37571,7 +36027,7 @@
       </c>
       <c r="C162" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D162" s="75" t="inlineStr">
@@ -37611,7 +36067,7 @@
       </c>
       <c r="C163" s="66" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D163" s="66" t="inlineStr">
@@ -37651,7 +36107,7 @@
       </c>
       <c r="C164" s="75" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D164" s="75" t="inlineStr">
@@ -37691,7 +36147,7 @@
       </c>
       <c r="C165" s="66" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D165" s="66" t="inlineStr">
@@ -37731,7 +36187,7 @@
       </c>
       <c r="C166" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D166" s="75" t="inlineStr">
@@ -37771,7 +36227,7 @@
       </c>
       <c r="C167" s="66" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D167" s="66" t="inlineStr">
@@ -37851,7 +36307,7 @@
       </c>
       <c r="C169" s="66" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D169" s="66" t="inlineStr">
@@ -37891,7 +36347,7 @@
       </c>
       <c r="C170" s="75" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D170" s="75" t="inlineStr">
@@ -37931,7 +36387,7 @@
       </c>
       <c r="C171" s="66" t="inlineStr">
         <is>
-          <t>T-260303-3</t>
+          <t>T-260303-2</t>
         </is>
       </c>
       <c r="D171" s="66" t="inlineStr">
@@ -37971,7 +36427,7 @@
       </c>
       <c r="C172" s="75" t="inlineStr">
         <is>
-          <t>T-260310-2</t>
+          <t>T-260310-1</t>
         </is>
       </c>
       <c r="D172" s="75" t="inlineStr">
@@ -38011,7 +36467,7 @@
       </c>
       <c r="C173" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D173" s="66" t="inlineStr">
@@ -38051,7 +36507,7 @@
       </c>
       <c r="C174" s="75" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D174" s="75" t="inlineStr">
@@ -38091,7 +36547,7 @@
       </c>
       <c r="C175" s="66" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D175" s="66" t="inlineStr">
@@ -38131,7 +36587,7 @@
       </c>
       <c r="C176" s="75" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D176" s="75" t="inlineStr">
@@ -38171,7 +36627,7 @@
       </c>
       <c r="C177" s="66" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D177" s="66" t="inlineStr">
@@ -38646,7 +37102,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D5" s="66" t="inlineStr">
@@ -38681,7 +37137,7 @@
       </c>
       <c r="C6" s="75" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D6" s="75" t="inlineStr">
@@ -38716,7 +37172,7 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D7" s="66" t="inlineStr">
@@ -38751,7 +37207,7 @@
       </c>
       <c r="C8" s="75" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D8" s="75" t="inlineStr">
@@ -38786,7 +37242,7 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D9" s="66" t="inlineStr">
@@ -38891,7 +37347,7 @@
       </c>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -38926,7 +37382,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D13" s="66" t="inlineStr">
@@ -38961,7 +37417,7 @@
       </c>
       <c r="C14" s="75" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -38996,7 +37452,7 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D15" s="66" t="inlineStr">
@@ -39031,7 +37487,7 @@
       </c>
       <c r="C16" s="75" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
@@ -39136,7 +37592,7 @@
       </c>
       <c r="C19" s="66" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D19" s="66" t="inlineStr">
@@ -39171,7 +37627,7 @@
       </c>
       <c r="C20" s="75" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -39206,7 +37662,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D21" s="66" t="inlineStr">
@@ -39241,7 +37697,7 @@
       </c>
       <c r="C22" s="75" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -39276,7 +37732,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D23" s="66" t="inlineStr">
@@ -39311,7 +37767,7 @@
       </c>
       <c r="C24" s="75" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
@@ -39346,7 +37802,7 @@
       </c>
       <c r="C25" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D25" s="66" t="inlineStr">
@@ -39381,7 +37837,7 @@
       </c>
       <c r="C26" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -39451,7 +37907,7 @@
       </c>
       <c r="C28" s="75" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D28" s="75" t="inlineStr">
@@ -39521,7 +37977,7 @@
       </c>
       <c r="C30" s="75" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
@@ -39556,7 +38012,7 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D31" s="66" t="inlineStr">
@@ -39591,7 +38047,7 @@
       </c>
       <c r="C32" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
@@ -39626,7 +38082,7 @@
       </c>
       <c r="C33" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D33" s="66" t="inlineStr">
@@ -39661,7 +38117,7 @@
       </c>
       <c r="C34" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -39696,7 +38152,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -39731,7 +38187,7 @@
       </c>
       <c r="C36" s="75" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D36" s="75" t="inlineStr">
@@ -39766,7 +38222,7 @@
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D37" s="66" t="inlineStr">
@@ -39801,7 +38257,7 @@
       </c>
       <c r="C38" s="75" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D38" s="75" t="inlineStr">
@@ -39836,7 +38292,7 @@
       </c>
       <c r="C39" s="66" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D39" s="66" t="inlineStr">
@@ -39871,7 +38327,7 @@
       </c>
       <c r="C40" s="75" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D40" s="75" t="inlineStr">
@@ -39906,7 +38362,7 @@
       </c>
       <c r="C41" s="66" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D41" s="66" t="inlineStr">
@@ -39941,7 +38397,7 @@
       </c>
       <c r="C42" s="75" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D42" s="75" t="inlineStr">
@@ -39976,7 +38432,7 @@
       </c>
       <c r="C43" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D43" s="66" t="inlineStr">
@@ -40011,7 +38467,7 @@
       </c>
       <c r="C44" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D44" s="75" t="inlineStr">
@@ -40046,7 +38502,7 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D45" s="66" t="inlineStr">
@@ -40081,7 +38537,7 @@
       </c>
       <c r="C46" s="75" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D46" s="75" t="inlineStr">
@@ -40116,7 +38572,7 @@
       </c>
       <c r="C47" s="66" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D47" s="66" t="inlineStr">
@@ -40151,7 +38607,7 @@
       </c>
       <c r="C48" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D48" s="75" t="inlineStr">
@@ -40186,7 +38642,7 @@
       </c>
       <c r="C49" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -40221,7 +38677,7 @@
       </c>
       <c r="C50" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D50" s="75" t="inlineStr">
@@ -40256,7 +38712,7 @@
       </c>
       <c r="C51" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -40291,7 +38747,7 @@
       </c>
       <c r="C52" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D52" s="75" t="inlineStr">
@@ -40361,7 +38817,7 @@
       </c>
       <c r="C54" s="75" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D54" s="75" t="inlineStr">
@@ -40396,7 +38852,7 @@
       </c>
       <c r="C55" s="66" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -40431,7 +38887,7 @@
       </c>
       <c r="C56" s="75" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D56" s="75" t="inlineStr">
@@ -40466,7 +38922,7 @@
       </c>
       <c r="C57" s="66" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -40501,7 +38957,7 @@
       </c>
       <c r="C58" s="75" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D58" s="75" t="inlineStr">
@@ -40606,7 +39062,7 @@
       </c>
       <c r="C61" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -40676,7 +39132,7 @@
       </c>
       <c r="C63" s="66" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -40746,7 +39202,7 @@
       </c>
       <c r="C65" s="66" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D65" s="66" t="inlineStr">
@@ -40781,7 +39237,7 @@
       </c>
       <c r="C66" s="75" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D66" s="75" t="inlineStr">
@@ -40851,7 +39307,7 @@
       </c>
       <c r="C68" s="75" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D68" s="75" t="inlineStr">
@@ -40886,7 +39342,7 @@
       </c>
       <c r="C69" s="66" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -40921,7 +39377,7 @@
       </c>
       <c r="C70" s="75" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D70" s="75" t="inlineStr">
@@ -40956,7 +39412,7 @@
       </c>
       <c r="C71" s="66" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D71" s="66" t="inlineStr">
@@ -40991,7 +39447,7 @@
       </c>
       <c r="C72" s="75" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D72" s="75" t="inlineStr">
@@ -41026,7 +39482,7 @@
       </c>
       <c r="C73" s="66" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D73" s="66" t="inlineStr">
@@ -41096,7 +39552,7 @@
       </c>
       <c r="C75" s="66" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D75" s="66" t="inlineStr">
@@ -41131,7 +39587,7 @@
       </c>
       <c r="C76" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D76" s="75" t="inlineStr">
@@ -41166,7 +39622,7 @@
       </c>
       <c r="C77" s="66" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D77" s="66" t="inlineStr">
@@ -41201,7 +39657,7 @@
       </c>
       <c r="C78" s="75" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D78" s="75" t="inlineStr">
@@ -41236,7 +39692,7 @@
       </c>
       <c r="C79" s="66" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D79" s="66" t="inlineStr">
@@ -41306,7 +39762,7 @@
       </c>
       <c r="C81" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D81" s="66" t="inlineStr">
@@ -41341,7 +39797,7 @@
       </c>
       <c r="C82" s="75" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D82" s="75" t="inlineStr">
@@ -41376,7 +39832,7 @@
       </c>
       <c r="C83" s="66" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D83" s="66" t="inlineStr">
@@ -41411,7 +39867,7 @@
       </c>
       <c r="C84" s="75" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D84" s="75" t="inlineStr">
@@ -41446,7 +39902,7 @@
       </c>
       <c r="C85" s="66" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D85" s="66" t="inlineStr">
@@ -41481,7 +39937,7 @@
       </c>
       <c r="C86" s="75" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D86" s="75" t="inlineStr">
@@ -41516,7 +39972,7 @@
       </c>
       <c r="C87" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D87" s="66" t="inlineStr">
@@ -41551,7 +40007,7 @@
       </c>
       <c r="C88" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D88" s="75" t="inlineStr">
@@ -41586,7 +40042,7 @@
       </c>
       <c r="C89" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D89" s="66" t="inlineStr">
@@ -41621,7 +40077,7 @@
       </c>
       <c r="C90" s="75" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D90" s="75" t="inlineStr">
@@ -41691,7 +40147,7 @@
       </c>
       <c r="C92" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D92" s="75" t="inlineStr">
@@ -41726,7 +40182,7 @@
       </c>
       <c r="C93" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D93" s="66" t="inlineStr">
@@ -41761,7 +40217,7 @@
       </c>
       <c r="C94" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D94" s="75" t="inlineStr">
@@ -41796,7 +40252,7 @@
       </c>
       <c r="C95" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D95" s="66" t="inlineStr">
@@ -41831,7 +40287,7 @@
       </c>
       <c r="C96" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D96" s="75" t="inlineStr">
@@ -41866,7 +40322,7 @@
       </c>
       <c r="C97" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D97" s="66" t="inlineStr">
@@ -41936,7 +40392,7 @@
       </c>
       <c r="C99" s="66" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="66" t="inlineStr">
@@ -41971,7 +40427,7 @@
       </c>
       <c r="C100" s="75" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D100" s="75" t="inlineStr">
@@ -42006,7 +40462,7 @@
       </c>
       <c r="C101" s="66" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D101" s="66" t="inlineStr">
@@ -42041,7 +40497,7 @@
       </c>
       <c r="C102" s="75" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D102" s="75" t="inlineStr">
@@ -42076,7 +40532,7 @@
       </c>
       <c r="C103" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D103" s="66" t="inlineStr">
@@ -42111,7 +40567,7 @@
       </c>
       <c r="C104" s="75" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D104" s="75" t="inlineStr">
@@ -42146,7 +40602,7 @@
       </c>
       <c r="C105" s="66" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D105" s="66" t="inlineStr">
@@ -42181,7 +40637,7 @@
       </c>
       <c r="C106" s="75" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D106" s="75" t="inlineStr">
@@ -42251,7 +40707,7 @@
       </c>
       <c r="C108" s="75" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D108" s="75" t="inlineStr">
@@ -42286,7 +40742,7 @@
       </c>
       <c r="C109" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D109" s="66" t="inlineStr">
@@ -42321,7 +40777,7 @@
       </c>
       <c r="C110" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D110" s="75" t="inlineStr">
@@ -42743,7 +41199,7 @@
       </c>
       <c r="B5" s="66" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="C5" s="66" t="inlineStr">
@@ -42833,7 +41289,7 @@
       </c>
       <c r="B8" s="75" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="C8" s="75" t="inlineStr">
@@ -42863,7 +41319,7 @@
       </c>
       <c r="B9" s="66" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="C9" s="66" t="inlineStr">
@@ -42923,7 +41379,7 @@
       </c>
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="C11" s="66" t="inlineStr">
@@ -42953,7 +41409,7 @@
       </c>
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="C12" s="75" t="inlineStr">
@@ -43013,7 +41469,7 @@
       </c>
       <c r="B14" s="75" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="C14" s="75" t="inlineStr">
@@ -43043,7 +41499,7 @@
       </c>
       <c r="B15" s="66" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="C15" s="66" t="inlineStr">
@@ -43073,7 +41529,7 @@
       </c>
       <c r="B16" s="75" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="C16" s="75" t="inlineStr">
@@ -43103,7 +41559,7 @@
       </c>
       <c r="B17" s="66" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="C17" s="66" t="inlineStr">
@@ -43133,7 +41589,7 @@
       </c>
       <c r="B18" s="75" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="C18" s="75" t="inlineStr">
@@ -43163,7 +41619,7 @@
       </c>
       <c r="B19" s="66" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="C19" s="66" t="inlineStr">
@@ -43193,7 +41649,7 @@
       </c>
       <c r="B20" s="75" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="C20" s="75" t="inlineStr">
@@ -43223,7 +41679,7 @@
       </c>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="C21" s="66" t="inlineStr">
@@ -43253,7 +41709,7 @@
       </c>
       <c r="B22" s="75" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="C22" s="75" t="inlineStr">
@@ -43283,7 +41739,7 @@
       </c>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="C23" s="66" t="inlineStr">
@@ -43313,7 +41769,7 @@
       </c>
       <c r="B24" s="75" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="C24" s="75" t="inlineStr">
@@ -43343,7 +41799,7 @@
       </c>
       <c r="B25" s="66" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="C25" s="66" t="inlineStr">
@@ -43373,7 +41829,7 @@
       </c>
       <c r="B26" s="75" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="C26" s="75" t="inlineStr">
@@ -43403,7 +41859,7 @@
       </c>
       <c r="B27" s="66" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="C27" s="66" t="inlineStr">
@@ -43433,7 +41889,7 @@
       </c>
       <c r="B28" s="75" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="C28" s="75" t="inlineStr">
@@ -43463,7 +41919,7 @@
       </c>
       <c r="B29" s="66" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="C29" s="66" t="inlineStr">
@@ -43493,7 +41949,7 @@
       </c>
       <c r="B30" s="75" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="C30" s="75" t="inlineStr">
@@ -43523,7 +41979,7 @@
       </c>
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr">
@@ -43553,7 +42009,7 @@
       </c>
       <c r="B32" s="75" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="C32" s="75" t="inlineStr">
@@ -43583,7 +42039,7 @@
       </c>
       <c r="B33" s="66" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="C33" s="66" t="inlineStr">
@@ -43643,7 +42099,7 @@
       </c>
       <c r="B35" s="66" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="C35" s="66" t="inlineStr">
@@ -43673,7 +42129,7 @@
       </c>
       <c r="B36" s="75" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="C36" s="75" t="inlineStr">
@@ -43703,7 +42159,7 @@
       </c>
       <c r="B37" s="66" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="C37" s="66" t="inlineStr">
@@ -43763,7 +42219,7 @@
       </c>
       <c r="B39" s="66" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="C39" s="66" t="inlineStr">
@@ -43793,7 +42249,7 @@
       </c>
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="C40" s="75" t="inlineStr">
@@ -43823,7 +42279,7 @@
       </c>
       <c r="B41" s="66" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="C41" s="66" t="inlineStr">
@@ -43853,7 +42309,7 @@
       </c>
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="C42" s="75" t="inlineStr">
@@ -43883,7 +42339,7 @@
       </c>
       <c r="B43" s="66" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="C43" s="66" t="inlineStr">
@@ -43913,7 +42369,7 @@
       </c>
       <c r="B44" s="75" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="C44" s="75" t="inlineStr">
@@ -43943,7 +42399,7 @@
       </c>
       <c r="B45" s="66" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="C45" s="66" t="inlineStr">
@@ -43973,7 +42429,7 @@
       </c>
       <c r="B46" s="75" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="C46" s="75" t="inlineStr">
@@ -44003,7 +42459,7 @@
       </c>
       <c r="B47" s="66" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="C47" s="66" t="inlineStr">
@@ -44033,7 +42489,7 @@
       </c>
       <c r="B48" s="75" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="C48" s="75" t="inlineStr">
@@ -44093,7 +42549,7 @@
       </c>
       <c r="B50" s="75" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="C50" s="75" t="inlineStr">
@@ -44123,7 +42579,7 @@
       </c>
       <c r="B51" s="66" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="C51" s="66" t="inlineStr">
@@ -44153,7 +42609,7 @@
       </c>
       <c r="B52" s="75" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="C52" s="75" t="inlineStr">
@@ -44183,7 +42639,7 @@
       </c>
       <c r="B53" s="66" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="C53" s="66" t="inlineStr">
@@ -44213,7 +42669,7 @@
       </c>
       <c r="B54" s="75" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="C54" s="75" t="inlineStr">
@@ -44243,7 +42699,7 @@
       </c>
       <c r="B55" s="66" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="C55" s="66" t="inlineStr">
@@ -44273,7 +42729,7 @@
       </c>
       <c r="B56" s="75" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="C56" s="75" t="inlineStr">
@@ -44303,7 +42759,7 @@
       </c>
       <c r="B57" s="66" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="C57" s="66" t="inlineStr">
@@ -44333,7 +42789,7 @@
       </c>
       <c r="B58" s="75" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="C58" s="75" t="inlineStr">
@@ -44393,7 +42849,7 @@
       </c>
       <c r="B60" s="75" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="C60" s="75" t="inlineStr">
@@ -44423,7 +42879,7 @@
       </c>
       <c r="B61" s="66" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="C61" s="66" t="inlineStr">
@@ -44453,7 +42909,7 @@
       </c>
       <c r="B62" s="75" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="C62" s="75" t="inlineStr">
@@ -44483,7 +42939,7 @@
       </c>
       <c r="B63" s="66" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="C63" s="66" t="inlineStr">
@@ -44513,7 +42969,7 @@
       </c>
       <c r="B64" s="75" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="C64" s="75" t="inlineStr">
@@ -44543,7 +42999,7 @@
       </c>
       <c r="B65" s="66" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="C65" s="66" t="inlineStr">
@@ -44573,7 +43029,7 @@
       </c>
       <c r="B66" s="75" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="C66" s="75" t="inlineStr">
@@ -44603,7 +43059,7 @@
       </c>
       <c r="B67" s="66" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="C67" s="66" t="inlineStr">
@@ -44633,7 +43089,7 @@
       </c>
       <c r="B68" s="75" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="C68" s="75" t="inlineStr">
@@ -44663,7 +43119,7 @@
       </c>
       <c r="B69" s="66" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="C69" s="66" t="inlineStr">
@@ -44693,7 +43149,7 @@
       </c>
       <c r="B70" s="75" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="C70" s="75" t="inlineStr">
@@ -44723,7 +43179,7 @@
       </c>
       <c r="B71" s="66" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="C71" s="66" t="inlineStr">
@@ -44753,7 +43209,7 @@
       </c>
       <c r="B72" s="75" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="C72" s="75" t="inlineStr">
@@ -44783,7 +43239,7 @@
       </c>
       <c r="B73" s="66" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="C73" s="66" t="inlineStr">
@@ -44813,7 +43269,7 @@
       </c>
       <c r="B74" s="75" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="C74" s="75" t="inlineStr">
@@ -44843,7 +43299,7 @@
       </c>
       <c r="B75" s="66" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="C75" s="66" t="inlineStr">
@@ -44873,7 +43329,7 @@
       </c>
       <c r="B76" s="75" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="C76" s="75" t="inlineStr">
@@ -44903,7 +43359,7 @@
       </c>
       <c r="B77" s="66" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="C77" s="66" t="inlineStr">
@@ -44933,7 +43389,7 @@
       </c>
       <c r="B78" s="75" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="C78" s="75" t="inlineStr">
@@ -44963,7 +43419,7 @@
       </c>
       <c r="B79" s="66" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="C79" s="66" t="inlineStr">
@@ -45023,7 +43479,7 @@
       </c>
       <c r="B81" s="66" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="C81" s="66" t="inlineStr">
@@ -45053,7 +43509,7 @@
       </c>
       <c r="B82" s="75" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="C82" s="75" t="inlineStr">
@@ -45083,7 +43539,7 @@
       </c>
       <c r="B83" s="66" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="C83" s="66" t="inlineStr">
@@ -45113,7 +43569,7 @@
       </c>
       <c r="B84" s="75" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="C84" s="75" t="inlineStr">
@@ -45143,7 +43599,7 @@
       </c>
       <c r="B85" s="66" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="C85" s="66" t="inlineStr">
@@ -45173,7 +43629,7 @@
       </c>
       <c r="B86" s="75" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="C86" s="75" t="inlineStr">
@@ -45203,7 +43659,7 @@
       </c>
       <c r="B87" s="66" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="C87" s="66" t="inlineStr">
@@ -45233,7 +43689,7 @@
       </c>
       <c r="B88" s="75" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="C88" s="75" t="inlineStr">
@@ -45263,7 +43719,7 @@
       </c>
       <c r="B89" s="66" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="C89" s="66" t="inlineStr">
@@ -45293,7 +43749,7 @@
       </c>
       <c r="B90" s="75" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="C90" s="75" t="inlineStr">
@@ -45353,7 +43809,7 @@
       </c>
       <c r="B92" s="75" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="C92" s="75" t="inlineStr">
@@ -45383,7 +43839,7 @@
       </c>
       <c r="B93" s="66" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="C93" s="66" t="inlineStr">
@@ -45413,7 +43869,7 @@
       </c>
       <c r="B94" s="75" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="C94" s="75" t="inlineStr">
@@ -45443,7 +43899,7 @@
       </c>
       <c r="B95" s="66" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="C95" s="66" t="inlineStr">
@@ -45473,7 +43929,7 @@
       </c>
       <c r="B96" s="75" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="C96" s="75" t="inlineStr">
@@ -45503,7 +43959,7 @@
       </c>
       <c r="B97" s="66" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="C97" s="66" t="inlineStr">
@@ -45533,7 +43989,7 @@
       </c>
       <c r="B98" s="75" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="C98" s="75" t="inlineStr">
@@ -45563,7 +44019,7 @@
       </c>
       <c r="B99" s="66" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="C99" s="66" t="inlineStr">
@@ -45593,7 +44049,7 @@
       </c>
       <c r="B100" s="75" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="C100" s="75" t="inlineStr">
@@ -45743,7 +44199,7 @@
       </c>
       <c r="B105" s="66" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="C105" s="66" t="inlineStr">
@@ -45803,7 +44259,7 @@
       </c>
       <c r="B107" s="66" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="C107" s="66" t="inlineStr">
@@ -45833,7 +44289,7 @@
       </c>
       <c r="B108" s="75" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="C108" s="75" t="inlineStr">
